--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2136F281-F082-44E1-95E3-86BA57682315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3035" uniqueCount="1425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="1424">
   <si>
     <t>Prénom</t>
   </si>
@@ -1523,9 +1529,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sacristie de Saint-Marc </t>
-  </si>
-  <si>
-    <t>Pinacothèque vaticane</t>
   </si>
   <si>
     <t>Réfectoire du couvent</t>
@@ -4294,8 +4297,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4340,18 +4343,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4389,7 +4400,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4423,6 +4434,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4457,9 +4469,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4632,11 +4645,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X218"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4710,7 +4723,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -4733,28 +4746,28 @@
         <v>413</v>
       </c>
       <c r="M2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="S2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="U2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="W2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -4777,31 +4790,31 @@
         <v>414</v>
       </c>
       <c r="M3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="Q3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="S3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="T3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="U3" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="W3" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -4824,28 +4837,28 @@
         <v>415</v>
       </c>
       <c r="M4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="S4" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="T4" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="U4" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="W4" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -4868,28 +4881,28 @@
         <v>414</v>
       </c>
       <c r="M5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="S5" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="T5" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="U5" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="W5" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -4912,28 +4925,28 @@
         <v>416</v>
       </c>
       <c r="M6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="S6" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T6" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="U6" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="W6" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -4956,28 +4969,28 @@
         <v>417</v>
       </c>
       <c r="M7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="S7" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="T7" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="U7" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="W7" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -5000,28 +5013,28 @@
         <v>418</v>
       </c>
       <c r="M8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="S8" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T8" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="U8" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="W8" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -5044,28 +5057,28 @@
         <v>416</v>
       </c>
       <c r="M9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="S9" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="T9" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="U9" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="W9" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -5088,28 +5101,28 @@
         <v>419</v>
       </c>
       <c r="M10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S10" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="T10" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="U10" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="W10" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -5132,31 +5145,31 @@
         <v>417</v>
       </c>
       <c r="M11" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="Q11" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="S11" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="T11" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="U11" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="W11" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -5179,31 +5192,31 @@
         <v>420</v>
       </c>
       <c r="M12" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="Q12" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="S12" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T12" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="U12" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="W12" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -5226,31 +5239,31 @@
         <v>421</v>
       </c>
       <c r="M13" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Q13" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="S13" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T13" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="U13" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="W13" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -5273,31 +5286,31 @@
         <v>416</v>
       </c>
       <c r="M14" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="Q14" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="S14" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="T14" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="U14" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="W14" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -5320,31 +5333,31 @@
         <v>422</v>
       </c>
       <c r="M15" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q15" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="S15" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="T15" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="U15" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="W15" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -5367,34 +5380,34 @@
         <v>423</v>
       </c>
       <c r="M16" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O16" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="Q16" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="S16" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="T16" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="U16" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="W16" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="X16">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -5417,31 +5430,31 @@
         <v>424</v>
       </c>
       <c r="M17" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q17" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="S17" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="T17" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="U17" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="W17" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="X17">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -5464,31 +5477,31 @@
         <v>423</v>
       </c>
       <c r="M18" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="Q18" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="S18" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T18" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="U18" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="W18" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -5511,31 +5524,31 @@
         <v>423</v>
       </c>
       <c r="M19" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="Q19" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="S19" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T19" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="U19" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="W19" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -5558,28 +5571,28 @@
         <v>418</v>
       </c>
       <c r="M20" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="S20" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T20" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="U20" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="W20" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -5602,31 +5615,31 @@
         <v>425</v>
       </c>
       <c r="M21" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="Q21" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="S21" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="T21" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="U21" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="W21" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="X21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -5649,31 +5662,31 @@
         <v>426</v>
       </c>
       <c r="M22" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Q22" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="S22" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T22" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="U22" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="W22" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -5696,34 +5709,34 @@
         <v>422</v>
       </c>
       <c r="M23" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="O23" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="Q23" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="S23" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T23" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="U23" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="W23" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -5746,31 +5759,31 @@
         <v>422</v>
       </c>
       <c r="M24" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="Q24" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="S24" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T24" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="U24" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="W24" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -5793,31 +5806,31 @@
         <v>422</v>
       </c>
       <c r="M25" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="Q25" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="S25" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="T25" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="U25" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="W25" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -5840,31 +5853,31 @@
         <v>422</v>
       </c>
       <c r="M26" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q26" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="S26" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="T26" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="U26" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="W26" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -5890,34 +5903,34 @@
         <v>483</v>
       </c>
       <c r="M27" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="O27" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="Q27" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="S27" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T27" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="U27" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="W27" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -5940,31 +5953,31 @@
         <v>417</v>
       </c>
       <c r="M28" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="Q28" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="S28" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="T28" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="U28" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="W28" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -5987,28 +6000,28 @@
         <v>422</v>
       </c>
       <c r="M29" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="S29" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="T29" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="U29" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W29" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -6031,31 +6044,31 @@
         <v>422</v>
       </c>
       <c r="M30" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="Q30" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="S30" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="T30" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="U30" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="W30" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -6078,31 +6091,31 @@
         <v>422</v>
       </c>
       <c r="M31" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="Q31" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="S31" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="T31" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="U31" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="W31" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -6125,31 +6138,31 @@
         <v>422</v>
       </c>
       <c r="M32" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="Q32" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="S32" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="U32" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="W32" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -6172,31 +6185,31 @@
         <v>422</v>
       </c>
       <c r="M33" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="Q33" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="S33" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T33" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="U33" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="W33" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -6222,31 +6235,31 @@
         <v>500</v>
       </c>
       <c r="M34" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="Q34" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="S34" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="T34" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="U34" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="W34" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X34">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -6269,31 +6282,31 @@
         <v>428</v>
       </c>
       <c r="M35" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="O35" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="S35" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="T35" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="U35" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="W35" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X35">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -6319,31 +6332,31 @@
         <v>501</v>
       </c>
       <c r="M36" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="Q36" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="S36" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T36" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="U36" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="W36" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X36">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -6366,34 +6379,34 @@
         <v>430</v>
       </c>
       <c r="M37" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="O37" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="Q37" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="S37" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="T37" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="U37" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="W37" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X37">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -6416,34 +6429,34 @@
         <v>416</v>
       </c>
       <c r="M38" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="O38" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q38" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="S38" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="T38" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="U38" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="W38" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -6466,31 +6479,31 @@
         <v>431</v>
       </c>
       <c r="M39" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="Q39" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="S39" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="U39" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="W39" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -6513,31 +6526,31 @@
         <v>432</v>
       </c>
       <c r="M40" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="Q40" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="S40" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T40" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="U40" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="W40" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -6560,34 +6573,34 @@
         <v>416</v>
       </c>
       <c r="M41" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="O41" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q41" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="S41" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="T41" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="U41" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="W41" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -6610,34 +6623,34 @@
         <v>416</v>
       </c>
       <c r="M42" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="O42" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q42" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="S42" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="T42" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="U42" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="W42" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>33</v>
       </c>
@@ -6660,34 +6673,34 @@
         <v>416</v>
       </c>
       <c r="M43" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="O43" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q43" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="S43" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="T43" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="U43" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="W43" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>33</v>
       </c>
@@ -6710,34 +6723,34 @@
         <v>416</v>
       </c>
       <c r="M44" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="O44" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q44" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="S44" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="T44" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="U44" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="W44" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>33</v>
       </c>
@@ -6760,34 +6773,34 @@
         <v>416</v>
       </c>
       <c r="M45" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O45" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q45" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="S45" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="T45" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="U45" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="W45" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X45">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>33</v>
       </c>
@@ -6810,34 +6823,34 @@
         <v>416</v>
       </c>
       <c r="M46" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="O46" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="Q46" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="S46" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="T46" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="U46" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="W46" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X46">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>33</v>
       </c>
@@ -6860,34 +6873,34 @@
         <v>416</v>
       </c>
       <c r="M47" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="O47" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q47" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="S47" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="T47" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="U47" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="W47" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>34</v>
       </c>
@@ -6910,28 +6923,28 @@
         <v>433</v>
       </c>
       <c r="M48" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="S48" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T48" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="U48" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="W48" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X48">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>34</v>
       </c>
@@ -6954,31 +6967,31 @@
         <v>418</v>
       </c>
       <c r="M49" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="Q49" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="S49" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T49" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="U49" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="W49" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X49">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>31</v>
       </c>
@@ -7001,28 +7014,28 @@
         <v>434</v>
       </c>
       <c r="M50" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="S50" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="T50" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="U50" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="W50" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X50">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -7045,31 +7058,31 @@
         <v>435</v>
       </c>
       <c r="M51" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="Q51" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="S51" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="T51" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="U51" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="W51" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>35</v>
       </c>
@@ -7092,31 +7105,31 @@
         <v>433</v>
       </c>
       <c r="M52" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="Q52" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="S52" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="T52" t="s">
+        <v>1201</v>
+      </c>
+      <c r="U52" t="s">
         <v>1202</v>
       </c>
-      <c r="U52" t="s">
-        <v>1203</v>
-      </c>
       <c r="W52" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X52">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>35</v>
       </c>
@@ -7139,31 +7152,31 @@
         <v>417</v>
       </c>
       <c r="M53" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="Q53" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="S53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="T53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="U53" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="W53" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X53">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>36</v>
       </c>
@@ -7186,31 +7199,31 @@
         <v>414</v>
       </c>
       <c r="M54" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="Q54" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="S54" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="T54" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="U54" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="W54" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X54">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>36</v>
       </c>
@@ -7233,28 +7246,28 @@
         <v>436</v>
       </c>
       <c r="M55" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="S55" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="T55" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="U55" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="W55" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X55">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>26</v>
       </c>
@@ -7277,28 +7290,28 @@
         <v>420</v>
       </c>
       <c r="M56" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="S56" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="T56" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="U56" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="W56" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X56">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>26</v>
       </c>
@@ -7321,31 +7334,31 @@
         <v>422</v>
       </c>
       <c r="M57" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="Q57" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="S57" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T57" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="U57" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="W57" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X57">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>37</v>
       </c>
@@ -7368,31 +7381,31 @@
         <v>437</v>
       </c>
       <c r="M58" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="Q58" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="S58" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="T58" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="U58" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="W58" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X58">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>37</v>
       </c>
@@ -7418,25 +7431,25 @@
         <v>502</v>
       </c>
       <c r="M59" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="Q59" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="S59" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="W59" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X59">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>38</v>
       </c>
@@ -7459,31 +7472,31 @@
         <v>414</v>
       </c>
       <c r="M60" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="Q60" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="S60" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="T60" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="U60" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="W60" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X60">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>38</v>
       </c>
@@ -7506,31 +7519,31 @@
         <v>439</v>
       </c>
       <c r="M61" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="Q61" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="S61" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="T61" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="U61" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="W61" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X61">
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>39</v>
       </c>
@@ -7553,28 +7566,28 @@
         <v>440</v>
       </c>
       <c r="M62" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="S62" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T62" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="U62" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="W62" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X62">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>40</v>
       </c>
@@ -7597,28 +7610,28 @@
         <v>417</v>
       </c>
       <c r="M63" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="S63" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T63" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="U63" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="W63" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X63">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -7641,31 +7654,31 @@
         <v>414</v>
       </c>
       <c r="M64" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="O64" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="S64" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T64" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="U64" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="W64" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X64">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>41</v>
       </c>
@@ -7688,31 +7701,31 @@
         <v>441</v>
       </c>
       <c r="M65" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="Q65" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="S65" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="T65" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="U65" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="W65" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X65">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>41</v>
       </c>
@@ -7735,31 +7748,31 @@
         <v>442</v>
       </c>
       <c r="M66" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="Q66" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="S66" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="T66" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="U66" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="W66" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X66">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>41</v>
       </c>
@@ -7782,31 +7795,31 @@
         <v>443</v>
       </c>
       <c r="M67" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="Q67" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="S67" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="T67" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="U67" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="W67" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X67">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>41</v>
       </c>
@@ -7828,35 +7841,32 @@
       <c r="J68" t="s">
         <v>389</v>
       </c>
-      <c r="L68" t="s">
-        <v>503</v>
-      </c>
       <c r="M68" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="Q68" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="S68" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="T68" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="U68" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="W68" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>41</v>
       </c>
@@ -7879,31 +7889,31 @@
         <v>441</v>
       </c>
       <c r="M69" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="Q69" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="S69" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T69" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="U69" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="W69" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>41</v>
       </c>
@@ -7926,31 +7936,31 @@
         <v>414</v>
       </c>
       <c r="M70" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="Q70" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="S70" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="T70" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="U70" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="W70" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>41</v>
       </c>
@@ -7973,31 +7983,31 @@
         <v>444</v>
       </c>
       <c r="M71" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="Q71" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="S71" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="T71" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="U71" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="W71" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>41</v>
       </c>
@@ -8020,31 +8030,31 @@
         <v>445</v>
       </c>
       <c r="M72" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="Q72" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="S72" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="T72" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="U72" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="W72" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>41</v>
       </c>
@@ -8067,31 +8077,31 @@
         <v>414</v>
       </c>
       <c r="M73" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="Q73" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="S73" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="T73" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="U73" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="W73" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>41</v>
       </c>
@@ -8114,34 +8124,34 @@
         <v>446</v>
       </c>
       <c r="L74" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M74" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q74" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="S74" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="T74" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="U74" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="W74" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>42</v>
       </c>
@@ -8164,34 +8174,34 @@
         <v>447</v>
       </c>
       <c r="L75" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="M75" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="Q75" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="S75" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T75" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="U75" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="W75" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X75">
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>42</v>
       </c>
@@ -8214,37 +8224,37 @@
         <v>448</v>
       </c>
       <c r="L76" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M76" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="O76" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="Q76" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="S76" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="T76" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="U76" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="W76" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X76">
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>43</v>
       </c>
@@ -8267,31 +8277,31 @@
         <v>449</v>
       </c>
       <c r="M77" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="Q77" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="S77" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T77" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="U77" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="W77" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X77">
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>43</v>
       </c>
@@ -8314,28 +8324,28 @@
         <v>450</v>
       </c>
       <c r="M78" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="S78" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T78" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="U78" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="W78" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X78">
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>42</v>
       </c>
@@ -8358,31 +8368,31 @@
         <v>417</v>
       </c>
       <c r="M79" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="Q79" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="S79" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="T79" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="U79" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="W79" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X79">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>42</v>
       </c>
@@ -8405,31 +8415,31 @@
         <v>422</v>
       </c>
       <c r="M80" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="Q80" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="S80" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="T80" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="U80" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="W80" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X80">
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>44</v>
       </c>
@@ -8452,31 +8462,31 @@
         <v>417</v>
       </c>
       <c r="M81" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="Q81" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="S81" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="T81" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="U81" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="W81" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X81">
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>44</v>
       </c>
@@ -8499,34 +8509,34 @@
         <v>451</v>
       </c>
       <c r="L82" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M82" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="Q82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="S82" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T82" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="U82" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="W82" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X82">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>44</v>
       </c>
@@ -8549,34 +8559,34 @@
         <v>452</v>
       </c>
       <c r="L83" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M83" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q83" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="S83" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T83" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="U83" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="W83" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X83">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -8599,28 +8609,28 @@
         <v>453</v>
       </c>
       <c r="M84" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="S84" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T84" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="U84" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="W84" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X84">
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>44</v>
       </c>
@@ -8643,28 +8653,28 @@
         <v>453</v>
       </c>
       <c r="M85" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="S85" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T85" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="U85" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="W85" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X85">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>44</v>
       </c>
@@ -8687,31 +8697,31 @@
         <v>422</v>
       </c>
       <c r="M86" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="Q86" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="S86" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="T86" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="U86" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="W86" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X86">
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -8734,28 +8744,28 @@
         <v>452</v>
       </c>
       <c r="M87" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="S87" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T87" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="U87" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="W87" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X87">
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:24">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -8778,28 +8788,28 @@
         <v>417</v>
       </c>
       <c r="M88" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="S88" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T88" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="U88" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="W88" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X88">
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:24">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>44</v>
       </c>
@@ -8822,28 +8832,28 @@
         <v>420</v>
       </c>
       <c r="M89" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="S89" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T89" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="U89" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="W89" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X89">
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:24">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>44</v>
       </c>
@@ -8866,28 +8876,28 @@
         <v>417</v>
       </c>
       <c r="M90" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="S90" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T90" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="U90" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="W90" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X90">
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:24">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>44</v>
       </c>
@@ -8910,31 +8920,31 @@
         <v>420</v>
       </c>
       <c r="M91" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="Q91" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="S91" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="T91" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="U91" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="W91" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X91">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:24">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -8963,28 +8973,28 @@
         <v>454</v>
       </c>
       <c r="M92" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="S92" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T92" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="U92" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="W92" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X92">
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:24">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>44</v>
       </c>
@@ -9004,31 +9014,31 @@
         <v>455</v>
       </c>
       <c r="M93" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="N93" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="Q93" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="S93" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T93" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="U93" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="W93" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X93">
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:24">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>44</v>
       </c>
@@ -9051,28 +9061,28 @@
         <v>417</v>
       </c>
       <c r="M94" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="S94" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="T94" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="U94" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="W94" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X94">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:24">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>46</v>
       </c>
@@ -9095,28 +9105,28 @@
         <v>417</v>
       </c>
       <c r="M95" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="S95" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T95" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="U95" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="W95" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X95">
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:24">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>46</v>
       </c>
@@ -9139,31 +9149,31 @@
         <v>456</v>
       </c>
       <c r="M96" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="Q96" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="S96" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T96" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="U96" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="W96" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X96">
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:24">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>47</v>
       </c>
@@ -9192,31 +9202,31 @@
         <v>422</v>
       </c>
       <c r="M97" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="Q97" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="S97" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="T97" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="U97" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="W97" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X97">
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:24">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>47</v>
       </c>
@@ -9245,37 +9255,37 @@
         <v>457</v>
       </c>
       <c r="L98" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M98" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="O98" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="Q98" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="S98" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="T98" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="U98" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="W98" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X98">
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:24">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>48</v>
       </c>
@@ -9304,28 +9314,28 @@
         <v>458</v>
       </c>
       <c r="M99" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="S99" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T99" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="U99" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="W99" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X99">
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:24">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>48</v>
       </c>
@@ -9354,31 +9364,31 @@
         <v>459</v>
       </c>
       <c r="L100" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M100" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="N100" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="S100" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T100" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="U100" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="W100" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X100">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:24">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>49</v>
       </c>
@@ -9407,34 +9417,34 @@
         <v>423</v>
       </c>
       <c r="L101" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="M101" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="Q101" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="S101" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="T101" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="U101" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="W101" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>49</v>
       </c>
@@ -9463,34 +9473,34 @@
         <v>414</v>
       </c>
       <c r="L102" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M102" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="Q102" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="S102" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="T102" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="U102" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="W102" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X102">
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>49</v>
       </c>
@@ -9519,37 +9529,37 @@
         <v>460</v>
       </c>
       <c r="L103" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M103" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="O103" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="Q103" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="S103" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="T103" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="U103" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="W103" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>49</v>
       </c>
@@ -9575,28 +9585,28 @@
         <v>461</v>
       </c>
       <c r="M104" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="S104" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T104" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="U104" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="W104" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>49</v>
       </c>
@@ -9622,28 +9632,28 @@
         <v>461</v>
       </c>
       <c r="M105" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="S105" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T105" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="U105" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="W105" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>49</v>
       </c>
@@ -9672,31 +9682,31 @@
         <v>461</v>
       </c>
       <c r="L106" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M106" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="S106" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T106" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="U106" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="W106" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X106">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>49</v>
       </c>
@@ -9725,34 +9735,34 @@
         <v>461</v>
       </c>
       <c r="L107" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="M107" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="O107" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="S107" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T107" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="U107" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="W107" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X107">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>49</v>
       </c>
@@ -9781,37 +9791,37 @@
         <v>461</v>
       </c>
       <c r="L108" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M108" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="N108" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="O108" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="Q108" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="S108" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T108" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="U108" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="W108" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X108">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>49</v>
       </c>
@@ -9840,34 +9850,34 @@
         <v>461</v>
       </c>
       <c r="L109" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M109" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="N109" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="O109" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="S109" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T109" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="U109" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W109" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X109">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:24">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>49</v>
       </c>
@@ -9896,34 +9906,34 @@
         <v>461</v>
       </c>
       <c r="L110" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M110" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="N110" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="O110" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="S110" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T110" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="U110" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="W110" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X110">
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:24">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>49</v>
       </c>
@@ -9952,34 +9962,34 @@
         <v>461</v>
       </c>
       <c r="L111" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M111" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="O111" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="S111" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T111" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="U111" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="W111" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X111">
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:24">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>49</v>
       </c>
@@ -10008,34 +10018,34 @@
         <v>389</v>
       </c>
       <c r="L112" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M112" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="O112" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="S112" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T112" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="U112" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="W112" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X112">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>50</v>
       </c>
@@ -10064,28 +10074,28 @@
         <v>462</v>
       </c>
       <c r="M113" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="S113" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T113" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="U113" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="W113" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X113">
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:24">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>50</v>
       </c>
@@ -10114,31 +10124,31 @@
         <v>463</v>
       </c>
       <c r="M114" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="N114" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="O114" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="S114" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T114" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="U114" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="W114" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X114">
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:24">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>51</v>
       </c>
@@ -10161,28 +10171,28 @@
         <v>464</v>
       </c>
       <c r="M115" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="S115" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T115" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="U115" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="W115" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X115">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:24">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>52</v>
       </c>
@@ -10205,31 +10215,31 @@
         <v>465</v>
       </c>
       <c r="M116" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="N116" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="Q116" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="S116" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T116" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="U116" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="W116" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X116">
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:24">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>31</v>
       </c>
@@ -10252,28 +10262,28 @@
         <v>414</v>
       </c>
       <c r="M117" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="N117" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="S117" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="T117" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="U117" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="W117" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X117">
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:24">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>31</v>
       </c>
@@ -10296,28 +10306,28 @@
         <v>414</v>
       </c>
       <c r="M118" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="S118" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="T118" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="U118" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="W118" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X118">
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:24">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>31</v>
       </c>
@@ -10340,28 +10350,28 @@
         <v>466</v>
       </c>
       <c r="M119" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="N119" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="S119" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T119" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="U119" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="W119" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X119">
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:24">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>31</v>
       </c>
@@ -10384,31 +10394,31 @@
         <v>418</v>
       </c>
       <c r="M120" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="O120" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="S120" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="T120" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="U120" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="W120" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X120">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>31</v>
       </c>
@@ -10431,31 +10441,31 @@
         <v>435</v>
       </c>
       <c r="M121" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O121" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="S121" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="T121" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="U121" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="W121" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X121">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>31</v>
       </c>
@@ -10478,28 +10488,28 @@
         <v>414</v>
       </c>
       <c r="M122" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="S122" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="T122" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="U122" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="W122" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X122">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:24">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>31</v>
       </c>
@@ -10522,31 +10532,31 @@
         <v>467</v>
       </c>
       <c r="L123" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M123" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="S123" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="T123" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="U123" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="W123" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X123">
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:24">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>31</v>
       </c>
@@ -10569,31 +10579,31 @@
         <v>435</v>
       </c>
       <c r="M124" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="O124" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="S124" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="T124" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="U124" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="W124" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X124">
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:24">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>53</v>
       </c>
@@ -10616,28 +10626,28 @@
         <v>423</v>
       </c>
       <c r="M125" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="S125" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T125" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="U125" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="W125" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="X125">
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:24">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>53</v>
       </c>
@@ -10660,28 +10670,28 @@
         <v>468</v>
       </c>
       <c r="M126" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="N126" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="S126" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T126" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="U126" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="W126" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="X126">
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:24">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>54</v>
       </c>
@@ -10704,37 +10714,37 @@
         <v>458</v>
       </c>
       <c r="L127" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M127" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="N127" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="O127" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="Q127" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="S127" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T127" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="U127" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="W127" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X127">
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:24">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>54</v>
       </c>
@@ -10757,34 +10767,34 @@
         <v>414</v>
       </c>
       <c r="L128" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M128" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="N128" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="Q128" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="S128" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="T128" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="U128" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="W128" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X128">
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>55</v>
       </c>
@@ -10807,28 +10817,28 @@
         <v>469</v>
       </c>
       <c r="M129" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="S129" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="T129" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="U129" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="W129" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="X129">
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:24">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>55</v>
       </c>
@@ -10851,31 +10861,31 @@
         <v>469</v>
       </c>
       <c r="M130" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="N130" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="Q130" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="S130" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="T130" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="U130" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="W130" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X130">
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:24">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>56</v>
       </c>
@@ -10898,34 +10908,34 @@
         <v>470</v>
       </c>
       <c r="L131" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M131" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="N131" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="Q131" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="S131" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="T131" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="U131" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="W131" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X131">
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>56</v>
       </c>
@@ -10948,31 +10958,31 @@
         <v>414</v>
       </c>
       <c r="M132" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N132" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="Q132" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="S132" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="T132" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="U132" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="W132" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X132">
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>57</v>
       </c>
@@ -10995,28 +11005,28 @@
         <v>471</v>
       </c>
       <c r="M133" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="S133" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T133" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="U133" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="W133" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="X133">
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:24">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>57</v>
       </c>
@@ -11039,28 +11049,28 @@
         <v>472</v>
       </c>
       <c r="M134" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="S134" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T134" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="U134" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="W134" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="X134">
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:24">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>58</v>
       </c>
@@ -11083,31 +11093,31 @@
         <v>473</v>
       </c>
       <c r="M135" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="Q135" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="S135" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T135" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="U135" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="W135" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X135">
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:24">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>58</v>
       </c>
@@ -11130,28 +11140,28 @@
         <v>422</v>
       </c>
       <c r="M136" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="S136" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="T136" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="U136" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="W136" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X136">
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:24">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>59</v>
       </c>
@@ -11174,28 +11184,28 @@
         <v>422</v>
       </c>
       <c r="M137" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="S137" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T137" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="U137" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="W137" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X137">
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>59</v>
       </c>
@@ -11218,31 +11228,31 @@
         <v>422</v>
       </c>
       <c r="M138" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="Q138" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="S138" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T138" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="U138" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="W138" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X138">
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:24">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>60</v>
       </c>
@@ -11265,28 +11275,28 @@
         <v>474</v>
       </c>
       <c r="M139" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="S139" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="T139" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="U139" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="W139" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="X139">
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:24">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>60</v>
       </c>
@@ -11309,28 +11319,28 @@
         <v>475</v>
       </c>
       <c r="M140" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="S140" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T140" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="U140" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="W140" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="X140">
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:24">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>42</v>
       </c>
@@ -11353,34 +11363,34 @@
         <v>476</v>
       </c>
       <c r="L141" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M141" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="Q141" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="S141" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T141" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="U141" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="W141" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X141">
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:24">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>42</v>
       </c>
@@ -11403,31 +11413,31 @@
         <v>417</v>
       </c>
       <c r="M142" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="Q142" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="S142" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="T142" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="U142" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="W142" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X142">
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:24">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>42</v>
       </c>
@@ -11450,31 +11460,31 @@
         <v>477</v>
       </c>
       <c r="M143" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="Q143" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="S143" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T143" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="U143" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="W143" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X143">
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:24">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>42</v>
       </c>
@@ -11497,31 +11507,31 @@
         <v>414</v>
       </c>
       <c r="M144" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="Q144" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="S144" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="T144" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="U144" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="W144" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X144">
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:24">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>42</v>
       </c>
@@ -11544,31 +11554,31 @@
         <v>420</v>
       </c>
       <c r="M145" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="Q145" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="S145" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="T145" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="U145" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="W145" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X145">
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:24">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>42</v>
       </c>
@@ -11591,28 +11601,28 @@
         <v>442</v>
       </c>
       <c r="M146" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="S146" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="T146" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="U146" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="W146" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X146">
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:24">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>42</v>
       </c>
@@ -11635,28 +11645,28 @@
         <v>442</v>
       </c>
       <c r="M147" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="S147" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="T147" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="U147" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="W147" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X147">
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:24">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>42</v>
       </c>
@@ -11679,34 +11689,34 @@
         <v>414</v>
       </c>
       <c r="M148" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O148" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="Q148" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="S148" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="T148" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="U148" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="W148" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X148">
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:24">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>61</v>
       </c>
@@ -11729,31 +11739,31 @@
         <v>418</v>
       </c>
       <c r="M149" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="Q149" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="S149" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T149" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="U149" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="W149" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X149">
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:24">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>61</v>
       </c>
@@ -11776,31 +11786,31 @@
         <v>478</v>
       </c>
       <c r="M150" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="Q150" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="S150" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="T150" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="U150" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="W150" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X150">
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:24">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>62</v>
       </c>
@@ -11823,31 +11833,31 @@
         <v>479</v>
       </c>
       <c r="M151" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="Q151" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="S151" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="T151" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="U151" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="W151" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X151">
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:24">
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>62</v>
       </c>
@@ -11870,34 +11880,34 @@
         <v>480</v>
       </c>
       <c r="L152" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M152" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="Q152" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="S152" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="T152" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="U152" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="W152" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X152">
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:24">
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>62</v>
       </c>
@@ -11920,31 +11930,31 @@
         <v>464</v>
       </c>
       <c r="M153" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="Q153" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="S153" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T153" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="U153" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="W153" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X153">
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:24">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>62</v>
       </c>
@@ -11967,28 +11977,28 @@
         <v>481</v>
       </c>
       <c r="M154" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="S154" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T154" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="U154" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="W154" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="X154">
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:24">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>62</v>
       </c>
@@ -12011,28 +12021,28 @@
         <v>440</v>
       </c>
       <c r="M155" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="S155" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T155" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="U155" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="W155" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="X155">
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:24">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>62</v>
       </c>
@@ -12055,34 +12065,34 @@
         <v>480</v>
       </c>
       <c r="L156" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M156" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="Q156" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="S156" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T156" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="U156" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="W156" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X156">
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:24">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>62</v>
       </c>
@@ -12105,28 +12115,28 @@
         <v>466</v>
       </c>
       <c r="M157" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="S157" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T157" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="U157" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="W157" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="X157">
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:24">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>62</v>
       </c>
@@ -12149,34 +12159,34 @@
         <v>480</v>
       </c>
       <c r="L158" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M158" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="Q158" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="S158" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="T158" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="U158" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="W158" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X158">
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:24">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>63</v>
       </c>
@@ -12199,28 +12209,28 @@
         <v>482</v>
       </c>
       <c r="M159" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="S159" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="T159" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="U159" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="W159" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="X159">
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:24">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>63</v>
       </c>
@@ -12243,28 +12253,28 @@
         <v>464</v>
       </c>
       <c r="M160" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="S160" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T160" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="U160" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="W160" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="X160">
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:24">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>64</v>
       </c>
@@ -12290,31 +12300,31 @@
         <v>483</v>
       </c>
       <c r="M161" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="Q161" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="S161" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T161" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="U161" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="W161" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X161">
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:24">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>64</v>
       </c>
@@ -12337,28 +12347,28 @@
         <v>422</v>
       </c>
       <c r="M162" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="S162" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T162" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="U162" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="W162" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X162">
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:24">
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>65</v>
       </c>
@@ -12381,34 +12391,34 @@
         <v>441</v>
       </c>
       <c r="M163" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="O163" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="Q163" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="S163" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="T163" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="U163" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="W163" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X163">
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:24">
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>65</v>
       </c>
@@ -12431,31 +12441,31 @@
         <v>417</v>
       </c>
       <c r="M164" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="Q164" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="S164" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="T164" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="U164" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="W164" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X164">
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:24">
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>31</v>
       </c>
@@ -12478,28 +12488,28 @@
         <v>484</v>
       </c>
       <c r="M165" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="S165" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="T165" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="U165" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="W165" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X165">
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:24">
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>66</v>
       </c>
@@ -12522,28 +12532,28 @@
         <v>485</v>
       </c>
       <c r="M166" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="S166" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T166" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="U166" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="W166" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X166">
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:24">
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>66</v>
       </c>
@@ -12566,28 +12576,28 @@
         <v>414</v>
       </c>
       <c r="M167" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="S167" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T167" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="U167" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="W167" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="X167">
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:24">
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>67</v>
       </c>
@@ -12610,37 +12620,37 @@
         <v>389</v>
       </c>
       <c r="L168" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="M168" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="O168" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="Q168" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="S168" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T168" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="U168" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="W168" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X168">
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:24">
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>67</v>
       </c>
@@ -12663,37 +12673,37 @@
         <v>389</v>
       </c>
       <c r="L169" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="M169" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="O169" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="Q169" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="S169" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T169" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="U169" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="W169" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X169">
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:24">
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>68</v>
       </c>
@@ -12716,28 +12726,28 @@
         <v>420</v>
       </c>
       <c r="M170" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N170" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="S170" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T170" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="U170" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="W170" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X170">
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:24">
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>69</v>
       </c>
@@ -12760,34 +12770,34 @@
         <v>486</v>
       </c>
       <c r="M171" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="N171" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="O171" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="Q171" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="S171" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="T171" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="U171" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="W171" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X171">
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:24">
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>69</v>
       </c>
@@ -12810,34 +12820,34 @@
         <v>417</v>
       </c>
       <c r="M172" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="N172" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="O172" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="Q172" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="S172" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="T172" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="U172" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="W172" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X172">
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:24">
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>70</v>
       </c>
@@ -12860,31 +12870,31 @@
         <v>422</v>
       </c>
       <c r="M173" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="Q173" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="S173" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="T173" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="U173" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="W173" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X173">
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:24">
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>70</v>
       </c>
@@ -12907,34 +12917,34 @@
         <v>448</v>
       </c>
       <c r="L174" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="M174" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="N174" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="Q174" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="S174" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="T174" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="U174" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="W174" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X174">
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:24">
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>70</v>
       </c>
@@ -12957,28 +12967,28 @@
         <v>448</v>
       </c>
       <c r="M175" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="N175" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="S175" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T175" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="U175" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="W175" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X175">
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:24">
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>70</v>
       </c>
@@ -13001,31 +13011,31 @@
         <v>417</v>
       </c>
       <c r="M176" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="Q176" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="S176" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="T176" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="U176" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="W176" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X176">
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:24">
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>70</v>
       </c>
@@ -13048,31 +13058,31 @@
         <v>414</v>
       </c>
       <c r="M177" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N177" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="Q177" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="S177" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="T177" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="U177" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="W177" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X177">
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:24">
+    <row r="178" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>70</v>
       </c>
@@ -13095,28 +13105,28 @@
         <v>487</v>
       </c>
       <c r="M178" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="S178" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="T178" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="U178" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="W178" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X178">
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:24">
+    <row r="179" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>70</v>
       </c>
@@ -13139,28 +13149,28 @@
         <v>488</v>
       </c>
       <c r="M179" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="N179" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="S179" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T179" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="U179" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="W179" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X179">
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:24">
+    <row r="180" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>70</v>
       </c>
@@ -13183,31 +13193,31 @@
         <v>417</v>
       </c>
       <c r="M180" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="Q180" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="S180" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="T180" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="U180" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="W180" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X180">
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:24">
+    <row r="181" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>71</v>
       </c>
@@ -13230,34 +13240,34 @@
         <v>418</v>
       </c>
       <c r="M181" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="N181" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="O181" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="Q181" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="S181" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="T181" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="U181" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="W181" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X181">
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:24">
+    <row r="182" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>71</v>
       </c>
@@ -13280,28 +13290,28 @@
         <v>489</v>
       </c>
       <c r="M182" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="N182" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="S182" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T182" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="U182" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="W182" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X182">
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:24">
+    <row r="183" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>71</v>
       </c>
@@ -13324,31 +13334,31 @@
         <v>422</v>
       </c>
       <c r="M183" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="N183" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="Q183" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="S183" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T183" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="U183" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="W183" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X183">
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:24">
+    <row r="184" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>71</v>
       </c>
@@ -13371,31 +13381,31 @@
         <v>490</v>
       </c>
       <c r="M184" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N184" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="Q184" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="S184" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T184" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="U184" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="W184" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X184">
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:24">
+    <row r="185" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>71</v>
       </c>
@@ -13418,31 +13428,31 @@
         <v>440</v>
       </c>
       <c r="M185" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="N185" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="Q185" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="S185" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="T185" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="U185" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="W185" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X185">
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:24">
+    <row r="186" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>71</v>
       </c>
@@ -13465,31 +13475,31 @@
         <v>418</v>
       </c>
       <c r="M186" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="N186" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="Q186" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="S186" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T186" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="U186" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="W186" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X186">
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:24">
+    <row r="187" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>72</v>
       </c>
@@ -13512,28 +13522,28 @@
         <v>423</v>
       </c>
       <c r="M187" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="N187" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="S187" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T187" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="U187" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="W187" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X187">
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:24">
+    <row r="188" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>72</v>
       </c>
@@ -13556,28 +13566,28 @@
         <v>491</v>
       </c>
       <c r="M188" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="N188" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="S188" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="T188" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="U188" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="W188" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X188">
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:24">
+    <row r="189" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>72</v>
       </c>
@@ -13600,28 +13610,28 @@
         <v>466</v>
       </c>
       <c r="M189" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="S189" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T189" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="U189" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="W189" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X189">
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:24">
+    <row r="190" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>72</v>
       </c>
@@ -13644,28 +13654,28 @@
         <v>430</v>
       </c>
       <c r="M190" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="S190" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T190" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="U190" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="W190" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X190">
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:24">
+    <row r="191" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>72</v>
       </c>
@@ -13688,28 +13698,28 @@
         <v>418</v>
       </c>
       <c r="M191" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="N191" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="S191" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T191" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="U191" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="W191" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X191">
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:24">
+    <row r="192" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>72</v>
       </c>
@@ -13732,31 +13742,31 @@
         <v>492</v>
       </c>
       <c r="M192" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="N192" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="O192" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="S192" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="T192" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="U192" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="W192" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X192">
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:24">
+    <row r="193" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>72</v>
       </c>
@@ -13779,28 +13789,28 @@
         <v>418</v>
       </c>
       <c r="M193" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="S193" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T193" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="U193" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="W193" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X193">
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:24">
+    <row r="194" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>72</v>
       </c>
@@ -13823,28 +13833,28 @@
         <v>414</v>
       </c>
       <c r="M194" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="N194" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="S194" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T194" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="U194" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="W194" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X194">
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:24">
+    <row r="195" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>72</v>
       </c>
@@ -13867,28 +13877,28 @@
         <v>464</v>
       </c>
       <c r="M195" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="N195" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="S195" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T195" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="U195" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="W195" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X195">
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:24">
+    <row r="196" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>72</v>
       </c>
@@ -13911,28 +13921,28 @@
         <v>442</v>
       </c>
       <c r="M196" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="N196" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="S196" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T196" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="U196" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="W196" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X196">
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:24">
+    <row r="197" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>72</v>
       </c>
@@ -13955,28 +13965,28 @@
         <v>422</v>
       </c>
       <c r="M197" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="N197" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="S197" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T197" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="U197" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="W197" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X197">
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:24">
+    <row r="198" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>73</v>
       </c>
@@ -13999,31 +14009,31 @@
         <v>493</v>
       </c>
       <c r="M198" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="Q198" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="S198" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T198" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="U198" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="W198" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X198">
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:24">
+    <row r="199" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>73</v>
       </c>
@@ -14046,31 +14056,31 @@
         <v>494</v>
       </c>
       <c r="M199" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="Q199" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="S199" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T199" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="U199" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="W199" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X199">
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:24">
+    <row r="200" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>73</v>
       </c>
@@ -14093,31 +14103,31 @@
         <v>417</v>
       </c>
       <c r="M200" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="N200" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="Q200" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="S200" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T200" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="U200" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="W200" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X200">
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:24">
+    <row r="201" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>73</v>
       </c>
@@ -14140,31 +14150,31 @@
         <v>417</v>
       </c>
       <c r="M201" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="N201" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="Q201" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="S201" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T201" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="U201" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="W201" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X201">
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:24">
+    <row r="202" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>73</v>
       </c>
@@ -14187,28 +14197,28 @@
         <v>417</v>
       </c>
       <c r="M202" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="N202" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="S202" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T202" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="U202" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="W202" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X202">
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:24">
+    <row r="203" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>73</v>
       </c>
@@ -14231,31 +14241,31 @@
         <v>442</v>
       </c>
       <c r="M203" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="N203" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="Q203" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="S203" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="T203" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="U203" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="W203" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X203">
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:24">
+    <row r="204" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>73</v>
       </c>
@@ -14278,31 +14288,31 @@
         <v>440</v>
       </c>
       <c r="M204" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="N204" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="Q204" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="S204" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T204" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="U204" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="W204" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X204">
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:24">
+    <row r="205" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>73</v>
       </c>
@@ -14325,31 +14335,31 @@
         <v>414</v>
       </c>
       <c r="M205" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="N205" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="Q205" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="S205" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T205" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="U205" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="W205" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X205">
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:24">
+    <row r="206" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>73</v>
       </c>
@@ -14372,31 +14382,31 @@
         <v>450</v>
       </c>
       <c r="M206" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="N206" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="Q206" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="S206" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T206" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="U206" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="W206" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X206">
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:24">
+    <row r="207" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>73</v>
       </c>
@@ -14419,28 +14429,28 @@
         <v>433</v>
       </c>
       <c r="M207" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="N207" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="S207" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T207" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="U207" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="W207" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X207">
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:24">
+    <row r="208" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>73</v>
       </c>
@@ -14463,31 +14473,31 @@
         <v>440</v>
       </c>
       <c r="M208" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="N208" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="Q208" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="S208" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T208" t="s">
+        <v>1309</v>
+      </c>
+      <c r="U208" t="s">
         <v>1310</v>
       </c>
-      <c r="U208" t="s">
-        <v>1311</v>
-      </c>
       <c r="W208" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="X208">
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:24">
+    <row r="209" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>54</v>
       </c>
@@ -14510,28 +14520,28 @@
         <v>418</v>
       </c>
       <c r="M209" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="N209" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="S209" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T209" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="U209" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="W209" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X209">
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:24">
+    <row r="210" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>54</v>
       </c>
@@ -14554,28 +14564,28 @@
         <v>422</v>
       </c>
       <c r="M210" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="N210" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="S210" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="T210" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="U210" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="W210" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X210">
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:24">
+    <row r="211" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>74</v>
       </c>
@@ -14598,31 +14608,31 @@
         <v>416</v>
       </c>
       <c r="M211" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="N211" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q211" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="S211" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="T211" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="U211" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="W211" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X211">
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:24">
+    <row r="212" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>74</v>
       </c>
@@ -14645,34 +14655,34 @@
         <v>495</v>
       </c>
       <c r="L212" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M212" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="Q212" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="S212" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="T212" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="U212" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="W212" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X212">
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:24">
+    <row r="213" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>65</v>
       </c>
@@ -14695,34 +14705,34 @@
         <v>496</v>
       </c>
       <c r="L213" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M213" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="Q213" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="S213" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="T213" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="U213" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="W213" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X213">
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:24">
+    <row r="214" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>65</v>
       </c>
@@ -14745,31 +14755,31 @@
         <v>416</v>
       </c>
       <c r="M214" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="N214" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="Q214" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="S214" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="T214" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="U214" t="s">
+        <v>1415</v>
+      </c>
+      <c r="W214" t="s">
         <v>1416</v>
-      </c>
-      <c r="W214" t="s">
-        <v>1417</v>
       </c>
       <c r="X214">
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:24">
+    <row r="215" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>75</v>
       </c>
@@ -14792,34 +14802,34 @@
         <v>497</v>
       </c>
       <c r="L215" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M215" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="N215" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="Q215" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="S215" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T215" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="U215" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="W215" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X215">
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:24">
+    <row r="216" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>75</v>
       </c>
@@ -14842,34 +14852,34 @@
         <v>498</v>
       </c>
       <c r="L216" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M216" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="N216" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="Q216" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="S216" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T216" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="U216" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="W216" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="X216">
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:24">
+    <row r="217" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>76</v>
       </c>
@@ -14892,28 +14902,28 @@
         <v>418</v>
       </c>
       <c r="M217" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="N217" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="S217" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="T217" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="U217" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="W217" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="X217">
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:24">
+    <row r="218" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>76</v>
       </c>
@@ -14936,22 +14946,22 @@
         <v>499</v>
       </c>
       <c r="M218" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N218" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="S218" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="T218" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="U218" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="W218" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="X218">
         <v>3</v>
@@ -14959,223 +14969,223 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
-    <hyperlink ref="N4" r:id="rId3"/>
-    <hyperlink ref="N5" r:id="rId4"/>
-    <hyperlink ref="N6" r:id="rId5"/>
-    <hyperlink ref="N7" r:id="rId6"/>
-    <hyperlink ref="N8" r:id="rId7"/>
-    <hyperlink ref="N9" r:id="rId8"/>
-    <hyperlink ref="N10" r:id="rId9"/>
-    <hyperlink ref="N11" r:id="rId10"/>
-    <hyperlink ref="N12" r:id="rId11"/>
-    <hyperlink ref="N13" r:id="rId12"/>
-    <hyperlink ref="N14" r:id="rId13"/>
-    <hyperlink ref="N15" r:id="rId14"/>
-    <hyperlink ref="N16" r:id="rId15"/>
-    <hyperlink ref="N17" r:id="rId16"/>
-    <hyperlink ref="N18" r:id="rId17"/>
-    <hyperlink ref="N19" r:id="rId18"/>
-    <hyperlink ref="N20" r:id="rId19"/>
-    <hyperlink ref="N21" r:id="rId20"/>
-    <hyperlink ref="N22" r:id="rId21"/>
-    <hyperlink ref="N23" r:id="rId22"/>
-    <hyperlink ref="N24" r:id="rId23"/>
-    <hyperlink ref="N25" r:id="rId24"/>
-    <hyperlink ref="N26" r:id="rId25"/>
-    <hyperlink ref="N27" r:id="rId26"/>
-    <hyperlink ref="N28" r:id="rId27"/>
-    <hyperlink ref="N29" r:id="rId28"/>
-    <hyperlink ref="N30" r:id="rId29"/>
-    <hyperlink ref="N31" r:id="rId30"/>
-    <hyperlink ref="N32" r:id="rId31"/>
-    <hyperlink ref="N33" r:id="rId32"/>
-    <hyperlink ref="N34" r:id="rId33"/>
-    <hyperlink ref="N35" r:id="rId34"/>
-    <hyperlink ref="N36" r:id="rId35"/>
-    <hyperlink ref="N37" r:id="rId36"/>
-    <hyperlink ref="N38" r:id="rId37"/>
-    <hyperlink ref="N39" r:id="rId38"/>
-    <hyperlink ref="N40" r:id="rId39"/>
-    <hyperlink ref="N41" r:id="rId40"/>
-    <hyperlink ref="N42" r:id="rId41"/>
-    <hyperlink ref="N43" r:id="rId42"/>
-    <hyperlink ref="N44" r:id="rId43"/>
-    <hyperlink ref="N45" r:id="rId44"/>
-    <hyperlink ref="N46" r:id="rId45"/>
-    <hyperlink ref="N47" r:id="rId46"/>
-    <hyperlink ref="N48" r:id="rId47"/>
-    <hyperlink ref="N49" r:id="rId48"/>
-    <hyperlink ref="N50" r:id="rId49"/>
-    <hyperlink ref="N51" r:id="rId50"/>
-    <hyperlink ref="N52" r:id="rId51"/>
-    <hyperlink ref="N53" r:id="rId52"/>
-    <hyperlink ref="N54" r:id="rId53"/>
-    <hyperlink ref="N55" r:id="rId54"/>
-    <hyperlink ref="N56" r:id="rId55"/>
-    <hyperlink ref="N57" r:id="rId56"/>
-    <hyperlink ref="N58" r:id="rId57"/>
-    <hyperlink ref="N59" r:id="rId58"/>
-    <hyperlink ref="N60" r:id="rId59"/>
-    <hyperlink ref="N61" r:id="rId60"/>
-    <hyperlink ref="N62" r:id="rId61"/>
-    <hyperlink ref="N63" r:id="rId62"/>
-    <hyperlink ref="N64" r:id="rId63"/>
-    <hyperlink ref="N65" r:id="rId64"/>
-    <hyperlink ref="N66" r:id="rId65"/>
-    <hyperlink ref="N67" r:id="rId66"/>
-    <hyperlink ref="N68" r:id="rId67"/>
-    <hyperlink ref="N69" r:id="rId68"/>
-    <hyperlink ref="N70" r:id="rId69"/>
-    <hyperlink ref="N71" r:id="rId70"/>
-    <hyperlink ref="N72" r:id="rId71"/>
-    <hyperlink ref="N73" r:id="rId72"/>
-    <hyperlink ref="N74" r:id="rId73"/>
-    <hyperlink ref="N75" r:id="rId74"/>
-    <hyperlink ref="N76" r:id="rId75"/>
-    <hyperlink ref="N77" r:id="rId76"/>
-    <hyperlink ref="N78" r:id="rId77"/>
-    <hyperlink ref="N79" r:id="rId78"/>
-    <hyperlink ref="N80" r:id="rId79"/>
-    <hyperlink ref="N81" r:id="rId80"/>
-    <hyperlink ref="N82" r:id="rId81"/>
-    <hyperlink ref="N83" r:id="rId82"/>
-    <hyperlink ref="N84" r:id="rId83"/>
-    <hyperlink ref="N85" r:id="rId84"/>
-    <hyperlink ref="N86" r:id="rId85"/>
-    <hyperlink ref="N87" r:id="rId86"/>
-    <hyperlink ref="N88" r:id="rId87"/>
-    <hyperlink ref="N89" r:id="rId88"/>
-    <hyperlink ref="N90" r:id="rId89"/>
-    <hyperlink ref="N91" r:id="rId90"/>
-    <hyperlink ref="N92" r:id="rId91"/>
-    <hyperlink ref="N93" r:id="rId92"/>
-    <hyperlink ref="N94" r:id="rId93"/>
-    <hyperlink ref="N95" r:id="rId94"/>
-    <hyperlink ref="N96" r:id="rId95"/>
-    <hyperlink ref="N97" r:id="rId96"/>
-    <hyperlink ref="N98" r:id="rId97"/>
-    <hyperlink ref="N99" r:id="rId98"/>
-    <hyperlink ref="N100" r:id="rId99"/>
-    <hyperlink ref="N101" r:id="rId100"/>
-    <hyperlink ref="N102" r:id="rId101"/>
-    <hyperlink ref="N103" r:id="rId102"/>
-    <hyperlink ref="N104" r:id="rId103"/>
-    <hyperlink ref="N105" r:id="rId104"/>
-    <hyperlink ref="N106" r:id="rId105"/>
-    <hyperlink ref="N107" r:id="rId106"/>
-    <hyperlink ref="N108" r:id="rId107"/>
-    <hyperlink ref="N109" r:id="rId108"/>
-    <hyperlink ref="N110" r:id="rId109"/>
-    <hyperlink ref="N111" r:id="rId110"/>
-    <hyperlink ref="N112" r:id="rId111"/>
-    <hyperlink ref="N113" r:id="rId112"/>
-    <hyperlink ref="N114" r:id="rId113"/>
-    <hyperlink ref="N115" r:id="rId114"/>
-    <hyperlink ref="N116" r:id="rId115"/>
-    <hyperlink ref="N117" r:id="rId116"/>
-    <hyperlink ref="N118" r:id="rId117"/>
-    <hyperlink ref="N119" r:id="rId118"/>
-    <hyperlink ref="N120" r:id="rId119"/>
-    <hyperlink ref="N121" r:id="rId120"/>
-    <hyperlink ref="N122" r:id="rId121"/>
-    <hyperlink ref="N123" r:id="rId122"/>
-    <hyperlink ref="N124" r:id="rId123"/>
-    <hyperlink ref="N125" r:id="rId124"/>
-    <hyperlink ref="N126" r:id="rId125"/>
-    <hyperlink ref="N127" r:id="rId126"/>
-    <hyperlink ref="N128" r:id="rId127"/>
-    <hyperlink ref="N129" r:id="rId128"/>
-    <hyperlink ref="N130" r:id="rId129"/>
-    <hyperlink ref="N131" r:id="rId130"/>
-    <hyperlink ref="N132" r:id="rId131"/>
-    <hyperlink ref="N133" r:id="rId132"/>
-    <hyperlink ref="N134" r:id="rId133"/>
-    <hyperlink ref="N135" r:id="rId134"/>
-    <hyperlink ref="N136" r:id="rId135"/>
-    <hyperlink ref="N137" r:id="rId136"/>
-    <hyperlink ref="N138" r:id="rId137"/>
-    <hyperlink ref="N139" r:id="rId138"/>
-    <hyperlink ref="N140" r:id="rId139"/>
-    <hyperlink ref="N141" r:id="rId140"/>
-    <hyperlink ref="N142" r:id="rId141"/>
-    <hyperlink ref="N143" r:id="rId142"/>
-    <hyperlink ref="N144" r:id="rId143"/>
-    <hyperlink ref="N145" r:id="rId144"/>
-    <hyperlink ref="N146" r:id="rId145"/>
-    <hyperlink ref="N147" r:id="rId146"/>
-    <hyperlink ref="N148" r:id="rId147"/>
-    <hyperlink ref="N149" r:id="rId148"/>
-    <hyperlink ref="N150" r:id="rId149"/>
-    <hyperlink ref="N151" r:id="rId150"/>
-    <hyperlink ref="N152" r:id="rId151"/>
-    <hyperlink ref="N153" r:id="rId152"/>
-    <hyperlink ref="N154" r:id="rId153"/>
-    <hyperlink ref="N155" r:id="rId154"/>
-    <hyperlink ref="N156" r:id="rId155"/>
-    <hyperlink ref="N157" r:id="rId156"/>
-    <hyperlink ref="N158" r:id="rId157"/>
-    <hyperlink ref="N159" r:id="rId158"/>
-    <hyperlink ref="N160" r:id="rId159"/>
-    <hyperlink ref="N161" r:id="rId160"/>
-    <hyperlink ref="N162" r:id="rId161"/>
-    <hyperlink ref="N163" r:id="rId162"/>
-    <hyperlink ref="N164" r:id="rId163"/>
-    <hyperlink ref="N165" r:id="rId164"/>
-    <hyperlink ref="N166" r:id="rId165"/>
-    <hyperlink ref="N167" r:id="rId166"/>
-    <hyperlink ref="N168" r:id="rId167"/>
-    <hyperlink ref="N169" r:id="rId168"/>
-    <hyperlink ref="N170" r:id="rId169"/>
-    <hyperlink ref="N171" r:id="rId170"/>
-    <hyperlink ref="N172" r:id="rId171"/>
-    <hyperlink ref="N173" r:id="rId172"/>
-    <hyperlink ref="N174" r:id="rId173"/>
-    <hyperlink ref="N175" r:id="rId174"/>
-    <hyperlink ref="N176" r:id="rId175"/>
-    <hyperlink ref="N177" r:id="rId176"/>
-    <hyperlink ref="N178" r:id="rId177"/>
-    <hyperlink ref="N179" r:id="rId178"/>
-    <hyperlink ref="N180" r:id="rId179"/>
-    <hyperlink ref="N181" r:id="rId180"/>
-    <hyperlink ref="N182" r:id="rId181"/>
-    <hyperlink ref="N183" r:id="rId182"/>
-    <hyperlink ref="N184" r:id="rId183"/>
-    <hyperlink ref="N185" r:id="rId184"/>
-    <hyperlink ref="N186" r:id="rId185"/>
-    <hyperlink ref="N187" r:id="rId186"/>
-    <hyperlink ref="N188" r:id="rId187"/>
-    <hyperlink ref="N189" r:id="rId188"/>
-    <hyperlink ref="N190" r:id="rId189"/>
-    <hyperlink ref="N191" r:id="rId190"/>
-    <hyperlink ref="N192" r:id="rId191"/>
-    <hyperlink ref="N193" r:id="rId192"/>
-    <hyperlink ref="N194" r:id="rId193"/>
-    <hyperlink ref="N195" r:id="rId194"/>
-    <hyperlink ref="N196" r:id="rId195"/>
-    <hyperlink ref="N197" r:id="rId196"/>
-    <hyperlink ref="N198" r:id="rId197"/>
-    <hyperlink ref="N199" r:id="rId198"/>
-    <hyperlink ref="N200" r:id="rId199"/>
-    <hyperlink ref="N201" r:id="rId200"/>
-    <hyperlink ref="N202" r:id="rId201"/>
-    <hyperlink ref="N203" r:id="rId202"/>
-    <hyperlink ref="N204" r:id="rId203"/>
-    <hyperlink ref="N205" r:id="rId204"/>
-    <hyperlink ref="N206" r:id="rId205"/>
-    <hyperlink ref="N207" r:id="rId206"/>
-    <hyperlink ref="N208" r:id="rId207"/>
-    <hyperlink ref="N209" r:id="rId208"/>
-    <hyperlink ref="N210" r:id="rId209"/>
-    <hyperlink ref="N211" r:id="rId210"/>
-    <hyperlink ref="N212" r:id="rId211"/>
-    <hyperlink ref="N213" r:id="rId212"/>
-    <hyperlink ref="N214" r:id="rId213"/>
-    <hyperlink ref="N215" r:id="rId214"/>
-    <hyperlink ref="N216" r:id="rId215"/>
-    <hyperlink ref="N217" r:id="rId216"/>
-    <hyperlink ref="N218" r:id="rId217"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="N42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="N43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="N44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="N45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="N46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="N47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="N48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="N49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="N50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="N51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="N52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="N53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="N54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="N55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="N56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="N57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="N58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="N59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="N60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="N61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="N62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="N63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="N64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="N65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="N66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="N67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="N68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="N69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="N70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="N71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="N72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="N73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="N74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="N75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="N76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="N77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="N78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="N79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="N80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="N81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="N82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="N83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="N84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="N85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="N86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="N87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="N88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="N89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="N90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="N91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="N92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="N93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="N94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="N95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="N96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="N97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="N98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="N99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="N100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="N101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="N102" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="N103" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="N104" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="N105" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="N106" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="N107" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="N108" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="N109" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="N110" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="N111" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="N112" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="N113" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="N114" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="N115" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="N116" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="N117" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="N118" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="N119" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="N120" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="N121" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="N122" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="N123" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="N124" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="N125" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="N126" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="N127" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="N128" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="N129" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="N130" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="N131" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="N132" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="N133" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="N134" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="N135" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="N136" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="N137" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="N138" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="N139" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="N140" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="N141" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="N142" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="N143" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="N144" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="N145" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="N146" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="N147" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="N148" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="N149" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="N150" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="N151" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="N152" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="N153" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="N154" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="N155" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="N156" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="N157" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="N158" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="N159" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="N160" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="N161" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="N162" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="N163" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="N164" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="N165" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="N166" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="N167" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="N168" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="N169" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="N170" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="N171" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="N172" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="N173" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="N174" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="N175" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="N176" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="N177" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="N178" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="N179" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="N180" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="N181" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="N182" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="N183" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="N184" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="N185" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="N186" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="N187" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="N188" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="N189" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="N190" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="N191" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="N192" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="N193" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="N194" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="N195" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="N196" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="N197" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="N198" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="N199" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="N200" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="N201" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="N202" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="N203" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="N204" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="N205" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="N206" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="N207" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="N208" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="N209" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="N210" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="N211" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="N212" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="N213" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="N214" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="N215" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="N216" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="N217" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="N218" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 3 - colonne Surnom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6563C8D-81FF-45C0-824F-11BF62BF9499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0423F4C-430B-413F-B963-233E74D4857F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3894" uniqueCount="1703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3919" uniqueCount="1698">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2287,9 +2287,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ef/Robert_Campin_-_Triptych_with_the_Annunciation%2C_known_as_the_%22Merode_Altarpiece%22_-_Google_Art_Project.jpg/1280px-Robert_Campin_-_Triptych_with_the_Annunciation%2C_known_as_the_%22Merode_Altarpiece%22_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Peinture</t>
-  </si>
-  <si>
     <t>64.1</t>
   </si>
   <si>
@@ -3562,12 +3559,12 @@
     <t>Antonio</t>
   </si>
   <si>
+    <t>di PUCCIO PISANO</t>
+  </si>
+  <si>
     <t>PISANELLO</t>
   </si>
   <si>
-    <t>c. 1420</t>
-  </si>
-  <si>
     <t>Museo di Castelvecchio</t>
   </si>
   <si>
@@ -3580,9 +3577,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/50/Pisanello_-_Madone_%C3%A0_la_caille.jpg/960px-Pisanello_-_Madone_%C3%A0_la_caille.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Peinture sur panneau</t>
-  </si>
-  <si>
     <t>Tempera et or sur bois</t>
   </si>
   <si>
@@ -3592,9 +3586,6 @@
     <t>32 cm</t>
   </si>
   <si>
-    <t>c. 1426</t>
-  </si>
-  <si>
     <t>Église San Fermo Maggiore</t>
   </si>
   <si>
@@ -3607,9 +3598,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Pisanello%2C_monumento_a_Niccol%C3%B2_Brenzoni%2C_00.jpg/960px-Pisanello%2C_monumento_a_Niccol%C3%B2_Brenzoni%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>c. 1433</t>
-  </si>
-  <si>
     <t>Portrait de l'empereur Sigismond de Luxembourg</t>
   </si>
   <si>
@@ -3640,9 +3628,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Ritratto_d%27uomo_detto_%22Principe_moscovita%22_PR_57_Musei_di_Strada_Nuova.jpg/960px-Ritratto_d%27uomo_detto_%22Principe_moscovita%22_PR_57_Musei_di_Strada_Nuova.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>c. 1433-1438</t>
-  </si>
-  <si>
     <t>Église Sant'Anastasia</t>
   </si>
   <si>
@@ -3661,9 +3646,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Saint_George_and_the_princess_by_Pisanello_-_Pellegrini_Chapel_-_Sant%27Anastasia_-_Verona_2016_%282%29.jpg/1280px-Saint_George_and_the_princess_by_Pisanello_-_Pellegrini_Chapel_-_Sant%27Anastasia_-_Verona_2016_%282%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>c. 1436-1438</t>
-  </si>
-  <si>
     <t>La Vision de saint Eustache</t>
   </si>
   <si>
@@ -3679,9 +3661,6 @@
     <t>53 cm</t>
   </si>
   <si>
-    <t>c. 1441</t>
-  </si>
-  <si>
     <t>Bergame</t>
   </si>
   <si>
@@ -3703,9 +3682,6 @@
     <t>19 cm</t>
   </si>
   <si>
-    <t>c. 1449</t>
-  </si>
-  <si>
     <t>Portrait d'une princesse de la maison d'Este</t>
   </si>
   <si>
@@ -4450,9 +4426,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/2/24/Pala_dei_Mercanti._Madonna_col_Bambino_in_trono_fra_i_Santi_Petronio_e_Giovanni_Evangelista_adorata_dal_committente_Alberto_Cattani._Pinacoteca%2C_Bologna.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>Retable avec une technique d'</t>
-  </si>
-  <si>
     <t>Huile et tempera sur toile</t>
   </si>
   <si>
@@ -4633,9 +4606,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6f/Fernando_gallego-piedad-prado.jpg/1280px-Fernando_gallego-piedad-prado.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>15e siècle</t>
-  </si>
-  <si>
     <t>Museu Nacional d'Art de Catalunya</t>
   </si>
   <si>
@@ -5128,7 +5098,22 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fd/Konrad_Witz_-_King_Solomon_and_the_Queen_of_Sheba_-_WGA25850.jpg/1280px-Konrad_Witz_-_King_Solomon_and_the_Queen_of_Sheba_-_WGA25850.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>di PUCCIO PISANO</t>
+    <t>1433-1438</t>
+  </si>
+  <si>
+    <t>1436-1438</t>
+  </si>
+  <si>
+    <t>1441 environ</t>
+  </si>
+  <si>
+    <t>MASACCIO</t>
+  </si>
+  <si>
+    <t>FRA ANGELICO</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/ad/Battesimo_dei_neofiti_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -5151,7 +5136,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5161,6 +5146,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -5180,7 +5170,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5190,6 +5180,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -7772,6 +7767,9 @@
       <c r="B50" t="s">
         <v>306</v>
       </c>
+      <c r="C50" t="s">
+        <v>1695</v>
+      </c>
       <c r="D50" t="s">
         <v>307</v>
       </c>
@@ -7819,6 +7817,9 @@
       <c r="B51" t="s">
         <v>306</v>
       </c>
+      <c r="C51" t="s">
+        <v>1695</v>
+      </c>
       <c r="D51" t="s">
         <v>315</v>
       </c>
@@ -7860,6 +7861,9 @@
       <c r="B52" t="s">
         <v>306</v>
       </c>
+      <c r="C52" t="s">
+        <v>1695</v>
+      </c>
       <c r="D52" t="s">
         <v>321</v>
       </c>
@@ -7904,6 +7908,9 @@
       <c r="B53" t="s">
         <v>306</v>
       </c>
+      <c r="C53" t="s">
+        <v>1695</v>
+      </c>
       <c r="D53" t="s">
         <v>330</v>
       </c>
@@ -7948,6 +7955,9 @@
       <c r="B54" t="s">
         <v>306</v>
       </c>
+      <c r="C54" t="s">
+        <v>1695</v>
+      </c>
       <c r="D54" t="s">
         <v>336</v>
       </c>
@@ -7998,6 +8008,9 @@
       <c r="B55" t="s">
         <v>306</v>
       </c>
+      <c r="C55" t="s">
+        <v>1695</v>
+      </c>
       <c r="D55" t="s">
         <v>336</v>
       </c>
@@ -8048,6 +8061,9 @@
       <c r="B56" t="s">
         <v>306</v>
       </c>
+      <c r="C56" t="s">
+        <v>1695</v>
+      </c>
       <c r="D56" t="s">
         <v>336</v>
       </c>
@@ -8098,6 +8114,9 @@
       <c r="B57" t="s">
         <v>306</v>
       </c>
+      <c r="C57" t="s">
+        <v>1695</v>
+      </c>
       <c r="D57" t="s">
         <v>336</v>
       </c>
@@ -8148,6 +8167,9 @@
       <c r="B58" t="s">
         <v>306</v>
       </c>
+      <c r="C58" t="s">
+        <v>1695</v>
+      </c>
       <c r="D58" t="s">
         <v>307</v>
       </c>
@@ -8204,6 +8226,9 @@
       <c r="B59" t="s">
         <v>306</v>
       </c>
+      <c r="C59" t="s">
+        <v>1695</v>
+      </c>
       <c r="D59" t="s">
         <v>307</v>
       </c>
@@ -8222,7 +8247,9 @@
       <c r="K59" t="s">
         <v>369</v>
       </c>
-      <c r="L59" s="1"/>
+      <c r="L59" s="6" t="s">
+        <v>1697</v>
+      </c>
       <c r="M59" t="s">
         <v>364</v>
       </c>
@@ -8255,6 +8282,9 @@
       <c r="B60" t="s">
         <v>306</v>
       </c>
+      <c r="C60" t="s">
+        <v>1695</v>
+      </c>
       <c r="D60" t="s">
         <v>371</v>
       </c>
@@ -8299,6 +8329,9 @@
       <c r="B61" t="s">
         <v>306</v>
       </c>
+      <c r="C61" t="s">
+        <v>1695</v>
+      </c>
       <c r="D61" t="s">
         <v>376</v>
       </c>
@@ -8346,6 +8379,9 @@
       <c r="B62" t="s">
         <v>384</v>
       </c>
+      <c r="C62" t="s">
+        <v>1696</v>
+      </c>
       <c r="D62" t="s">
         <v>385</v>
       </c>
@@ -8387,6 +8423,9 @@
       <c r="B63" t="s">
         <v>384</v>
       </c>
+      <c r="C63" t="s">
+        <v>1696</v>
+      </c>
       <c r="D63" t="s">
         <v>389</v>
       </c>
@@ -8431,6 +8470,9 @@
       <c r="B64" t="s">
         <v>384</v>
       </c>
+      <c r="C64" t="s">
+        <v>1696</v>
+      </c>
       <c r="D64" t="s">
         <v>393</v>
       </c>
@@ -8475,6 +8517,9 @@
       <c r="B65" t="s">
         <v>384</v>
       </c>
+      <c r="C65" t="s">
+        <v>1696</v>
+      </c>
       <c r="D65" t="s">
         <v>397</v>
       </c>
@@ -8525,6 +8570,9 @@
       <c r="B66" t="s">
         <v>384</v>
       </c>
+      <c r="C66" t="s">
+        <v>1696</v>
+      </c>
       <c r="D66" t="s">
         <v>404</v>
       </c>
@@ -8566,6 +8614,9 @@
       <c r="B67" t="s">
         <v>384</v>
       </c>
+      <c r="C67" t="s">
+        <v>1696</v>
+      </c>
       <c r="D67" t="s">
         <v>407</v>
       </c>
@@ -8610,6 +8661,9 @@
       <c r="B68" t="s">
         <v>384</v>
       </c>
+      <c r="C68" t="s">
+        <v>1696</v>
+      </c>
       <c r="D68" t="s">
         <v>411</v>
       </c>
@@ -8657,6 +8711,9 @@
       <c r="B69" t="s">
         <v>384</v>
       </c>
+      <c r="C69" t="s">
+        <v>1696</v>
+      </c>
       <c r="D69" t="s">
         <v>411</v>
       </c>
@@ -8704,6 +8761,9 @@
       <c r="B70" t="s">
         <v>384</v>
       </c>
+      <c r="C70" t="s">
+        <v>1696</v>
+      </c>
       <c r="D70" t="s">
         <v>411</v>
       </c>
@@ -8751,6 +8811,9 @@
       <c r="B71" t="s">
         <v>384</v>
       </c>
+      <c r="C71" t="s">
+        <v>1696</v>
+      </c>
       <c r="D71" t="s">
         <v>421</v>
       </c>
@@ -8801,6 +8864,9 @@
       <c r="B72" t="s">
         <v>384</v>
       </c>
+      <c r="C72" t="s">
+        <v>1696</v>
+      </c>
       <c r="D72" t="s">
         <v>426</v>
       </c>
@@ -8845,6 +8911,9 @@
       <c r="B73" t="s">
         <v>384</v>
       </c>
+      <c r="C73" t="s">
+        <v>1696</v>
+      </c>
       <c r="D73" t="s">
         <v>429</v>
       </c>
@@ -11724,16 +11793,16 @@
         <v>754</v>
       </c>
       <c r="R138" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S138" t="s">
         <v>38</v>
       </c>
       <c r="T138" t="s">
+        <v>755</v>
+      </c>
+      <c r="U138" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="U138" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="W138" s="2">
         <v>2</v>
@@ -11750,34 +11819,34 @@
         <v>749</v>
       </c>
       <c r="D139" t="s">
+        <v>757</v>
+      </c>
+      <c r="E139" t="s">
         <v>758</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>759</v>
-      </c>
-      <c r="F139" t="s">
-        <v>760</v>
       </c>
       <c r="J139" t="s">
         <v>265</v>
       </c>
       <c r="K139" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="L139" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="L139" s="1" t="s">
-        <v>762</v>
-      </c>
       <c r="R139" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S139" t="s">
         <v>38</v>
       </c>
       <c r="T139" t="s">
+        <v>762</v>
+      </c>
+      <c r="U139" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="U139" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="W139" s="2">
         <v>2</v>
@@ -11803,25 +11872,25 @@
         <v>96</v>
       </c>
       <c r="J140" t="s">
+        <v>764</v>
+      </c>
+      <c r="K140" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="K140" s="3" t="s">
+      <c r="L140" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="L140" s="1" t="s">
-        <v>767</v>
-      </c>
       <c r="R140" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S140" t="s">
         <v>167</v>
       </c>
       <c r="T140" t="s">
+        <v>767</v>
+      </c>
+      <c r="U140" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="U140" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="W140" s="2">
         <v>2</v>
@@ -11838,7 +11907,7 @@
         <v>749</v>
       </c>
       <c r="D141" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E141" t="s">
         <v>95</v>
@@ -11847,25 +11916,25 @@
         <v>96</v>
       </c>
       <c r="J141" t="s">
+        <v>770</v>
+      </c>
+      <c r="K141" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="K141" s="3" t="s">
+      <c r="L141" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="L141" s="1" t="s">
-        <v>773</v>
-      </c>
       <c r="R141" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S141" t="s">
         <v>167</v>
       </c>
       <c r="T141" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="U141" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="W141" s="2">
         <v>2</v>
@@ -11882,34 +11951,34 @@
         <v>749</v>
       </c>
       <c r="D142" t="s">
+        <v>774</v>
+      </c>
+      <c r="E142" t="s">
         <v>775</v>
-      </c>
-      <c r="E142" t="s">
-        <v>776</v>
       </c>
       <c r="F142" t="s">
         <v>52</v>
       </c>
       <c r="J142" t="s">
+        <v>776</v>
+      </c>
+      <c r="K142" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="K142" s="3" t="s">
+      <c r="L142" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="L142" s="1" t="s">
-        <v>779</v>
-      </c>
       <c r="R142" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S142" t="s">
         <v>38</v>
       </c>
       <c r="T142" t="s">
+        <v>779</v>
+      </c>
+      <c r="U142" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="U142" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="W142" s="2">
         <v>2</v>
@@ -11935,22 +12004,22 @@
         <v>27</v>
       </c>
       <c r="J143" t="s">
+        <v>781</v>
+      </c>
+      <c r="K143" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="K143" s="3" t="s">
+      <c r="L143" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="L143" s="1" t="s">
-        <v>784</v>
-      </c>
       <c r="R143" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S143" t="s">
         <v>38</v>
       </c>
       <c r="T143" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="U143" s="2" t="s">
         <v>258</v>
@@ -11970,7 +12039,7 @@
         <v>749</v>
       </c>
       <c r="D144" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E144" t="s">
         <v>95</v>
@@ -11979,25 +12048,25 @@
         <v>96</v>
       </c>
       <c r="J144" t="s">
+        <v>786</v>
+      </c>
+      <c r="K144" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="K144" s="3" t="s">
+      <c r="L144" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="L144" s="1" t="s">
-        <v>789</v>
-      </c>
       <c r="R144" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S144" t="s">
         <v>38</v>
       </c>
       <c r="T144" t="s">
+        <v>789</v>
+      </c>
+      <c r="U144" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="U144" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="W144" s="2">
         <v>2</v>
@@ -12026,19 +12095,19 @@
         <v>317</v>
       </c>
       <c r="K145" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="L145" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="L145" s="1" t="s">
-        <v>793</v>
-      </c>
       <c r="R145" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S145" t="s">
         <v>38</v>
       </c>
       <c r="T145" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="U145" s="2" t="s">
         <v>345</v>
@@ -12052,13 +12121,13 @@
     </row>
     <row r="146" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>794</v>
+      </c>
+      <c r="B146" t="s">
         <v>795</v>
       </c>
-      <c r="B146" t="s">
+      <c r="D146" t="s">
         <v>796</v>
-      </c>
-      <c r="D146" t="s">
-        <v>797</v>
       </c>
       <c r="E146" t="s">
         <v>654</v>
@@ -12067,13 +12136,13 @@
         <v>655</v>
       </c>
       <c r="J146" t="s">
+        <v>797</v>
+      </c>
+      <c r="K146" t="s">
         <v>798</v>
       </c>
-      <c r="K146" t="s">
+      <c r="L146" s="1" t="s">
         <v>799</v>
-      </c>
-      <c r="L146" s="1" t="s">
-        <v>800</v>
       </c>
       <c r="R146" t="s">
         <v>31</v>
@@ -12091,18 +12160,18 @@
         <v>2</v>
       </c>
       <c r="X146" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="147" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>794</v>
+      </c>
+      <c r="B147" t="s">
         <v>795</v>
       </c>
-      <c r="B147" t="s">
-        <v>796</v>
-      </c>
       <c r="D147" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E147" t="s">
         <v>95</v>
@@ -12111,13 +12180,13 @@
         <v>96</v>
       </c>
       <c r="J147" t="s">
+        <v>801</v>
+      </c>
+      <c r="K147" t="s">
         <v>802</v>
       </c>
-      <c r="K147" t="s">
+      <c r="L147" s="1" t="s">
         <v>803</v>
-      </c>
-      <c r="L147" s="1" t="s">
-        <v>804</v>
       </c>
       <c r="R147" t="s">
         <v>31</v>
@@ -12135,18 +12204,18 @@
         <v>2</v>
       </c>
       <c r="X147" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="148" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>794</v>
+      </c>
+      <c r="B148" t="s">
         <v>795</v>
       </c>
-      <c r="B148" t="s">
-        <v>796</v>
-      </c>
       <c r="D148" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E148" t="s">
         <v>34</v>
@@ -12155,22 +12224,22 @@
         <v>35</v>
       </c>
       <c r="J148" t="s">
+        <v>805</v>
+      </c>
+      <c r="K148" t="s">
         <v>806</v>
       </c>
-      <c r="K148" t="s">
+      <c r="L148" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="L148" s="1" t="s">
+      <c r="N148" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="N148" s="1" t="s">
+      <c r="R148" t="s">
+        <v>31</v>
+      </c>
+      <c r="S148" t="s">
         <v>809</v>
-      </c>
-      <c r="R148" t="s">
-        <v>31</v>
-      </c>
-      <c r="S148" t="s">
-        <v>810</v>
       </c>
       <c r="T148">
         <v>134</v>
@@ -12182,18 +12251,18 @@
         <v>2</v>
       </c>
       <c r="X148" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="149" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>794</v>
+      </c>
+      <c r="B149" t="s">
         <v>795</v>
       </c>
-      <c r="B149" t="s">
-        <v>796</v>
-      </c>
       <c r="D149" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E149" t="s">
         <v>34</v>
@@ -12202,22 +12271,22 @@
         <v>35</v>
       </c>
       <c r="J149" t="s">
+        <v>810</v>
+      </c>
+      <c r="K149" t="s">
         <v>811</v>
       </c>
-      <c r="K149" t="s">
+      <c r="L149" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="L149" s="1" t="s">
-        <v>813</v>
-      </c>
       <c r="N149" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="R149" t="s">
+        <v>31</v>
+      </c>
+      <c r="S149" t="s">
         <v>809</v>
-      </c>
-      <c r="R149" t="s">
-        <v>31</v>
-      </c>
-      <c r="S149" t="s">
-        <v>810</v>
       </c>
       <c r="T149">
         <v>134</v>
@@ -12229,18 +12298,18 @@
         <v>2</v>
       </c>
       <c r="X149" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="150" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>794</v>
+      </c>
+      <c r="B150" t="s">
         <v>795</v>
       </c>
-      <c r="B150" t="s">
-        <v>796</v>
-      </c>
       <c r="D150" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E150" t="s">
         <v>575</v>
@@ -12249,13 +12318,13 @@
         <v>576</v>
       </c>
       <c r="J150" t="s">
+        <v>814</v>
+      </c>
+      <c r="K150" t="s">
         <v>815</v>
       </c>
-      <c r="K150" t="s">
+      <c r="L150" s="1" t="s">
         <v>816</v>
-      </c>
-      <c r="L150" s="1" t="s">
-        <v>817</v>
       </c>
       <c r="R150" t="s">
         <v>31</v>
@@ -12273,15 +12342,15 @@
         <v>2</v>
       </c>
       <c r="X150" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="151" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>794</v>
+      </c>
+      <c r="B151" t="s">
         <v>795</v>
-      </c>
-      <c r="B151" t="s">
-        <v>796</v>
       </c>
       <c r="D151" t="s">
         <v>238</v>
@@ -12296,10 +12365,10 @@
         <v>265</v>
       </c>
       <c r="K151" t="s">
+        <v>817</v>
+      </c>
+      <c r="L151" s="1" t="s">
         <v>818</v>
-      </c>
-      <c r="L151" s="1" t="s">
-        <v>819</v>
       </c>
       <c r="R151" t="s">
         <v>31</v>
@@ -12317,18 +12386,18 @@
         <v>2</v>
       </c>
       <c r="X151" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="152" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>819</v>
+      </c>
+      <c r="B152" t="s">
         <v>820</v>
       </c>
-      <c r="B152" t="s">
+      <c r="D152" t="s">
         <v>821</v>
-      </c>
-      <c r="D152" t="s">
-        <v>822</v>
       </c>
       <c r="E152" t="s">
         <v>95</v>
@@ -12337,39 +12406,39 @@
         <v>96</v>
       </c>
       <c r="J152" t="s">
+        <v>822</v>
+      </c>
+      <c r="K152" t="s">
         <v>823</v>
       </c>
-      <c r="K152" t="s">
+      <c r="L152" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="L152" s="1" t="s">
-        <v>825</v>
-      </c>
       <c r="R152" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S152" t="s">
         <v>458</v>
       </c>
       <c r="T152" t="s">
+        <v>825</v>
+      </c>
+      <c r="U152" s="2" t="s">
         <v>826</v>
-      </c>
-      <c r="U152" s="2" t="s">
-        <v>827</v>
       </c>
       <c r="W152" s="2">
         <v>2</v>
       </c>
       <c r="X152" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="153" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>819</v>
+      </c>
+      <c r="B153" t="s">
         <v>820</v>
-      </c>
-      <c r="B153" t="s">
-        <v>821</v>
       </c>
       <c r="D153" t="s">
         <v>33</v>
@@ -12381,42 +12450,42 @@
         <v>655</v>
       </c>
       <c r="J153" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="K153" t="s">
         <v>347</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="R153" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S153" t="s">
         <v>327</v>
       </c>
       <c r="T153" t="s">
+        <v>829</v>
+      </c>
+      <c r="U153" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="U153" s="2" t="s">
-        <v>831</v>
       </c>
       <c r="W153" s="2">
         <v>2</v>
       </c>
       <c r="X153" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="154" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>819</v>
+      </c>
+      <c r="B154" t="s">
         <v>820</v>
       </c>
-      <c r="B154" t="s">
-        <v>821</v>
-      </c>
       <c r="D154" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E154" t="s">
         <v>95</v>
@@ -12425,22 +12494,22 @@
         <v>96</v>
       </c>
       <c r="J154" t="s">
+        <v>832</v>
+      </c>
+      <c r="K154" t="s">
         <v>833</v>
       </c>
-      <c r="K154" t="s">
+      <c r="L154" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="L154" s="1" t="s">
-        <v>835</v>
-      </c>
       <c r="R154" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S154" t="s">
         <v>327</v>
       </c>
       <c r="T154" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="U154" s="2" t="s">
         <v>451</v>
@@ -12449,15 +12518,15 @@
         <v>2</v>
       </c>
       <c r="X154" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="155" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>819</v>
+      </c>
+      <c r="B155" t="s">
         <v>820</v>
-      </c>
-      <c r="B155" t="s">
-        <v>821</v>
       </c>
       <c r="D155" t="s">
         <v>135</v>
@@ -12469,42 +12538,42 @@
         <v>270</v>
       </c>
       <c r="J155" t="s">
+        <v>836</v>
+      </c>
+      <c r="K155" t="s">
         <v>837</v>
       </c>
-      <c r="K155" t="s">
+      <c r="L155" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="L155" s="1" t="s">
-        <v>839</v>
-      </c>
       <c r="R155" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S155" t="s">
         <v>327</v>
       </c>
       <c r="T155" t="s">
+        <v>839</v>
+      </c>
+      <c r="U155" s="2" t="s">
         <v>840</v>
-      </c>
-      <c r="U155" s="2" t="s">
-        <v>841</v>
       </c>
       <c r="W155" s="2">
         <v>2</v>
       </c>
       <c r="X155" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="156" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>819</v>
+      </c>
+      <c r="B156" t="s">
         <v>820</v>
       </c>
-      <c r="B156" t="s">
-        <v>821</v>
-      </c>
       <c r="D156" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E156" t="s">
         <v>197</v>
@@ -12513,39 +12582,39 @@
         <v>270</v>
       </c>
       <c r="J156" t="s">
+        <v>842</v>
+      </c>
+      <c r="K156" t="s">
         <v>843</v>
       </c>
-      <c r="K156" t="s">
+      <c r="L156" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="L156" s="1" t="s">
-        <v>845</v>
-      </c>
       <c r="R156" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S156" t="s">
         <v>327</v>
       </c>
       <c r="T156" t="s">
+        <v>845</v>
+      </c>
+      <c r="U156" s="2" t="s">
         <v>846</v>
-      </c>
-      <c r="U156" s="2" t="s">
-        <v>847</v>
       </c>
       <c r="W156" s="2">
         <v>2</v>
       </c>
       <c r="X156" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="157" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>819</v>
+      </c>
+      <c r="B157" t="s">
         <v>820</v>
-      </c>
-      <c r="B157" t="s">
-        <v>821</v>
       </c>
       <c r="D157" t="s">
         <v>124</v>
@@ -12557,39 +12626,39 @@
         <v>96</v>
       </c>
       <c r="J157" t="s">
+        <v>847</v>
+      </c>
+      <c r="K157" t="s">
         <v>848</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="L157" s="1" t="s">
-        <v>850</v>
-      </c>
       <c r="R157" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S157" t="s">
         <v>327</v>
       </c>
       <c r="T157" t="s">
+        <v>850</v>
+      </c>
+      <c r="U157" s="2" t="s">
         <v>851</v>
-      </c>
-      <c r="U157" s="2" t="s">
-        <v>852</v>
       </c>
       <c r="W157" s="2">
         <v>2</v>
       </c>
       <c r="X157" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="158" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>819</v>
+      </c>
+      <c r="B158" t="s">
         <v>820</v>
-      </c>
-      <c r="B158" t="s">
-        <v>821</v>
       </c>
       <c r="D158" t="s">
         <v>686</v>
@@ -12598,89 +12667,89 @@
         <v>529</v>
       </c>
       <c r="F158" t="s">
+        <v>852</v>
+      </c>
+      <c r="J158" t="s">
         <v>853</v>
-      </c>
-      <c r="J158" t="s">
-        <v>854</v>
       </c>
       <c r="K158" t="s">
         <v>354</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R158" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S158" t="s">
         <v>327</v>
       </c>
       <c r="T158" t="s">
+        <v>839</v>
+      </c>
+      <c r="U158" s="2" t="s">
         <v>840</v>
-      </c>
-      <c r="U158" s="2" t="s">
-        <v>841</v>
       </c>
       <c r="W158" s="2">
         <v>2</v>
       </c>
       <c r="X158" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="159" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>819</v>
+      </c>
+      <c r="B159" t="s">
         <v>820</v>
       </c>
-      <c r="B159" t="s">
-        <v>821</v>
-      </c>
       <c r="D159" t="s">
+        <v>855</v>
+      </c>
+      <c r="E159" t="s">
         <v>856</v>
       </c>
-      <c r="E159" t="s">
+      <c r="F159" t="s">
         <v>857</v>
       </c>
-      <c r="F159" t="s">
+      <c r="H159" t="s">
         <v>858</v>
       </c>
-      <c r="H159" t="s">
+      <c r="J159" t="s">
         <v>859</v>
       </c>
-      <c r="J159" t="s">
+      <c r="K159" t="s">
         <v>860</v>
       </c>
-      <c r="K159" t="s">
+      <c r="L159" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="L159" s="1" t="s">
-        <v>862</v>
-      </c>
       <c r="R159" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S159" t="s">
         <v>327</v>
       </c>
       <c r="T159" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="U159" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="W159" s="2">
         <v>2</v>
       </c>
       <c r="X159" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="160" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>863</v>
+      </c>
+      <c r="B160" t="s">
         <v>864</v>
-      </c>
-      <c r="B160" t="s">
-        <v>865</v>
       </c>
       <c r="D160">
         <v>1475</v>
@@ -12692,13 +12761,13 @@
         <v>192</v>
       </c>
       <c r="J160" t="s">
+        <v>865</v>
+      </c>
+      <c r="K160" t="s">
         <v>866</v>
       </c>
-      <c r="K160" t="s">
+      <c r="L160" s="1" t="s">
         <v>867</v>
-      </c>
-      <c r="L160" s="1" t="s">
-        <v>868</v>
       </c>
       <c r="R160" t="s">
         <v>31</v>
@@ -12716,33 +12785,33 @@
         <v>2</v>
       </c>
       <c r="X160" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="161" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>863</v>
+      </c>
+      <c r="B161" t="s">
         <v>864</v>
-      </c>
-      <c r="B161" t="s">
-        <v>865</v>
       </c>
       <c r="D161">
         <v>1476</v>
       </c>
       <c r="E161" t="s">
+        <v>868</v>
+      </c>
+      <c r="F161" t="s">
         <v>869</v>
       </c>
-      <c r="F161" t="s">
+      <c r="J161" t="s">
         <v>870</v>
       </c>
-      <c r="J161" t="s">
+      <c r="K161" t="s">
         <v>871</v>
       </c>
-      <c r="K161" t="s">
+      <c r="L161" s="1" t="s">
         <v>872</v>
-      </c>
-      <c r="L161" s="1" t="s">
-        <v>873</v>
       </c>
       <c r="R161" t="s">
         <v>31</v>
@@ -12760,18 +12829,18 @@
         <v>2</v>
       </c>
       <c r="X161" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="162" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>863</v>
+      </c>
+      <c r="B162" t="s">
         <v>864</v>
       </c>
-      <c r="B162" t="s">
-        <v>865</v>
-      </c>
       <c r="D162" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E162" t="s">
         <v>95</v>
@@ -12780,16 +12849,16 @@
         <v>96</v>
       </c>
       <c r="J162" t="s">
+        <v>874</v>
+      </c>
+      <c r="K162" t="s">
         <v>875</v>
       </c>
-      <c r="K162" t="s">
+      <c r="L162" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="L162" s="1" t="s">
-        <v>877</v>
-      </c>
       <c r="R162" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S162" t="s">
         <v>32</v>
@@ -12804,39 +12873,39 @@
         <v>2</v>
       </c>
       <c r="X162" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="163" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>863</v>
+      </c>
+      <c r="B163" t="s">
         <v>864</v>
       </c>
-      <c r="B163" t="s">
-        <v>865</v>
-      </c>
       <c r="D163" t="s">
+        <v>877</v>
+      </c>
+      <c r="E163" t="s">
         <v>878</v>
       </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
         <v>879</v>
       </c>
-      <c r="F163" t="s">
+      <c r="J163" t="s">
         <v>880</v>
-      </c>
-      <c r="J163" t="s">
-        <v>881</v>
       </c>
       <c r="K163" t="s">
         <v>165</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="R163" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S163" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="T163">
         <v>180</v>
@@ -12848,15 +12917,15 @@
         <v>2</v>
       </c>
       <c r="X163" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="164" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
+        <v>863</v>
+      </c>
+      <c r="B164" t="s">
         <v>864</v>
-      </c>
-      <c r="B164" t="s">
-        <v>865</v>
       </c>
       <c r="D164" t="s">
         <v>66</v>
@@ -12868,16 +12937,16 @@
         <v>576</v>
       </c>
       <c r="J164" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K164" t="s">
         <v>354</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="R164" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S164" t="s">
         <v>32</v>
@@ -12892,24 +12961,24 @@
         <v>2</v>
       </c>
       <c r="X164" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="165" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>863</v>
+      </c>
+      <c r="B165" t="s">
         <v>864</v>
-      </c>
-      <c r="B165" t="s">
-        <v>865</v>
       </c>
       <c r="D165" t="s">
         <v>66</v>
       </c>
       <c r="E165" t="s">
+        <v>884</v>
+      </c>
+      <c r="F165" t="s">
         <v>885</v>
-      </c>
-      <c r="F165" t="s">
-        <v>886</v>
       </c>
       <c r="J165" t="s">
         <v>54</v>
@@ -12918,10 +12987,10 @@
         <v>54</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="R165" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S165" t="s">
         <v>38</v>
@@ -12936,24 +13005,24 @@
         <v>2</v>
       </c>
       <c r="X165" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="166" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>863</v>
+      </c>
+      <c r="B166" t="s">
         <v>864</v>
       </c>
-      <c r="B166" t="s">
-        <v>865</v>
-      </c>
       <c r="D166" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E166" t="s">
         <v>51</v>
       </c>
       <c r="F166" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J166" t="s">
         <v>443</v>
@@ -12962,13 +13031,13 @@
         <v>444</v>
       </c>
       <c r="L166" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="R166" t="s">
+        <v>31</v>
+      </c>
+      <c r="S166" t="s">
         <v>890</v>
-      </c>
-      <c r="R166" t="s">
-        <v>755</v>
-      </c>
-      <c r="S166" t="s">
-        <v>891</v>
       </c>
       <c r="T166">
         <v>171</v>
@@ -12980,36 +13049,36 @@
         <v>2</v>
       </c>
       <c r="X166" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="167" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>863</v>
+      </c>
+      <c r="B167" t="s">
         <v>864</v>
-      </c>
-      <c r="B167" t="s">
-        <v>865</v>
       </c>
       <c r="D167" t="s">
         <v>679</v>
       </c>
       <c r="E167" t="s">
+        <v>891</v>
+      </c>
+      <c r="F167" t="s">
         <v>892</v>
       </c>
-      <c r="F167" t="s">
+      <c r="J167" t="s">
         <v>893</v>
       </c>
-      <c r="J167" t="s">
+      <c r="K167" t="s">
         <v>894</v>
       </c>
-      <c r="K167" t="s">
+      <c r="L167" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="L167" s="1" t="s">
-        <v>896</v>
-      </c>
       <c r="R167" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S167" t="s">
         <v>32</v>
@@ -13024,18 +13093,18 @@
         <v>2</v>
       </c>
       <c r="X167" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="168" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>896</v>
+      </c>
+      <c r="B168" t="s">
         <v>897</v>
       </c>
-      <c r="B168" t="s">
+      <c r="D168" t="s">
         <v>898</v>
-      </c>
-      <c r="D168" t="s">
-        <v>899</v>
       </c>
       <c r="E168" t="s">
         <v>636</v>
@@ -13044,10 +13113,10 @@
         <v>637</v>
       </c>
       <c r="J168" t="s">
+        <v>899</v>
+      </c>
+      <c r="L168" s="1" t="s">
         <v>900</v>
-      </c>
-      <c r="L168" s="1" t="s">
-        <v>901</v>
       </c>
       <c r="R168" t="s">
         <v>31</v>
@@ -13065,7 +13134,7 @@
         <v>2</v>
       </c>
       <c r="X168" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="169" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13073,7 +13142,7 @@
         <v>440</v>
       </c>
       <c r="B169" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D169" t="s">
         <v>702</v>
@@ -13085,19 +13154,19 @@
         <v>96</v>
       </c>
       <c r="J169" t="s">
+        <v>902</v>
+      </c>
+      <c r="K169" t="s">
         <v>903</v>
       </c>
-      <c r="K169" t="s">
+      <c r="L169" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="L169" s="1" t="s">
+      <c r="R169" t="s">
+        <v>31</v>
+      </c>
+      <c r="S169" t="s">
         <v>905</v>
-      </c>
-      <c r="R169" t="s">
-        <v>31</v>
-      </c>
-      <c r="S169" t="s">
-        <v>906</v>
       </c>
       <c r="T169">
         <v>84</v>
@@ -13109,7 +13178,7 @@
         <v>2</v>
       </c>
       <c r="X169" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="170" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13117,10 +13186,10 @@
         <v>440</v>
       </c>
       <c r="B170" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D170" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E170" t="s">
         <v>59</v>
@@ -13135,13 +13204,13 @@
         <v>225</v>
       </c>
       <c r="L170" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="R170" t="s">
+        <v>31</v>
+      </c>
+      <c r="S170" t="s">
         <v>908</v>
-      </c>
-      <c r="R170" t="s">
-        <v>31</v>
-      </c>
-      <c r="S170" t="s">
-        <v>909</v>
       </c>
       <c r="T170">
         <v>177</v>
@@ -13153,7 +13222,7 @@
         <v>2</v>
       </c>
       <c r="X170" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="171" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13161,25 +13230,25 @@
         <v>440</v>
       </c>
       <c r="B171" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D171" t="s">
+        <v>909</v>
+      </c>
+      <c r="E171" t="s">
         <v>910</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>911</v>
       </c>
-      <c r="F171" t="s">
+      <c r="J171" t="s">
         <v>912</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>913</v>
       </c>
-      <c r="K171" t="s">
+      <c r="L171" s="1" t="s">
         <v>914</v>
-      </c>
-      <c r="L171" s="1" t="s">
-        <v>915</v>
       </c>
       <c r="R171" t="s">
         <v>31</v>
@@ -13197,7 +13266,7 @@
         <v>2</v>
       </c>
       <c r="X171" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="172" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13205,7 +13274,7 @@
         <v>440</v>
       </c>
       <c r="B172" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D172" t="s">
         <v>58</v>
@@ -13217,13 +13286,13 @@
         <v>35</v>
       </c>
       <c r="J172" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="K172" t="s">
         <v>347</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="R172" t="s">
         <v>31</v>
@@ -13241,7 +13310,7 @@
         <v>2</v>
       </c>
       <c r="X172" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="173" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13249,10 +13318,10 @@
         <v>440</v>
       </c>
       <c r="B173" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D173" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E173" t="s">
         <v>95</v>
@@ -13261,13 +13330,13 @@
         <v>96</v>
       </c>
       <c r="J173" t="s">
+        <v>918</v>
+      </c>
+      <c r="K173" t="s">
         <v>919</v>
       </c>
-      <c r="K173" t="s">
+      <c r="L173" s="1" t="s">
         <v>920</v>
-      </c>
-      <c r="L173" s="1" t="s">
-        <v>921</v>
       </c>
       <c r="R173" t="s">
         <v>31</v>
@@ -13285,7 +13354,7 @@
         <v>2</v>
       </c>
       <c r="X173" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="174" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13293,10 +13362,10 @@
         <v>440</v>
       </c>
       <c r="B174" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D174" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E174" t="s">
         <v>654</v>
@@ -13305,13 +13374,13 @@
         <v>655</v>
       </c>
       <c r="J174" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="K174" t="s">
         <v>347</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="R174" t="s">
         <v>31</v>
@@ -13329,7 +13398,7 @@
         <v>2</v>
       </c>
       <c r="X174" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="175" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13337,10 +13406,10 @@
         <v>440</v>
       </c>
       <c r="B175" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D175" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E175" t="s">
         <v>95</v>
@@ -13349,13 +13418,13 @@
         <v>96</v>
       </c>
       <c r="J175" t="s">
+        <v>923</v>
+      </c>
+      <c r="K175" t="s">
         <v>924</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" s="1" t="s">
         <v>925</v>
-      </c>
-      <c r="L175" s="1" t="s">
-        <v>926</v>
       </c>
       <c r="R175" t="s">
         <v>31</v>
@@ -13373,7 +13442,7 @@
         <v>2</v>
       </c>
       <c r="X175" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="176" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13381,7 +13450,7 @@
         <v>440</v>
       </c>
       <c r="B176" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D176" t="s">
         <v>660</v>
@@ -13390,22 +13459,22 @@
         <v>59</v>
       </c>
       <c r="F176" t="s">
+        <v>926</v>
+      </c>
+      <c r="J176" t="s">
         <v>927</v>
-      </c>
-      <c r="J176" t="s">
-        <v>928</v>
       </c>
       <c r="K176" t="s">
         <v>185</v>
       </c>
       <c r="L176" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="R176" t="s">
+        <v>31</v>
+      </c>
+      <c r="S176" t="s">
         <v>929</v>
-      </c>
-      <c r="R176" t="s">
-        <v>31</v>
-      </c>
-      <c r="S176" t="s">
-        <v>930</v>
       </c>
       <c r="T176">
         <v>41</v>
@@ -13417,30 +13486,30 @@
         <v>2</v>
       </c>
       <c r="X176" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="177" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>930</v>
+      </c>
+      <c r="B177" t="s">
         <v>931</v>
       </c>
-      <c r="B177" t="s">
+      <c r="D177" t="s">
         <v>932</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>933</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>934</v>
       </c>
-      <c r="F177" t="s">
+      <c r="J177" t="s">
         <v>935</v>
       </c>
-      <c r="J177" t="s">
+      <c r="L177" s="1" t="s">
         <v>936</v>
-      </c>
-      <c r="L177" s="1" t="s">
-        <v>937</v>
       </c>
       <c r="R177" t="s">
         <v>31</v>
@@ -13458,18 +13527,18 @@
         <v>2</v>
       </c>
       <c r="X177" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="178" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>937</v>
+      </c>
+      <c r="B178" t="s">
         <v>938</v>
       </c>
-      <c r="B178" t="s">
-        <v>939</v>
-      </c>
       <c r="D178" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E178" t="s">
         <v>191</v>
@@ -13481,13 +13550,13 @@
         <v>666</v>
       </c>
       <c r="L178" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="R178" s="4" t="s">
         <v>940</v>
       </c>
-      <c r="R178" s="4" t="s">
+      <c r="S178" t="s">
         <v>941</v>
-      </c>
-      <c r="S178" t="s">
-        <v>942</v>
       </c>
       <c r="T178">
         <v>7</v>
@@ -13499,18 +13568,18 @@
         <v>2</v>
       </c>
       <c r="X178" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="179" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>937</v>
+      </c>
+      <c r="B179" t="s">
         <v>938</v>
       </c>
-      <c r="B179" t="s">
-        <v>939</v>
-      </c>
       <c r="D179" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E179" t="s">
         <v>191</v>
@@ -13519,16 +13588,16 @@
         <v>192</v>
       </c>
       <c r="J179" t="s">
+        <v>943</v>
+      </c>
+      <c r="L179" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="L179" s="1" t="s">
+      <c r="R179" t="s">
+        <v>31</v>
+      </c>
+      <c r="S179" t="s">
         <v>945</v>
-      </c>
-      <c r="R179" t="s">
-        <v>31</v>
-      </c>
-      <c r="S179" t="s">
-        <v>946</v>
       </c>
       <c r="T179">
         <v>86</v>
@@ -13540,18 +13609,18 @@
         <v>2</v>
       </c>
       <c r="X179" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="180" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>937</v>
+      </c>
+      <c r="B180" t="s">
         <v>938</v>
       </c>
-      <c r="B180" t="s">
-        <v>939</v>
-      </c>
       <c r="D180" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E180" t="s">
         <v>575</v>
@@ -13560,10 +13629,10 @@
         <v>576</v>
       </c>
       <c r="J180" t="s">
+        <v>947</v>
+      </c>
+      <c r="L180" s="1" t="s">
         <v>948</v>
-      </c>
-      <c r="L180" s="1" t="s">
-        <v>949</v>
       </c>
       <c r="R180" t="s">
         <v>31</v>
@@ -13581,18 +13650,18 @@
         <v>2</v>
       </c>
       <c r="X180" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="181" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>937</v>
+      </c>
+      <c r="B181" t="s">
         <v>938</v>
       </c>
-      <c r="B181" t="s">
-        <v>939</v>
-      </c>
       <c r="D181" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E181" t="s">
         <v>34</v>
@@ -13601,13 +13670,13 @@
         <v>35</v>
       </c>
       <c r="J181" t="s">
+        <v>950</v>
+      </c>
+      <c r="L181" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="L181" s="1" t="s">
+      <c r="M181" t="s">
         <v>952</v>
-      </c>
-      <c r="M181" t="s">
-        <v>953</v>
       </c>
       <c r="R181" t="s">
         <v>31</v>
@@ -13625,39 +13694,39 @@
         <v>2</v>
       </c>
       <c r="X181" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="182" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>937</v>
+      </c>
+      <c r="B182" t="s">
         <v>938</v>
-      </c>
-      <c r="B182" t="s">
-        <v>939</v>
       </c>
       <c r="D182" t="s">
         <v>238</v>
       </c>
       <c r="E182" t="s">
+        <v>953</v>
+      </c>
+      <c r="F182" t="s">
         <v>954</v>
-      </c>
-      <c r="F182" t="s">
-        <v>955</v>
       </c>
       <c r="J182" t="s">
         <v>67</v>
       </c>
       <c r="L182" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="M182" t="s">
         <v>956</v>
       </c>
-      <c r="M182" t="s">
+      <c r="R182" s="4" t="s">
         <v>957</v>
       </c>
-      <c r="R182" s="4" t="s">
+      <c r="S182" t="s">
         <v>958</v>
-      </c>
-      <c r="S182" t="s">
-        <v>959</v>
       </c>
       <c r="T182">
         <v>17</v>
@@ -13669,18 +13738,18 @@
         <v>2</v>
       </c>
       <c r="X182" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="183" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>937</v>
+      </c>
+      <c r="B183" t="s">
         <v>938</v>
       </c>
-      <c r="B183" t="s">
-        <v>939</v>
-      </c>
       <c r="D183" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E183" t="s">
         <v>191</v>
@@ -13689,10 +13758,10 @@
         <v>192</v>
       </c>
       <c r="J183" t="s">
+        <v>960</v>
+      </c>
+      <c r="L183" s="1" t="s">
         <v>961</v>
-      </c>
-      <c r="L183" s="1" t="s">
-        <v>962</v>
       </c>
       <c r="R183" t="s">
         <v>31</v>
@@ -13710,30 +13779,30 @@
         <v>2</v>
       </c>
       <c r="X183" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="184" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>937</v>
+      </c>
+      <c r="B184" t="s">
         <v>938</v>
       </c>
-      <c r="B184" t="s">
-        <v>939</v>
-      </c>
       <c r="D184" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E184" t="s">
+        <v>962</v>
+      </c>
+      <c r="F184" t="s">
         <v>963</v>
       </c>
-      <c r="F184" t="s">
+      <c r="J184" t="s">
         <v>964</v>
       </c>
-      <c r="J184" t="s">
+      <c r="L184" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="L184" s="1" t="s">
-        <v>966</v>
       </c>
       <c r="R184" t="s">
         <v>31</v>
@@ -13751,39 +13820,39 @@
         <v>2</v>
       </c>
       <c r="X184" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="185" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>937</v>
+      </c>
+      <c r="B185" t="s">
         <v>938</v>
-      </c>
-      <c r="B185" t="s">
-        <v>939</v>
       </c>
       <c r="D185" t="s">
         <v>260</v>
       </c>
       <c r="E185" t="s">
+        <v>953</v>
+      </c>
+      <c r="F185" t="s">
         <v>954</v>
-      </c>
-      <c r="F185" t="s">
-        <v>955</v>
       </c>
       <c r="J185" t="s">
         <v>394</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="M185" t="s">
+        <v>956</v>
+      </c>
+      <c r="R185" s="4" t="s">
         <v>957</v>
       </c>
-      <c r="R185" s="4" t="s">
+      <c r="S185" t="s">
         <v>958</v>
-      </c>
-      <c r="S185" t="s">
-        <v>959</v>
       </c>
       <c r="T185">
         <v>17</v>
@@ -13795,15 +13864,15 @@
         <v>2</v>
       </c>
       <c r="X185" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="186" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>967</v>
+      </c>
+      <c r="B186" t="s">
         <v>968</v>
-      </c>
-      <c r="B186" t="s">
-        <v>969</v>
       </c>
       <c r="D186" t="s">
         <v>116</v>
@@ -13815,42 +13884,42 @@
         <v>192</v>
       </c>
       <c r="J186" t="s">
+        <v>969</v>
+      </c>
+      <c r="K186" t="s">
         <v>970</v>
       </c>
-      <c r="K186" t="s">
+      <c r="L186" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="L186" s="1" t="s">
-        <v>972</v>
-      </c>
       <c r="R186" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S186" t="s">
         <v>65</v>
       </c>
       <c r="T186" t="s">
+        <v>972</v>
+      </c>
+      <c r="U186" s="2" t="s">
         <v>973</v>
-      </c>
-      <c r="U186" s="2" t="s">
-        <v>974</v>
       </c>
       <c r="W186" s="2">
         <v>2</v>
       </c>
       <c r="X186" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="187" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>967</v>
+      </c>
+      <c r="B187" t="s">
         <v>968</v>
       </c>
-      <c r="B187" t="s">
-        <v>969</v>
-      </c>
       <c r="D187" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E187" t="s">
         <v>59</v>
@@ -13859,22 +13928,22 @@
         <v>316</v>
       </c>
       <c r="H187" t="s">
+        <v>975</v>
+      </c>
+      <c r="J187" t="s">
         <v>976</v>
       </c>
-      <c r="J187" t="s">
+      <c r="K187" t="s">
         <v>977</v>
       </c>
-      <c r="K187" t="s">
+      <c r="L187" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="L187" s="1" t="s">
+      <c r="M187" t="s">
         <v>979</v>
       </c>
-      <c r="M187" t="s">
-        <v>980</v>
-      </c>
       <c r="R187" t="s">
-        <v>755</v>
+        <v>89</v>
       </c>
       <c r="S187" t="s">
         <v>89</v>
@@ -13889,83 +13958,83 @@
         <v>2</v>
       </c>
       <c r="X187" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="188" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>967</v>
+      </c>
+      <c r="B188" t="s">
         <v>968</v>
       </c>
-      <c r="B188" t="s">
-        <v>969</v>
-      </c>
       <c r="D188" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E188" t="s">
         <v>59</v>
       </c>
       <c r="F188" t="s">
+        <v>980</v>
+      </c>
+      <c r="J188" t="s">
         <v>981</v>
       </c>
-      <c r="J188" t="s">
+      <c r="K188" t="s">
         <v>982</v>
       </c>
-      <c r="K188" t="s">
+      <c r="L188" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="L188" s="1" t="s">
-        <v>984</v>
-      </c>
       <c r="R188" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S188" t="s">
         <v>65</v>
       </c>
       <c r="T188" t="s">
+        <v>984</v>
+      </c>
+      <c r="U188" s="2" t="s">
         <v>985</v>
-      </c>
-      <c r="U188" s="2" t="s">
-        <v>986</v>
       </c>
       <c r="W188" s="2">
         <v>2</v>
       </c>
       <c r="X188" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="189" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>967</v>
+      </c>
+      <c r="B189" t="s">
         <v>968</v>
       </c>
-      <c r="B189" t="s">
-        <v>969</v>
-      </c>
       <c r="D189" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E189" t="s">
         <v>59</v>
       </c>
       <c r="F189" t="s">
+        <v>987</v>
+      </c>
+      <c r="H189" t="s">
         <v>988</v>
       </c>
-      <c r="H189" t="s">
+      <c r="J189" t="s">
         <v>989</v>
       </c>
-      <c r="J189" t="s">
+      <c r="K189" t="s">
         <v>990</v>
       </c>
-      <c r="K189" t="s">
+      <c r="L189" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="L189" s="1" t="s">
-        <v>992</v>
-      </c>
       <c r="R189" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S189" t="s">
         <v>65</v>
@@ -13980,103 +14049,103 @@
         <v>2</v>
       </c>
       <c r="X189" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="190" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>967</v>
+      </c>
+      <c r="B190" t="s">
         <v>968</v>
       </c>
-      <c r="B190" t="s">
-        <v>969</v>
-      </c>
       <c r="D190" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E190" t="s">
         <v>26</v>
       </c>
       <c r="F190" t="s">
+        <v>992</v>
+      </c>
+      <c r="J190" t="s">
         <v>993</v>
       </c>
-      <c r="J190" t="s">
+      <c r="K190" t="s">
         <v>994</v>
       </c>
-      <c r="K190" t="s">
+      <c r="L190" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="L190" s="1" t="s">
-        <v>996</v>
-      </c>
       <c r="R190" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S190" t="s">
         <v>65</v>
       </c>
       <c r="T190" t="s">
+        <v>996</v>
+      </c>
+      <c r="U190" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="U190" s="2" t="s">
-        <v>998</v>
       </c>
       <c r="W190" s="2">
         <v>2</v>
       </c>
       <c r="X190" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="191" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>967</v>
+      </c>
+      <c r="B191" t="s">
         <v>968</v>
-      </c>
-      <c r="B191" t="s">
-        <v>969</v>
       </c>
       <c r="D191" t="s">
         <v>78</v>
       </c>
       <c r="E191" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F191" t="s">
         <v>84</v>
       </c>
       <c r="J191" t="s">
+        <v>999</v>
+      </c>
+      <c r="K191" t="s">
         <v>1000</v>
       </c>
-      <c r="K191" t="s">
+      <c r="L191" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="L191" s="1" t="s">
-        <v>1002</v>
-      </c>
       <c r="R191" t="s">
-        <v>755</v>
+        <v>89</v>
       </c>
       <c r="S191" t="s">
         <v>89</v>
       </c>
       <c r="T191" t="s">
+        <v>1002</v>
+      </c>
+      <c r="U191" s="2" t="s">
         <v>1003</v>
-      </c>
-      <c r="U191" s="2" t="s">
-        <v>1004</v>
       </c>
       <c r="W191" s="2">
         <v>2</v>
       </c>
       <c r="X191" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="192" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>967</v>
+      </c>
+      <c r="B192" t="s">
         <v>968</v>
-      </c>
-      <c r="B192" t="s">
-        <v>969</v>
       </c>
       <c r="D192" t="s">
         <v>442</v>
@@ -14085,42 +14154,42 @@
         <v>59</v>
       </c>
       <c r="F192" t="s">
+        <v>1004</v>
+      </c>
+      <c r="J192" t="s">
+        <v>874</v>
+      </c>
+      <c r="K192" t="s">
+        <v>875</v>
+      </c>
+      <c r="L192" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="J192" t="s">
-        <v>875</v>
-      </c>
-      <c r="K192" t="s">
-        <v>876</v>
-      </c>
-      <c r="L192" s="1" t="s">
-        <v>1006</v>
-      </c>
       <c r="R192" t="s">
-        <v>755</v>
+        <v>89</v>
       </c>
       <c r="S192" t="s">
         <v>89</v>
       </c>
       <c r="T192" t="s">
+        <v>1006</v>
+      </c>
+      <c r="U192" s="2" t="s">
         <v>1007</v>
-      </c>
-      <c r="U192" s="2" t="s">
-        <v>1008</v>
       </c>
       <c r="W192" s="2">
         <v>2</v>
       </c>
       <c r="X192" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="193" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>967</v>
+      </c>
+      <c r="B193" t="s">
         <v>968</v>
-      </c>
-      <c r="B193" t="s">
-        <v>969</v>
       </c>
       <c r="D193" t="s">
         <v>442</v>
@@ -14129,22 +14198,22 @@
         <v>59</v>
       </c>
       <c r="F193" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H193" t="s">
+        <v>1008</v>
+      </c>
+      <c r="J193" t="s">
         <v>1009</v>
       </c>
-      <c r="J193" t="s">
+      <c r="K193" t="s">
         <v>1010</v>
       </c>
-      <c r="K193" t="s">
+      <c r="L193" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="L193" s="1" t="s">
-        <v>1012</v>
-      </c>
       <c r="R193" t="s">
-        <v>755</v>
+        <v>89</v>
       </c>
       <c r="S193" t="s">
         <v>89</v>
@@ -14153,45 +14222,45 @@
         <v>480</v>
       </c>
       <c r="U193" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="W193" s="2">
         <v>2</v>
       </c>
       <c r="X193" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="194" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B194" t="s">
         <v>1014</v>
       </c>
-      <c r="B194" t="s">
+      <c r="D194" t="s">
         <v>1015</v>
-      </c>
-      <c r="D194" t="s">
-        <v>1016</v>
       </c>
       <c r="E194" t="s">
         <v>59</v>
       </c>
       <c r="F194" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H194" t="s">
         <v>1017</v>
       </c>
-      <c r="H194" t="s">
+      <c r="J194" t="s">
         <v>1018</v>
       </c>
-      <c r="J194" t="s">
+      <c r="K194" t="s">
         <v>1019</v>
       </c>
-      <c r="K194" t="s">
+      <c r="L194" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="1" t="s">
+      <c r="M194" t="s">
         <v>1021</v>
-      </c>
-      <c r="M194" t="s">
-        <v>1022</v>
       </c>
       <c r="R194" t="s">
         <v>89</v>
@@ -14200,27 +14269,27 @@
         <v>89</v>
       </c>
       <c r="T194" t="s">
+        <v>1022</v>
+      </c>
+      <c r="U194" s="2" t="s">
         <v>1023</v>
-      </c>
-      <c r="U194" s="2" t="s">
-        <v>1024</v>
       </c>
       <c r="W194" s="2">
         <v>2</v>
       </c>
       <c r="X194" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="195" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B195" t="s">
         <v>1014</v>
       </c>
-      <c r="B195" t="s">
-        <v>1015</v>
-      </c>
       <c r="D195" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E195" t="s">
         <v>191</v>
@@ -14229,13 +14298,13 @@
         <v>192</v>
       </c>
       <c r="J195" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K195" t="s">
         <v>1025</v>
       </c>
-      <c r="K195" t="s">
+      <c r="L195" s="1" t="s">
         <v>1026</v>
-      </c>
-      <c r="L195" s="1" t="s">
-        <v>1027</v>
       </c>
       <c r="R195" t="s">
         <v>31</v>
@@ -14247,54 +14316,54 @@
         <v>290</v>
       </c>
       <c r="U195" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="W195" s="2">
         <v>2</v>
       </c>
       <c r="X195" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="196" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B196" t="s">
         <v>1014</v>
       </c>
-      <c r="B196" t="s">
-        <v>1015</v>
-      </c>
       <c r="D196" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E196" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F196" t="s">
         <v>1029</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="G196" s="1" t="s">
+      <c r="H196" t="s">
         <v>1031</v>
       </c>
-      <c r="H196" t="s">
+      <c r="I196" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="I196" s="1" t="s">
+      <c r="J196" t="s">
         <v>1033</v>
       </c>
-      <c r="J196" t="s">
+      <c r="K196" t="s">
         <v>1034</v>
       </c>
-      <c r="K196" t="s">
+      <c r="L196" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="L196" s="1" t="s">
+      <c r="M196" t="s">
         <v>1036</v>
       </c>
-      <c r="M196" t="s">
+      <c r="N196" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="N196" s="1" t="s">
-        <v>1038</v>
       </c>
       <c r="R196" t="s">
         <v>89</v>
@@ -14303,51 +14372,51 @@
         <v>89</v>
       </c>
       <c r="T196" t="s">
+        <v>1038</v>
+      </c>
+      <c r="U196" s="2" t="s">
         <v>1039</v>
-      </c>
-      <c r="U196" s="2" t="s">
-        <v>1040</v>
       </c>
       <c r="W196" s="2">
         <v>2</v>
       </c>
       <c r="X196" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="197" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B197" t="s">
         <v>1014</v>
       </c>
-      <c r="B197" t="s">
-        <v>1015</v>
-      </c>
       <c r="D197" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E197" t="s">
         <v>1041</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>1042</v>
       </c>
-      <c r="F197" t="s">
+      <c r="H197" t="s">
         <v>1043</v>
       </c>
-      <c r="H197" t="s">
+      <c r="I197" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="I197" s="1" t="s">
+      <c r="J197" t="s">
         <v>1045</v>
       </c>
-      <c r="J197" t="s">
+      <c r="K197" t="s">
         <v>1046</v>
       </c>
-      <c r="K197" t="s">
+      <c r="L197" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="L197" s="1" t="s">
+      <c r="M197" t="s">
         <v>1048</v>
-      </c>
-      <c r="M197" t="s">
-        <v>1049</v>
       </c>
       <c r="R197" t="s">
         <v>89</v>
@@ -14356,7 +14425,7 @@
         <v>89</v>
       </c>
       <c r="T197" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="U197" s="2" t="s">
         <v>290</v>
@@ -14365,18 +14434,18 @@
         <v>2</v>
       </c>
       <c r="X197" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="198" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B198" t="s">
         <v>1014</v>
       </c>
-      <c r="B198" t="s">
-        <v>1015</v>
-      </c>
       <c r="D198" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E198" t="s">
         <v>284</v>
@@ -14385,13 +14454,13 @@
         <v>285</v>
       </c>
       <c r="J198" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K198" t="s">
         <v>1051</v>
       </c>
-      <c r="K198" t="s">
+      <c r="L198" s="1" t="s">
         <v>1052</v>
-      </c>
-      <c r="L198" s="1" t="s">
-        <v>1053</v>
       </c>
       <c r="R198" t="s">
         <v>410</v>
@@ -14400,27 +14469,27 @@
         <v>65</v>
       </c>
       <c r="T198" t="s">
+        <v>1053</v>
+      </c>
+      <c r="U198" s="2" t="s">
         <v>1054</v>
-      </c>
-      <c r="U198" s="2" t="s">
-        <v>1055</v>
       </c>
       <c r="W198" s="2">
         <v>2</v>
       </c>
       <c r="X198" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="199" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B199" t="s">
         <v>1014</v>
       </c>
-      <c r="B199" t="s">
-        <v>1015</v>
-      </c>
       <c r="D199" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E199" t="s">
         <v>95</v>
@@ -14429,16 +14498,16 @@
         <v>96</v>
       </c>
       <c r="J199" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K199" t="s">
         <v>1057</v>
       </c>
-      <c r="K199" t="s">
+      <c r="L199" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="L199" s="1" t="s">
+      <c r="M199" t="s">
         <v>1059</v>
-      </c>
-      <c r="M199" t="s">
-        <v>1060</v>
       </c>
       <c r="R199" t="s">
         <v>31</v>
@@ -14447,7 +14516,7 @@
         <v>65</v>
       </c>
       <c r="T199" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="U199" s="2" t="s">
         <v>275</v>
@@ -14456,33 +14525,33 @@
         <v>2</v>
       </c>
       <c r="X199" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="200" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B200" t="s">
         <v>1014</v>
       </c>
-      <c r="B200" t="s">
-        <v>1015</v>
-      </c>
       <c r="D200" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E200" t="s">
         <v>59</v>
       </c>
       <c r="F200" t="s">
+        <v>1062</v>
+      </c>
+      <c r="J200" t="s">
         <v>1063</v>
       </c>
-      <c r="J200" t="s">
+      <c r="K200" t="s">
         <v>1064</v>
       </c>
-      <c r="K200" t="s">
+      <c r="L200" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="L200" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="R200" t="s">
         <v>31</v>
@@ -14494,39 +14563,39 @@
         <v>727</v>
       </c>
       <c r="U200" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="W200" s="2">
         <v>2</v>
       </c>
       <c r="X200" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="201" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B201" t="s">
         <v>1014</v>
-      </c>
-      <c r="B201" t="s">
-        <v>1015</v>
       </c>
       <c r="D201" t="s">
         <v>660</v>
       </c>
       <c r="E201" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F201" t="s">
         <v>1042</v>
       </c>
-      <c r="F201" t="s">
-        <v>1043</v>
-      </c>
       <c r="J201" t="s">
+        <v>1067</v>
+      </c>
+      <c r="K201" t="s">
         <v>1068</v>
       </c>
-      <c r="K201" t="s">
+      <c r="L201" s="1" t="s">
         <v>1069</v>
-      </c>
-      <c r="L201" s="1" t="s">
-        <v>1070</v>
       </c>
       <c r="R201" t="s">
         <v>89</v>
@@ -14535,7 +14604,7 @@
         <v>89</v>
       </c>
       <c r="T201" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="U201" s="2" t="s">
         <v>274</v>
@@ -14544,18 +14613,18 @@
         <v>2</v>
       </c>
       <c r="X201" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="202" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B202" t="s">
         <v>1072</v>
       </c>
-      <c r="B202" t="s">
+      <c r="D202" t="s">
         <v>1073</v>
-      </c>
-      <c r="D202" t="s">
-        <v>1074</v>
       </c>
       <c r="E202" t="s">
         <v>59</v>
@@ -14570,7 +14639,7 @@
         <v>395</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="R202" t="s">
         <v>31</v>
@@ -14588,18 +14657,18 @@
         <v>2</v>
       </c>
       <c r="X202" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="203" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B203" t="s">
         <v>1072</v>
       </c>
-      <c r="B203" t="s">
-        <v>1073</v>
-      </c>
       <c r="D203" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E203" t="s">
         <v>59</v>
@@ -14608,13 +14677,13 @@
         <v>60</v>
       </c>
       <c r="J203" t="s">
+        <v>1076</v>
+      </c>
+      <c r="K203" t="s">
         <v>1077</v>
       </c>
-      <c r="K203" t="s">
+      <c r="L203" s="1" t="s">
         <v>1078</v>
-      </c>
-      <c r="L203" s="1" t="s">
-        <v>1079</v>
       </c>
       <c r="R203" t="s">
         <v>31</v>
@@ -14632,33 +14701,33 @@
         <v>2</v>
       </c>
       <c r="X203" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="204" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B204" t="s">
         <v>1072</v>
-      </c>
-      <c r="B204" t="s">
-        <v>1073</v>
       </c>
       <c r="D204" t="s">
         <v>629</v>
       </c>
       <c r="E204" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F204" t="s">
         <v>1080</v>
       </c>
-      <c r="F204" t="s">
+      <c r="J204" t="s">
         <v>1081</v>
       </c>
-      <c r="J204" t="s">
+      <c r="K204" t="s">
         <v>1082</v>
       </c>
-      <c r="K204" t="s">
+      <c r="L204" s="1" t="s">
         <v>1083</v>
-      </c>
-      <c r="L204" s="1" t="s">
-        <v>1084</v>
       </c>
       <c r="R204" t="s">
         <v>31</v>
@@ -14676,18 +14745,18 @@
         <v>2</v>
       </c>
       <c r="X204" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="205" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B205" t="s">
         <v>1072</v>
       </c>
-      <c r="B205" t="s">
-        <v>1073</v>
-      </c>
       <c r="D205" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E205" t="s">
         <v>191</v>
@@ -14696,13 +14765,13 @@
         <v>192</v>
       </c>
       <c r="J205" t="s">
+        <v>1085</v>
+      </c>
+      <c r="K205" t="s">
         <v>1086</v>
       </c>
-      <c r="K205" t="s">
+      <c r="L205" s="1" t="s">
         <v>1087</v>
-      </c>
-      <c r="L205" s="1" t="s">
-        <v>1088</v>
       </c>
       <c r="R205" t="s">
         <v>410</v>
@@ -14720,18 +14789,18 @@
         <v>2</v>
       </c>
       <c r="X205" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Y205" t="s">
         <v>1072</v>
-      </c>
-      <c r="Y205" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="206" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B206" t="s">
         <v>1072</v>
-      </c>
-      <c r="B206" t="s">
-        <v>1073</v>
       </c>
       <c r="D206" t="s">
         <v>421</v>
@@ -14740,25 +14809,25 @@
         <v>59</v>
       </c>
       <c r="F206" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H206" t="s">
         <v>1089</v>
       </c>
-      <c r="H206" t="s">
+      <c r="J206" t="s">
         <v>1090</v>
       </c>
-      <c r="J206" t="s">
+      <c r="K206" t="s">
         <v>1091</v>
       </c>
-      <c r="K206" t="s">
+      <c r="L206" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="L206" s="1" t="s">
+      <c r="M206" t="s">
         <v>1093</v>
       </c>
-      <c r="M206" t="s">
+      <c r="N206" s="1" t="s">
         <v>1094</v>
-      </c>
-      <c r="N206" s="1" t="s">
-        <v>1095</v>
       </c>
       <c r="R206" t="s">
         <v>31</v>
@@ -14776,39 +14845,39 @@
         <v>2</v>
       </c>
       <c r="X206" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Y206" t="s">
         <v>1072</v>
-      </c>
-      <c r="Y206" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="207" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B207" t="s">
         <v>1072</v>
       </c>
-      <c r="B207" t="s">
-        <v>1073</v>
-      </c>
       <c r="D207" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E207" t="s">
         <v>59</v>
       </c>
       <c r="F207" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H207" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J207" t="s">
         <v>1096</v>
       </c>
-      <c r="J207" t="s">
+      <c r="K207" t="s">
         <v>1097</v>
       </c>
-      <c r="K207" t="s">
+      <c r="L207" s="1" t="s">
         <v>1098</v>
-      </c>
-      <c r="L207" s="1" t="s">
-        <v>1099</v>
       </c>
       <c r="R207" t="s">
         <v>31</v>
@@ -14826,45 +14895,45 @@
         <v>2</v>
       </c>
       <c r="X207" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Y207" t="s">
         <v>1072</v>
-      </c>
-      <c r="Y207" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="208" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B208" t="s">
         <v>1072</v>
       </c>
-      <c r="B208" t="s">
-        <v>1073</v>
-      </c>
       <c r="D208" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E208" t="s">
         <v>1100</v>
       </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
         <v>1101</v>
       </c>
-      <c r="F208" t="s">
+      <c r="H208" t="s">
         <v>1102</v>
       </c>
-      <c r="H208" t="s">
+      <c r="J208" t="s">
         <v>1103</v>
       </c>
-      <c r="J208" t="s">
+      <c r="K208" t="s">
         <v>1104</v>
       </c>
-      <c r="K208" t="s">
+      <c r="L208" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="L208" s="1" t="s">
+      <c r="M208" t="s">
         <v>1106</v>
       </c>
-      <c r="M208" t="s">
+      <c r="N208" s="1" t="s">
         <v>1107</v>
-      </c>
-      <c r="N208" s="1" t="s">
-        <v>1108</v>
       </c>
       <c r="R208" t="s">
         <v>89</v>
@@ -14882,18 +14951,18 @@
         <v>2</v>
       </c>
       <c r="X208" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Y208" t="s">
         <v>1072</v>
-      </c>
-      <c r="Y208" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="209" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B209" t="s">
         <v>1072</v>
-      </c>
-      <c r="B209" t="s">
-        <v>1073</v>
       </c>
       <c r="D209" t="s">
         <v>469</v>
@@ -14905,13 +14974,13 @@
         <v>96</v>
       </c>
       <c r="J209" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K209" t="s">
         <v>1109</v>
       </c>
-      <c r="K209" t="s">
+      <c r="L209" s="1" t="s">
         <v>1110</v>
-      </c>
-      <c r="L209" s="1" t="s">
-        <v>1111</v>
       </c>
       <c r="R209" t="s">
         <v>31</v>
@@ -14929,18 +14998,18 @@
         <v>2</v>
       </c>
       <c r="X209" t="s">
+        <v>1071</v>
+      </c>
+      <c r="Y209" t="s">
         <v>1072</v>
-      </c>
-      <c r="Y209" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="210" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B210" t="s">
         <v>1112</v>
-      </c>
-      <c r="B210" t="s">
-        <v>1113</v>
       </c>
       <c r="D210" t="s">
         <v>442</v>
@@ -14952,13 +15021,13 @@
         <v>437</v>
       </c>
       <c r="J210" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K210" t="s">
         <v>1114</v>
       </c>
-      <c r="K210" t="s">
+      <c r="L210" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="L210" s="1" t="s">
-        <v>1116</v>
       </c>
       <c r="R210" t="s">
         <v>31</v>
@@ -14976,36 +15045,36 @@
         <v>2</v>
       </c>
       <c r="X210" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="Y210" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="211" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B211" t="s">
         <v>1112</v>
       </c>
-      <c r="B211" t="s">
-        <v>1113</v>
-      </c>
       <c r="D211" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E211" t="s">
         <v>636</v>
       </c>
       <c r="F211" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J211" t="s">
         <v>1118</v>
       </c>
-      <c r="J211" t="s">
+      <c r="K211" t="s">
         <v>1119</v>
       </c>
-      <c r="K211" t="s">
+      <c r="L211" s="1" t="s">
         <v>1120</v>
-      </c>
-      <c r="L211" s="1" t="s">
-        <v>1121</v>
       </c>
       <c r="R211" t="s">
         <v>257</v>
@@ -15023,42 +15092,42 @@
         <v>2</v>
       </c>
       <c r="X211" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="Y211" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="212" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B212" t="s">
         <v>1112</v>
       </c>
-      <c r="B212" t="s">
-        <v>1113</v>
-      </c>
       <c r="D212" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E212" t="s">
         <v>636</v>
       </c>
       <c r="F212" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J212" t="s">
+        <v>1122</v>
+      </c>
+      <c r="K212" t="s">
         <v>1123</v>
       </c>
-      <c r="K212" t="s">
+      <c r="L212" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="L212" s="1" t="s">
+      <c r="R212" t="s">
+        <v>31</v>
+      </c>
+      <c r="S212" t="s">
         <v>1125</v>
-      </c>
-      <c r="R212" t="s">
-        <v>31</v>
-      </c>
-      <c r="S212" t="s">
-        <v>1126</v>
       </c>
       <c r="T212">
         <v>87</v>
@@ -15070,36 +15139,36 @@
         <v>2</v>
       </c>
       <c r="X212" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="Y212" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="213" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B213" t="s">
         <v>1112</v>
       </c>
-      <c r="B213" t="s">
-        <v>1113</v>
-      </c>
       <c r="D213" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E213" t="s">
         <v>1127</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
         <v>1128</v>
-      </c>
-      <c r="F213" t="s">
-        <v>1129</v>
       </c>
       <c r="J213" t="s">
         <v>405</v>
       </c>
       <c r="K213" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L213" s="1" t="s">
         <v>1130</v>
-      </c>
-      <c r="L213" s="1" t="s">
-        <v>1131</v>
       </c>
       <c r="R213" t="s">
         <v>31</v>
@@ -15117,33 +15186,33 @@
         <v>2</v>
       </c>
       <c r="X213" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="214" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B214" t="s">
         <v>1112</v>
       </c>
-      <c r="B214" t="s">
-        <v>1113</v>
-      </c>
       <c r="D214" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="E214" t="s">
         <v>636</v>
       </c>
       <c r="F214" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J214" t="s">
+        <v>1132</v>
+      </c>
+      <c r="K214" t="s">
         <v>1133</v>
       </c>
-      <c r="K214" t="s">
+      <c r="L214" s="1" t="s">
         <v>1134</v>
-      </c>
-      <c r="L214" s="1" t="s">
-        <v>1135</v>
       </c>
       <c r="R214" t="s">
         <v>410</v>
@@ -15161,30 +15230,30 @@
         <v>2</v>
       </c>
       <c r="X214" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="215" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B215" t="s">
         <v>1112</v>
-      </c>
-      <c r="B215" t="s">
-        <v>1113</v>
       </c>
       <c r="D215" t="s">
         <v>33</v>
       </c>
       <c r="E215" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F215" t="s">
         <v>1136</v>
       </c>
-      <c r="F215" t="s">
+      <c r="J215" t="s">
         <v>1137</v>
       </c>
-      <c r="J215" t="s">
+      <c r="L215" s="1" t="s">
         <v>1138</v>
-      </c>
-      <c r="L215" s="1" t="s">
-        <v>1139</v>
       </c>
       <c r="R215" t="s">
         <v>31</v>
@@ -15202,18 +15271,18 @@
         <v>2</v>
       </c>
       <c r="X215" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="216" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B216" t="s">
         <v>1112</v>
       </c>
-      <c r="B216" t="s">
-        <v>1113</v>
-      </c>
       <c r="D216" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E216" t="s">
         <v>636</v>
@@ -15222,10 +15291,10 @@
         <v>637</v>
       </c>
       <c r="J216" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L216" s="1" t="s">
         <v>1141</v>
-      </c>
-      <c r="L216" s="1" t="s">
-        <v>1142</v>
       </c>
       <c r="R216" t="s">
         <v>326</v>
@@ -15243,15 +15312,15 @@
         <v>2</v>
       </c>
       <c r="X216" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="217" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B217" t="s">
         <v>1112</v>
-      </c>
-      <c r="B217" t="s">
-        <v>1113</v>
       </c>
       <c r="D217" t="s">
         <v>686</v>
@@ -15263,10 +15332,10 @@
         <v>576</v>
       </c>
       <c r="J217" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L217" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="L217" s="1" t="s">
-        <v>1144</v>
       </c>
       <c r="R217" t="s">
         <v>31</v>
@@ -15284,33 +15353,33 @@
         <v>2</v>
       </c>
       <c r="X217" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="218" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B218" t="s">
         <v>1145</v>
-      </c>
-      <c r="B218" t="s">
-        <v>1146</v>
       </c>
       <c r="D218" t="s">
         <v>78</v>
       </c>
       <c r="E218" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F218" t="s">
         <v>84</v>
       </c>
       <c r="J218" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K218" t="s">
         <v>1147</v>
       </c>
-      <c r="K218" t="s">
+      <c r="L218" s="1" t="s">
         <v>1148</v>
-      </c>
-      <c r="L218" s="1" t="s">
-        <v>1149</v>
       </c>
       <c r="R218" t="s">
         <v>89</v>
@@ -15328,18 +15397,18 @@
         <v>2</v>
       </c>
       <c r="X218" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="219" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B219" t="s">
         <v>1145</v>
       </c>
-      <c r="B219" t="s">
-        <v>1146</v>
-      </c>
       <c r="D219" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="E219" t="s">
         <v>59</v>
@@ -15348,13 +15417,13 @@
         <v>60</v>
       </c>
       <c r="J219" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K219" t="s">
         <v>1151</v>
       </c>
-      <c r="K219" t="s">
+      <c r="L219" s="1" t="s">
         <v>1152</v>
-      </c>
-      <c r="L219" s="1" t="s">
-        <v>1153</v>
       </c>
       <c r="R219" t="s">
         <v>31</v>
@@ -15372,33 +15441,33 @@
         <v>2</v>
       </c>
       <c r="X219" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="220" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B220" t="s">
         <v>1145</v>
       </c>
-      <c r="B220" t="s">
-        <v>1146</v>
-      </c>
       <c r="D220" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E220" t="s">
         <v>59</v>
       </c>
       <c r="F220" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="J220" t="s">
         <v>483</v>
       </c>
       <c r="K220" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L220" s="1" t="s">
         <v>1156</v>
-      </c>
-      <c r="L220" s="1" t="s">
-        <v>1157</v>
       </c>
       <c r="R220" t="s">
         <v>31</v>
@@ -15416,42 +15485,42 @@
         <v>2</v>
       </c>
       <c r="X220" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="221" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B221" t="s">
         <v>1145</v>
       </c>
-      <c r="B221" t="s">
-        <v>1146</v>
-      </c>
       <c r="D221" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="E221" t="s">
         <v>284</v>
       </c>
       <c r="F221" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H221" t="s">
         <v>1159</v>
       </c>
-      <c r="H221" t="s">
+      <c r="J221" t="s">
         <v>1160</v>
       </c>
-      <c r="J221" t="s">
+      <c r="K221" t="s">
         <v>1161</v>
       </c>
-      <c r="K221" t="s">
+      <c r="L221" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="L221" s="1" t="s">
+      <c r="M221" t="s">
+        <v>1160</v>
+      </c>
+      <c r="N221" s="1" t="s">
         <v>1163</v>
-      </c>
-      <c r="M221" t="s">
-        <v>1161</v>
-      </c>
-      <c r="N221" s="1" t="s">
-        <v>1164</v>
       </c>
       <c r="R221" t="s">
         <v>89</v>
@@ -15469,18 +15538,18 @@
         <v>2</v>
       </c>
       <c r="X221" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="222" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B222" t="s">
         <v>1145</v>
       </c>
-      <c r="B222" t="s">
-        <v>1146</v>
-      </c>
       <c r="D222" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E222" t="s">
         <v>169</v>
@@ -15489,19 +15558,19 @@
         <v>170</v>
       </c>
       <c r="J222" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="K222" t="s">
         <v>354</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="R222" t="s">
         <v>31</v>
       </c>
       <c r="S222" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="T222">
         <v>101</v>
@@ -15513,18 +15582,18 @@
         <v>2</v>
       </c>
       <c r="X222" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="223" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B223" t="s">
         <v>1145</v>
       </c>
-      <c r="B223" t="s">
-        <v>1146</v>
-      </c>
       <c r="D223" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E223" t="s">
         <v>191</v>
@@ -15533,13 +15602,13 @@
         <v>192</v>
       </c>
       <c r="J223" t="s">
+        <v>1168</v>
+      </c>
+      <c r="K223" t="s">
         <v>1169</v>
       </c>
-      <c r="K223" t="s">
+      <c r="L223" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="L223" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="R223" t="s">
         <v>31</v>
@@ -15557,18 +15626,18 @@
         <v>2</v>
       </c>
       <c r="X223" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="224" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B224" t="s">
         <v>1145</v>
       </c>
-      <c r="B224" t="s">
-        <v>1146</v>
-      </c>
       <c r="D224" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="E224" t="s">
         <v>176</v>
@@ -15583,7 +15652,7 @@
         <v>444</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="R224" t="s">
         <v>31</v>
@@ -15601,15 +15670,15 @@
         <v>2</v>
       </c>
       <c r="X224" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="225" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B225" t="s">
         <v>1145</v>
-      </c>
-      <c r="B225" t="s">
-        <v>1146</v>
       </c>
       <c r="D225" t="s">
         <v>488</v>
@@ -15618,19 +15687,19 @@
         <v>59</v>
       </c>
       <c r="F225" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H225" t="s">
         <v>1174</v>
       </c>
-      <c r="H225" t="s">
+      <c r="J225" t="s">
         <v>1175</v>
       </c>
-      <c r="J225" t="s">
+      <c r="K225" t="s">
         <v>1176</v>
       </c>
-      <c r="K225" t="s">
+      <c r="L225" s="1" t="s">
         <v>1177</v>
-      </c>
-      <c r="L225" s="1" t="s">
-        <v>1178</v>
       </c>
       <c r="R225" t="s">
         <v>89</v>
@@ -15648,48 +15717,48 @@
         <v>2</v>
       </c>
       <c r="X225" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="226" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B226" t="s">
         <v>1179</v>
-      </c>
-      <c r="B226" t="s">
-        <v>1702</v>
       </c>
       <c r="C226" t="s">
         <v>1180</v>
       </c>
       <c r="D226" t="s">
-        <v>1181</v>
+        <v>1406</v>
       </c>
       <c r="E226" t="s">
         <v>462</v>
       </c>
       <c r="F226" t="s">
+        <v>1181</v>
+      </c>
+      <c r="J226" t="s">
         <v>1182</v>
       </c>
-      <c r="J226" t="s">
+      <c r="K226" t="s">
         <v>1183</v>
       </c>
-      <c r="K226" t="s">
+      <c r="L226" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="L226" s="1" t="s">
+      <c r="R226" t="s">
+        <v>31</v>
+      </c>
+      <c r="S226" t="s">
         <v>1185</v>
       </c>
-      <c r="R226" t="s">
+      <c r="T226" t="s">
         <v>1186</v>
       </c>
-      <c r="S226" t="s">
+      <c r="U226" s="2" t="s">
         <v>1187</v>
-      </c>
-      <c r="T226" t="s">
-        <v>1188</v>
-      </c>
-      <c r="U226" s="2" t="s">
-        <v>1189</v>
       </c>
       <c r="W226" s="2">
         <v>2</v>
@@ -15700,34 +15769,34 @@
     </row>
     <row r="227" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B227" t="s">
         <v>1179</v>
-      </c>
-      <c r="B227" t="s">
-        <v>1702</v>
       </c>
       <c r="C227" t="s">
         <v>1180</v>
       </c>
       <c r="D227" t="s">
-        <v>1190</v>
+        <v>371</v>
       </c>
       <c r="E227" t="s">
         <v>462</v>
       </c>
       <c r="F227" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="H227" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="J227" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="K227" t="s">
         <v>165</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="R227" t="s">
         <v>89</v>
@@ -15744,16 +15813,16 @@
     </row>
     <row r="228" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B228" t="s">
         <v>1179</v>
-      </c>
-      <c r="B228" t="s">
-        <v>1702</v>
       </c>
       <c r="C228" t="s">
         <v>1180</v>
       </c>
       <c r="D228" t="s">
-        <v>1195</v>
+        <v>404</v>
       </c>
       <c r="E228" t="s">
         <v>493</v>
@@ -15762,25 +15831,25 @@
         <v>494</v>
       </c>
       <c r="J228" t="s">
+        <v>1192</v>
+      </c>
+      <c r="K228" t="s">
+        <v>1193</v>
+      </c>
+      <c r="L228" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="R228" t="s">
+        <v>31</v>
+      </c>
+      <c r="S228" t="s">
+        <v>1195</v>
+      </c>
+      <c r="T228" t="s">
         <v>1196</v>
       </c>
-      <c r="K228" t="s">
+      <c r="U228" s="2" t="s">
         <v>1197</v>
-      </c>
-      <c r="L228" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="R228" t="s">
-        <v>1186</v>
-      </c>
-      <c r="S228" t="s">
-        <v>1199</v>
-      </c>
-      <c r="T228" t="s">
-        <v>1200</v>
-      </c>
-      <c r="U228" s="2" t="s">
-        <v>1201</v>
       </c>
       <c r="W228" s="2">
         <v>2</v>
@@ -15791,34 +15860,34 @@
     </row>
     <row r="229" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B229" t="s">
         <v>1179</v>
-      </c>
-      <c r="B229" t="s">
-        <v>1702</v>
       </c>
       <c r="C229" t="s">
         <v>1180</v>
       </c>
       <c r="D229" t="s">
-        <v>1195</v>
+        <v>404</v>
       </c>
       <c r="E229" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="F229" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="J229" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K229" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="R229" t="s">
-        <v>1186</v>
+        <v>31</v>
       </c>
       <c r="S229" t="s">
         <v>523</v>
@@ -15832,37 +15901,37 @@
     </row>
     <row r="230" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B230" t="s">
         <v>1179</v>
-      </c>
-      <c r="B230" t="s">
-        <v>1702</v>
       </c>
       <c r="C230" t="s">
         <v>1180</v>
       </c>
       <c r="D230" t="s">
-        <v>1206</v>
+        <v>1692</v>
       </c>
       <c r="E230" t="s">
         <v>462</v>
       </c>
       <c r="F230" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H230" t="s">
+        <v>1203</v>
+      </c>
+      <c r="J230" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K230" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L230" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N230" s="1" t="s">
         <v>1207</v>
-      </c>
-      <c r="H230" t="s">
-        <v>1208</v>
-      </c>
-      <c r="J230" t="s">
-        <v>1209</v>
-      </c>
-      <c r="K230" t="s">
-        <v>1210</v>
-      </c>
-      <c r="L230" s="1" t="s">
-        <v>1211</v>
-      </c>
-      <c r="N230" s="1" t="s">
-        <v>1212</v>
       </c>
       <c r="R230" t="s">
         <v>89</v>
@@ -15879,16 +15948,16 @@
     </row>
     <row r="231" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B231" t="s">
         <v>1179</v>
-      </c>
-      <c r="B231" t="s">
-        <v>1702</v>
       </c>
       <c r="C231" t="s">
         <v>1180</v>
       </c>
       <c r="D231" t="s">
-        <v>1213</v>
+        <v>1693</v>
       </c>
       <c r="E231" t="s">
         <v>95</v>
@@ -15897,25 +15966,25 @@
         <v>96</v>
       </c>
       <c r="J231" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="K231" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="R231" t="s">
-        <v>1186</v>
+        <v>31</v>
       </c>
       <c r="S231" t="s">
         <v>523</v>
       </c>
       <c r="T231" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="U231" s="2" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="W231" s="2">
         <v>2</v>
@@ -15926,43 +15995,43 @@
     </row>
     <row r="232" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B232" t="s">
         <v>1179</v>
-      </c>
-      <c r="B232" t="s">
-        <v>1702</v>
       </c>
       <c r="C232" t="s">
         <v>1180</v>
       </c>
       <c r="D232" t="s">
-        <v>1219</v>
+        <v>1694</v>
       </c>
       <c r="E232" t="s">
-        <v>1220</v>
+        <v>1213</v>
       </c>
       <c r="F232" t="s">
-        <v>1221</v>
+        <v>1214</v>
       </c>
       <c r="J232" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="K232" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
       <c r="R232" t="s">
-        <v>1186</v>
+        <v>31</v>
       </c>
       <c r="S232" t="s">
         <v>523</v>
       </c>
       <c r="T232" t="s">
-        <v>1225</v>
+        <v>1218</v>
       </c>
       <c r="U232" s="2" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
       <c r="W232" s="2">
         <v>2</v>
@@ -15973,16 +16042,16 @@
     </row>
     <row r="233" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B233" t="s">
         <v>1179</v>
-      </c>
-      <c r="B233" t="s">
-        <v>1702</v>
       </c>
       <c r="C233" t="s">
         <v>1180</v>
       </c>
       <c r="D233" t="s">
-        <v>1227</v>
+        <v>1377</v>
       </c>
       <c r="E233" t="s">
         <v>191</v>
@@ -15991,25 +16060,25 @@
         <v>192</v>
       </c>
       <c r="J233" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="K233" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="R233" t="s">
-        <v>1186</v>
+        <v>31</v>
       </c>
       <c r="S233" t="s">
         <v>523</v>
       </c>
       <c r="T233" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
       <c r="U233" s="2" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
       <c r="W233" s="2">
         <v>2</v>
@@ -16020,13 +16089,13 @@
     </row>
     <row r="234" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="B234" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="D234" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="E234" t="s">
         <v>197</v>
@@ -16035,16 +16104,16 @@
         <v>270</v>
       </c>
       <c r="J234" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="K234" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
       <c r="R234" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S234" t="s">
         <v>523</v>
@@ -16059,39 +16128,39 @@
         <v>2</v>
       </c>
       <c r="X234" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="235" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="B235" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="D235" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
       <c r="E235" t="s">
         <v>284</v>
       </c>
       <c r="F235" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="H235" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="J235" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
       <c r="K235" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
       <c r="R235" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S235" t="s">
         <v>523</v>
@@ -16106,36 +16175,36 @@
         <v>2</v>
       </c>
       <c r="X235" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="236" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="B236" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="D236" t="s">
         <v>124</v>
       </c>
       <c r="E236" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
       <c r="F236" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="J236" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K236" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="R236" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S236" t="s">
         <v>65</v>
@@ -16150,15 +16219,15 @@
         <v>2</v>
       </c>
       <c r="X236" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="237" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="B237" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="D237" t="s">
         <v>131</v>
@@ -16170,16 +16239,16 @@
         <v>60</v>
       </c>
       <c r="J237" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
       <c r="K237" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
       <c r="R237" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S237" t="s">
         <v>523</v>
@@ -16194,39 +16263,39 @@
         <v>2</v>
       </c>
       <c r="X237" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="238" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="B238" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="D238" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
       <c r="E238" t="s">
         <v>59</v>
       </c>
       <c r="F238" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="J238" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K238" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="R238" t="s">
         <v>89</v>
       </c>
       <c r="S238" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
       <c r="T238">
         <v>820</v>
@@ -16238,18 +16307,18 @@
         <v>2</v>
       </c>
       <c r="X238" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="239" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D239" t="s">
         <v>1252</v>
-      </c>
-      <c r="B239" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D239" t="s">
-        <v>1260</v>
       </c>
       <c r="E239" t="s">
         <v>59</v>
@@ -16258,19 +16327,19 @@
         <v>60</v>
       </c>
       <c r="J239" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="K239" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
       <c r="R239" t="s">
         <v>31</v>
       </c>
       <c r="S239" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="T239">
         <v>182</v>
@@ -16282,30 +16351,30 @@
         <v>2</v>
       </c>
       <c r="X239" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="240" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="B240" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="D240" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
       <c r="E240" t="s">
         <v>59</v>
       </c>
       <c r="F240" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="J240" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="R240" t="s">
         <v>89</v>
@@ -16323,15 +16392,15 @@
         <v>2</v>
       </c>
       <c r="X240" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="241" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="B241" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="D241" t="s">
         <v>407</v>
@@ -16343,19 +16412,19 @@
         <v>96</v>
       </c>
       <c r="J241" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="K241" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="R241" t="s">
         <v>31</v>
       </c>
       <c r="S241" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="T241">
         <v>182</v>
@@ -16367,18 +16436,18 @@
         <v>2</v>
       </c>
       <c r="X241" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="242" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="B242" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="D242" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="E242" t="s">
         <v>191</v>
@@ -16387,19 +16456,19 @@
         <v>192</v>
       </c>
       <c r="J242" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="K242" t="s">
-        <v>1273</v>
+        <v>1265</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="R242" t="s">
         <v>31</v>
       </c>
       <c r="S242" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
       <c r="T242">
         <v>182</v>
@@ -16411,30 +16480,30 @@
         <v>2</v>
       </c>
       <c r="X242" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="243" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="B243" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="D243" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E243" t="s">
         <v>59</v>
       </c>
       <c r="F243" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
       <c r="J243" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>1278</v>
+        <v>1270</v>
       </c>
       <c r="R243" t="s">
         <v>89</v>
@@ -16452,30 +16521,30 @@
         <v>2</v>
       </c>
       <c r="X243" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="244" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="B244" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="D244" t="s">
         <v>679</v>
       </c>
       <c r="E244" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="F244" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
       <c r="J244" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>1282</v>
+        <v>1274</v>
       </c>
       <c r="R244" t="s">
         <v>31</v>
@@ -16493,15 +16562,15 @@
         <v>2</v>
       </c>
       <c r="X244" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="245" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="B245" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="D245" t="s">
         <v>260</v>
@@ -16513,13 +16582,13 @@
         <v>96</v>
       </c>
       <c r="J245" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
       <c r="K245" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="R245" t="s">
         <v>31</v>
@@ -16537,15 +16606,15 @@
         <v>2</v>
       </c>
       <c r="X245" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="246" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="B246" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="D246" t="s">
         <v>260</v>
@@ -16557,16 +16626,16 @@
         <v>35</v>
       </c>
       <c r="J246" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
       <c r="K246" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="M246" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
       <c r="R246" t="s">
         <v>31</v>
@@ -16584,15 +16653,15 @@
         <v>2</v>
       </c>
       <c r="X246" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="247" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="B247" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="D247" t="s">
         <v>260</v>
@@ -16604,10 +16673,10 @@
         <v>494</v>
       </c>
       <c r="J247" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="R247" t="s">
         <v>31</v>
@@ -16625,18 +16694,18 @@
         <v>2</v>
       </c>
       <c r="X247" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="248" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D248" t="s">
         <v>1286</v>
-      </c>
-      <c r="B248" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D248" t="s">
-        <v>1294</v>
       </c>
       <c r="E248" t="s">
         <v>59</v>
@@ -16645,13 +16714,13 @@
         <v>60</v>
       </c>
       <c r="J248" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="K248" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
       <c r="R248" t="s">
         <v>326</v>
@@ -16669,33 +16738,33 @@
         <v>2</v>
       </c>
       <c r="X248" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="249" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="B249" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="D249" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
       <c r="E249" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
       <c r="F249" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
       <c r="J249" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
       <c r="K249" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
       <c r="R249" t="s">
         <v>31</v>
@@ -16713,15 +16782,15 @@
         <v>2</v>
       </c>
       <c r="X249" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="250" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="B250" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="D250" t="s">
         <v>33</v>
@@ -16733,13 +16802,13 @@
         <v>637</v>
       </c>
       <c r="J250" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
       <c r="K250" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>1306</v>
+        <v>1298</v>
       </c>
       <c r="R250" t="s">
         <v>31</v>
@@ -16757,15 +16826,15 @@
         <v>2</v>
       </c>
       <c r="X250" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="251" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="B251" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="D251" t="s">
         <v>33</v>
@@ -16777,13 +16846,13 @@
         <v>35</v>
       </c>
       <c r="J251" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
       <c r="K251" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>1309</v>
+        <v>1301</v>
       </c>
       <c r="R251" t="s">
         <v>31</v>
@@ -16801,36 +16870,36 @@
         <v>2</v>
       </c>
       <c r="X251" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="252" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="B252" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="D252" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="E252" t="s">
         <v>59</v>
       </c>
       <c r="F252" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
       <c r="J252" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="R252" t="s">
         <v>89</v>
       </c>
       <c r="S252" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
       <c r="T252">
         <v>390</v>
@@ -16842,18 +16911,18 @@
         <v>3</v>
       </c>
       <c r="X252" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="253" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="B253" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="D253" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
       <c r="E253" t="s">
         <v>191</v>
@@ -16862,19 +16931,19 @@
         <v>192</v>
       </c>
       <c r="J253" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="K253" t="s">
         <v>347</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="R253" t="s">
         <v>31</v>
       </c>
       <c r="S253" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="T253">
         <v>106</v>
@@ -16886,18 +16955,18 @@
         <v>3</v>
       </c>
       <c r="X253" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="254" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="B254" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="D254" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
       <c r="E254" t="s">
         <v>59</v>
@@ -16906,16 +16975,16 @@
         <v>60</v>
       </c>
       <c r="H254" t="s">
-        <v>1322</v>
+        <v>1314</v>
       </c>
       <c r="J254" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K254" t="s">
         <v>165</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
       <c r="R254" t="s">
         <v>31</v>
@@ -16933,39 +17002,39 @@
         <v>3</v>
       </c>
       <c r="X254" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="255" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
       <c r="B255" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="D255" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="E255" t="s">
         <v>59</v>
       </c>
       <c r="F255" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
       <c r="H255" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="J255" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="K255" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="R255" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
       <c r="S255" t="s">
         <v>523</v>
@@ -16974,30 +17043,30 @@
         <v>3</v>
       </c>
       <c r="X255" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="256" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
       <c r="B256" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
       <c r="D256" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
       <c r="E256" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F256" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
       <c r="J256" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="R256" t="s">
         <v>410</v>
@@ -17009,24 +17078,24 @@
         <v>370</v>
       </c>
       <c r="U256" s="2" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
       <c r="W256" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X256" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="257" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D257" t="s">
         <v>1331</v>
-      </c>
-      <c r="B257" t="s">
-        <v>1332</v>
-      </c>
-      <c r="D257" t="s">
-        <v>1339</v>
       </c>
       <c r="E257" t="s">
         <v>191</v>
@@ -17035,39 +17104,39 @@
         <v>192</v>
       </c>
       <c r="J257" t="s">
-        <v>1340</v>
+        <v>1332</v>
       </c>
       <c r="L257" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
       <c r="R257" t="s">
         <v>410</v>
       </c>
       <c r="S257" t="s">
-        <v>1342</v>
+        <v>1334</v>
       </c>
       <c r="T257" t="s">
         <v>370</v>
       </c>
       <c r="U257" s="2" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
       <c r="W257" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X257" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="258" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
       <c r="B258" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
       <c r="D258" t="s">
-        <v>1343</v>
+        <v>1335</v>
       </c>
       <c r="E258" t="s">
         <v>34</v>
@@ -17076,54 +17145,54 @@
         <v>35</v>
       </c>
       <c r="J258" t="s">
-        <v>1344</v>
+        <v>1336</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
       <c r="R258" t="s">
         <v>31</v>
       </c>
       <c r="S258" t="s">
-        <v>1346</v>
+        <v>1338</v>
       </c>
       <c r="T258" t="s">
-        <v>1347</v>
+        <v>1339</v>
       </c>
       <c r="U258" s="2" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
       <c r="W258" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X258" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="259" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
       <c r="B259" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
       <c r="D259" t="s">
         <v>116</v>
       </c>
       <c r="E259" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
       <c r="F259" t="s">
-        <v>1352</v>
+        <v>1344</v>
       </c>
       <c r="J259" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
       <c r="K259" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
       <c r="R259" t="s">
         <v>31</v>
@@ -17132,27 +17201,27 @@
         <v>38</v>
       </c>
       <c r="T259" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
       <c r="U259" s="2" t="s">
         <v>720</v>
       </c>
       <c r="W259" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X259" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="260" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D260" t="s">
         <v>1349</v>
-      </c>
-      <c r="B260" t="s">
-        <v>1350</v>
-      </c>
-      <c r="D260" t="s">
-        <v>1357</v>
       </c>
       <c r="E260" t="s">
         <v>26</v>
@@ -17161,13 +17230,13 @@
         <v>27</v>
       </c>
       <c r="J260" t="s">
-        <v>1358</v>
+        <v>1350</v>
       </c>
       <c r="K260" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
       <c r="R260" t="s">
         <v>31</v>
@@ -17176,27 +17245,27 @@
         <v>32</v>
       </c>
       <c r="T260" t="s">
-        <v>1361</v>
+        <v>1353</v>
       </c>
       <c r="U260" s="2" t="s">
-        <v>1362</v>
+        <v>1354</v>
       </c>
       <c r="W260" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X260" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="261" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
       <c r="B261" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
       <c r="D261" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
       <c r="E261" t="s">
         <v>95</v>
@@ -17205,42 +17274,42 @@
         <v>96</v>
       </c>
       <c r="J261" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
       <c r="K261" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="R261" t="s">
         <v>31</v>
       </c>
       <c r="S261" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
       <c r="T261" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="U261" s="2" t="s">
         <v>245</v>
       </c>
       <c r="W261" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X261" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="262" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
       <c r="B262" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
       <c r="D262" t="s">
-        <v>1369</v>
+        <v>1361</v>
       </c>
       <c r="E262" t="s">
         <v>34</v>
@@ -17249,13 +17318,13 @@
         <v>35</v>
       </c>
       <c r="J262" t="s">
-        <v>1370</v>
+        <v>1362</v>
       </c>
       <c r="K262" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
       <c r="R262" t="s">
         <v>31</v>
@@ -17264,24 +17333,24 @@
         <v>32</v>
       </c>
       <c r="T262" t="s">
-        <v>1373</v>
+        <v>1365</v>
       </c>
       <c r="U262" s="2" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
       <c r="W262" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X262" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="263" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B263" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="D263" t="s">
         <v>50</v>
@@ -17290,22 +17359,22 @@
         <v>351</v>
       </c>
       <c r="F263" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="J263" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
       <c r="K263" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
       <c r="R263" t="s">
         <v>31</v>
       </c>
       <c r="S263" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="T263">
         <v>116</v>
@@ -17317,18 +17386,18 @@
         <v>3</v>
       </c>
       <c r="X263" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="264" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B264" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="D264" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
       <c r="E264" t="s">
         <v>150</v>
@@ -17337,19 +17406,19 @@
         <v>151</v>
       </c>
       <c r="J264" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>1382</v>
+        <v>1374</v>
       </c>
       <c r="M264" t="s">
-        <v>1383</v>
+        <v>1375</v>
       </c>
       <c r="R264" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="S264" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="T264">
         <v>24</v>
@@ -17361,18 +17430,18 @@
         <v>3</v>
       </c>
       <c r="X264" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="265" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>794</v>
+      </c>
+      <c r="B265" t="s">
         <v>795</v>
       </c>
-      <c r="B265" t="s">
-        <v>796</v>
-      </c>
       <c r="D265" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
       <c r="E265" t="s">
         <v>654</v>
@@ -17381,10 +17450,10 @@
         <v>655</v>
       </c>
       <c r="J265" t="s">
-        <v>1386</v>
+        <v>1378</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
       <c r="R265" t="s">
         <v>31</v>
@@ -17402,15 +17471,15 @@
         <v>3</v>
       </c>
       <c r="X265" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="266" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>794</v>
+      </c>
+      <c r="B266" t="s">
         <v>795</v>
-      </c>
-      <c r="B266" t="s">
-        <v>796</v>
       </c>
       <c r="D266" t="s">
         <v>679</v>
@@ -17422,13 +17491,13 @@
         <v>35</v>
       </c>
       <c r="J266" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="K266" t="s">
-        <v>1389</v>
+        <v>1381</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
       <c r="R266" t="s">
         <v>31</v>
@@ -17446,36 +17515,36 @@
         <v>3</v>
       </c>
       <c r="X266" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="267" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B267" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
       <c r="D267" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
       <c r="E267" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
       <c r="F267" t="s">
-        <v>1394</v>
+        <v>1386</v>
       </c>
       <c r="J267" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="R267" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="S267" t="s">
-        <v>1397</v>
+        <v>1389</v>
       </c>
       <c r="T267">
         <v>40</v>
@@ -17487,39 +17556,39 @@
         <v>3</v>
       </c>
       <c r="X267" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="268" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B268" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D268" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E268" t="s">
+        <v>953</v>
+      </c>
+      <c r="F268" t="s">
+        <v>954</v>
+      </c>
+      <c r="J268" t="s">
         <v>1391</v>
       </c>
-      <c r="D268" t="s">
-        <v>1398</v>
-      </c>
-      <c r="E268" t="s">
-        <v>954</v>
-      </c>
-      <c r="F268" t="s">
-        <v>955</v>
-      </c>
-      <c r="J268" t="s">
-        <v>1399</v>
-      </c>
       <c r="K268" t="s">
-        <v>1400</v>
+        <v>1392</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
       <c r="R268" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="S268" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="T268">
         <v>29</v>
@@ -17531,7 +17600,7 @@
         <v>3</v>
       </c>
       <c r="X268" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="269" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17539,10 +17608,10 @@
         <v>658</v>
       </c>
       <c r="B269" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
       <c r="D269" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="E269" t="s">
         <v>59</v>
@@ -17551,19 +17620,19 @@
         <v>60</v>
       </c>
       <c r="J269" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
       <c r="K269" t="s">
         <v>68</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="R269" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S269" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="T269">
         <v>203</v>
@@ -17575,7 +17644,7 @@
         <v>3</v>
       </c>
       <c r="X269" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="270" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17583,10 +17652,10 @@
         <v>658</v>
       </c>
       <c r="B270" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
       <c r="D270" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
       <c r="E270" t="s">
         <v>197</v>
@@ -17595,19 +17664,19 @@
         <v>270</v>
       </c>
       <c r="J270" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
       <c r="K270" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
       <c r="R270" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S270" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="T270">
         <v>280</v>
@@ -17619,7 +17688,7 @@
         <v>3</v>
       </c>
       <c r="X270" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="271" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17627,28 +17696,28 @@
         <v>658</v>
       </c>
       <c r="B271" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D271" t="s">
         <v>1402</v>
-      </c>
-      <c r="D271" t="s">
-        <v>1410</v>
       </c>
       <c r="E271" t="s">
         <v>284</v>
       </c>
       <c r="F271" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J271" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>1413</v>
+        <v>1405</v>
       </c>
       <c r="R271" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S271" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="T271">
         <v>113</v>
@@ -17660,7 +17729,7 @@
         <v>3</v>
       </c>
       <c r="X271" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="272" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17668,10 +17737,10 @@
         <v>658</v>
       </c>
       <c r="B272" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
       <c r="D272" t="s">
-        <v>1414</v>
+        <v>1406</v>
       </c>
       <c r="E272" t="s">
         <v>169</v>
@@ -17680,19 +17749,19 @@
         <v>170</v>
       </c>
       <c r="J272" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="K272" t="s">
         <v>347</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="R272" t="s">
-        <v>755</v>
+        <v>31</v>
       </c>
       <c r="S272" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="T272">
         <v>96</v>
@@ -17704,39 +17773,39 @@
         <v>3</v>
       </c>
       <c r="X272" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="273" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
       <c r="B273" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
       <c r="D273" t="s">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="E273" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F273" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
       <c r="J273" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
       <c r="K273" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
       <c r="R273" t="s">
         <v>89</v>
       </c>
       <c r="S273" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
       <c r="T273">
         <v>370</v>
@@ -17748,56 +17817,56 @@
         <v>3</v>
       </c>
       <c r="X273" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="274" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B274" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D274" t="s">
         <v>1416</v>
       </c>
-      <c r="B274" t="s">
+      <c r="E274" t="s">
         <v>1417</v>
       </c>
-      <c r="D274" t="s">
-        <v>1424</v>
-      </c>
-      <c r="E274" t="s">
-        <v>1425</v>
-      </c>
       <c r="F274" t="s">
-        <v>1426</v>
+        <v>1418</v>
       </c>
       <c r="H274" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
       <c r="J274" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="K274" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>1430</v>
+        <v>1422</v>
       </c>
       <c r="R274" t="s">
         <v>89</v>
       </c>
       <c r="S274" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
       <c r="W274" s="2">
         <v>3</v>
       </c>
       <c r="X274" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="275" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="B275" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="D275" t="s">
         <v>679</v>
@@ -17809,10 +17878,10 @@
         <v>96</v>
       </c>
       <c r="J275" t="s">
-        <v>1434</v>
+        <v>1426</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
       <c r="R275" t="s">
         <v>31</v>
@@ -17830,21 +17899,21 @@
         <v>3</v>
       </c>
       <c r="X275" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="Y275" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="276" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="B276" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="D276" t="s">
-        <v>1437</v>
+        <v>1429</v>
       </c>
       <c r="E276" t="s">
         <v>191</v>
@@ -17853,16 +17922,16 @@
         <v>192</v>
       </c>
       <c r="J276" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
       <c r="M276" t="s">
-        <v>1440</v>
+        <v>1432</v>
       </c>
       <c r="N276" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="R276" t="s">
         <v>31</v>
@@ -17880,10 +17949,10 @@
         <v>3</v>
       </c>
       <c r="X276" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="Y276" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="277" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17891,7 +17960,7 @@
         <v>440</v>
       </c>
       <c r="B277" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
       <c r="D277">
         <v>1447</v>
@@ -17900,22 +17969,22 @@
         <v>59</v>
       </c>
       <c r="F277" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="H277" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="J277" t="s">
         <v>217</v>
       </c>
       <c r="K277" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="N277" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="R277" t="s">
         <v>89</v>
@@ -17933,10 +18002,10 @@
         <v>3</v>
       </c>
       <c r="X277" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
       <c r="Y277" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="278" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17944,7 +18013,7 @@
         <v>440</v>
       </c>
       <c r="B278" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
       <c r="D278">
         <v>1456</v>
@@ -17953,31 +18022,31 @@
         <v>59</v>
       </c>
       <c r="F278" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="H278" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="J278" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="K278" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="M278" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
       <c r="N278" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="R278" t="s">
         <v>89</v>
       </c>
       <c r="S278" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="T278">
         <v>833</v>
@@ -17989,36 +18058,36 @@
         <v>3</v>
       </c>
       <c r="X278" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
       <c r="Y278" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="279" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B279" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="D279" t="s">
-        <v>1454</v>
+        <v>1446</v>
       </c>
       <c r="E279" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="F279" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
       <c r="J279" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
       <c r="K279" t="s">
-        <v>1458</v>
+        <v>1450</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>1459</v>
+        <v>1451</v>
       </c>
       <c r="R279" t="s">
         <v>89</v>
@@ -18027,27 +18096,27 @@
         <v>89</v>
       </c>
       <c r="T279" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
       <c r="U279" s="2" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
       <c r="W279" s="2">
         <v>3</v>
       </c>
       <c r="X279" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="280" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B280" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="D280" t="s">
-        <v>1462</v>
+        <v>1454</v>
       </c>
       <c r="E280" t="s">
         <v>630</v>
@@ -18059,7 +18128,7 @@
         <v>164</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>1463</v>
+        <v>1455</v>
       </c>
       <c r="R280" t="s">
         <v>31</v>
@@ -18077,36 +18146,36 @@
         <v>3</v>
       </c>
       <c r="X280" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="281" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B281" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="D281" t="s">
-        <v>1464</v>
+        <v>1456</v>
       </c>
       <c r="E281" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
       <c r="F281" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
       <c r="J281" t="s">
-        <v>1467</v>
+        <v>1459</v>
       </c>
       <c r="K281" t="s">
-        <v>1468</v>
+        <v>1460</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>1469</v>
+        <v>1461</v>
       </c>
       <c r="M281" s="1" t="s">
-        <v>1470</v>
+        <v>1462</v>
       </c>
       <c r="R281" t="s">
         <v>280</v>
@@ -18115,71 +18184,71 @@
         <v>523</v>
       </c>
       <c r="T281" t="s">
-        <v>1471</v>
+        <v>1463</v>
       </c>
       <c r="U281" s="2" t="s">
         <v>375</v>
       </c>
       <c r="W281" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X281" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="282" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B282" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="D282" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E282" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F282" t="s">
+        <v>1464</v>
+      </c>
+      <c r="J282" t="s">
         <v>1465</v>
       </c>
-      <c r="F282" t="s">
-        <v>1472</v>
-      </c>
-      <c r="J282" t="s">
-        <v>1473</v>
-      </c>
       <c r="K282" t="s">
-        <v>1474</v>
+        <v>1466</v>
       </c>
       <c r="L282" s="1" t="s">
-        <v>1475</v>
-      </c>
-      <c r="R282" t="s">
-        <v>1476</v>
+        <v>1467</v>
+      </c>
+      <c r="R282" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="S282" t="s">
-        <v>1477</v>
+        <v>1468</v>
       </c>
       <c r="T282" t="s">
-        <v>1478</v>
+        <v>1469</v>
       </c>
       <c r="U282" s="2" t="s">
-        <v>1479</v>
+        <v>1470</v>
       </c>
       <c r="W282" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X282" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="283" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
+        <v>930</v>
+      </c>
+      <c r="B283" t="s">
         <v>931</v>
       </c>
-      <c r="B283" t="s">
-        <v>932</v>
-      </c>
       <c r="D283" t="s">
-        <v>1480</v>
+        <v>1471</v>
       </c>
       <c r="E283" t="s">
         <v>191</v>
@@ -18188,13 +18257,13 @@
         <v>192</v>
       </c>
       <c r="J283" t="s">
-        <v>1481</v>
+        <v>1472</v>
       </c>
       <c r="K283" t="s">
-        <v>1482</v>
+        <v>1473</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>1483</v>
+        <v>1474</v>
       </c>
       <c r="R283" t="s">
         <v>31</v>
@@ -18212,30 +18281,30 @@
         <v>3</v>
       </c>
       <c r="X283" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="284" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>1484</v>
+        <v>1475</v>
       </c>
       <c r="B284" t="s">
-        <v>1485</v>
+        <v>1476</v>
       </c>
       <c r="D284" t="s">
-        <v>1486</v>
+        <v>1477</v>
       </c>
       <c r="E284" t="s">
         <v>83</v>
       </c>
       <c r="F284" t="s">
-        <v>1487</v>
+        <v>1478</v>
       </c>
       <c r="J284" t="s">
-        <v>1488</v>
+        <v>1479</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>1489</v>
+        <v>1480</v>
       </c>
       <c r="R284" t="s">
         <v>89</v>
@@ -18244,16 +18313,16 @@
         <v>89</v>
       </c>
       <c r="T284" t="s">
-        <v>1490</v>
+        <v>1481</v>
       </c>
       <c r="U284" s="2" t="s">
-        <v>1491</v>
+        <v>1482</v>
       </c>
       <c r="W284" s="2">
         <v>3</v>
       </c>
       <c r="X284" t="s">
-        <v>1485</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="285" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18261,22 +18330,22 @@
         <v>221</v>
       </c>
       <c r="B285" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
       <c r="D285" t="s">
         <v>442</v>
       </c>
       <c r="F285" t="s">
-        <v>1493</v>
+        <v>1484</v>
       </c>
       <c r="J285" t="s">
-        <v>1494</v>
+        <v>1485</v>
       </c>
       <c r="K285" t="s">
-        <v>1495</v>
+        <v>1486</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>1496</v>
+        <v>1487</v>
       </c>
       <c r="R285" t="s">
         <v>31</v>
@@ -18294,7 +18363,7 @@
         <v>3</v>
       </c>
       <c r="X285" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="286" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18302,7 +18371,7 @@
         <v>221</v>
       </c>
       <c r="B286" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
       <c r="D286" t="s">
         <v>488</v>
@@ -18314,10 +18383,10 @@
         <v>96</v>
       </c>
       <c r="J286" t="s">
-        <v>1497</v>
+        <v>1488</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>1498</v>
+        <v>1489</v>
       </c>
       <c r="R286" t="s">
         <v>31</v>
@@ -18335,18 +18404,18 @@
         <v>3</v>
       </c>
       <c r="X286" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="287" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1499</v>
+        <v>1490</v>
       </c>
       <c r="B287" t="s">
-        <v>1500</v>
+        <v>1491</v>
       </c>
       <c r="D287" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E287" t="s">
         <v>95</v>
@@ -18355,10 +18424,10 @@
         <v>96</v>
       </c>
       <c r="J287" t="s">
-        <v>1501</v>
+        <v>1492</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>1502</v>
+        <v>1493</v>
       </c>
       <c r="R287" t="s">
         <v>31</v>
@@ -18376,33 +18445,33 @@
         <v>3</v>
       </c>
       <c r="X287" t="s">
-        <v>1500</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="288" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1499</v>
+        <v>1490</v>
       </c>
       <c r="B288" t="s">
-        <v>1500</v>
+        <v>1491</v>
       </c>
       <c r="D288" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E288" t="s">
-        <v>1503</v>
+        <v>1494</v>
       </c>
       <c r="F288" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="J288" t="s">
-        <v>1504</v>
+        <v>1495</v>
       </c>
       <c r="K288" t="s">
-        <v>1505</v>
+        <v>1496</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>1506</v>
+        <v>1497</v>
       </c>
       <c r="R288" t="s">
         <v>89</v>
@@ -18420,18 +18489,18 @@
         <v>3</v>
       </c>
       <c r="X288" t="s">
-        <v>1500</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="289" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>1507</v>
+        <v>1498</v>
       </c>
       <c r="B289" t="s">
-        <v>1500</v>
+        <v>1491</v>
       </c>
       <c r="D289" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E289" t="s">
         <v>59</v>
@@ -18440,19 +18509,19 @@
         <v>60</v>
       </c>
       <c r="J289" t="s">
-        <v>1508</v>
+        <v>1499</v>
       </c>
       <c r="K289" t="s">
-        <v>1509</v>
+        <v>1500</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>1510</v>
+        <v>1501</v>
       </c>
       <c r="R289" t="s">
         <v>31</v>
       </c>
       <c r="S289" t="s">
-        <v>1511</v>
+        <v>1502</v>
       </c>
       <c r="T289">
         <v>240</v>
@@ -18464,39 +18533,39 @@
         <v>3</v>
       </c>
       <c r="X289" t="s">
-        <v>1500</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="290" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1507</v>
+        <v>1498</v>
       </c>
       <c r="B290" t="s">
-        <v>1500</v>
+        <v>1491</v>
       </c>
       <c r="D290" t="s">
-        <v>1512</v>
+        <v>1503</v>
       </c>
       <c r="E290" t="s">
         <v>59</v>
       </c>
       <c r="F290" t="s">
-        <v>1513</v>
+        <v>1504</v>
       </c>
       <c r="H290" t="s">
-        <v>1514</v>
+        <v>1505</v>
       </c>
       <c r="J290" t="s">
-        <v>1515</v>
+        <v>1506</v>
       </c>
       <c r="K290" t="s">
-        <v>1516</v>
+        <v>1507</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>1517</v>
+        <v>1508</v>
       </c>
       <c r="M290" t="s">
-        <v>1518</v>
+        <v>1509</v>
       </c>
       <c r="R290" t="s">
         <v>31</v>
@@ -18514,7 +18583,7 @@
         <v>3</v>
       </c>
       <c r="X290" t="s">
-        <v>1500</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="291" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18525,22 +18594,22 @@
         <v>384</v>
       </c>
       <c r="D291" t="s">
-        <v>1519</v>
+        <v>1510</v>
       </c>
       <c r="E291" t="s">
-        <v>1503</v>
+        <v>1494</v>
       </c>
       <c r="F291" t="s">
-        <v>1520</v>
+        <v>1511</v>
       </c>
       <c r="J291" t="s">
-        <v>1521</v>
+        <v>1512</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>1522</v>
+        <v>1513</v>
       </c>
       <c r="M291" t="s">
-        <v>1523</v>
+        <v>1514</v>
       </c>
       <c r="R291" t="s">
         <v>31</v>
@@ -18569,19 +18638,19 @@
         <v>384</v>
       </c>
       <c r="D292" t="s">
-        <v>1524</v>
+        <v>1515</v>
       </c>
       <c r="E292" t="s">
-        <v>1525</v>
+        <v>1516</v>
       </c>
       <c r="F292" t="s">
-        <v>1526</v>
+        <v>1517</v>
       </c>
       <c r="J292" t="s">
-        <v>1501</v>
+        <v>1492</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>1527</v>
+        <v>1518</v>
       </c>
       <c r="R292" t="s">
         <v>31</v>
@@ -18604,28 +18673,28 @@
     </row>
     <row r="293" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>1528</v>
+        <v>1519</v>
       </c>
       <c r="B293" t="s">
-        <v>1529</v>
+        <v>1520</v>
       </c>
       <c r="D293" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
       <c r="E293" t="s">
         <v>197</v>
       </c>
       <c r="F293" t="s">
-        <v>1530</v>
+        <v>1521</v>
       </c>
       <c r="J293" t="s">
-        <v>1531</v>
+        <v>1522</v>
       </c>
       <c r="K293" t="s">
-        <v>1532</v>
+        <v>1523</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>1533</v>
+        <v>1524</v>
       </c>
       <c r="R293" t="s">
         <v>89</v>
@@ -18643,15 +18712,15 @@
         <v>3</v>
       </c>
       <c r="X293" t="s">
-        <v>1529</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="294" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>1534</v>
+        <v>1525</v>
       </c>
       <c r="B294" t="s">
-        <v>1535</v>
+        <v>1526</v>
       </c>
       <c r="D294" t="s">
         <v>679</v>
@@ -18666,7 +18735,7 @@
         <v>582</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>1536</v>
+        <v>1527</v>
       </c>
       <c r="R294" t="s">
         <v>31</v>
@@ -18684,30 +18753,30 @@
         <v>3</v>
       </c>
       <c r="X294" t="s">
-        <v>1535</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="295" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>1534</v>
+        <v>1525</v>
       </c>
       <c r="B295" t="s">
-        <v>1535</v>
+        <v>1526</v>
       </c>
       <c r="D295" t="s">
-        <v>1537</v>
+        <v>482</v>
       </c>
       <c r="E295" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
       <c r="F295" t="s">
-        <v>1538</v>
+        <v>1528</v>
       </c>
       <c r="J295" t="s">
-        <v>1539</v>
+        <v>1529</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>1540</v>
+        <v>1530</v>
       </c>
       <c r="R295" t="s">
         <v>31</v>
@@ -18725,36 +18794,36 @@
         <v>3</v>
       </c>
       <c r="X295" t="s">
-        <v>1535</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="296" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>1541</v>
+        <v>1531</v>
       </c>
       <c r="B296" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
       <c r="D296" t="s">
         <v>260</v>
       </c>
       <c r="E296" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
       <c r="F296" t="s">
-        <v>1544</v>
+        <v>1534</v>
       </c>
       <c r="J296" t="s">
-        <v>1545</v>
+        <v>1535</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>1546</v>
+        <v>1536</v>
       </c>
       <c r="R296" t="s">
         <v>31</v>
       </c>
       <c r="S296" t="s">
-        <v>1547</v>
+        <v>1537</v>
       </c>
       <c r="T296">
         <v>206</v>
@@ -18766,39 +18835,39 @@
         <v>3</v>
       </c>
       <c r="X296" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="297" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>1541</v>
+        <v>1531</v>
       </c>
       <c r="B297" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
       <c r="D297" t="s">
         <v>260</v>
       </c>
       <c r="E297" t="s">
-        <v>1543</v>
+        <v>1533</v>
       </c>
       <c r="F297" t="s">
-        <v>1544</v>
+        <v>1534</v>
       </c>
       <c r="J297" t="s">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="K297" t="s">
-        <v>1549</v>
+        <v>1539</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>1550</v>
+        <v>1540</v>
       </c>
       <c r="R297" t="s">
         <v>31</v>
       </c>
       <c r="S297" t="s">
-        <v>1551</v>
+        <v>1541</v>
       </c>
       <c r="T297">
         <v>211</v>
@@ -18810,30 +18879,30 @@
         <v>3</v>
       </c>
       <c r="X297" t="s">
-        <v>1542</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="298" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>1552</v>
+        <v>1542</v>
       </c>
       <c r="B298" t="s">
-        <v>1553</v>
+        <v>1543</v>
       </c>
       <c r="D298" t="s">
         <v>660</v>
       </c>
       <c r="E298" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
       <c r="F298" t="s">
-        <v>1554</v>
+        <v>1544</v>
       </c>
       <c r="J298" t="s">
-        <v>1555</v>
+        <v>1545</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>1556</v>
+        <v>1546</v>
       </c>
       <c r="R298" t="s">
         <v>410</v>
@@ -18851,30 +18920,30 @@
         <v>3</v>
       </c>
       <c r="X298" t="s">
-        <v>1553</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="299" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>1552</v>
+        <v>1542</v>
       </c>
       <c r="B299" t="s">
-        <v>1553</v>
+        <v>1543</v>
       </c>
       <c r="D299" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E299" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
       <c r="F299" t="s">
-        <v>1557</v>
+        <v>1547</v>
       </c>
       <c r="J299" t="s">
-        <v>1558</v>
+        <v>1548</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>1559</v>
+        <v>1549</v>
       </c>
       <c r="R299" t="s">
         <v>410</v>
@@ -18892,15 +18961,15 @@
         <v>3</v>
       </c>
       <c r="X299" t="s">
-        <v>1553</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="300" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>1560</v>
+        <v>1550</v>
       </c>
       <c r="B300" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D300" t="s">
         <v>447</v>
@@ -18915,13 +18984,13 @@
         <v>67</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>1561</v>
+        <v>1551</v>
       </c>
       <c r="R300" t="s">
         <v>31</v>
       </c>
       <c r="S300" t="s">
-        <v>1562</v>
+        <v>1552</v>
       </c>
       <c r="T300">
         <v>258</v>
@@ -18933,33 +19002,33 @@
         <v>3</v>
       </c>
       <c r="X300" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="301" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1560</v>
+        <v>1550</v>
       </c>
       <c r="B301" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D301" t="s">
-        <v>1563</v>
+        <v>1553</v>
       </c>
       <c r="E301" t="s">
         <v>59</v>
       </c>
       <c r="F301" t="s">
-        <v>1564</v>
+        <v>1554</v>
       </c>
       <c r="J301" t="s">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="K301" t="s">
-        <v>1566</v>
+        <v>1556</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>1567</v>
+        <v>1557</v>
       </c>
       <c r="R301" t="s">
         <v>31</v>
@@ -18977,30 +19046,30 @@
         <v>3</v>
       </c>
       <c r="X301" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="302" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="B302" t="s">
-        <v>1569</v>
+        <v>1559</v>
       </c>
       <c r="D302" t="s">
         <v>566</v>
       </c>
       <c r="E302" t="s">
-        <v>1570</v>
+        <v>1560</v>
       </c>
       <c r="F302" t="s">
-        <v>1571</v>
+        <v>1561</v>
       </c>
       <c r="J302" t="s">
         <v>405</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>1572</v>
+        <v>1562</v>
       </c>
       <c r="R302" t="s">
         <v>31</v>
@@ -19018,30 +19087,30 @@
         <v>3</v>
       </c>
       <c r="X302" t="s">
-        <v>1569</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="303" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>1568</v>
+        <v>1558</v>
       </c>
       <c r="B303" t="s">
-        <v>1569</v>
+        <v>1559</v>
       </c>
       <c r="D303" t="s">
-        <v>1573</v>
+        <v>1563</v>
       </c>
       <c r="E303" t="s">
-        <v>1570</v>
+        <v>1560</v>
       </c>
       <c r="F303" t="s">
-        <v>1574</v>
+        <v>1564</v>
       </c>
       <c r="J303" t="s">
-        <v>1575</v>
+        <v>1565</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>1576</v>
+        <v>1566</v>
       </c>
       <c r="R303" t="s">
         <v>31</v>
@@ -19059,18 +19128,18 @@
         <v>3</v>
       </c>
       <c r="X303" t="s">
-        <v>1569</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="304" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>1577</v>
+        <v>1567</v>
       </c>
       <c r="B304" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
       <c r="D304" t="s">
-        <v>1579</v>
+        <v>1569</v>
       </c>
       <c r="E304" t="s">
         <v>34</v>
@@ -19079,13 +19148,13 @@
         <v>35</v>
       </c>
       <c r="J304" t="s">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="K304" t="s">
-        <v>1581</v>
+        <v>1571</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>1582</v>
+        <v>1572</v>
       </c>
       <c r="R304" t="s">
         <v>410</v>
@@ -19103,33 +19172,33 @@
         <v>3</v>
       </c>
       <c r="X304" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="305" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B305" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D305" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E305" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F305" t="s">
+        <v>1575</v>
+      </c>
+      <c r="J305" t="s">
+        <v>1576</v>
+      </c>
+      <c r="K305" t="s">
         <v>1577</v>
       </c>
-      <c r="B305" t="s">
+      <c r="L305" s="1" t="s">
         <v>1578</v>
-      </c>
-      <c r="D305" t="s">
-        <v>1583</v>
-      </c>
-      <c r="E305" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F305" t="s">
-        <v>1585</v>
-      </c>
-      <c r="J305" t="s">
-        <v>1586</v>
-      </c>
-      <c r="K305" t="s">
-        <v>1587</v>
-      </c>
-      <c r="L305" s="1" t="s">
-        <v>1588</v>
       </c>
       <c r="R305" t="s">
         <v>31</v>
@@ -19147,18 +19216,18 @@
         <v>3</v>
       </c>
       <c r="X305" t="s">
-        <v>1578</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="306" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>1589</v>
+        <v>1579</v>
       </c>
       <c r="B306" t="s">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="D306" t="s">
-        <v>1591</v>
+        <v>1581</v>
       </c>
       <c r="E306" t="s">
         <v>436</v>
@@ -19167,10 +19236,10 @@
         <v>437</v>
       </c>
       <c r="J306" t="s">
-        <v>1592</v>
+        <v>1582</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>1593</v>
+        <v>1583</v>
       </c>
       <c r="R306" t="s">
         <v>410</v>
@@ -19188,36 +19257,36 @@
         <v>3</v>
       </c>
       <c r="X306" t="s">
-        <v>1590</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="307" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>1589</v>
+        <v>1579</v>
       </c>
       <c r="B307" t="s">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="D307" t="s">
-        <v>1594</v>
+        <v>1584</v>
       </c>
       <c r="E307" t="s">
-        <v>1595</v>
+        <v>1585</v>
       </c>
       <c r="F307" t="s">
-        <v>1596</v>
+        <v>1586</v>
       </c>
       <c r="J307" t="s">
-        <v>1597</v>
+        <v>1587</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>1598</v>
+        <v>1588</v>
       </c>
       <c r="R307" t="s">
         <v>410</v>
       </c>
       <c r="S307" t="s">
-        <v>1599</v>
+        <v>1589</v>
       </c>
       <c r="T307">
         <v>1088</v>
@@ -19229,15 +19298,15 @@
         <v>3</v>
       </c>
       <c r="X307" t="s">
-        <v>1590</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="308" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B308" t="s">
-        <v>1600</v>
+        <v>1590</v>
       </c>
       <c r="D308">
         <v>1475</v>
@@ -19249,13 +19318,13 @@
         <v>96</v>
       </c>
       <c r="J308" t="s">
-        <v>1601</v>
+        <v>1591</v>
       </c>
       <c r="K308" t="s">
-        <v>1602</v>
+        <v>1592</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>1603</v>
+        <v>1593</v>
       </c>
       <c r="R308" t="s">
         <v>31</v>
@@ -19273,18 +19342,18 @@
         <v>3</v>
       </c>
       <c r="X308" t="s">
-        <v>1600</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="309" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B309" t="s">
-        <v>1600</v>
+        <v>1590</v>
       </c>
       <c r="D309" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
       <c r="E309" t="s">
         <v>59</v>
@@ -19293,16 +19362,16 @@
         <v>163</v>
       </c>
       <c r="J309" t="s">
-        <v>1604</v>
+        <v>1594</v>
       </c>
       <c r="K309" t="s">
-        <v>1605</v>
+        <v>1595</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>1606</v>
+        <v>1596</v>
       </c>
       <c r="M309" t="s">
-        <v>1607</v>
+        <v>1597</v>
       </c>
       <c r="R309" t="s">
         <v>31</v>
@@ -19320,36 +19389,36 @@
         <v>3</v>
       </c>
       <c r="X309" t="s">
-        <v>1600</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="310" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B310" t="s">
-        <v>1608</v>
+        <v>1598</v>
       </c>
       <c r="D310" t="s">
-        <v>1609</v>
+        <v>1599</v>
       </c>
       <c r="E310" t="s">
-        <v>1610</v>
+        <v>1600</v>
       </c>
       <c r="F310" t="s">
-        <v>1611</v>
+        <v>1601</v>
       </c>
       <c r="J310" t="s">
-        <v>1612</v>
+        <v>1602</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>1613</v>
+        <v>1603</v>
       </c>
       <c r="R310" t="s">
         <v>326</v>
       </c>
       <c r="S310" t="s">
-        <v>1614</v>
+        <v>1604</v>
       </c>
       <c r="T310">
         <v>143</v>
@@ -19361,30 +19430,30 @@
         <v>3</v>
       </c>
       <c r="X310" t="s">
-        <v>1608</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="311" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>1615</v>
+        <v>1605</v>
       </c>
       <c r="B311" t="s">
-        <v>1616</v>
+        <v>1606</v>
       </c>
       <c r="D311" t="s">
-        <v>1617</v>
+        <v>1607</v>
       </c>
       <c r="E311" t="s">
-        <v>1618</v>
+        <v>1608</v>
       </c>
       <c r="F311" t="s">
-        <v>1619</v>
+        <v>1609</v>
       </c>
       <c r="J311" t="s">
         <v>394</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="R311" t="s">
         <v>31</v>
@@ -19402,15 +19471,15 @@
         <v>3</v>
       </c>
       <c r="X311" t="s">
-        <v>1616</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="312" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>1615</v>
+        <v>1605</v>
       </c>
       <c r="B312" t="s">
-        <v>1616</v>
+        <v>1606</v>
       </c>
       <c r="D312" t="s">
         <v>238</v>
@@ -19422,10 +19491,10 @@
         <v>192</v>
       </c>
       <c r="J312" t="s">
-        <v>1621</v>
+        <v>1611</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>1622</v>
+        <v>1612</v>
       </c>
       <c r="R312" t="s">
         <v>31</v>
@@ -19443,15 +19512,15 @@
         <v>3</v>
       </c>
       <c r="X312" t="s">
-        <v>1616</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="313" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>1623</v>
+        <v>1613</v>
       </c>
       <c r="B313" t="s">
-        <v>1624</v>
+        <v>1614</v>
       </c>
       <c r="D313" t="s">
         <v>78</v>
@@ -19466,16 +19535,16 @@
         <v>84</v>
       </c>
       <c r="J313" t="s">
-        <v>1625</v>
+        <v>1615</v>
       </c>
       <c r="K313" t="s">
-        <v>1626</v>
+        <v>1616</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>1627</v>
+        <v>1617</v>
       </c>
       <c r="M313" t="s">
-        <v>1628</v>
+        <v>1618</v>
       </c>
       <c r="R313" t="s">
         <v>89</v>
@@ -19493,15 +19562,15 @@
         <v>3</v>
       </c>
       <c r="X313" t="s">
-        <v>1624</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="314" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>1623</v>
+        <v>1613</v>
       </c>
       <c r="B314" t="s">
-        <v>1624</v>
+        <v>1614</v>
       </c>
       <c r="D314" t="s">
         <v>78</v>
@@ -19519,13 +19588,13 @@
         <v>217</v>
       </c>
       <c r="K314" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>1629</v>
+        <v>1619</v>
       </c>
       <c r="M314" t="s">
-        <v>1628</v>
+        <v>1618</v>
       </c>
       <c r="R314" t="s">
         <v>89</v>
@@ -19543,39 +19612,39 @@
         <v>3</v>
       </c>
       <c r="X314" t="s">
-        <v>1624</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="315" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
       <c r="B315" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="D315" t="s">
-        <v>1631</v>
+        <v>1621</v>
       </c>
       <c r="E315" t="s">
-        <v>1632</v>
+        <v>1622</v>
       </c>
       <c r="F315" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="J315" t="s">
-        <v>1633</v>
+        <v>1623</v>
       </c>
       <c r="K315" t="s">
-        <v>1634</v>
+        <v>1624</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>1635</v>
+        <v>1625</v>
       </c>
       <c r="R315" t="s">
         <v>410</v>
       </c>
       <c r="S315" t="s">
-        <v>1636</v>
+        <v>1626</v>
       </c>
       <c r="T315" t="s">
         <v>252</v>
@@ -19584,189 +19653,189 @@
         <v>746</v>
       </c>
       <c r="W315" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X315" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="316" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
       <c r="B316" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="D316" t="s">
-        <v>1637</v>
+        <v>1627</v>
       </c>
       <c r="E316" t="s">
-        <v>1632</v>
+        <v>1622</v>
       </c>
       <c r="F316" t="s">
-        <v>1638</v>
+        <v>1628</v>
       </c>
       <c r="J316" t="s">
         <v>265</v>
       </c>
       <c r="K316" t="s">
-        <v>1639</v>
+        <v>1629</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>1640</v>
+        <v>1630</v>
       </c>
       <c r="M316" t="s">
-        <v>1641</v>
+        <v>1631</v>
       </c>
       <c r="N316" s="1" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="R316" t="s">
-        <v>1642</v>
+        <v>1632</v>
       </c>
       <c r="S316" t="s">
-        <v>1636</v>
+        <v>1626</v>
       </c>
       <c r="T316" t="s">
         <v>746</v>
       </c>
       <c r="U316" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="W316" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X316" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="317" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
       <c r="B317" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="D317" t="s">
-        <v>1637</v>
+        <v>1627</v>
       </c>
       <c r="E317" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F317" t="s">
+        <v>1628</v>
+      </c>
+      <c r="J317" t="s">
+        <v>1633</v>
+      </c>
+      <c r="K317" t="s">
+        <v>1634</v>
+      </c>
+      <c r="L317" s="1" t="s">
+        <v>1635</v>
+      </c>
+      <c r="M317" t="s">
+        <v>1631</v>
+      </c>
+      <c r="N317" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="R317" t="s">
         <v>1632</v>
       </c>
-      <c r="F317" t="s">
-        <v>1638</v>
-      </c>
-      <c r="J317" t="s">
-        <v>1643</v>
-      </c>
-      <c r="K317" t="s">
-        <v>1644</v>
-      </c>
-      <c r="L317" s="1" t="s">
-        <v>1645</v>
-      </c>
-      <c r="M317" t="s">
-        <v>1641</v>
-      </c>
-      <c r="N317" s="1" t="s">
-        <v>1441</v>
-      </c>
-      <c r="R317" t="s">
-        <v>1642</v>
-      </c>
       <c r="S317" t="s">
-        <v>1636</v>
+        <v>1626</v>
       </c>
       <c r="T317" t="s">
         <v>746</v>
       </c>
       <c r="U317" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="W317" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X317" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="318" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
       <c r="B318" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="D318" t="s">
+        <v>1627</v>
+      </c>
+      <c r="E318" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F318" t="s">
+        <v>1628</v>
+      </c>
+      <c r="J318" t="s">
+        <v>1636</v>
+      </c>
+      <c r="K318" t="s">
         <v>1637</v>
       </c>
-      <c r="E318" t="s">
+      <c r="L318" s="1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="M318" t="s">
+        <v>1631</v>
+      </c>
+      <c r="N318" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="R318" t="s">
         <v>1632</v>
       </c>
-      <c r="F318" t="s">
-        <v>1638</v>
-      </c>
-      <c r="J318" t="s">
-        <v>1646</v>
-      </c>
-      <c r="K318" t="s">
-        <v>1647</v>
-      </c>
-      <c r="L318" s="1" t="s">
-        <v>1648</v>
-      </c>
-      <c r="M318" t="s">
-        <v>1641</v>
-      </c>
-      <c r="N318" s="1" t="s">
-        <v>1441</v>
-      </c>
-      <c r="R318" t="s">
-        <v>1642</v>
-      </c>
       <c r="S318" t="s">
-        <v>1636</v>
+        <v>1626</v>
       </c>
       <c r="T318" t="s">
         <v>746</v>
       </c>
       <c r="U318" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="W318" s="2" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="X318" t="s">
-        <v>1630</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="319" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>1649</v>
+        <v>1639</v>
       </c>
       <c r="B319" t="s">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D319">
         <v>1469</v>
       </c>
       <c r="E319" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="F319" t="s">
-        <v>1651</v>
+        <v>1641</v>
       </c>
       <c r="J319" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
       <c r="K319" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>1652</v>
+        <v>1642</v>
       </c>
       <c r="M319" t="s">
-        <v>1653</v>
+        <v>1643</v>
       </c>
       <c r="R319" t="s">
         <v>31</v>
@@ -19784,18 +19853,18 @@
         <v>3</v>
       </c>
       <c r="X319" t="s">
-        <v>1650</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="320" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1649</v>
+        <v>1639</v>
       </c>
       <c r="B320" t="s">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="D320" t="s">
-        <v>1654</v>
+        <v>1644</v>
       </c>
       <c r="E320" t="s">
         <v>95</v>
@@ -19804,22 +19873,22 @@
         <v>96</v>
       </c>
       <c r="J320" t="s">
-        <v>1655</v>
+        <v>1645</v>
       </c>
       <c r="K320" t="s">
-        <v>1656</v>
+        <v>1646</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>1657</v>
+        <v>1647</v>
       </c>
       <c r="M320" t="s">
-        <v>1658</v>
+        <v>1648</v>
       </c>
       <c r="R320" t="s">
         <v>31</v>
       </c>
       <c r="S320" t="s">
-        <v>1659</v>
+        <v>1649</v>
       </c>
       <c r="T320">
         <v>239</v>
@@ -19831,18 +19900,18 @@
         <v>3</v>
       </c>
       <c r="X320" t="s">
-        <v>1650</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="321" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B321" t="s">
-        <v>1660</v>
+        <v>1650</v>
       </c>
       <c r="D321" t="s">
-        <v>1661</v>
+        <v>1651</v>
       </c>
       <c r="E321" t="s">
         <v>34</v>
@@ -19854,7 +19923,7 @@
         <v>67</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>1662</v>
+        <v>1652</v>
       </c>
       <c r="R321" t="s">
         <v>31</v>
@@ -19872,18 +19941,18 @@
         <v>3</v>
       </c>
       <c r="X321" t="s">
-        <v>1660</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="322" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B322" t="s">
-        <v>1660</v>
+        <v>1650</v>
       </c>
       <c r="D322" t="s">
-        <v>1663</v>
+        <v>1653</v>
       </c>
       <c r="E322" t="s">
         <v>59</v>
@@ -19892,10 +19961,10 @@
         <v>60</v>
       </c>
       <c r="J322" t="s">
-        <v>1664</v>
+        <v>1654</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>1665</v>
+        <v>1655</v>
       </c>
       <c r="R322" t="s">
         <v>410</v>
@@ -19913,15 +19982,15 @@
         <v>3</v>
       </c>
       <c r="X322" t="s">
-        <v>1660</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="323" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>1666</v>
+        <v>1656</v>
       </c>
       <c r="B323" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
       <c r="D323">
         <v>1480</v>
@@ -19933,13 +20002,13 @@
         <v>118</v>
       </c>
       <c r="J323" t="s">
-        <v>1668</v>
+        <v>1658</v>
       </c>
       <c r="K323" t="s">
-        <v>1669</v>
+        <v>1659</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>1670</v>
+        <v>1660</v>
       </c>
       <c r="R323" t="s">
         <v>31</v>
@@ -19957,39 +20026,39 @@
         <v>3</v>
       </c>
       <c r="X323" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="324" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>1666</v>
+        <v>1656</v>
       </c>
       <c r="B324" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
       <c r="D324" t="s">
-        <v>1671</v>
+        <v>1661</v>
       </c>
       <c r="E324" t="s">
         <v>117</v>
       </c>
       <c r="F324" t="s">
-        <v>1672</v>
+        <v>1662</v>
       </c>
       <c r="J324" t="s">
-        <v>1673</v>
+        <v>1663</v>
       </c>
       <c r="K324" t="s">
-        <v>1674</v>
+        <v>1664</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>1675</v>
+        <v>1665</v>
       </c>
       <c r="R324" t="s">
         <v>31</v>
       </c>
       <c r="S324" t="s">
-        <v>1676</v>
+        <v>1666</v>
       </c>
       <c r="T324">
         <v>141</v>
@@ -20001,15 +20070,15 @@
         <v>3</v>
       </c>
       <c r="X324" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="325" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B325" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
       <c r="D325">
         <v>1444</v>
@@ -20018,7 +20087,7 @@
         <v>117</v>
       </c>
       <c r="F325" t="s">
-        <v>1677</v>
+        <v>1667</v>
       </c>
       <c r="J325" t="s">
         <v>394</v>
@@ -20027,13 +20096,13 @@
         <v>395</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>1678</v>
+        <v>1668</v>
       </c>
       <c r="R325" t="s">
         <v>31</v>
       </c>
       <c r="S325" t="s">
-        <v>1679</v>
+        <v>1669</v>
       </c>
       <c r="T325">
         <v>230</v>
@@ -20045,15 +20114,15 @@
         <v>3</v>
       </c>
       <c r="X325" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="326" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B326" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
       <c r="D326">
         <v>1446</v>
@@ -20065,19 +20134,19 @@
         <v>118</v>
       </c>
       <c r="J326" t="s">
-        <v>1680</v>
+        <v>1670</v>
       </c>
       <c r="K326" t="s">
-        <v>1681</v>
+        <v>1671</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>1682</v>
+        <v>1672</v>
       </c>
       <c r="R326" t="s">
         <v>326</v>
       </c>
       <c r="S326" t="s">
-        <v>1683</v>
+        <v>1673</v>
       </c>
       <c r="T326">
         <v>292</v>
@@ -20089,15 +20158,15 @@
         <v>3</v>
       </c>
       <c r="X326" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="327" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>1684</v>
+        <v>1674</v>
       </c>
       <c r="B327" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
       <c r="D327">
         <v>1474</v>
@@ -20106,16 +20175,16 @@
         <v>117</v>
       </c>
       <c r="F327" t="s">
-        <v>1685</v>
+        <v>1675</v>
       </c>
       <c r="J327" t="s">
-        <v>1686</v>
+        <v>1676</v>
       </c>
       <c r="K327" t="s">
-        <v>1687</v>
+        <v>1677</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>1688</v>
+        <v>1678</v>
       </c>
       <c r="R327" t="s">
         <v>326</v>
@@ -20133,15 +20202,15 @@
         <v>3</v>
       </c>
       <c r="X327" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="328" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>1684</v>
+        <v>1674</v>
       </c>
       <c r="B328" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
       <c r="D328">
         <v>1482</v>
@@ -20150,16 +20219,16 @@
         <v>117</v>
       </c>
       <c r="F328" t="s">
-        <v>1689</v>
+        <v>1679</v>
       </c>
       <c r="J328" t="s">
-        <v>1690</v>
+        <v>1680</v>
       </c>
       <c r="K328" t="s">
-        <v>1691</v>
+        <v>1681</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>1692</v>
+        <v>1682</v>
       </c>
       <c r="R328" t="s">
         <v>326</v>
@@ -20177,30 +20246,30 @@
         <v>3</v>
       </c>
       <c r="X328" t="s">
-        <v>1667</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="329" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>1693</v>
+        <v>1683</v>
       </c>
       <c r="B329" t="s">
-        <v>1694</v>
+        <v>1684</v>
       </c>
       <c r="D329" t="s">
-        <v>1695</v>
+        <v>1685</v>
       </c>
       <c r="E329" t="s">
-        <v>1696</v>
+        <v>1686</v>
       </c>
       <c r="F329" t="s">
-        <v>1697</v>
+        <v>1687</v>
       </c>
       <c r="J329" t="s">
-        <v>1698</v>
+        <v>1688</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>1699</v>
+        <v>1689</v>
       </c>
       <c r="R329" t="s">
         <v>31</v>
@@ -20218,15 +20287,15 @@
         <v>3</v>
       </c>
       <c r="X329" t="s">
-        <v>1694</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="330" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>1693</v>
+        <v>1683</v>
       </c>
       <c r="B330" t="s">
-        <v>1694</v>
+        <v>1684</v>
       </c>
       <c r="D330" t="s">
         <v>566</v>
@@ -20238,10 +20307,10 @@
         <v>35</v>
       </c>
       <c r="J330" t="s">
-        <v>1700</v>
+        <v>1690</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>1701</v>
+        <v>1691</v>
       </c>
       <c r="R330" t="s">
         <v>31</v>
@@ -20259,7 +20328,7 @@
         <v>3</v>
       </c>
       <c r="X330" t="s">
-        <v>1694</v>
+        <v>1684</v>
       </c>
     </row>
   </sheetData>
@@ -20646,6 +20715,7 @@
     <hyperlink ref="L328" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
     <hyperlink ref="L329" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
     <hyperlink ref="L330" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="L59" r:id="rId361" xr:uid="{EE76E790-8305-4F56-A3E3-311C24C6AFBA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8246FA-8984-4776-BF70-EE8629136347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090B29AE-BEDE-4D87-97A5-F2209D2C4B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16275" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2501,9 +2501,6 @@
     <t>196</t>
   </si>
   <si>
-    <t>Art Institute of Chicago</t>
-  </si>
-  <si>
     <t>Crucifixion</t>
   </si>
   <si>
@@ -5037,6 +5034,9 @@
   </si>
   <si>
     <t xml:space="preserve">La Vierge et l'Enfant entourés d'anges et de saints </t>
+  </si>
+  <si>
+    <t>Art Institute</t>
   </si>
 </sst>
 </file>
@@ -5559,31 +5559,31 @@
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B2" t="s">
         <v>1267</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>1268</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1269</v>
       </c>
       <c r="E2" t="s">
         <v>59</v>
       </c>
       <c r="F2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="J2" t="s">
         <v>1270</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" s="1" t="s">
         <v>1271</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>1272</v>
       </c>
       <c r="R2" t="s">
         <v>89</v>
       </c>
       <c r="S2" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="T2" s="2">
         <v>390</v>
@@ -5595,18 +5595,18 @@
         <v>3</v>
       </c>
       <c r="X2" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B3" t="s">
         <v>1267</v>
       </c>
-      <c r="B3" t="s">
-        <v>1268</v>
-      </c>
       <c r="D3" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="E3" t="s">
         <v>191</v>
@@ -5615,19 +5615,19 @@
         <v>192</v>
       </c>
       <c r="J3" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="K3" t="s">
         <v>346</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="R3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" t="s">
         <v>1276</v>
-      </c>
-      <c r="R3" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" t="s">
-        <v>1277</v>
       </c>
       <c r="T3" s="2">
         <v>106</v>
@@ -5639,18 +5639,18 @@
         <v>3</v>
       </c>
       <c r="X3" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B4" t="s">
         <v>1267</v>
       </c>
-      <c r="B4" t="s">
-        <v>1268</v>
-      </c>
       <c r="D4" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E4" t="s">
         <v>59</v>
@@ -5659,16 +5659,16 @@
         <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="J4" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="K4" t="s">
         <v>165</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="R4" t="s">
         <v>31</v>
@@ -5686,39 +5686,39 @@
         <v>3</v>
       </c>
       <c r="X4" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B5" t="s">
         <v>1267</v>
       </c>
-      <c r="B5" t="s">
-        <v>1268</v>
-      </c>
       <c r="D5" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E5" t="s">
         <v>59</v>
       </c>
       <c r="F5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H5" t="s">
         <v>1282</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>1283</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>1284</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="R5" t="s">
         <v>1286</v>
-      </c>
-      <c r="R5" t="s">
-        <v>1287</v>
       </c>
       <c r="S5" t="s">
         <v>514</v>
@@ -5727,30 +5727,30 @@
         <v>3</v>
       </c>
       <c r="X5" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B6" t="s">
         <v>1288</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>1289</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1290</v>
       </c>
       <c r="E6" t="s">
         <v>736</v>
       </c>
       <c r="F6" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J6" t="s">
         <v>1291</v>
       </c>
-      <c r="J6" t="s">
+      <c r="L6" s="1" t="s">
         <v>1292</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>1293</v>
       </c>
       <c r="R6" t="s">
         <v>408</v>
@@ -5762,24 +5762,24 @@
         <v>369</v>
       </c>
       <c r="U6" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>1294</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>1295</v>
-      </c>
       <c r="X6" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B7" t="s">
         <v>1288</v>
       </c>
-      <c r="B7" t="s">
-        <v>1289</v>
-      </c>
       <c r="D7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E7" t="s">
         <v>191</v>
@@ -5788,39 +5788,39 @@
         <v>192</v>
       </c>
       <c r="J7" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L7" s="6" t="s">
         <v>1297</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>1298</v>
       </c>
       <c r="R7" t="s">
         <v>408</v>
       </c>
       <c r="S7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>369</v>
       </c>
       <c r="U7" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="W7" s="2" t="s">
         <v>1294</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>1295</v>
-      </c>
       <c r="X7" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B8" t="s">
         <v>1288</v>
       </c>
-      <c r="B8" t="s">
-        <v>1289</v>
-      </c>
       <c r="D8" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>
@@ -5829,16 +5829,16 @@
         <v>35</v>
       </c>
       <c r="J8" t="s">
+        <v>1300</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>1301</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="R8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S8" t="s">
         <v>1302</v>
-      </c>
-      <c r="R8" t="s">
-        <v>31</v>
-      </c>
-      <c r="S8" t="s">
-        <v>1303</v>
       </c>
       <c r="T8" s="2">
         <v>107</v>
@@ -5847,10 +5847,10 @@
         <v>81</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X8" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6281,28 +6281,28 @@
     </row>
     <row r="19" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B19" t="s">
         <v>1304</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1305</v>
       </c>
       <c r="D19" t="s">
         <v>116</v>
       </c>
       <c r="E19" t="s">
+        <v>1305</v>
+      </c>
+      <c r="F19" t="s">
         <v>1306</v>
       </c>
-      <c r="F19" t="s">
+      <c r="J19" t="s">
         <v>1307</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>1308</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" s="1" t="s">
         <v>1309</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>1310</v>
       </c>
       <c r="R19" t="s">
         <v>31</v>
@@ -6311,27 +6311,27 @@
         <v>38</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>707</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X19" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B20" t="s">
         <v>1304</v>
       </c>
-      <c r="B20" t="s">
-        <v>1305</v>
-      </c>
       <c r="D20" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E20" t="s">
         <v>26</v>
@@ -6340,13 +6340,13 @@
         <v>27</v>
       </c>
       <c r="J20" t="s">
+        <v>1312</v>
+      </c>
+      <c r="K20" t="s">
         <v>1313</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" s="1" t="s">
         <v>1314</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>1315</v>
       </c>
       <c r="R20" t="s">
         <v>31</v>
@@ -6355,27 +6355,27 @@
         <v>32</v>
       </c>
       <c r="T20" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="U20" s="2" t="s">
         <v>1316</v>
       </c>
-      <c r="U20" s="2" t="s">
-        <v>1317</v>
-      </c>
       <c r="W20" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X20" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B21" t="s">
         <v>1304</v>
       </c>
-      <c r="B21" t="s">
-        <v>1305</v>
-      </c>
       <c r="D21" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E21" t="s">
         <v>95</v>
@@ -6384,42 +6384,42 @@
         <v>96</v>
       </c>
       <c r="J21" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K21" t="s">
         <v>1319</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="R21" t="s">
+        <v>31</v>
+      </c>
+      <c r="S21" t="s">
         <v>1321</v>
       </c>
-      <c r="R21" t="s">
-        <v>31</v>
-      </c>
-      <c r="S21" t="s">
+      <c r="T21" s="2" t="s">
         <v>1322</v>
-      </c>
-      <c r="T21" s="2" t="s">
-        <v>1323</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>245</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X21" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B22" t="s">
         <v>1304</v>
       </c>
-      <c r="B22" t="s">
-        <v>1305</v>
-      </c>
       <c r="D22" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E22" t="s">
         <v>34</v>
@@ -6428,13 +6428,13 @@
         <v>35</v>
       </c>
       <c r="J22" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K22" t="s">
         <v>1325</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" s="1" t="s">
         <v>1326</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>1327</v>
       </c>
       <c r="R22" t="s">
         <v>31</v>
@@ -6443,16 +6443,16 @@
         <v>32</v>
       </c>
       <c r="T22" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="U22" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="U22" s="2" t="s">
-        <v>1329</v>
-      </c>
       <c r="W22" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X22" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7164,10 +7164,10 @@
     </row>
     <row r="39" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B39" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D39" t="s">
         <v>50</v>
@@ -7176,22 +7176,22 @@
         <v>350</v>
       </c>
       <c r="F39" t="s">
+        <v>1330</v>
+      </c>
+      <c r="J39" t="s">
         <v>1331</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>1332</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>1334</v>
-      </c>
       <c r="R39" t="s">
         <v>31</v>
       </c>
       <c r="S39" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="T39" s="2">
         <v>116</v>
@@ -7203,18 +7203,18 @@
         <v>3</v>
       </c>
       <c r="X39" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B40" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D40" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="E40" t="s">
         <v>150</v>
@@ -7223,19 +7223,19 @@
         <v>151</v>
       </c>
       <c r="J40" t="s">
+        <v>1335</v>
+      </c>
+      <c r="L40" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="M40" t="s">
         <v>1337</v>
       </c>
-      <c r="M40" t="s">
+      <c r="R40" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="S40" t="s">
         <v>1338</v>
-      </c>
-      <c r="R40" s="4" t="s">
-        <v>927</v>
-      </c>
-      <c r="S40" t="s">
-        <v>1339</v>
       </c>
       <c r="T40" s="2">
         <v>24</v>
@@ -7247,7 +7247,7 @@
         <v>3</v>
       </c>
       <c r="X40" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7349,7 +7349,7 @@
         <v>686</v>
       </c>
       <c r="D43" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="E43" t="s">
         <v>26</v>
@@ -7393,7 +7393,7 @@
         <v>686</v>
       </c>
       <c r="D44" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="E44" t="s">
         <v>704</v>
@@ -7402,7 +7402,7 @@
         <v>705</v>
       </c>
       <c r="J44" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>706</v>
@@ -8699,7 +8699,7 @@
         <v>765</v>
       </c>
       <c r="D73" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="E73" t="s">
         <v>645</v>
@@ -8708,10 +8708,10 @@
         <v>646</v>
       </c>
       <c r="J73" t="s">
+        <v>1340</v>
+      </c>
+      <c r="L73" s="1" t="s">
         <v>1341</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>1342</v>
       </c>
       <c r="R73" t="s">
         <v>31</v>
@@ -8749,13 +8749,13 @@
         <v>35</v>
       </c>
       <c r="J74" t="s">
+        <v>1342</v>
+      </c>
+      <c r="K74" t="s">
         <v>1343</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" s="1" t="s">
         <v>1344</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>1345</v>
       </c>
       <c r="R74" t="s">
         <v>31</v>
@@ -8778,31 +8778,31 @@
     </row>
     <row r="75" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B75" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D75" t="s">
         <v>1346</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>1347</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>1348</v>
       </c>
-      <c r="F75" t="s">
+      <c r="J75" t="s">
         <v>1349</v>
       </c>
-      <c r="J75" t="s">
+      <c r="L75" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="L75" s="1" t="s">
+      <c r="R75" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="S75" t="s">
         <v>1351</v>
-      </c>
-      <c r="R75" s="4" t="s">
-        <v>927</v>
-      </c>
-      <c r="S75" t="s">
-        <v>1352</v>
       </c>
       <c r="T75" s="2">
         <v>40</v>
@@ -8814,39 +8814,39 @@
         <v>3</v>
       </c>
       <c r="X75" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="76" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B76" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D76" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E76" t="s">
+        <v>922</v>
+      </c>
+      <c r="F76" t="s">
+        <v>923</v>
+      </c>
+      <c r="J76" t="s">
         <v>1353</v>
       </c>
-      <c r="E76" t="s">
-        <v>923</v>
-      </c>
-      <c r="F76" t="s">
-        <v>924</v>
-      </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>1354</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="L76" s="1" t="s">
-        <v>1356</v>
-      </c>
       <c r="R76" s="4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="S76" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="T76" s="2">
         <v>29</v>
@@ -8858,7 +8858,7 @@
         <v>3</v>
       </c>
       <c r="X76" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="77" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9139,16 +9139,16 @@
         <v>520</v>
       </c>
       <c r="F83" t="s">
+        <v>1667</v>
+      </c>
+      <c r="J83" t="s">
         <v>822</v>
-      </c>
-      <c r="J83" t="s">
-        <v>823</v>
       </c>
       <c r="K83" t="s">
         <v>353</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="R83" t="s">
         <v>31</v>
@@ -9177,25 +9177,25 @@
         <v>790</v>
       </c>
       <c r="D84" t="s">
+        <v>824</v>
+      </c>
+      <c r="E84" t="s">
         <v>825</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>826</v>
       </c>
-      <c r="F84" t="s">
+      <c r="H84" t="s">
         <v>827</v>
       </c>
-      <c r="H84" t="s">
+      <c r="J84" t="s">
         <v>828</v>
       </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>829</v>
       </c>
-      <c r="K84" t="s">
+      <c r="L84" s="1" t="s">
         <v>830</v>
-      </c>
-      <c r="L84" s="1" t="s">
-        <v>831</v>
       </c>
       <c r="R84" t="s">
         <v>31</v>
@@ -9207,7 +9207,7 @@
         <v>805</v>
       </c>
       <c r="U84" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="W84" s="2">
         <v>2</v>
@@ -9221,10 +9221,10 @@
         <v>649</v>
       </c>
       <c r="B85" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D85" t="s">
         <v>1357</v>
-      </c>
-      <c r="D85" t="s">
-        <v>1358</v>
       </c>
       <c r="E85" t="s">
         <v>59</v>
@@ -9233,19 +9233,19 @@
         <v>60</v>
       </c>
       <c r="J85" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="K85" t="s">
         <v>68</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="R85" t="s">
         <v>31</v>
       </c>
       <c r="S85" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="T85" s="2">
         <v>203</v>
@@ -9257,7 +9257,7 @@
         <v>3</v>
       </c>
       <c r="X85" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9265,10 +9265,10 @@
         <v>649</v>
       </c>
       <c r="B86" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D86" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="E86" t="s">
         <v>197</v>
@@ -9277,19 +9277,19 @@
         <v>270</v>
       </c>
       <c r="J86" t="s">
+        <v>1361</v>
+      </c>
+      <c r="K86" t="s">
         <v>1362</v>
       </c>
-      <c r="K86" t="s">
+      <c r="L86" s="1" t="s">
         <v>1363</v>
       </c>
-      <c r="L86" s="1" t="s">
-        <v>1364</v>
-      </c>
       <c r="R86" t="s">
         <v>31</v>
       </c>
       <c r="S86" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="T86" s="2">
         <v>280</v>
@@ -9301,7 +9301,7 @@
         <v>3</v>
       </c>
       <c r="X86" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9309,28 +9309,28 @@
         <v>649</v>
       </c>
       <c r="B87" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D87" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="E87" t="s">
         <v>284</v>
       </c>
       <c r="F87" t="s">
+        <v>1365</v>
+      </c>
+      <c r="J87" t="s">
         <v>1366</v>
       </c>
-      <c r="J87" t="s">
+      <c r="L87" s="1" t="s">
         <v>1367</v>
       </c>
-      <c r="L87" s="1" t="s">
-        <v>1368</v>
-      </c>
       <c r="R87" t="s">
         <v>31</v>
       </c>
       <c r="S87" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="T87" s="2">
         <v>113</v>
@@ -9342,7 +9342,7 @@
         <v>3</v>
       </c>
       <c r="X87" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9350,10 +9350,10 @@
         <v>649</v>
       </c>
       <c r="B88" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D88" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E88" t="s">
         <v>169</v>
@@ -9362,19 +9362,19 @@
         <v>170</v>
       </c>
       <c r="J88" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K88" t="s">
         <v>346</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="R88" t="s">
         <v>31</v>
       </c>
       <c r="S88" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="T88" s="2">
         <v>96</v>
@@ -9386,39 +9386,39 @@
         <v>3</v>
       </c>
       <c r="X88" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B89" t="s">
         <v>1371</v>
       </c>
-      <c r="B89" t="s">
+      <c r="D89" t="s">
         <v>1372</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
+        <v>967</v>
+      </c>
+      <c r="F89" t="s">
         <v>1373</v>
       </c>
-      <c r="E89" t="s">
-        <v>968</v>
-      </c>
-      <c r="F89" t="s">
+      <c r="J89" t="s">
         <v>1374</v>
       </c>
-      <c r="J89" t="s">
+      <c r="K89" t="s">
         <v>1375</v>
       </c>
-      <c r="K89" t="s">
+      <c r="L89" s="1" t="s">
         <v>1376</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>1377</v>
       </c>
       <c r="R89" t="s">
         <v>89</v>
       </c>
       <c r="S89" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="T89" s="2">
         <v>370</v>
@@ -9430,56 +9430,56 @@
         <v>3</v>
       </c>
       <c r="X89" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B90" t="s">
         <v>1371</v>
       </c>
-      <c r="B90" t="s">
-        <v>1372</v>
-      </c>
       <c r="D90" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E90" t="s">
         <v>1379</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>1380</v>
       </c>
-      <c r="F90" t="s">
+      <c r="H90" t="s">
         <v>1381</v>
       </c>
-      <c r="H90" t="s">
+      <c r="J90" t="s">
         <v>1382</v>
       </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
         <v>1383</v>
       </c>
-      <c r="K90" t="s">
+      <c r="L90" s="1" t="s">
         <v>1384</v>
-      </c>
-      <c r="L90" s="1" t="s">
-        <v>1385</v>
       </c>
       <c r="R90" t="s">
         <v>89</v>
       </c>
       <c r="S90" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="W90" s="2">
         <v>3</v>
       </c>
       <c r="X90" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>832</v>
+      </c>
+      <c r="B91" t="s">
         <v>833</v>
-      </c>
-      <c r="B91" t="s">
-        <v>834</v>
       </c>
       <c r="D91">
         <v>1475</v>
@@ -9491,13 +9491,13 @@
         <v>192</v>
       </c>
       <c r="J91" t="s">
+        <v>834</v>
+      </c>
+      <c r="K91" t="s">
         <v>835</v>
       </c>
-      <c r="K91" t="s">
+      <c r="L91" s="1" t="s">
         <v>836</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>837</v>
       </c>
       <c r="R91" t="s">
         <v>31</v>
@@ -9515,33 +9515,33 @@
         <v>2</v>
       </c>
       <c r="X91" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>832</v>
+      </c>
+      <c r="B92" t="s">
         <v>833</v>
-      </c>
-      <c r="B92" t="s">
-        <v>834</v>
       </c>
       <c r="D92">
         <v>1476</v>
       </c>
       <c r="E92" t="s">
+        <v>837</v>
+      </c>
+      <c r="F92" t="s">
         <v>838</v>
       </c>
-      <c r="F92" t="s">
+      <c r="J92" t="s">
         <v>839</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>840</v>
       </c>
-      <c r="K92" t="s">
+      <c r="L92" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>842</v>
       </c>
       <c r="R92" t="s">
         <v>31</v>
@@ -9559,18 +9559,18 @@
         <v>2</v>
       </c>
       <c r="X92" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>832</v>
+      </c>
+      <c r="B93" t="s">
         <v>833</v>
       </c>
-      <c r="B93" t="s">
-        <v>834</v>
-      </c>
       <c r="D93" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E93" t="s">
         <v>95</v>
@@ -9579,13 +9579,13 @@
         <v>96</v>
       </c>
       <c r="J93" t="s">
+        <v>843</v>
+      </c>
+      <c r="K93" t="s">
         <v>844</v>
       </c>
-      <c r="K93" t="s">
+      <c r="L93" s="1" t="s">
         <v>845</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>846</v>
       </c>
       <c r="R93" t="s">
         <v>31</v>
@@ -9603,33 +9603,33 @@
         <v>2</v>
       </c>
       <c r="X93" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>832</v>
+      </c>
+      <c r="B94" t="s">
         <v>833</v>
       </c>
-      <c r="B94" t="s">
-        <v>834</v>
-      </c>
       <c r="D94" t="s">
+        <v>846</v>
+      </c>
+      <c r="E94" t="s">
         <v>847</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>848</v>
       </c>
-      <c r="F94" t="s">
+      <c r="J94" t="s">
         <v>849</v>
-      </c>
-      <c r="J94" t="s">
-        <v>850</v>
       </c>
       <c r="K94" t="s">
         <v>165</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R94" t="s">
         <v>31</v>
@@ -9647,15 +9647,15 @@
         <v>2</v>
       </c>
       <c r="X94" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>832</v>
+      </c>
+      <c r="B95" t="s">
         <v>833</v>
-      </c>
-      <c r="B95" t="s">
-        <v>834</v>
       </c>
       <c r="D95" t="s">
         <v>66</v>
@@ -9667,13 +9667,13 @@
         <v>567</v>
       </c>
       <c r="J95" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K95" t="s">
         <v>353</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R95" t="s">
         <v>31</v>
@@ -9691,24 +9691,24 @@
         <v>2</v>
       </c>
       <c r="X95" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>832</v>
+      </c>
+      <c r="B96" t="s">
         <v>833</v>
-      </c>
-      <c r="B96" t="s">
-        <v>834</v>
       </c>
       <c r="D96" t="s">
         <v>66</v>
       </c>
       <c r="E96" t="s">
+        <v>853</v>
+      </c>
+      <c r="F96" t="s">
         <v>854</v>
-      </c>
-      <c r="F96" t="s">
-        <v>855</v>
       </c>
       <c r="J96" t="s">
         <v>54</v>
@@ -9717,7 +9717,7 @@
         <v>54</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="R96" t="s">
         <v>31</v>
@@ -9735,24 +9735,24 @@
         <v>2</v>
       </c>
       <c r="X96" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>832</v>
+      </c>
+      <c r="B97" t="s">
         <v>833</v>
       </c>
-      <c r="B97" t="s">
-        <v>834</v>
-      </c>
       <c r="D97" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E97" t="s">
         <v>51</v>
       </c>
       <c r="F97" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="J97" t="s">
         <v>434</v>
@@ -9761,13 +9761,13 @@
         <v>435</v>
       </c>
       <c r="L97" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="R97" t="s">
+        <v>31</v>
+      </c>
+      <c r="S97" t="s">
         <v>859</v>
-      </c>
-      <c r="R97" t="s">
-        <v>31</v>
-      </c>
-      <c r="S97" t="s">
-        <v>860</v>
       </c>
       <c r="T97" s="2">
         <v>171</v>
@@ -9779,33 +9779,33 @@
         <v>2</v>
       </c>
       <c r="X97" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>832</v>
+      </c>
+      <c r="B98" t="s">
         <v>833</v>
-      </c>
-      <c r="B98" t="s">
-        <v>834</v>
       </c>
       <c r="D98" t="s">
         <v>670</v>
       </c>
       <c r="E98" t="s">
+        <v>860</v>
+      </c>
+      <c r="F98" t="s">
         <v>861</v>
       </c>
-      <c r="F98" t="s">
+      <c r="J98" t="s">
         <v>862</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>863</v>
       </c>
-      <c r="K98" t="s">
+      <c r="L98" s="1" t="s">
         <v>864</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>865</v>
       </c>
       <c r="R98" t="s">
         <v>31</v>
@@ -9823,18 +9823,18 @@
         <v>2</v>
       </c>
       <c r="X98" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>865</v>
+      </c>
+      <c r="B99" t="s">
         <v>866</v>
       </c>
-      <c r="B99" t="s">
+      <c r="D99" t="s">
         <v>867</v>
-      </c>
-      <c r="D99" t="s">
-        <v>868</v>
       </c>
       <c r="E99" t="s">
         <v>627</v>
@@ -9843,10 +9843,10 @@
         <v>628</v>
       </c>
       <c r="J99" t="s">
+        <v>868</v>
+      </c>
+      <c r="L99" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>870</v>
       </c>
       <c r="R99" t="s">
         <v>31</v>
@@ -9864,15 +9864,15 @@
         <v>2</v>
       </c>
       <c r="X99" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="100" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B100" t="s">
         <v>1387</v>
-      </c>
-      <c r="B100" t="s">
-        <v>1388</v>
       </c>
       <c r="D100" t="s">
         <v>670</v>
@@ -9884,10 +9884,10 @@
         <v>96</v>
       </c>
       <c r="J100" t="s">
+        <v>1388</v>
+      </c>
+      <c r="L100" s="1" t="s">
         <v>1389</v>
-      </c>
-      <c r="L100" s="1" t="s">
-        <v>1390</v>
       </c>
       <c r="R100" t="s">
         <v>31</v>
@@ -9905,18 +9905,18 @@
         <v>3</v>
       </c>
       <c r="X100" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B101" t="s">
         <v>1387</v>
       </c>
-      <c r="B101" t="s">
-        <v>1388</v>
-      </c>
       <c r="D101" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="E101" t="s">
         <v>191</v>
@@ -9925,16 +9925,16 @@
         <v>192</v>
       </c>
       <c r="J101" t="s">
+        <v>1392</v>
+      </c>
+      <c r="L101" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="L101" s="1" t="s">
+      <c r="M101" t="s">
         <v>1394</v>
       </c>
-      <c r="M101" t="s">
+      <c r="N101" t="s">
         <v>1395</v>
-      </c>
-      <c r="N101" t="s">
-        <v>1396</v>
       </c>
       <c r="R101" t="s">
         <v>31</v>
@@ -9952,7 +9952,7 @@
         <v>3</v>
       </c>
       <c r="X101" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="102" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10403,7 +10403,7 @@
         <v>431</v>
       </c>
       <c r="B112" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D112">
         <v>1447</v>
@@ -10412,22 +10412,22 @@
         <v>59</v>
       </c>
       <c r="F112" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H112" t="s">
         <v>1398</v>
-      </c>
-      <c r="H112" t="s">
-        <v>1399</v>
       </c>
       <c r="J112" t="s">
         <v>217</v>
       </c>
       <c r="K112" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="N112" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="R112" t="s">
         <v>89</v>
@@ -10445,7 +10445,7 @@
         <v>3</v>
       </c>
       <c r="X112" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10453,7 +10453,7 @@
         <v>431</v>
       </c>
       <c r="B113" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D113">
         <v>1456</v>
@@ -10462,31 +10462,31 @@
         <v>59</v>
       </c>
       <c r="F113" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="H113" t="s">
+        <v>1400</v>
+      </c>
+      <c r="J113" t="s">
         <v>1401</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>1402</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="L113" s="1" t="s">
+      <c r="M113" t="s">
         <v>1404</v>
       </c>
-      <c r="M113" t="s">
-        <v>1405</v>
-      </c>
       <c r="N113" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="R113" t="s">
         <v>89</v>
       </c>
       <c r="S113" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="T113" s="2">
         <v>833</v>
@@ -10498,33 +10498,33 @@
         <v>3</v>
       </c>
       <c r="X113" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="114" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B114" t="s">
         <v>1407</v>
       </c>
-      <c r="B114" t="s">
+      <c r="D114" t="s">
         <v>1408</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>1409</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>1410</v>
       </c>
-      <c r="F114" t="s">
+      <c r="J114" t="s">
         <v>1411</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>1412</v>
       </c>
-      <c r="K114" t="s">
+      <c r="L114" s="1" t="s">
         <v>1413</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>1414</v>
       </c>
       <c r="R114" t="s">
         <v>89</v>
@@ -10533,27 +10533,27 @@
         <v>89</v>
       </c>
       <c r="T114" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="U114" s="2" t="s">
         <v>1415</v>
-      </c>
-      <c r="U114" s="2" t="s">
-        <v>1416</v>
       </c>
       <c r="W114" s="2">
         <v>3</v>
       </c>
       <c r="X114" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B115" t="s">
         <v>1407</v>
       </c>
-      <c r="B115" t="s">
-        <v>1408</v>
-      </c>
       <c r="D115" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="E115" t="s">
         <v>621</v>
@@ -10565,7 +10565,7 @@
         <v>164</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="R115" t="s">
         <v>31</v>
@@ -10583,99 +10583,99 @@
         <v>3</v>
       </c>
       <c r="X115" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="116" spans="1:24" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B116" s="7" t="s">
         <v>1407</v>
       </c>
-      <c r="B116" s="7" t="s">
-        <v>1408</v>
-      </c>
       <c r="D116" s="7" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E116" s="7" t="s">
         <v>1419</v>
       </c>
-      <c r="E116" s="7" t="s">
+      <c r="F116" s="7" t="s">
         <v>1420</v>
       </c>
-      <c r="F116" s="7" t="s">
+      <c r="J116" s="7" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K116" s="7" t="s">
         <v>1421</v>
       </c>
-      <c r="J116" s="7" t="s">
+      <c r="L116" s="8" t="s">
+        <v>1422</v>
+      </c>
+      <c r="M116" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="R116" s="7" t="s">
         <v>1665</v>
-      </c>
-      <c r="K116" s="7" t="s">
-        <v>1422</v>
-      </c>
-      <c r="L116" s="8" t="s">
-        <v>1423</v>
-      </c>
-      <c r="M116" s="8" t="s">
-        <v>1424</v>
-      </c>
-      <c r="R116" s="7" t="s">
-        <v>1666</v>
       </c>
       <c r="S116" s="7" t="s">
         <v>514</v>
       </c>
       <c r="T116" s="9" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="U116" s="9" t="s">
         <v>374</v>
       </c>
       <c r="V116" s="9"/>
       <c r="W116" s="9" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X116" s="7" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B117" t="s">
         <v>1407</v>
       </c>
-      <c r="B117" t="s">
-        <v>1408</v>
-      </c>
       <c r="D117" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E117" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F117" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J117" t="s">
         <v>1426</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>1427</v>
       </c>
-      <c r="K117" t="s">
+      <c r="L117" s="1" t="s">
         <v>1428</v>
-      </c>
-      <c r="L117" s="1" t="s">
-        <v>1429</v>
       </c>
       <c r="R117" s="5" t="s">
         <v>408</v>
       </c>
       <c r="S117" t="s">
+        <v>1429</v>
+      </c>
+      <c r="T117" s="2" t="s">
         <v>1430</v>
       </c>
-      <c r="T117" s="2" t="s">
+      <c r="U117" s="2" t="s">
         <v>1431</v>
       </c>
-      <c r="U117" s="2" t="s">
-        <v>1432</v>
-      </c>
       <c r="W117" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X117" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="118" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10683,7 +10683,7 @@
         <v>431</v>
       </c>
       <c r="B118" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D118" t="s">
         <v>693</v>
@@ -10695,19 +10695,19 @@
         <v>96</v>
       </c>
       <c r="J118" t="s">
+        <v>871</v>
+      </c>
+      <c r="K118" t="s">
         <v>872</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="L118" s="1" t="s">
+      <c r="R118" t="s">
+        <v>31</v>
+      </c>
+      <c r="S118" t="s">
         <v>874</v>
-      </c>
-      <c r="R118" t="s">
-        <v>31</v>
-      </c>
-      <c r="S118" t="s">
-        <v>875</v>
       </c>
       <c r="T118" s="2">
         <v>84</v>
@@ -10719,7 +10719,7 @@
         <v>2</v>
       </c>
       <c r="X118" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="119" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10727,10 +10727,10 @@
         <v>431</v>
       </c>
       <c r="B119" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D119" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E119" t="s">
         <v>59</v>
@@ -10745,13 +10745,13 @@
         <v>225</v>
       </c>
       <c r="L119" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="R119" t="s">
+        <v>31</v>
+      </c>
+      <c r="S119" t="s">
         <v>877</v>
-      </c>
-      <c r="R119" t="s">
-        <v>31</v>
-      </c>
-      <c r="S119" t="s">
-        <v>878</v>
       </c>
       <c r="T119" s="2">
         <v>177</v>
@@ -10763,7 +10763,7 @@
         <v>2</v>
       </c>
       <c r="X119" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="120" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10771,25 +10771,25 @@
         <v>431</v>
       </c>
       <c r="B120" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D120" t="s">
+        <v>878</v>
+      </c>
+      <c r="E120" t="s">
         <v>879</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>880</v>
       </c>
-      <c r="F120" t="s">
+      <c r="J120" t="s">
         <v>881</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>882</v>
       </c>
-      <c r="K120" t="s">
+      <c r="L120" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="L120" s="1" t="s">
-        <v>884</v>
       </c>
       <c r="R120" t="s">
         <v>31</v>
@@ -10807,7 +10807,7 @@
         <v>2</v>
       </c>
       <c r="X120" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="121" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10815,7 +10815,7 @@
         <v>431</v>
       </c>
       <c r="B121" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D121" t="s">
         <v>58</v>
@@ -10827,13 +10827,13 @@
         <v>35</v>
       </c>
       <c r="J121" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K121" t="s">
         <v>346</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="R121" t="s">
         <v>31</v>
@@ -10851,7 +10851,7 @@
         <v>2</v>
       </c>
       <c r="X121" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10859,10 +10859,10 @@
         <v>431</v>
       </c>
       <c r="B122" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D122" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E122" t="s">
         <v>95</v>
@@ -10871,13 +10871,13 @@
         <v>96</v>
       </c>
       <c r="J122" t="s">
+        <v>887</v>
+      </c>
+      <c r="K122" t="s">
         <v>888</v>
       </c>
-      <c r="K122" t="s">
+      <c r="L122" s="1" t="s">
         <v>889</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>890</v>
       </c>
       <c r="R122" t="s">
         <v>31</v>
@@ -10895,7 +10895,7 @@
         <v>2</v>
       </c>
       <c r="X122" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10903,10 +10903,10 @@
         <v>431</v>
       </c>
       <c r="B123" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D123" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E123" t="s">
         <v>645</v>
@@ -10915,13 +10915,13 @@
         <v>646</v>
       </c>
       <c r="J123" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="K123" t="s">
         <v>346</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="R123" t="s">
         <v>31</v>
@@ -10939,7 +10939,7 @@
         <v>2</v>
       </c>
       <c r="X123" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="124" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10947,10 +10947,10 @@
         <v>431</v>
       </c>
       <c r="B124" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D124" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E124" t="s">
         <v>95</v>
@@ -10959,13 +10959,13 @@
         <v>96</v>
       </c>
       <c r="J124" t="s">
+        <v>892</v>
+      </c>
+      <c r="K124" t="s">
         <v>893</v>
       </c>
-      <c r="K124" t="s">
+      <c r="L124" s="1" t="s">
         <v>894</v>
-      </c>
-      <c r="L124" s="1" t="s">
-        <v>895</v>
       </c>
       <c r="R124" t="s">
         <v>31</v>
@@ -10983,7 +10983,7 @@
         <v>2</v>
       </c>
       <c r="X124" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10991,7 +10991,7 @@
         <v>431</v>
       </c>
       <c r="B125" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D125" t="s">
         <v>651</v>
@@ -11000,22 +11000,22 @@
         <v>59</v>
       </c>
       <c r="F125" t="s">
+        <v>895</v>
+      </c>
+      <c r="J125" t="s">
         <v>896</v>
-      </c>
-      <c r="J125" t="s">
-        <v>897</v>
       </c>
       <c r="K125" t="s">
         <v>185</v>
       </c>
       <c r="L125" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="R125" t="s">
+        <v>31</v>
+      </c>
+      <c r="S125" t="s">
         <v>898</v>
-      </c>
-      <c r="R125" t="s">
-        <v>31</v>
-      </c>
-      <c r="S125" t="s">
-        <v>899</v>
       </c>
       <c r="T125" s="2">
         <v>41</v>
@@ -11027,7 +11027,7 @@
         <v>2</v>
       </c>
       <c r="X125" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="126" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11554,25 +11554,25 @@
     </row>
     <row r="138" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>899</v>
+      </c>
+      <c r="B138" t="s">
         <v>900</v>
       </c>
-      <c r="B138" t="s">
+      <c r="D138" t="s">
         <v>901</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
         <v>902</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>903</v>
       </c>
-      <c r="F138" t="s">
+      <c r="J138" t="s">
         <v>904</v>
       </c>
-      <c r="J138" t="s">
+      <c r="L138" s="1" t="s">
         <v>905</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>906</v>
       </c>
       <c r="R138" t="s">
         <v>31</v>
@@ -11590,18 +11590,18 @@
         <v>2</v>
       </c>
       <c r="X138" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="139" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>899</v>
+      </c>
+      <c r="B139" t="s">
         <v>900</v>
       </c>
-      <c r="B139" t="s">
-        <v>901</v>
-      </c>
       <c r="D139" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="E139" t="s">
         <v>191</v>
@@ -11610,13 +11610,13 @@
         <v>192</v>
       </c>
       <c r="J139" t="s">
+        <v>1433</v>
+      </c>
+      <c r="K139" t="s">
         <v>1434</v>
       </c>
-      <c r="K139" t="s">
+      <c r="L139" s="1" t="s">
         <v>1435</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>1436</v>
       </c>
       <c r="R139" t="s">
         <v>31</v>
@@ -11634,30 +11634,30 @@
         <v>3</v>
       </c>
       <c r="X139" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="140" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B140" t="s">
         <v>1437</v>
       </c>
-      <c r="B140" t="s">
+      <c r="D140" t="s">
         <v>1438</v>
-      </c>
-      <c r="D140" t="s">
-        <v>1439</v>
       </c>
       <c r="E140" t="s">
         <v>83</v>
       </c>
       <c r="F140" t="s">
+        <v>1439</v>
+      </c>
+      <c r="J140" t="s">
         <v>1440</v>
       </c>
-      <c r="J140" t="s">
+      <c r="L140" s="1" t="s">
         <v>1441</v>
-      </c>
-      <c r="L140" s="1" t="s">
-        <v>1442</v>
       </c>
       <c r="R140" t="s">
         <v>89</v>
@@ -11666,16 +11666,16 @@
         <v>89</v>
       </c>
       <c r="T140" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="U140" s="2" t="s">
         <v>1443</v>
-      </c>
-      <c r="U140" s="2" t="s">
-        <v>1444</v>
       </c>
       <c r="W140" s="2">
         <v>3</v>
       </c>
       <c r="X140" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="141" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11683,22 +11683,22 @@
         <v>221</v>
       </c>
       <c r="B141" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D141" t="s">
         <v>433</v>
       </c>
       <c r="F141" t="s">
+        <v>1445</v>
+      </c>
+      <c r="J141" t="s">
         <v>1446</v>
       </c>
-      <c r="J141" t="s">
+      <c r="K141" t="s">
         <v>1447</v>
       </c>
-      <c r="K141" t="s">
+      <c r="L141" s="1" t="s">
         <v>1448</v>
-      </c>
-      <c r="L141" s="1" t="s">
-        <v>1449</v>
       </c>
       <c r="R141" t="s">
         <v>31</v>
@@ -11716,7 +11716,7 @@
         <v>3</v>
       </c>
       <c r="X141" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="142" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11724,7 +11724,7 @@
         <v>221</v>
       </c>
       <c r="B142" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D142" t="s">
         <v>479</v>
@@ -11736,10 +11736,10 @@
         <v>96</v>
       </c>
       <c r="J142" t="s">
+        <v>1449</v>
+      </c>
+      <c r="L142" s="1" t="s">
         <v>1450</v>
-      </c>
-      <c r="L142" s="1" t="s">
-        <v>1451</v>
       </c>
       <c r="R142" t="s">
         <v>31</v>
@@ -11757,18 +11757,18 @@
         <v>3</v>
       </c>
       <c r="X142" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="143" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B143" t="s">
         <v>1452</v>
       </c>
-      <c r="B143" t="s">
-        <v>1453</v>
-      </c>
       <c r="D143" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E143" t="s">
         <v>95</v>
@@ -11777,10 +11777,10 @@
         <v>96</v>
       </c>
       <c r="J143" t="s">
+        <v>1453</v>
+      </c>
+      <c r="L143" s="1" t="s">
         <v>1454</v>
-      </c>
-      <c r="L143" s="1" t="s">
-        <v>1455</v>
       </c>
       <c r="R143" t="s">
         <v>31</v>
@@ -11798,33 +11798,33 @@
         <v>3</v>
       </c>
       <c r="X143" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="144" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B144" t="s">
         <v>1452</v>
-      </c>
-      <c r="B144" t="s">
-        <v>1453</v>
       </c>
       <c r="D144" t="s">
         <v>811</v>
       </c>
       <c r="E144" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J144" t="s">
         <v>1456</v>
       </c>
-      <c r="F144" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J144" t="s">
+      <c r="K144" t="s">
         <v>1457</v>
       </c>
-      <c r="K144" t="s">
+      <c r="L144" s="1" t="s">
         <v>1458</v>
-      </c>
-      <c r="L144" s="1" t="s">
-        <v>1459</v>
       </c>
       <c r="R144" t="s">
         <v>89</v>
@@ -11842,15 +11842,15 @@
         <v>3</v>
       </c>
       <c r="X144" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="145" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B145" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D145" t="s">
         <v>749</v>
@@ -11862,19 +11862,19 @@
         <v>60</v>
       </c>
       <c r="J145" t="s">
+        <v>1460</v>
+      </c>
+      <c r="K145" t="s">
         <v>1461</v>
       </c>
-      <c r="K145" t="s">
+      <c r="L145" s="1" t="s">
         <v>1462</v>
       </c>
-      <c r="L145" s="1" t="s">
+      <c r="R145" t="s">
+        <v>31</v>
+      </c>
+      <c r="S145" t="s">
         <v>1463</v>
-      </c>
-      <c r="R145" t="s">
-        <v>31</v>
-      </c>
-      <c r="S145" t="s">
-        <v>1464</v>
       </c>
       <c r="T145" s="2">
         <v>240</v>
@@ -11886,39 +11886,39 @@
         <v>3</v>
       </c>
       <c r="X145" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="146" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B146" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D146" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="E146" t="s">
         <v>59</v>
       </c>
       <c r="F146" t="s">
+        <v>1465</v>
+      </c>
+      <c r="H146" t="s">
         <v>1466</v>
       </c>
-      <c r="H146" t="s">
+      <c r="J146" t="s">
         <v>1467</v>
       </c>
-      <c r="J146" t="s">
+      <c r="K146" t="s">
         <v>1468</v>
       </c>
-      <c r="K146" t="s">
+      <c r="L146" s="1" t="s">
         <v>1469</v>
       </c>
-      <c r="L146" s="1" t="s">
+      <c r="M146" t="s">
         <v>1470</v>
-      </c>
-      <c r="M146" t="s">
-        <v>1471</v>
       </c>
       <c r="R146" t="s">
         <v>31</v>
@@ -11936,7 +11936,7 @@
         <v>3</v>
       </c>
       <c r="X146" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="147" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11947,7 +11947,7 @@
         <v>305</v>
       </c>
       <c r="C147" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D147" t="s">
         <v>306</v>
@@ -11997,7 +11997,7 @@
         <v>305</v>
       </c>
       <c r="C148" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D148" t="s">
         <v>314</v>
@@ -12041,7 +12041,7 @@
         <v>305</v>
       </c>
       <c r="C149" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D149" t="s">
         <v>320</v>
@@ -12088,7 +12088,7 @@
         <v>305</v>
       </c>
       <c r="C150" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D150" t="s">
         <v>329</v>
@@ -12135,7 +12135,7 @@
         <v>305</v>
       </c>
       <c r="C151" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D151" t="s">
         <v>335</v>
@@ -12188,7 +12188,7 @@
         <v>305</v>
       </c>
       <c r="C152" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D152" t="s">
         <v>335</v>
@@ -12241,7 +12241,7 @@
         <v>305</v>
       </c>
       <c r="C153" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D153" t="s">
         <v>335</v>
@@ -12294,7 +12294,7 @@
         <v>305</v>
       </c>
       <c r="C154" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D154" t="s">
         <v>335</v>
@@ -12347,7 +12347,7 @@
         <v>305</v>
       </c>
       <c r="C155" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D155" t="s">
         <v>306</v>
@@ -12406,7 +12406,7 @@
         <v>305</v>
       </c>
       <c r="C156" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D156" t="s">
         <v>306</v>
@@ -12427,7 +12427,7 @@
         <v>368</v>
       </c>
       <c r="L156" s="6" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="M156" t="s">
         <v>363</v>
@@ -12462,7 +12462,7 @@
         <v>305</v>
       </c>
       <c r="C157" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D157" t="s">
         <v>370</v>
@@ -12509,7 +12509,7 @@
         <v>305</v>
       </c>
       <c r="C158" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D158" t="s">
         <v>375</v>
@@ -12559,7 +12559,7 @@
         <v>383</v>
       </c>
       <c r="C159" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D159" t="s">
         <v>384</v>
@@ -12603,7 +12603,7 @@
         <v>383</v>
       </c>
       <c r="C160" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D160" t="s">
         <v>388</v>
@@ -12650,7 +12650,7 @@
         <v>383</v>
       </c>
       <c r="C161" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D161" t="s">
         <v>392</v>
@@ -12697,7 +12697,7 @@
         <v>383</v>
       </c>
       <c r="C162" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D162" t="s">
         <v>396</v>
@@ -12747,7 +12747,7 @@
         <v>383</v>
       </c>
       <c r="C163" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D163" t="s">
         <v>402</v>
@@ -12791,7 +12791,7 @@
         <v>383</v>
       </c>
       <c r="C164" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D164" t="s">
         <v>405</v>
@@ -12835,7 +12835,7 @@
         <v>383</v>
       </c>
       <c r="C165" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D165" t="s">
         <v>409</v>
@@ -12879,7 +12879,7 @@
         <v>383</v>
       </c>
       <c r="C166" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D166" t="s">
         <v>409</v>
@@ -12923,7 +12923,7 @@
         <v>383</v>
       </c>
       <c r="C167" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D167" t="s">
         <v>409</v>
@@ -12967,7 +12967,7 @@
         <v>383</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D168" s="7" t="s">
         <v>415</v>
@@ -13015,7 +13015,7 @@
         <v>383</v>
       </c>
       <c r="C169" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D169" t="s">
         <v>418</v>
@@ -13059,7 +13059,7 @@
         <v>383</v>
       </c>
       <c r="C170" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D170" t="s">
         <v>421</v>
@@ -13103,22 +13103,22 @@
         <v>383</v>
       </c>
       <c r="D171" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E171" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F171" t="s">
         <v>1472</v>
       </c>
-      <c r="E171" t="s">
-        <v>1456</v>
-      </c>
-      <c r="F171" t="s">
+      <c r="J171" t="s">
         <v>1473</v>
       </c>
-      <c r="J171" t="s">
+      <c r="L171" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="L171" s="1" t="s">
+      <c r="M171" t="s">
         <v>1475</v>
-      </c>
-      <c r="M171" t="s">
-        <v>1476</v>
       </c>
       <c r="R171" t="s">
         <v>31</v>
@@ -13147,19 +13147,19 @@
         <v>383</v>
       </c>
       <c r="D172" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E172" t="s">
         <v>1477</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>1478</v>
       </c>
-      <c r="F172" t="s">
+      <c r="J172" t="s">
+        <v>1453</v>
+      </c>
+      <c r="L172" s="1" t="s">
         <v>1479</v>
-      </c>
-      <c r="J172" t="s">
-        <v>1454</v>
-      </c>
-      <c r="L172" s="1" t="s">
-        <v>1480</v>
       </c>
       <c r="R172" t="s">
         <v>31</v>
@@ -13182,60 +13182,60 @@
     </row>
     <row r="173" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B173" t="s">
         <v>1144</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C173" t="s">
         <v>1145</v>
       </c>
-      <c r="C173" t="s">
-        <v>1146</v>
-      </c>
       <c r="D173" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E173" t="s">
         <v>453</v>
       </c>
       <c r="F173" t="s">
+        <v>1146</v>
+      </c>
+      <c r="J173" t="s">
         <v>1147</v>
       </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>1148</v>
       </c>
-      <c r="K173" t="s">
+      <c r="L173" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="L173" s="1" t="s">
+      <c r="R173" t="s">
+        <v>31</v>
+      </c>
+      <c r="S173" t="s">
         <v>1150</v>
       </c>
-      <c r="R173" t="s">
-        <v>31</v>
-      </c>
-      <c r="S173" t="s">
+      <c r="T173" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="T173" s="2" t="s">
+      <c r="U173" s="2" t="s">
         <v>1152</v>
-      </c>
-      <c r="U173" s="2" t="s">
-        <v>1153</v>
       </c>
       <c r="W173" s="2">
         <v>2</v>
       </c>
       <c r="X173" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="174" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B174" t="s">
         <v>1144</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>1145</v>
-      </c>
-      <c r="C174" t="s">
-        <v>1146</v>
       </c>
       <c r="D174" t="s">
         <v>370</v>
@@ -13244,19 +13244,19 @@
         <v>453</v>
       </c>
       <c r="F174" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H174" t="s">
         <v>1154</v>
       </c>
-      <c r="H174" t="s">
+      <c r="J174" t="s">
         <v>1155</v>
-      </c>
-      <c r="J174" t="s">
-        <v>1156</v>
       </c>
       <c r="K174" t="s">
         <v>165</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="R174" t="s">
         <v>89</v>
@@ -13268,18 +13268,18 @@
         <v>2</v>
       </c>
       <c r="X174" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="175" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B175" t="s">
         <v>1144</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>1145</v>
-      </c>
-      <c r="C175" t="s">
-        <v>1146</v>
       </c>
       <c r="D175" t="s">
         <v>402</v>
@@ -13291,60 +13291,60 @@
         <v>485</v>
       </c>
       <c r="J175" t="s">
+        <v>1157</v>
+      </c>
+      <c r="K175" t="s">
         <v>1158</v>
       </c>
-      <c r="K175" t="s">
+      <c r="L175" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="L175" s="1" t="s">
+      <c r="R175" t="s">
+        <v>31</v>
+      </c>
+      <c r="S175" t="s">
         <v>1160</v>
-      </c>
-      <c r="R175" t="s">
-        <v>31</v>
-      </c>
-      <c r="S175" t="s">
-        <v>1161</v>
       </c>
       <c r="T175" s="2">
         <v>58</v>
       </c>
       <c r="U175" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="W175" s="2">
         <v>2</v>
       </c>
       <c r="X175" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="176" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B176" t="s">
         <v>1144</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
         <v>1145</v>
-      </c>
-      <c r="C176" t="s">
-        <v>1146</v>
       </c>
       <c r="D176" t="s">
         <v>402</v>
       </c>
       <c r="E176" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F176" t="s">
         <v>1163</v>
-      </c>
-      <c r="F176" t="s">
-        <v>1164</v>
       </c>
       <c r="J176" t="s">
         <v>746</v>
       </c>
       <c r="K176" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L176" s="1" t="s">
         <v>1165</v>
-      </c>
-      <c r="L176" s="1" t="s">
-        <v>1166</v>
       </c>
       <c r="R176" t="s">
         <v>31</v>
@@ -13356,42 +13356,42 @@
         <v>2</v>
       </c>
       <c r="X176" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="177" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B177" t="s">
         <v>1144</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C177" t="s">
         <v>1145</v>
       </c>
-      <c r="C177" t="s">
-        <v>1146</v>
-      </c>
       <c r="D177" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E177" t="s">
         <v>453</v>
       </c>
       <c r="F177" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H177" t="s">
         <v>1167</v>
       </c>
-      <c r="H177" t="s">
+      <c r="J177" t="s">
         <v>1168</v>
       </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>1169</v>
       </c>
-      <c r="K177" t="s">
+      <c r="L177" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="L177" s="1" t="s">
+      <c r="N177" s="1" t="s">
         <v>1171</v>
-      </c>
-      <c r="N177" s="1" t="s">
-        <v>1172</v>
       </c>
       <c r="R177" t="s">
         <v>89</v>
@@ -13403,21 +13403,21 @@
         <v>2</v>
       </c>
       <c r="X177" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="178" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B178" t="s">
         <v>1144</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>1145</v>
       </c>
-      <c r="C178" t="s">
-        <v>1146</v>
-      </c>
       <c r="D178" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E178" t="s">
         <v>95</v>
@@ -13426,13 +13426,13 @@
         <v>96</v>
       </c>
       <c r="J178" t="s">
+        <v>1172</v>
+      </c>
+      <c r="K178" t="s">
         <v>1173</v>
       </c>
-      <c r="K178" t="s">
+      <c r="L178" s="1" t="s">
         <v>1174</v>
-      </c>
-      <c r="L178" s="1" t="s">
-        <v>1175</v>
       </c>
       <c r="R178" t="s">
         <v>31</v>
@@ -13441,45 +13441,45 @@
         <v>514</v>
       </c>
       <c r="T178" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="U178" s="2" t="s">
         <v>1176</v>
-      </c>
-      <c r="U178" s="2" t="s">
-        <v>1177</v>
       </c>
       <c r="W178" s="2">
         <v>2</v>
       </c>
       <c r="X178" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="179" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B179" t="s">
         <v>1144</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
         <v>1145</v>
       </c>
-      <c r="C179" t="s">
-        <v>1146</v>
-      </c>
       <c r="D179" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="E179" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F179" t="s">
         <v>1178</v>
       </c>
-      <c r="F179" t="s">
+      <c r="J179" t="s">
         <v>1179</v>
       </c>
-      <c r="J179" t="s">
+      <c r="K179" t="s">
         <v>1180</v>
       </c>
-      <c r="K179" t="s">
+      <c r="L179" s="1" t="s">
         <v>1181</v>
-      </c>
-      <c r="L179" s="1" t="s">
-        <v>1182</v>
       </c>
       <c r="R179" t="s">
         <v>31</v>
@@ -13488,30 +13488,30 @@
         <v>514</v>
       </c>
       <c r="T179" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="U179" s="2" t="s">
         <v>1183</v>
-      </c>
-      <c r="U179" s="2" t="s">
-        <v>1184</v>
       </c>
       <c r="W179" s="2">
         <v>2</v>
       </c>
       <c r="X179" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="180" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B180" t="s">
         <v>1144</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>1145</v>
       </c>
-      <c r="C180" t="s">
-        <v>1146</v>
-      </c>
       <c r="D180" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="E180" t="s">
         <v>191</v>
@@ -13520,13 +13520,13 @@
         <v>192</v>
       </c>
       <c r="J180" t="s">
+        <v>1184</v>
+      </c>
+      <c r="K180" t="s">
         <v>1185</v>
       </c>
-      <c r="K180" t="s">
+      <c r="L180" s="1" t="s">
         <v>1186</v>
-      </c>
-      <c r="L180" s="1" t="s">
-        <v>1187</v>
       </c>
       <c r="R180" t="s">
         <v>31</v>
@@ -13535,16 +13535,16 @@
         <v>514</v>
       </c>
       <c r="T180" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="U180" s="2" t="s">
         <v>1188</v>
-      </c>
-      <c r="U180" s="2" t="s">
-        <v>1189</v>
       </c>
       <c r="W180" s="2">
         <v>2</v>
       </c>
       <c r="X180" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="181" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13590,28 +13590,28 @@
     </row>
     <row r="182" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B182" t="s">
         <v>1481</v>
       </c>
-      <c r="B182" t="s">
-        <v>1482</v>
-      </c>
       <c r="D182" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E182" t="s">
         <v>197</v>
       </c>
       <c r="F182" t="s">
+        <v>1482</v>
+      </c>
+      <c r="J182" t="s">
         <v>1483</v>
       </c>
-      <c r="J182" t="s">
+      <c r="K182" t="s">
         <v>1484</v>
       </c>
-      <c r="K182" t="s">
+      <c r="L182" s="1" t="s">
         <v>1485</v>
-      </c>
-      <c r="L182" s="1" t="s">
-        <v>1486</v>
       </c>
       <c r="R182" t="s">
         <v>89</v>
@@ -13629,15 +13629,15 @@
         <v>3</v>
       </c>
       <c r="X182" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="183" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>906</v>
+      </c>
+      <c r="B183" t="s">
         <v>907</v>
-      </c>
-      <c r="B183" t="s">
-        <v>908</v>
       </c>
       <c r="D183" t="s">
         <v>783</v>
@@ -13652,13 +13652,13 @@
         <v>657</v>
       </c>
       <c r="L183" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="R183" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="R183" s="4" t="s">
+      <c r="S183" t="s">
         <v>910</v>
-      </c>
-      <c r="S183" t="s">
-        <v>911</v>
       </c>
       <c r="T183" s="2">
         <v>7</v>
@@ -13670,18 +13670,18 @@
         <v>2</v>
       </c>
       <c r="X183" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="184" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>906</v>
+      </c>
+      <c r="B184" t="s">
         <v>907</v>
       </c>
-      <c r="B184" t="s">
-        <v>908</v>
-      </c>
       <c r="D184" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E184" t="s">
         <v>191</v>
@@ -13690,16 +13690,16 @@
         <v>192</v>
       </c>
       <c r="J184" t="s">
+        <v>912</v>
+      </c>
+      <c r="L184" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="L184" s="1" t="s">
+      <c r="R184" t="s">
+        <v>31</v>
+      </c>
+      <c r="S184" t="s">
         <v>914</v>
-      </c>
-      <c r="R184" t="s">
-        <v>31</v>
-      </c>
-      <c r="S184" t="s">
-        <v>915</v>
       </c>
       <c r="T184" s="2">
         <v>86</v>
@@ -13711,18 +13711,18 @@
         <v>2</v>
       </c>
       <c r="X184" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="185" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>906</v>
+      </c>
+      <c r="B185" t="s">
         <v>907</v>
       </c>
-      <c r="B185" t="s">
-        <v>908</v>
-      </c>
       <c r="D185" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E185" t="s">
         <v>566</v>
@@ -13731,10 +13731,10 @@
         <v>567</v>
       </c>
       <c r="J185" t="s">
+        <v>916</v>
+      </c>
+      <c r="L185" s="1" t="s">
         <v>917</v>
-      </c>
-      <c r="L185" s="1" t="s">
-        <v>918</v>
       </c>
       <c r="R185" t="s">
         <v>31</v>
@@ -13752,18 +13752,18 @@
         <v>2</v>
       </c>
       <c r="X185" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="186" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>906</v>
+      </c>
+      <c r="B186" t="s">
         <v>907</v>
       </c>
-      <c r="B186" t="s">
-        <v>908</v>
-      </c>
       <c r="D186" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E186" t="s">
         <v>34</v>
@@ -13772,13 +13772,13 @@
         <v>35</v>
       </c>
       <c r="J186" t="s">
+        <v>919</v>
+      </c>
+      <c r="L186" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="L186" s="1" t="s">
+      <c r="M186" t="s">
         <v>921</v>
-      </c>
-      <c r="M186" t="s">
-        <v>922</v>
       </c>
       <c r="R186" t="s">
         <v>31</v>
@@ -13796,39 +13796,39 @@
         <v>2</v>
       </c>
       <c r="X186" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="187" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>906</v>
+      </c>
+      <c r="B187" t="s">
         <v>907</v>
-      </c>
-      <c r="B187" t="s">
-        <v>908</v>
       </c>
       <c r="D187" t="s">
         <v>238</v>
       </c>
       <c r="E187" t="s">
+        <v>922</v>
+      </c>
+      <c r="F187" t="s">
         <v>923</v>
-      </c>
-      <c r="F187" t="s">
-        <v>924</v>
       </c>
       <c r="J187" t="s">
         <v>67</v>
       </c>
       <c r="L187" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="M187" t="s">
         <v>925</v>
       </c>
-      <c r="M187" t="s">
+      <c r="R187" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="R187" s="4" t="s">
+      <c r="S187" t="s">
         <v>927</v>
-      </c>
-      <c r="S187" t="s">
-        <v>928</v>
       </c>
       <c r="T187" s="2">
         <v>17</v>
@@ -13840,18 +13840,18 @@
         <v>2</v>
       </c>
       <c r="X187" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="188" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>906</v>
+      </c>
+      <c r="B188" t="s">
         <v>907</v>
       </c>
-      <c r="B188" t="s">
-        <v>908</v>
-      </c>
       <c r="D188" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E188" t="s">
         <v>191</v>
@@ -13860,10 +13860,10 @@
         <v>192</v>
       </c>
       <c r="J188" t="s">
+        <v>929</v>
+      </c>
+      <c r="L188" s="1" t="s">
         <v>930</v>
-      </c>
-      <c r="L188" s="1" t="s">
-        <v>931</v>
       </c>
       <c r="R188" t="s">
         <v>31</v>
@@ -13881,30 +13881,30 @@
         <v>2</v>
       </c>
       <c r="X188" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="189" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>906</v>
+      </c>
+      <c r="B189" t="s">
         <v>907</v>
       </c>
-      <c r="B189" t="s">
-        <v>908</v>
-      </c>
       <c r="D189" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E189" t="s">
+        <v>931</v>
+      </c>
+      <c r="F189" t="s">
         <v>932</v>
       </c>
-      <c r="F189" t="s">
+      <c r="J189" t="s">
         <v>933</v>
       </c>
-      <c r="J189" t="s">
+      <c r="L189" s="1" t="s">
         <v>934</v>
-      </c>
-      <c r="L189" s="1" t="s">
-        <v>935</v>
       </c>
       <c r="R189" t="s">
         <v>31</v>
@@ -13922,39 +13922,39 @@
         <v>2</v>
       </c>
       <c r="X189" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="190" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>906</v>
+      </c>
+      <c r="B190" t="s">
         <v>907</v>
-      </c>
-      <c r="B190" t="s">
-        <v>908</v>
       </c>
       <c r="D190" t="s">
         <v>260</v>
       </c>
       <c r="E190" t="s">
+        <v>922</v>
+      </c>
+      <c r="F190" t="s">
         <v>923</v>
-      </c>
-      <c r="F190" t="s">
-        <v>924</v>
       </c>
       <c r="J190" t="s">
         <v>393</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="M190" t="s">
+        <v>925</v>
+      </c>
+      <c r="R190" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="R190" s="4" t="s">
+      <c r="S190" t="s">
         <v>927</v>
-      </c>
-      <c r="S190" t="s">
-        <v>928</v>
       </c>
       <c r="T190" s="2">
         <v>17</v>
@@ -13966,15 +13966,15 @@
         <v>2</v>
       </c>
       <c r="X190" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="191" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B191" t="s">
         <v>1487</v>
-      </c>
-      <c r="B191" t="s">
-        <v>1488</v>
       </c>
       <c r="D191" t="s">
         <v>670</v>
@@ -13989,7 +13989,7 @@
         <v>573</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="R191" t="s">
         <v>31</v>
@@ -14007,30 +14007,30 @@
         <v>3</v>
       </c>
       <c r="X191" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="192" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B192" t="s">
         <v>1487</v>
-      </c>
-      <c r="B192" t="s">
-        <v>1488</v>
       </c>
       <c r="D192" t="s">
         <v>473</v>
       </c>
       <c r="E192" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F192" t="s">
+        <v>1489</v>
+      </c>
+      <c r="J192" t="s">
         <v>1490</v>
       </c>
-      <c r="J192" t="s">
+      <c r="L192" s="1" t="s">
         <v>1491</v>
-      </c>
-      <c r="L192" s="1" t="s">
-        <v>1492</v>
       </c>
       <c r="R192" t="s">
         <v>31</v>
@@ -14048,15 +14048,15 @@
         <v>3</v>
       </c>
       <c r="X192" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="193" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>936</v>
+      </c>
+      <c r="B193" t="s">
         <v>937</v>
-      </c>
-      <c r="B193" t="s">
-        <v>938</v>
       </c>
       <c r="D193" t="s">
         <v>116</v>
@@ -14068,13 +14068,13 @@
         <v>192</v>
       </c>
       <c r="J193" t="s">
+        <v>938</v>
+      </c>
+      <c r="K193" t="s">
         <v>939</v>
       </c>
-      <c r="K193" t="s">
+      <c r="L193" s="1" t="s">
         <v>940</v>
-      </c>
-      <c r="L193" s="1" t="s">
-        <v>941</v>
       </c>
       <c r="R193" t="s">
         <v>31</v>
@@ -14083,27 +14083,27 @@
         <v>65</v>
       </c>
       <c r="T193" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="U193" s="2" t="s">
         <v>942</v>
-      </c>
-      <c r="U193" s="2" t="s">
-        <v>943</v>
       </c>
       <c r="W193" s="2">
         <v>2</v>
       </c>
       <c r="X193" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="194" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>936</v>
+      </c>
+      <c r="B194" t="s">
         <v>937</v>
       </c>
-      <c r="B194" t="s">
-        <v>938</v>
-      </c>
       <c r="D194" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E194" t="s">
         <v>59</v>
@@ -14112,19 +14112,19 @@
         <v>315</v>
       </c>
       <c r="H194" t="s">
+        <v>944</v>
+      </c>
+      <c r="J194" t="s">
         <v>945</v>
       </c>
-      <c r="J194" t="s">
+      <c r="K194" t="s">
         <v>946</v>
       </c>
-      <c r="K194" t="s">
+      <c r="L194" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="L194" s="1" t="s">
+      <c r="M194" t="s">
         <v>948</v>
-      </c>
-      <c r="M194" t="s">
-        <v>949</v>
       </c>
       <c r="R194" t="s">
         <v>89</v>
@@ -14142,33 +14142,33 @@
         <v>2</v>
       </c>
       <c r="X194" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="195" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>936</v>
+      </c>
+      <c r="B195" t="s">
         <v>937</v>
       </c>
-      <c r="B195" t="s">
-        <v>938</v>
-      </c>
       <c r="D195" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E195" t="s">
         <v>59</v>
       </c>
       <c r="F195" t="s">
+        <v>949</v>
+      </c>
+      <c r="J195" t="s">
         <v>950</v>
       </c>
-      <c r="J195" t="s">
+      <c r="K195" t="s">
         <v>951</v>
       </c>
-      <c r="K195" t="s">
+      <c r="L195" s="1" t="s">
         <v>952</v>
-      </c>
-      <c r="L195" s="1" t="s">
-        <v>953</v>
       </c>
       <c r="R195" t="s">
         <v>31</v>
@@ -14177,45 +14177,45 @@
         <v>65</v>
       </c>
       <c r="T195" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="U195" s="2" t="s">
         <v>954</v>
-      </c>
-      <c r="U195" s="2" t="s">
-        <v>955</v>
       </c>
       <c r="W195" s="2">
         <v>2</v>
       </c>
       <c r="X195" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="196" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>936</v>
+      </c>
+      <c r="B196" t="s">
         <v>937</v>
       </c>
-      <c r="B196" t="s">
-        <v>938</v>
-      </c>
       <c r="D196" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E196" t="s">
         <v>59</v>
       </c>
       <c r="F196" t="s">
+        <v>956</v>
+      </c>
+      <c r="H196" t="s">
         <v>957</v>
       </c>
-      <c r="H196" t="s">
+      <c r="J196" t="s">
         <v>958</v>
       </c>
-      <c r="J196" t="s">
+      <c r="K196" t="s">
         <v>959</v>
       </c>
-      <c r="K196" t="s">
+      <c r="L196" s="1" t="s">
         <v>960</v>
-      </c>
-      <c r="L196" s="1" t="s">
-        <v>961</v>
       </c>
       <c r="R196" t="s">
         <v>31</v>
@@ -14233,33 +14233,33 @@
         <v>2</v>
       </c>
       <c r="X196" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="197" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>936</v>
+      </c>
+      <c r="B197" t="s">
         <v>937</v>
       </c>
-      <c r="B197" t="s">
-        <v>938</v>
-      </c>
       <c r="D197" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E197" t="s">
         <v>26</v>
       </c>
       <c r="F197" t="s">
+        <v>961</v>
+      </c>
+      <c r="J197" t="s">
         <v>962</v>
       </c>
-      <c r="J197" t="s">
+      <c r="K197" t="s">
         <v>963</v>
       </c>
-      <c r="K197" t="s">
+      <c r="L197" s="1" t="s">
         <v>964</v>
-      </c>
-      <c r="L197" s="1" t="s">
-        <v>965</v>
       </c>
       <c r="R197" t="s">
         <v>31</v>
@@ -14268,42 +14268,42 @@
         <v>65</v>
       </c>
       <c r="T197" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="U197" s="2" t="s">
         <v>966</v>
-      </c>
-      <c r="U197" s="2" t="s">
-        <v>967</v>
       </c>
       <c r="W197" s="2">
         <v>2</v>
       </c>
       <c r="X197" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="198" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>936</v>
+      </c>
+      <c r="B198" t="s">
         <v>937</v>
-      </c>
-      <c r="B198" t="s">
-        <v>938</v>
       </c>
       <c r="D198" t="s">
         <v>78</v>
       </c>
       <c r="E198" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F198" t="s">
         <v>84</v>
       </c>
       <c r="J198" t="s">
+        <v>968</v>
+      </c>
+      <c r="K198" t="s">
         <v>969</v>
       </c>
-      <c r="K198" t="s">
+      <c r="L198" s="1" t="s">
         <v>970</v>
-      </c>
-      <c r="L198" s="1" t="s">
-        <v>971</v>
       </c>
       <c r="R198" t="s">
         <v>89</v>
@@ -14312,24 +14312,24 @@
         <v>89</v>
       </c>
       <c r="T198" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="U198" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="U198" s="2" t="s">
-        <v>973</v>
       </c>
       <c r="W198" s="2">
         <v>2</v>
       </c>
       <c r="X198" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="199" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>936</v>
+      </c>
+      <c r="B199" t="s">
         <v>937</v>
-      </c>
-      <c r="B199" t="s">
-        <v>938</v>
       </c>
       <c r="D199" t="s">
         <v>433</v>
@@ -14338,16 +14338,16 @@
         <v>59</v>
       </c>
       <c r="F199" t="s">
+        <v>973</v>
+      </c>
+      <c r="J199" t="s">
+        <v>843</v>
+      </c>
+      <c r="K199" t="s">
+        <v>844</v>
+      </c>
+      <c r="L199" s="1" t="s">
         <v>974</v>
-      </c>
-      <c r="J199" t="s">
-        <v>844</v>
-      </c>
-      <c r="K199" t="s">
-        <v>845</v>
-      </c>
-      <c r="L199" s="1" t="s">
-        <v>975</v>
       </c>
       <c r="R199" t="s">
         <v>89</v>
@@ -14356,24 +14356,24 @@
         <v>89</v>
       </c>
       <c r="T199" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="U199" s="2" t="s">
         <v>976</v>
-      </c>
-      <c r="U199" s="2" t="s">
-        <v>977</v>
       </c>
       <c r="W199" s="2">
         <v>2</v>
       </c>
       <c r="X199" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="200" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>936</v>
+      </c>
+      <c r="B200" t="s">
         <v>937</v>
-      </c>
-      <c r="B200" t="s">
-        <v>938</v>
       </c>
       <c r="D200" t="s">
         <v>433</v>
@@ -14382,19 +14382,19 @@
         <v>59</v>
       </c>
       <c r="F200" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H200" t="s">
+        <v>977</v>
+      </c>
+      <c r="J200" t="s">
         <v>978</v>
       </c>
-      <c r="J200" t="s">
+      <c r="K200" t="s">
         <v>979</v>
       </c>
-      <c r="K200" t="s">
+      <c r="L200" s="1" t="s">
         <v>980</v>
-      </c>
-      <c r="L200" s="1" t="s">
-        <v>981</v>
       </c>
       <c r="R200" t="s">
         <v>89</v>
@@ -14406,42 +14406,42 @@
         <v>471</v>
       </c>
       <c r="U200" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="W200" s="2">
         <v>2</v>
       </c>
       <c r="X200" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="201" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B201" t="s">
         <v>1493</v>
-      </c>
-      <c r="B201" t="s">
-        <v>1494</v>
       </c>
       <c r="D201" t="s">
         <v>260</v>
       </c>
       <c r="E201" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F201" t="s">
         <v>1495</v>
       </c>
-      <c r="F201" t="s">
+      <c r="J201" t="s">
         <v>1496</v>
       </c>
-      <c r="J201" t="s">
+      <c r="L201" s="1" t="s">
         <v>1497</v>
       </c>
-      <c r="L201" s="1" t="s">
+      <c r="R201" t="s">
+        <v>31</v>
+      </c>
+      <c r="S201" t="s">
         <v>1498</v>
-      </c>
-      <c r="R201" t="s">
-        <v>31</v>
-      </c>
-      <c r="S201" t="s">
-        <v>1499</v>
       </c>
       <c r="T201" s="2">
         <v>206</v>
@@ -14453,39 +14453,39 @@
         <v>3</v>
       </c>
       <c r="X201" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="202" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B202" t="s">
         <v>1493</v>
-      </c>
-      <c r="B202" t="s">
-        <v>1494</v>
       </c>
       <c r="D202" t="s">
         <v>260</v>
       </c>
       <c r="E202" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F202" t="s">
         <v>1495</v>
       </c>
-      <c r="F202" t="s">
-        <v>1496</v>
-      </c>
       <c r="J202" t="s">
+        <v>1499</v>
+      </c>
+      <c r="K202" t="s">
         <v>1500</v>
       </c>
-      <c r="K202" t="s">
+      <c r="L202" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="L202" s="1" t="s">
+      <c r="R202" t="s">
+        <v>31</v>
+      </c>
+      <c r="S202" t="s">
         <v>1502</v>
-      </c>
-      <c r="R202" t="s">
-        <v>31</v>
-      </c>
-      <c r="S202" t="s">
-        <v>1503</v>
       </c>
       <c r="T202" s="2">
         <v>211</v>
@@ -14497,39 +14497,39 @@
         <v>3</v>
       </c>
       <c r="X202" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="203" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>982</v>
+      </c>
+      <c r="B203" t="s">
         <v>983</v>
       </c>
-      <c r="B203" t="s">
+      <c r="D203" t="s">
         <v>984</v>
-      </c>
-      <c r="D203" t="s">
-        <v>985</v>
       </c>
       <c r="E203" t="s">
         <v>59</v>
       </c>
       <c r="F203" t="s">
+        <v>985</v>
+      </c>
+      <c r="H203" t="s">
         <v>986</v>
       </c>
-      <c r="H203" t="s">
+      <c r="J203" t="s">
         <v>987</v>
       </c>
-      <c r="J203" t="s">
+      <c r="K203" t="s">
         <v>988</v>
       </c>
-      <c r="K203" t="s">
+      <c r="L203" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="L203" s="1" t="s">
+      <c r="M203" t="s">
         <v>990</v>
-      </c>
-      <c r="M203" t="s">
-        <v>991</v>
       </c>
       <c r="R203" t="s">
         <v>89</v>
@@ -14538,27 +14538,27 @@
         <v>89</v>
       </c>
       <c r="T203" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="U203" s="2" t="s">
         <v>992</v>
-      </c>
-      <c r="U203" s="2" t="s">
-        <v>993</v>
       </c>
       <c r="W203" s="2">
         <v>2</v>
       </c>
       <c r="X203" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="204" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>982</v>
+      </c>
+      <c r="B204" t="s">
         <v>983</v>
       </c>
-      <c r="B204" t="s">
-        <v>984</v>
-      </c>
       <c r="D204" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E204" t="s">
         <v>191</v>
@@ -14567,13 +14567,13 @@
         <v>192</v>
       </c>
       <c r="J204" t="s">
+        <v>993</v>
+      </c>
+      <c r="K204" t="s">
         <v>994</v>
       </c>
-      <c r="K204" t="s">
+      <c r="L204" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="L204" s="1" t="s">
-        <v>996</v>
       </c>
       <c r="R204" t="s">
         <v>31</v>
@@ -14585,54 +14585,54 @@
         <v>290</v>
       </c>
       <c r="U204" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="W204" s="2">
         <v>2</v>
       </c>
       <c r="X204" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="205" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>982</v>
+      </c>
+      <c r="B205" t="s">
         <v>983</v>
-      </c>
-      <c r="B205" t="s">
-        <v>984</v>
       </c>
       <c r="D205" t="s">
         <v>774</v>
       </c>
       <c r="E205" t="s">
+        <v>997</v>
+      </c>
+      <c r="F205" t="s">
         <v>998</v>
       </c>
-      <c r="F205" t="s">
+      <c r="G205" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="G205" s="1" t="s">
+      <c r="H205" t="s">
         <v>1000</v>
       </c>
-      <c r="H205" t="s">
+      <c r="I205" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="I205" s="1" t="s">
+      <c r="J205" t="s">
         <v>1002</v>
       </c>
-      <c r="J205" t="s">
+      <c r="K205" t="s">
         <v>1003</v>
       </c>
-      <c r="K205" t="s">
+      <c r="L205" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="L205" s="1" t="s">
+      <c r="M205" t="s">
         <v>1005</v>
       </c>
-      <c r="M205" t="s">
+      <c r="N205" s="1" t="s">
         <v>1006</v>
-      </c>
-      <c r="N205" s="1" t="s">
-        <v>1007</v>
       </c>
       <c r="R205" t="s">
         <v>89</v>
@@ -14641,54 +14641,54 @@
         <v>89</v>
       </c>
       <c r="T205" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="U205" s="2" t="s">
         <v>1008</v>
-      </c>
-      <c r="U205" s="2" t="s">
-        <v>1009</v>
       </c>
       <c r="W205" s="2">
         <v>2</v>
       </c>
       <c r="X205" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="Y205" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="206" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>982</v>
+      </c>
+      <c r="B206" t="s">
         <v>983</v>
       </c>
-      <c r="B206" t="s">
-        <v>984</v>
-      </c>
       <c r="D206" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E206" t="s">
         <v>1010</v>
       </c>
-      <c r="E206" t="s">
+      <c r="F206" t="s">
         <v>1011</v>
       </c>
-      <c r="F206" t="s">
+      <c r="H206" t="s">
         <v>1012</v>
       </c>
-      <c r="H206" t="s">
+      <c r="I206" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="I206" s="1" t="s">
+      <c r="J206" t="s">
         <v>1014</v>
       </c>
-      <c r="J206" t="s">
+      <c r="K206" t="s">
         <v>1015</v>
       </c>
-      <c r="K206" t="s">
+      <c r="L206" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="L206" s="1" t="s">
+      <c r="M206" t="s">
         <v>1017</v>
-      </c>
-      <c r="M206" t="s">
-        <v>1018</v>
       </c>
       <c r="R206" t="s">
         <v>89</v>
@@ -14697,7 +14697,7 @@
         <v>89</v>
       </c>
       <c r="T206" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="U206" s="2" t="s">
         <v>290</v>
@@ -14706,21 +14706,21 @@
         <v>2</v>
       </c>
       <c r="X206" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="Y206" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="207" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>982</v>
+      </c>
+      <c r="B207" t="s">
         <v>983</v>
       </c>
-      <c r="B207" t="s">
-        <v>984</v>
-      </c>
       <c r="D207" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E207" t="s">
         <v>284</v>
@@ -14729,13 +14729,13 @@
         <v>285</v>
       </c>
       <c r="J207" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K207" t="s">
         <v>1020</v>
       </c>
-      <c r="K207" t="s">
+      <c r="L207" s="1" t="s">
         <v>1021</v>
-      </c>
-      <c r="L207" s="1" t="s">
-        <v>1022</v>
       </c>
       <c r="R207" t="s">
         <v>408</v>
@@ -14744,30 +14744,30 @@
         <v>65</v>
       </c>
       <c r="T207" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="U207" s="2" t="s">
         <v>1023</v>
-      </c>
-      <c r="U207" s="2" t="s">
-        <v>1024</v>
       </c>
       <c r="W207" s="2">
         <v>2</v>
       </c>
       <c r="X207" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="Y207" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="208" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>982</v>
+      </c>
+      <c r="B208" t="s">
         <v>983</v>
       </c>
-      <c r="B208" t="s">
-        <v>984</v>
-      </c>
       <c r="D208" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E208" t="s">
         <v>95</v>
@@ -14776,16 +14776,16 @@
         <v>96</v>
       </c>
       <c r="J208" t="s">
+        <v>1025</v>
+      </c>
+      <c r="K208" t="s">
         <v>1026</v>
       </c>
-      <c r="K208" t="s">
+      <c r="L208" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="L208" s="1" t="s">
+      <c r="M208" t="s">
         <v>1028</v>
-      </c>
-      <c r="M208" t="s">
-        <v>1029</v>
       </c>
       <c r="R208" t="s">
         <v>31</v>
@@ -14794,7 +14794,7 @@
         <v>65</v>
       </c>
       <c r="T208" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="U208" s="2" t="s">
         <v>275</v>
@@ -14803,36 +14803,36 @@
         <v>2</v>
       </c>
       <c r="X208" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="Y208" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="209" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>982</v>
+      </c>
+      <c r="B209" t="s">
         <v>983</v>
       </c>
-      <c r="B209" t="s">
-        <v>984</v>
-      </c>
       <c r="D209" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E209" t="s">
         <v>59</v>
       </c>
       <c r="F209" t="s">
+        <v>1031</v>
+      </c>
+      <c r="J209" t="s">
         <v>1032</v>
       </c>
-      <c r="J209" t="s">
+      <c r="K209" t="s">
         <v>1033</v>
       </c>
-      <c r="K209" t="s">
+      <c r="L209" s="1" t="s">
         <v>1034</v>
-      </c>
-      <c r="L209" s="1" t="s">
-        <v>1035</v>
       </c>
       <c r="R209" t="s">
         <v>31</v>
@@ -14844,42 +14844,42 @@
         <v>712</v>
       </c>
       <c r="U209" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="W209" s="2">
         <v>2</v>
       </c>
       <c r="X209" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="Y209" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="210" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>982</v>
+      </c>
+      <c r="B210" t="s">
         <v>983</v>
-      </c>
-      <c r="B210" t="s">
-        <v>984</v>
       </c>
       <c r="D210" t="s">
         <v>651</v>
       </c>
       <c r="E210" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F210" t="s">
         <v>1011</v>
       </c>
-      <c r="F210" t="s">
-        <v>1012</v>
-      </c>
       <c r="J210" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K210" t="s">
         <v>1037</v>
       </c>
-      <c r="K210" t="s">
+      <c r="L210" s="1" t="s">
         <v>1038</v>
-      </c>
-      <c r="L210" s="1" t="s">
-        <v>1039</v>
       </c>
       <c r="R210" t="s">
         <v>89</v>
@@ -14888,7 +14888,7 @@
         <v>89</v>
       </c>
       <c r="T210" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="U210" s="2" t="s">
         <v>274</v>
@@ -14897,33 +14897,33 @@
         <v>2</v>
       </c>
       <c r="X210" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="Y210" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="211" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B211" t="s">
         <v>1504</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1505</v>
       </c>
       <c r="D211" t="s">
         <v>651</v>
       </c>
       <c r="E211" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F211" t="s">
+        <v>1505</v>
+      </c>
+      <c r="J211" t="s">
         <v>1506</v>
       </c>
-      <c r="J211" t="s">
+      <c r="L211" s="1" t="s">
         <v>1507</v>
-      </c>
-      <c r="L211" s="1" t="s">
-        <v>1508</v>
       </c>
       <c r="R211" t="s">
         <v>408</v>
@@ -14941,33 +14941,33 @@
         <v>3</v>
       </c>
       <c r="X211" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Y211" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="212" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B212" t="s">
         <v>1504</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1505</v>
       </c>
       <c r="D212" t="s">
         <v>791</v>
       </c>
       <c r="E212" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F212" t="s">
+        <v>1508</v>
+      </c>
+      <c r="J212" t="s">
         <v>1509</v>
       </c>
-      <c r="J212" t="s">
+      <c r="L212" s="1" t="s">
         <v>1510</v>
-      </c>
-      <c r="L212" s="1" t="s">
-        <v>1511</v>
       </c>
       <c r="R212" t="s">
         <v>408</v>
@@ -14985,21 +14985,21 @@
         <v>3</v>
       </c>
       <c r="X212" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="Y212" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="213" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B213" t="s">
         <v>1041</v>
       </c>
-      <c r="B213" t="s">
+      <c r="D213" t="s">
         <v>1042</v>
-      </c>
-      <c r="D213" t="s">
-        <v>1043</v>
       </c>
       <c r="E213" t="s">
         <v>59</v>
@@ -15014,7 +15014,7 @@
         <v>394</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="R213" t="s">
         <v>31</v>
@@ -15032,18 +15032,18 @@
         <v>2</v>
       </c>
       <c r="X213" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="214" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B214" t="s">
         <v>1041</v>
       </c>
-      <c r="B214" t="s">
-        <v>1042</v>
-      </c>
       <c r="D214" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E214" t="s">
         <v>59</v>
@@ -15052,13 +15052,13 @@
         <v>60</v>
       </c>
       <c r="J214" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K214" t="s">
         <v>1046</v>
       </c>
-      <c r="K214" t="s">
+      <c r="L214" s="1" t="s">
         <v>1047</v>
-      </c>
-      <c r="L214" s="1" t="s">
-        <v>1048</v>
       </c>
       <c r="R214" t="s">
         <v>31</v>
@@ -15076,33 +15076,33 @@
         <v>2</v>
       </c>
       <c r="X214" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="215" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B215" t="s">
         <v>1041</v>
-      </c>
-      <c r="B215" t="s">
-        <v>1042</v>
       </c>
       <c r="D215" t="s">
         <v>620</v>
       </c>
       <c r="E215" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F215" t="s">
         <v>1049</v>
       </c>
-      <c r="F215" t="s">
+      <c r="J215" t="s">
         <v>1050</v>
       </c>
-      <c r="J215" t="s">
+      <c r="K215" t="s">
         <v>1051</v>
       </c>
-      <c r="K215" t="s">
+      <c r="L215" s="1" t="s">
         <v>1052</v>
-      </c>
-      <c r="L215" s="1" t="s">
-        <v>1053</v>
       </c>
       <c r="R215" t="s">
         <v>31</v>
@@ -15120,15 +15120,15 @@
         <v>2</v>
       </c>
       <c r="X215" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="216" spans="1:25" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B216" s="7" t="s">
         <v>1041</v>
-      </c>
-      <c r="B216" s="7" t="s">
-        <v>1042</v>
       </c>
       <c r="D216" s="7">
         <v>1437</v>
@@ -15140,13 +15140,13 @@
         <v>192</v>
       </c>
       <c r="J216" s="7" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="K216" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L216" s="8" t="s">
         <v>1054</v>
-      </c>
-      <c r="L216" s="8" t="s">
-        <v>1055</v>
       </c>
       <c r="R216" s="7" t="s">
         <v>408</v>
@@ -15165,15 +15165,15 @@
         <v>2</v>
       </c>
       <c r="X216" s="7" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="217" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B217" t="s">
         <v>1041</v>
-      </c>
-      <c r="B217" t="s">
-        <v>1042</v>
       </c>
       <c r="D217" t="s">
         <v>415</v>
@@ -15182,25 +15182,25 @@
         <v>59</v>
       </c>
       <c r="F217" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H217" t="s">
         <v>1056</v>
       </c>
-      <c r="H217" t="s">
+      <c r="J217" t="s">
         <v>1057</v>
       </c>
-      <c r="J217" t="s">
+      <c r="K217" t="s">
         <v>1058</v>
       </c>
-      <c r="K217" t="s">
+      <c r="L217" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="L217" s="1" t="s">
+      <c r="M217" t="s">
         <v>1060</v>
       </c>
-      <c r="M217" t="s">
+      <c r="N217" s="1" t="s">
         <v>1061</v>
-      </c>
-      <c r="N217" s="1" t="s">
-        <v>1062</v>
       </c>
       <c r="R217" t="s">
         <v>31</v>
@@ -15218,15 +15218,15 @@
         <v>2</v>
       </c>
       <c r="X217" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="218" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B218" t="s">
         <v>1041</v>
-      </c>
-      <c r="B218" t="s">
-        <v>1042</v>
       </c>
       <c r="D218" t="s">
         <v>774</v>
@@ -15235,19 +15235,19 @@
         <v>59</v>
       </c>
       <c r="F218" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H218" t="s">
+        <v>1062</v>
+      </c>
+      <c r="J218" t="s">
         <v>1063</v>
       </c>
-      <c r="J218" t="s">
+      <c r="K218" t="s">
         <v>1064</v>
       </c>
-      <c r="K218" t="s">
+      <c r="L218" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="L218" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="R218" t="s">
         <v>31</v>
@@ -15265,42 +15265,42 @@
         <v>2</v>
       </c>
       <c r="X218" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="219" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B219" t="s">
         <v>1041</v>
       </c>
-      <c r="B219" t="s">
-        <v>1042</v>
-      </c>
       <c r="D219" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E219" t="s">
         <v>1067</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
         <v>1068</v>
       </c>
-      <c r="F219" t="s">
+      <c r="H219" t="s">
         <v>1069</v>
       </c>
-      <c r="H219" t="s">
+      <c r="J219" t="s">
         <v>1070</v>
       </c>
-      <c r="J219" t="s">
+      <c r="K219" t="s">
         <v>1071</v>
       </c>
-      <c r="K219" t="s">
+      <c r="L219" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="L219" s="1" t="s">
+      <c r="M219" t="s">
         <v>1073</v>
       </c>
-      <c r="M219" t="s">
+      <c r="N219" s="1" t="s">
         <v>1074</v>
-      </c>
-      <c r="N219" s="1" t="s">
-        <v>1075</v>
       </c>
       <c r="R219" t="s">
         <v>89</v>
@@ -15318,15 +15318,15 @@
         <v>2</v>
       </c>
       <c r="X219" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="220" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B220" t="s">
         <v>1041</v>
-      </c>
-      <c r="B220" t="s">
-        <v>1042</v>
       </c>
       <c r="D220" t="s">
         <v>460</v>
@@ -15338,13 +15338,13 @@
         <v>96</v>
       </c>
       <c r="J220" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K220" t="s">
         <v>1076</v>
       </c>
-      <c r="K220" t="s">
+      <c r="L220" s="1" t="s">
         <v>1077</v>
-      </c>
-      <c r="L220" s="1" t="s">
-        <v>1078</v>
       </c>
       <c r="R220" t="s">
         <v>31</v>
@@ -15362,15 +15362,15 @@
         <v>2</v>
       </c>
       <c r="X220" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="221" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B221" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D221" t="s">
         <v>438</v>
@@ -15385,13 +15385,13 @@
         <v>67</v>
       </c>
       <c r="L221" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="R221" t="s">
+        <v>31</v>
+      </c>
+      <c r="S221" t="s">
         <v>1513</v>
-      </c>
-      <c r="R221" t="s">
-        <v>31</v>
-      </c>
-      <c r="S221" t="s">
-        <v>1514</v>
       </c>
       <c r="T221" s="2">
         <v>258</v>
@@ -15403,33 +15403,33 @@
         <v>3</v>
       </c>
       <c r="X221" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="222" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B222" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D222" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="E222" t="s">
         <v>59</v>
       </c>
       <c r="F222" t="s">
+        <v>1515</v>
+      </c>
+      <c r="J222" t="s">
         <v>1516</v>
       </c>
-      <c r="J222" t="s">
+      <c r="K222" t="s">
         <v>1517</v>
       </c>
-      <c r="K222" t="s">
+      <c r="L222" s="1" t="s">
         <v>1518</v>
-      </c>
-      <c r="L222" s="1" t="s">
-        <v>1519</v>
       </c>
       <c r="R222" t="s">
         <v>31</v>
@@ -15447,30 +15447,30 @@
         <v>3</v>
       </c>
       <c r="X222" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="223" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B223" t="s">
         <v>1520</v>
-      </c>
-      <c r="B223" t="s">
-        <v>1521</v>
       </c>
       <c r="D223" t="s">
         <v>557</v>
       </c>
       <c r="E223" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F223" t="s">
         <v>1522</v>
-      </c>
-      <c r="F223" t="s">
-        <v>1523</v>
       </c>
       <c r="J223" t="s">
         <v>403</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="R223" t="s">
         <v>31</v>
@@ -15488,30 +15488,30 @@
         <v>3</v>
       </c>
       <c r="X223" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="224" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B224" t="s">
         <v>1520</v>
       </c>
-      <c r="B224" t="s">
+      <c r="D224" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E224" t="s">
         <v>1521</v>
       </c>
-      <c r="D224" t="s">
+      <c r="F224" t="s">
         <v>1525</v>
       </c>
-      <c r="E224" t="s">
-        <v>1522</v>
-      </c>
-      <c r="F224" t="s">
+      <c r="J224" t="s">
         <v>1526</v>
       </c>
-      <c r="J224" t="s">
+      <c r="L224" s="1" t="s">
         <v>1527</v>
-      </c>
-      <c r="L224" s="1" t="s">
-        <v>1528</v>
       </c>
       <c r="R224" t="s">
         <v>31</v>
@@ -15529,7 +15529,7 @@
         <v>3</v>
       </c>
       <c r="X224" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="225" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16065,13 +16065,13 @@
     </row>
     <row r="237" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B237" t="s">
         <v>1529</v>
       </c>
-      <c r="B237" t="s">
+      <c r="D237" t="s">
         <v>1530</v>
-      </c>
-      <c r="D237" t="s">
-        <v>1531</v>
       </c>
       <c r="E237" t="s">
         <v>34</v>
@@ -16080,13 +16080,13 @@
         <v>35</v>
       </c>
       <c r="J237" t="s">
+        <v>1531</v>
+      </c>
+      <c r="K237" t="s">
         <v>1532</v>
       </c>
-      <c r="K237" t="s">
+      <c r="L237" s="1" t="s">
         <v>1533</v>
-      </c>
-      <c r="L237" s="1" t="s">
-        <v>1534</v>
       </c>
       <c r="R237" t="s">
         <v>408</v>
@@ -16104,33 +16104,33 @@
         <v>3</v>
       </c>
       <c r="X237" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="238" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B238" t="s">
         <v>1529</v>
       </c>
-      <c r="B238" t="s">
-        <v>1530</v>
-      </c>
       <c r="D238" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E238" t="s">
         <v>1535</v>
       </c>
-      <c r="E238" t="s">
+      <c r="F238" t="s">
         <v>1536</v>
       </c>
-      <c r="F238" t="s">
+      <c r="J238" t="s">
         <v>1537</v>
       </c>
-      <c r="J238" t="s">
+      <c r="K238" t="s">
         <v>1538</v>
       </c>
-      <c r="K238" t="s">
+      <c r="L238" s="1" t="s">
         <v>1539</v>
-      </c>
-      <c r="L238" s="1" t="s">
-        <v>1540</v>
       </c>
       <c r="R238" t="s">
         <v>31</v>
@@ -16148,15 +16148,15 @@
         <v>3</v>
       </c>
       <c r="X238" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="239" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B239" t="s">
         <v>1079</v>
-      </c>
-      <c r="B239" t="s">
-        <v>1080</v>
       </c>
       <c r="D239" t="s">
         <v>433</v>
@@ -16168,13 +16168,13 @@
         <v>428</v>
       </c>
       <c r="J239" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K239" t="s">
         <v>1081</v>
       </c>
-      <c r="K239" t="s">
+      <c r="L239" s="1" t="s">
         <v>1082</v>
-      </c>
-      <c r="L239" s="1" t="s">
-        <v>1083</v>
       </c>
       <c r="R239" t="s">
         <v>31</v>
@@ -16192,33 +16192,33 @@
         <v>2</v>
       </c>
       <c r="X239" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="240" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B240" t="s">
         <v>1079</v>
       </c>
-      <c r="B240" t="s">
-        <v>1080</v>
-      </c>
       <c r="D240" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E240" t="s">
         <v>627</v>
       </c>
       <c r="F240" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J240" t="s">
         <v>1085</v>
       </c>
-      <c r="J240" t="s">
+      <c r="K240" t="s">
         <v>1086</v>
       </c>
-      <c r="K240" t="s">
+      <c r="L240" s="1" t="s">
         <v>1087</v>
-      </c>
-      <c r="L240" s="1" t="s">
-        <v>1088</v>
       </c>
       <c r="R240" t="s">
         <v>257</v>
@@ -16236,39 +16236,39 @@
         <v>2</v>
       </c>
       <c r="X240" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="241" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B241" t="s">
         <v>1079</v>
       </c>
-      <c r="B241" t="s">
-        <v>1080</v>
-      </c>
       <c r="D241" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E241" t="s">
         <v>627</v>
       </c>
       <c r="F241" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J241" t="s">
+        <v>1089</v>
+      </c>
+      <c r="K241" t="s">
         <v>1090</v>
       </c>
-      <c r="K241" t="s">
+      <c r="L241" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="L241" s="1" t="s">
+      <c r="R241" t="s">
+        <v>31</v>
+      </c>
+      <c r="S241" t="s">
         <v>1092</v>
-      </c>
-      <c r="R241" t="s">
-        <v>31</v>
-      </c>
-      <c r="S241" t="s">
-        <v>1093</v>
       </c>
       <c r="T241" s="2">
         <v>87</v>
@@ -16280,33 +16280,33 @@
         <v>2</v>
       </c>
       <c r="X241" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="242" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B242" t="s">
         <v>1079</v>
       </c>
-      <c r="B242" t="s">
-        <v>1080</v>
-      </c>
       <c r="D242" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E242" t="s">
         <v>1094</v>
       </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>1095</v>
-      </c>
-      <c r="F242" t="s">
-        <v>1096</v>
       </c>
       <c r="J242" t="s">
         <v>403</v>
       </c>
       <c r="K242" t="s">
+        <v>1096</v>
+      </c>
+      <c r="L242" s="1" t="s">
         <v>1097</v>
-      </c>
-      <c r="L242" s="1" t="s">
-        <v>1098</v>
       </c>
       <c r="R242" t="s">
         <v>31</v>
@@ -16324,33 +16324,33 @@
         <v>2</v>
       </c>
       <c r="X242" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="243" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B243" t="s">
         <v>1079</v>
       </c>
-      <c r="B243" t="s">
-        <v>1080</v>
-      </c>
       <c r="D243" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E243" t="s">
         <v>627</v>
       </c>
       <c r="F243" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J243" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K243" t="s">
         <v>1100</v>
       </c>
-      <c r="K243" t="s">
+      <c r="L243" s="1" t="s">
         <v>1101</v>
-      </c>
-      <c r="L243" s="1" t="s">
-        <v>1102</v>
       </c>
       <c r="R243" t="s">
         <v>408</v>
@@ -16368,30 +16368,30 @@
         <v>2</v>
       </c>
       <c r="X243" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="244" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B244" t="s">
         <v>1079</v>
-      </c>
-      <c r="B244" t="s">
-        <v>1080</v>
       </c>
       <c r="D244" t="s">
         <v>33</v>
       </c>
       <c r="E244" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F244" t="s">
         <v>1103</v>
       </c>
-      <c r="F244" t="s">
+      <c r="J244" t="s">
         <v>1104</v>
       </c>
-      <c r="J244" t="s">
+      <c r="L244" s="1" t="s">
         <v>1105</v>
-      </c>
-      <c r="L244" s="1" t="s">
-        <v>1106</v>
       </c>
       <c r="R244" t="s">
         <v>31</v>
@@ -16409,18 +16409,18 @@
         <v>2</v>
       </c>
       <c r="X244" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="245" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B245" t="s">
         <v>1079</v>
       </c>
-      <c r="B245" t="s">
-        <v>1080</v>
-      </c>
       <c r="D245" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E245" t="s">
         <v>627</v>
@@ -16429,10 +16429,10 @@
         <v>628</v>
       </c>
       <c r="J245" t="s">
+        <v>1107</v>
+      </c>
+      <c r="L245" s="1" t="s">
         <v>1108</v>
-      </c>
-      <c r="L245" s="1" t="s">
-        <v>1109</v>
       </c>
       <c r="R245" t="s">
         <v>325</v>
@@ -16450,15 +16450,15 @@
         <v>2</v>
       </c>
       <c r="X245" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="246" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B246" t="s">
         <v>1079</v>
-      </c>
-      <c r="B246" t="s">
-        <v>1080</v>
       </c>
       <c r="D246" t="s">
         <v>677</v>
@@ -16470,10 +16470,10 @@
         <v>567</v>
       </c>
       <c r="J246" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L246" s="1" t="s">
         <v>1110</v>
-      </c>
-      <c r="L246" s="1" t="s">
-        <v>1111</v>
       </c>
       <c r="R246" t="s">
         <v>31</v>
@@ -16491,7 +16491,7 @@
         <v>2</v>
       </c>
       <c r="X246" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="247" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17025,13 +17025,13 @@
     </row>
     <row r="258" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B258" t="s">
         <v>1541</v>
       </c>
-      <c r="B258" t="s">
+      <c r="D258" t="s">
         <v>1542</v>
-      </c>
-      <c r="D258" t="s">
-        <v>1543</v>
       </c>
       <c r="E258" t="s">
         <v>427</v>
@@ -17040,10 +17040,10 @@
         <v>428</v>
       </c>
       <c r="J258" t="s">
+        <v>1543</v>
+      </c>
+      <c r="L258" s="1" t="s">
         <v>1544</v>
-      </c>
-      <c r="L258" s="1" t="s">
-        <v>1545</v>
       </c>
       <c r="R258" t="s">
         <v>408</v>
@@ -17061,36 +17061,36 @@
         <v>3</v>
       </c>
       <c r="X258" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="259" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B259" t="s">
         <v>1541</v>
       </c>
-      <c r="B259" t="s">
-        <v>1542</v>
-      </c>
       <c r="D259" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E259" t="s">
         <v>1546</v>
       </c>
-      <c r="E259" t="s">
+      <c r="F259" t="s">
         <v>1547</v>
       </c>
-      <c r="F259" t="s">
+      <c r="J259" t="s">
         <v>1548</v>
       </c>
-      <c r="J259" t="s">
+      <c r="L259" s="1" t="s">
         <v>1549</v>
-      </c>
-      <c r="L259" s="1" t="s">
-        <v>1550</v>
       </c>
       <c r="R259" t="s">
         <v>408</v>
       </c>
       <c r="S259" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="T259" s="2">
         <v>1088</v>
@@ -17102,36 +17102,36 @@
         <v>3</v>
       </c>
       <c r="X259" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="260" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B260" t="s">
         <v>1112</v>
       </c>
-      <c r="B260" t="s">
-        <v>1113</v>
-      </c>
       <c r="C260" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D260" t="s">
         <v>78</v>
       </c>
       <c r="E260" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F260" t="s">
         <v>84</v>
       </c>
       <c r="J260" t="s">
+        <v>1113</v>
+      </c>
+      <c r="K260" t="s">
         <v>1114</v>
       </c>
-      <c r="K260" t="s">
+      <c r="L260" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="L260" s="1" t="s">
-        <v>1116</v>
       </c>
       <c r="R260" t="s">
         <v>89</v>
@@ -17149,21 +17149,21 @@
         <v>2</v>
       </c>
       <c r="X260" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="261" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B261" t="s">
         <v>1112</v>
       </c>
-      <c r="B261" t="s">
-        <v>1113</v>
-      </c>
       <c r="C261" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D261" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E261" t="s">
         <v>59</v>
@@ -17172,13 +17172,13 @@
         <v>60</v>
       </c>
       <c r="J261" t="s">
+        <v>1117</v>
+      </c>
+      <c r="K261" t="s">
         <v>1118</v>
       </c>
-      <c r="K261" t="s">
+      <c r="L261" s="1" t="s">
         <v>1119</v>
-      </c>
-      <c r="L261" s="1" t="s">
-        <v>1120</v>
       </c>
       <c r="R261" t="s">
         <v>31</v>
@@ -17196,36 +17196,36 @@
         <v>2</v>
       </c>
       <c r="X261" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="262" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B262" t="s">
         <v>1112</v>
       </c>
-      <c r="B262" t="s">
-        <v>1113</v>
-      </c>
       <c r="C262" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D262" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E262" t="s">
         <v>59</v>
       </c>
       <c r="F262" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="J262" t="s">
         <v>474</v>
       </c>
       <c r="K262" t="s">
+        <v>1122</v>
+      </c>
+      <c r="L262" s="1" t="s">
         <v>1123</v>
-      </c>
-      <c r="L262" s="1" t="s">
-        <v>1124</v>
       </c>
       <c r="R262" t="s">
         <v>31</v>
@@ -17243,42 +17243,42 @@
         <v>2</v>
       </c>
       <c r="X262" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="263" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B263" t="s">
         <v>1112</v>
       </c>
-      <c r="B263" t="s">
-        <v>1113</v>
-      </c>
       <c r="C263" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D263" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E263" t="s">
         <v>284</v>
       </c>
       <c r="F263" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="J263" t="s">
+        <v>1126</v>
+      </c>
+      <c r="K263" t="s">
+        <v>1126</v>
+      </c>
+      <c r="L263" s="1" t="s">
         <v>1127</v>
       </c>
-      <c r="K263" t="s">
-        <v>1127</v>
-      </c>
-      <c r="L263" s="1" t="s">
+      <c r="M263" t="s">
+        <v>1125</v>
+      </c>
+      <c r="N263" s="1" t="s">
         <v>1128</v>
-      </c>
-      <c r="M263" t="s">
-        <v>1126</v>
-      </c>
-      <c r="N263" s="1" t="s">
-        <v>1129</v>
       </c>
       <c r="R263" t="s">
         <v>89</v>
@@ -17296,21 +17296,21 @@
         <v>2</v>
       </c>
       <c r="X263" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="264" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B264" t="s">
         <v>1112</v>
       </c>
-      <c r="B264" t="s">
-        <v>1113</v>
-      </c>
       <c r="C264" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D264" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E264" t="s">
         <v>169</v>
@@ -17319,13 +17319,13 @@
         <v>170</v>
       </c>
       <c r="J264" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="K264" t="s">
         <v>353</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="R264" t="s">
         <v>31</v>
@@ -17343,21 +17343,21 @@
         <v>2</v>
       </c>
       <c r="X264" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="265" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B265" t="s">
         <v>1112</v>
       </c>
-      <c r="B265" t="s">
-        <v>1113</v>
-      </c>
       <c r="C265" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D265" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="E265" t="s">
         <v>191</v>
@@ -17366,13 +17366,13 @@
         <v>192</v>
       </c>
       <c r="J265" t="s">
+        <v>1133</v>
+      </c>
+      <c r="K265" t="s">
         <v>1134</v>
       </c>
-      <c r="K265" t="s">
+      <c r="L265" s="1" t="s">
         <v>1135</v>
-      </c>
-      <c r="L265" s="1" t="s">
-        <v>1136</v>
       </c>
       <c r="R265" t="s">
         <v>31</v>
@@ -17390,21 +17390,21 @@
         <v>2</v>
       </c>
       <c r="X265" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="266" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B266" t="s">
         <v>1112</v>
       </c>
-      <c r="B266" t="s">
-        <v>1113</v>
-      </c>
       <c r="C266" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D266" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E266" t="s">
         <v>176</v>
@@ -17419,7 +17419,7 @@
         <v>435</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="R266" t="s">
         <v>31</v>
@@ -17437,18 +17437,18 @@
         <v>2</v>
       </c>
       <c r="X266" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="267" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B267" t="s">
         <v>1112</v>
       </c>
-      <c r="B267" t="s">
-        <v>1113</v>
-      </c>
       <c r="C267" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D267" t="s">
         <v>479</v>
@@ -17457,19 +17457,19 @@
         <v>59</v>
       </c>
       <c r="F267" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H267" t="s">
         <v>1139</v>
       </c>
-      <c r="H267" t="s">
+      <c r="J267" t="s">
         <v>1140</v>
       </c>
-      <c r="J267" t="s">
+      <c r="K267" t="s">
         <v>1141</v>
       </c>
-      <c r="K267" t="s">
+      <c r="L267" s="1" t="s">
         <v>1142</v>
-      </c>
-      <c r="L267" s="1" t="s">
-        <v>1143</v>
       </c>
       <c r="R267" t="s">
         <v>89</v>
@@ -17487,15 +17487,15 @@
         <v>2</v>
       </c>
       <c r="X267" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="268" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B268" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D268">
         <v>1475</v>
@@ -17507,13 +17507,13 @@
         <v>96</v>
       </c>
       <c r="J268" t="s">
+        <v>1552</v>
+      </c>
+      <c r="K268" t="s">
         <v>1553</v>
       </c>
-      <c r="K268" t="s">
+      <c r="L268" s="1" t="s">
         <v>1554</v>
-      </c>
-      <c r="L268" s="1" t="s">
-        <v>1555</v>
       </c>
       <c r="R268" t="s">
         <v>31</v>
@@ -17531,18 +17531,18 @@
         <v>3</v>
       </c>
       <c r="X268" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="269" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B269" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D269" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="E269" t="s">
         <v>59</v>
@@ -17551,16 +17551,16 @@
         <v>163</v>
       </c>
       <c r="J269" t="s">
+        <v>1555</v>
+      </c>
+      <c r="K269" t="s">
         <v>1556</v>
       </c>
-      <c r="K269" t="s">
+      <c r="L269" s="1" t="s">
         <v>1557</v>
       </c>
-      <c r="L269" s="1" t="s">
+      <c r="M269" t="s">
         <v>1558</v>
-      </c>
-      <c r="M269" t="s">
-        <v>1559</v>
       </c>
       <c r="R269" t="s">
         <v>31</v>
@@ -17578,36 +17578,36 @@
         <v>3</v>
       </c>
       <c r="X269" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="270" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B270" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D270" t="s">
         <v>1560</v>
       </c>
-      <c r="D270" t="s">
+      <c r="E270" t="s">
         <v>1561</v>
       </c>
-      <c r="E270" t="s">
+      <c r="F270" t="s">
         <v>1562</v>
       </c>
-      <c r="F270" t="s">
+      <c r="J270" t="s">
         <v>1563</v>
       </c>
-      <c r="J270" t="s">
+      <c r="L270" s="1" t="s">
         <v>1564</v>
-      </c>
-      <c r="L270" s="1" t="s">
-        <v>1565</v>
       </c>
       <c r="R270" t="s">
         <v>325</v>
       </c>
       <c r="S270" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="T270" s="2">
         <v>143</v>
@@ -17619,30 +17619,30 @@
         <v>3</v>
       </c>
       <c r="X270" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="271" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B271" t="s">
         <v>1567</v>
       </c>
-      <c r="B271" t="s">
+      <c r="D271" t="s">
         <v>1568</v>
       </c>
-      <c r="D271" t="s">
+      <c r="E271" t="s">
         <v>1569</v>
       </c>
-      <c r="E271" t="s">
+      <c r="F271" t="s">
         <v>1570</v>
-      </c>
-      <c r="F271" t="s">
-        <v>1571</v>
       </c>
       <c r="J271" t="s">
         <v>393</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="R271" t="s">
         <v>31</v>
@@ -17660,15 +17660,15 @@
         <v>3</v>
       </c>
       <c r="X271" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="272" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B272" t="s">
         <v>1567</v>
-      </c>
-      <c r="B272" t="s">
-        <v>1568</v>
       </c>
       <c r="D272" t="s">
         <v>238</v>
@@ -17680,10 +17680,10 @@
         <v>192</v>
       </c>
       <c r="J272" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L272" s="1" t="s">
         <v>1573</v>
-      </c>
-      <c r="L272" s="1" t="s">
-        <v>1574</v>
       </c>
       <c r="R272" t="s">
         <v>31</v>
@@ -17701,15 +17701,15 @@
         <v>3</v>
       </c>
       <c r="X272" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="273" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B273" t="s">
         <v>1575</v>
-      </c>
-      <c r="B273" t="s">
-        <v>1576</v>
       </c>
       <c r="D273" t="s">
         <v>78</v>
@@ -17724,16 +17724,16 @@
         <v>84</v>
       </c>
       <c r="J273" t="s">
+        <v>1576</v>
+      </c>
+      <c r="K273" t="s">
         <v>1577</v>
       </c>
-      <c r="K273" t="s">
+      <c r="L273" s="1" t="s">
         <v>1578</v>
       </c>
-      <c r="L273" s="1" t="s">
+      <c r="M273" t="s">
         <v>1579</v>
-      </c>
-      <c r="M273" t="s">
-        <v>1580</v>
       </c>
       <c r="R273" t="s">
         <v>89</v>
@@ -17751,15 +17751,15 @@
         <v>3</v>
       </c>
       <c r="X273" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="274" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B274" t="s">
         <v>1575</v>
-      </c>
-      <c r="B274" t="s">
-        <v>1576</v>
       </c>
       <c r="D274" t="s">
         <v>78</v>
@@ -17777,13 +17777,13 @@
         <v>217</v>
       </c>
       <c r="K274" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="M274" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="R274" t="s">
         <v>89</v>
@@ -17801,39 +17801,39 @@
         <v>3</v>
       </c>
       <c r="X274" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="275" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B275" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D275" t="s">
         <v>1582</v>
       </c>
-      <c r="B275" t="s">
-        <v>1391</v>
-      </c>
-      <c r="D275" t="s">
+      <c r="E275" t="s">
         <v>1583</v>
       </c>
-      <c r="E275" t="s">
+      <c r="F275" t="s">
+        <v>932</v>
+      </c>
+      <c r="J275" t="s">
         <v>1584</v>
       </c>
-      <c r="F275" t="s">
-        <v>933</v>
-      </c>
-      <c r="J275" t="s">
+      <c r="K275" t="s">
         <v>1585</v>
       </c>
-      <c r="K275" t="s">
+      <c r="L275" s="1" t="s">
         <v>1586</v>
-      </c>
-      <c r="L275" s="1" t="s">
-        <v>1587</v>
       </c>
       <c r="R275" t="s">
         <v>408</v>
       </c>
       <c r="S275" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="T275" s="2" t="s">
         <v>252</v>
@@ -17842,183 +17842,183 @@
         <v>727</v>
       </c>
       <c r="W275" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X275" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="Y275" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="276" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B276" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D276" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E276" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F276" t="s">
         <v>1589</v>
-      </c>
-      <c r="E276" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F276" t="s">
-        <v>1590</v>
       </c>
       <c r="J276" t="s">
         <v>265</v>
       </c>
       <c r="K276" t="s">
+        <v>1590</v>
+      </c>
+      <c r="L276" s="1" t="s">
         <v>1591</v>
       </c>
-      <c r="L276" s="1" t="s">
+      <c r="M276" t="s">
         <v>1592</v>
       </c>
-      <c r="M276" t="s">
+      <c r="N276" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="R276" t="s">
         <v>1593</v>
       </c>
-      <c r="N276" s="1" t="s">
-        <v>1396</v>
-      </c>
-      <c r="R276" t="s">
-        <v>1594</v>
-      </c>
       <c r="S276" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="T276" s="2" t="s">
         <v>727</v>
       </c>
       <c r="U276" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="W276" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X276" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="Y276" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="277" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B277" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D277" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E277" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F277" t="s">
         <v>1589</v>
       </c>
-      <c r="E277" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F277" t="s">
-        <v>1590</v>
-      </c>
       <c r="J277" t="s">
+        <v>1594</v>
+      </c>
+      <c r="K277" t="s">
         <v>1595</v>
       </c>
-      <c r="K277" t="s">
+      <c r="L277" s="1" t="s">
         <v>1596</v>
       </c>
-      <c r="L277" s="1" t="s">
-        <v>1597</v>
-      </c>
       <c r="M277" t="s">
+        <v>1592</v>
+      </c>
+      <c r="N277" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="R277" t="s">
         <v>1593</v>
       </c>
-      <c r="N277" s="1" t="s">
-        <v>1396</v>
-      </c>
-      <c r="R277" t="s">
-        <v>1594</v>
-      </c>
       <c r="S277" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="T277" s="2" t="s">
         <v>727</v>
       </c>
       <c r="U277" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="W277" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X277" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="Y277" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="278" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B278" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D278" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E278" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F278" t="s">
         <v>1589</v>
       </c>
-      <c r="E278" t="s">
-        <v>1584</v>
-      </c>
-      <c r="F278" t="s">
-        <v>1590</v>
-      </c>
       <c r="J278" t="s">
+        <v>1597</v>
+      </c>
+      <c r="K278" t="s">
         <v>1598</v>
       </c>
-      <c r="K278" t="s">
+      <c r="L278" s="1" t="s">
         <v>1599</v>
       </c>
-      <c r="L278" s="1" t="s">
-        <v>1600</v>
-      </c>
       <c r="M278" t="s">
+        <v>1592</v>
+      </c>
+      <c r="N278" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="R278" t="s">
         <v>1593</v>
       </c>
-      <c r="N278" s="1" t="s">
-        <v>1396</v>
-      </c>
-      <c r="R278" t="s">
-        <v>1594</v>
-      </c>
       <c r="S278" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="T278" s="2" t="s">
         <v>727</v>
       </c>
       <c r="U278" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="W278" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="X278" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="Y278" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="279" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B279" t="s">
         <v>1190</v>
       </c>
-      <c r="B279" t="s">
+      <c r="D279" t="s">
         <v>1191</v>
-      </c>
-      <c r="D279" t="s">
-        <v>1192</v>
       </c>
       <c r="E279" t="s">
         <v>197</v>
@@ -18027,13 +18027,13 @@
         <v>270</v>
       </c>
       <c r="J279" t="s">
+        <v>1192</v>
+      </c>
+      <c r="K279" t="s">
         <v>1193</v>
       </c>
-      <c r="K279" t="s">
+      <c r="L279" s="1" t="s">
         <v>1194</v>
-      </c>
-      <c r="L279" s="1" t="s">
-        <v>1195</v>
       </c>
       <c r="R279" t="s">
         <v>31</v>
@@ -18051,36 +18051,36 @@
         <v>2</v>
       </c>
       <c r="X279" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="280" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B280" t="s">
         <v>1190</v>
       </c>
-      <c r="B280" t="s">
-        <v>1191</v>
-      </c>
       <c r="D280" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E280" t="s">
         <v>284</v>
       </c>
       <c r="F280" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H280" t="s">
         <v>1197</v>
       </c>
-      <c r="H280" t="s">
+      <c r="J280" t="s">
         <v>1198</v>
       </c>
-      <c r="J280" t="s">
+      <c r="K280" t="s">
         <v>1199</v>
       </c>
-      <c r="K280" t="s">
+      <c r="L280" s="1" t="s">
         <v>1200</v>
-      </c>
-      <c r="L280" s="1" t="s">
-        <v>1201</v>
       </c>
       <c r="R280" t="s">
         <v>31</v>
@@ -18098,33 +18098,33 @@
         <v>2</v>
       </c>
       <c r="X280" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="281" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B281" t="s">
         <v>1190</v>
-      </c>
-      <c r="B281" t="s">
-        <v>1191</v>
       </c>
       <c r="D281" t="s">
         <v>124</v>
       </c>
       <c r="E281" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F281" t="s">
         <v>1202</v>
       </c>
-      <c r="F281" t="s">
+      <c r="J281" t="s">
+        <v>849</v>
+      </c>
+      <c r="K281" t="s">
         <v>1203</v>
       </c>
-      <c r="J281" t="s">
-        <v>850</v>
-      </c>
-      <c r="K281" t="s">
+      <c r="L281" s="1" t="s">
         <v>1204</v>
-      </c>
-      <c r="L281" s="1" t="s">
-        <v>1205</v>
       </c>
       <c r="R281" t="s">
         <v>31</v>
@@ -18142,15 +18142,15 @@
         <v>2</v>
       </c>
       <c r="X281" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="282" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B282" t="s">
         <v>1190</v>
-      </c>
-      <c r="B282" t="s">
-        <v>1191</v>
       </c>
       <c r="D282" t="s">
         <v>131</v>
@@ -18162,13 +18162,13 @@
         <v>60</v>
       </c>
       <c r="J282" t="s">
+        <v>1205</v>
+      </c>
+      <c r="K282" t="s">
         <v>1206</v>
       </c>
-      <c r="K282" t="s">
+      <c r="L282" s="1" t="s">
         <v>1207</v>
-      </c>
-      <c r="L282" s="1" t="s">
-        <v>1208</v>
       </c>
       <c r="R282" t="s">
         <v>31</v>
@@ -18186,36 +18186,36 @@
         <v>2</v>
       </c>
       <c r="X282" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="283" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B283" t="s">
         <v>1601</v>
-      </c>
-      <c r="B283" t="s">
-        <v>1602</v>
       </c>
       <c r="D283">
         <v>1469</v>
       </c>
       <c r="E283" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="F283" t="s">
+        <v>1602</v>
+      </c>
+      <c r="J283" t="s">
+        <v>1239</v>
+      </c>
+      <c r="K283" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L283" s="1" t="s">
         <v>1603</v>
       </c>
-      <c r="J283" t="s">
-        <v>1240</v>
-      </c>
-      <c r="K283" t="s">
-        <v>1241</v>
-      </c>
-      <c r="L283" s="1" t="s">
+      <c r="M283" t="s">
         <v>1604</v>
-      </c>
-      <c r="M283" t="s">
-        <v>1605</v>
       </c>
       <c r="R283" t="s">
         <v>31</v>
@@ -18233,18 +18233,18 @@
         <v>3</v>
       </c>
       <c r="X283" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="284" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B284" t="s">
         <v>1601</v>
       </c>
-      <c r="B284" t="s">
-        <v>1602</v>
-      </c>
       <c r="D284" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="E284" t="s">
         <v>95</v>
@@ -18253,22 +18253,22 @@
         <v>96</v>
       </c>
       <c r="J284" t="s">
+        <v>1606</v>
+      </c>
+      <c r="K284" t="s">
         <v>1607</v>
       </c>
-      <c r="K284" t="s">
+      <c r="L284" s="1" t="s">
         <v>1608</v>
       </c>
-      <c r="L284" s="1" t="s">
+      <c r="M284" t="s">
         <v>1609</v>
       </c>
-      <c r="M284" t="s">
+      <c r="R284" t="s">
+        <v>31</v>
+      </c>
+      <c r="S284" t="s">
         <v>1610</v>
-      </c>
-      <c r="R284" t="s">
-        <v>31</v>
-      </c>
-      <c r="S284" t="s">
-        <v>1611</v>
       </c>
       <c r="T284" s="2">
         <v>239</v>
@@ -18280,39 +18280,39 @@
         <v>3</v>
       </c>
       <c r="X284" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="285" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B285" t="s">
         <v>1209</v>
       </c>
-      <c r="B285" t="s">
+      <c r="D285" t="s">
         <v>1210</v>
-      </c>
-      <c r="D285" t="s">
-        <v>1211</v>
       </c>
       <c r="E285" t="s">
         <v>59</v>
       </c>
       <c r="F285" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J285" t="s">
         <v>1212</v>
       </c>
-      <c r="J285" t="s">
+      <c r="K285" t="s">
         <v>1213</v>
       </c>
-      <c r="K285" t="s">
+      <c r="L285" s="1" t="s">
         <v>1214</v>
-      </c>
-      <c r="L285" s="1" t="s">
-        <v>1215</v>
       </c>
       <c r="R285" t="s">
         <v>89</v>
       </c>
       <c r="S285" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="T285" s="2">
         <v>820</v>
@@ -18324,18 +18324,18 @@
         <v>2</v>
       </c>
       <c r="X285" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="286" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B286" t="s">
         <v>1209</v>
       </c>
-      <c r="B286" t="s">
-        <v>1210</v>
-      </c>
       <c r="D286" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E286" t="s">
         <v>59</v>
@@ -18344,19 +18344,19 @@
         <v>60</v>
       </c>
       <c r="J286" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K286" t="s">
         <v>1218</v>
       </c>
-      <c r="K286" t="s">
+      <c r="L286" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="L286" s="1" t="s">
-        <v>1220</v>
-      </c>
       <c r="R286" t="s">
         <v>31</v>
       </c>
       <c r="S286" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="T286" s="2">
         <v>182</v>
@@ -18368,30 +18368,30 @@
         <v>2</v>
       </c>
       <c r="X286" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="287" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B287" t="s">
         <v>1209</v>
       </c>
-      <c r="B287" t="s">
-        <v>1210</v>
-      </c>
       <c r="D287" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E287" t="s">
         <v>59</v>
       </c>
       <c r="F287" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="J287" t="s">
+        <v>1221</v>
+      </c>
+      <c r="L287" s="1" t="s">
         <v>1222</v>
-      </c>
-      <c r="L287" s="1" t="s">
-        <v>1223</v>
       </c>
       <c r="R287" t="s">
         <v>89</v>
@@ -18409,15 +18409,15 @@
         <v>2</v>
       </c>
       <c r="X287" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="288" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B288" t="s">
         <v>1209</v>
-      </c>
-      <c r="B288" t="s">
-        <v>1210</v>
       </c>
       <c r="D288" t="s">
         <v>405</v>
@@ -18429,19 +18429,19 @@
         <v>96</v>
       </c>
       <c r="J288" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K288" t="s">
         <v>1224</v>
       </c>
-      <c r="K288" t="s">
+      <c r="L288" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="L288" s="1" t="s">
+      <c r="R288" t="s">
+        <v>31</v>
+      </c>
+      <c r="S288" t="s">
         <v>1226</v>
-      </c>
-      <c r="R288" t="s">
-        <v>31</v>
-      </c>
-      <c r="S288" t="s">
-        <v>1227</v>
       </c>
       <c r="T288" s="2">
         <v>182</v>
@@ -18453,18 +18453,18 @@
         <v>2</v>
       </c>
       <c r="X288" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="289" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B289" t="s">
         <v>1209</v>
       </c>
-      <c r="B289" t="s">
-        <v>1210</v>
-      </c>
       <c r="D289" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E289" t="s">
         <v>191</v>
@@ -18473,19 +18473,19 @@
         <v>192</v>
       </c>
       <c r="J289" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K289" t="s">
         <v>1229</v>
       </c>
-      <c r="K289" t="s">
+      <c r="L289" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="L289" s="1" t="s">
+      <c r="R289" t="s">
+        <v>31</v>
+      </c>
+      <c r="S289" t="s">
         <v>1231</v>
-      </c>
-      <c r="R289" t="s">
-        <v>31</v>
-      </c>
-      <c r="S289" t="s">
-        <v>1232</v>
       </c>
       <c r="T289" s="2">
         <v>182</v>
@@ -18497,15 +18497,15 @@
         <v>2</v>
       </c>
       <c r="X289" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="290" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B290" t="s">
         <v>1209</v>
-      </c>
-      <c r="B290" t="s">
-        <v>1210</v>
       </c>
       <c r="D290" t="s">
         <v>783</v>
@@ -18514,13 +18514,13 @@
         <v>59</v>
       </c>
       <c r="F290" t="s">
+        <v>1232</v>
+      </c>
+      <c r="J290" t="s">
         <v>1233</v>
       </c>
-      <c r="J290" t="s">
+      <c r="L290" s="1" t="s">
         <v>1234</v>
-      </c>
-      <c r="L290" s="1" t="s">
-        <v>1235</v>
       </c>
       <c r="R290" t="s">
         <v>89</v>
@@ -18538,30 +18538,30 @@
         <v>2</v>
       </c>
       <c r="X290" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="291" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B291" t="s">
         <v>1209</v>
-      </c>
-      <c r="B291" t="s">
-        <v>1210</v>
       </c>
       <c r="D291" t="s">
         <v>670</v>
       </c>
       <c r="E291" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F291" t="s">
         <v>1236</v>
       </c>
-      <c r="F291" t="s">
+      <c r="J291" t="s">
         <v>1237</v>
       </c>
-      <c r="J291" t="s">
+      <c r="L291" s="1" t="s">
         <v>1238</v>
-      </c>
-      <c r="L291" s="1" t="s">
-        <v>1239</v>
       </c>
       <c r="R291" t="s">
         <v>31</v>
@@ -18579,15 +18579,15 @@
         <v>2</v>
       </c>
       <c r="X291" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="292" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B292" t="s">
         <v>1209</v>
-      </c>
-      <c r="B292" t="s">
-        <v>1210</v>
       </c>
       <c r="D292" t="s">
         <v>260</v>
@@ -18599,13 +18599,13 @@
         <v>96</v>
       </c>
       <c r="J292" t="s">
+        <v>1239</v>
+      </c>
+      <c r="K292" t="s">
         <v>1240</v>
       </c>
-      <c r="K292" t="s">
+      <c r="L292" s="1" t="s">
         <v>1241</v>
-      </c>
-      <c r="L292" s="1" t="s">
-        <v>1242</v>
       </c>
       <c r="R292" t="s">
         <v>31</v>
@@ -18623,15 +18623,15 @@
         <v>2</v>
       </c>
       <c r="X292" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="293" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B293" t="s">
         <v>1243</v>
-      </c>
-      <c r="B293" t="s">
-        <v>1244</v>
       </c>
       <c r="D293" t="s">
         <v>260</v>
@@ -18643,16 +18643,16 @@
         <v>35</v>
       </c>
       <c r="J293" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K293" t="s">
         <v>1245</v>
       </c>
-      <c r="K293" t="s">
+      <c r="L293" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="L293" s="1" t="s">
+      <c r="M293" t="s">
         <v>1247</v>
-      </c>
-      <c r="M293" t="s">
-        <v>1248</v>
       </c>
       <c r="R293" t="s">
         <v>31</v>
@@ -18670,15 +18670,15 @@
         <v>2</v>
       </c>
       <c r="X293" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="294" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B294" t="s">
         <v>1243</v>
-      </c>
-      <c r="B294" t="s">
-        <v>1244</v>
       </c>
       <c r="D294" t="s">
         <v>260</v>
@@ -18690,10 +18690,10 @@
         <v>485</v>
       </c>
       <c r="J294" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L294" s="1" t="s">
         <v>1249</v>
-      </c>
-      <c r="L294" s="1" t="s">
-        <v>1250</v>
       </c>
       <c r="R294" t="s">
         <v>31</v>
@@ -18711,18 +18711,18 @@
         <v>2</v>
       </c>
       <c r="X294" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="295" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B295" t="s">
         <v>1243</v>
       </c>
-      <c r="B295" t="s">
-        <v>1244</v>
-      </c>
       <c r="D295" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E295" t="s">
         <v>59</v>
@@ -18731,13 +18731,13 @@
         <v>60</v>
       </c>
       <c r="J295" t="s">
+        <v>1251</v>
+      </c>
+      <c r="K295" t="s">
         <v>1252</v>
       </c>
-      <c r="K295" t="s">
+      <c r="L295" s="1" t="s">
         <v>1253</v>
-      </c>
-      <c r="L295" s="1" t="s">
-        <v>1254</v>
       </c>
       <c r="R295" t="s">
         <v>325</v>
@@ -18755,33 +18755,33 @@
         <v>2</v>
       </c>
       <c r="X295" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="296" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B296" t="s">
         <v>1243</v>
       </c>
-      <c r="B296" t="s">
-        <v>1244</v>
-      </c>
       <c r="D296" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E296" t="s">
         <v>1255</v>
       </c>
-      <c r="E296" t="s">
+      <c r="F296" t="s">
         <v>1256</v>
       </c>
-      <c r="F296" t="s">
+      <c r="J296" t="s">
         <v>1257</v>
       </c>
-      <c r="J296" t="s">
+      <c r="K296" t="s">
         <v>1258</v>
       </c>
-      <c r="K296" t="s">
+      <c r="L296" s="1" t="s">
         <v>1259</v>
-      </c>
-      <c r="L296" s="1" t="s">
-        <v>1260</v>
       </c>
       <c r="R296" t="s">
         <v>31</v>
@@ -18799,15 +18799,15 @@
         <v>2</v>
       </c>
       <c r="X296" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="297" spans="1:24" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="7" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B297" s="7" t="s">
         <v>1243</v>
-      </c>
-      <c r="B297" s="7" t="s">
-        <v>1244</v>
       </c>
       <c r="D297" s="7" t="s">
         <v>33</v>
@@ -18819,13 +18819,13 @@
         <v>628</v>
       </c>
       <c r="J297" s="7" t="s">
+        <v>1260</v>
+      </c>
+      <c r="K297" s="7" t="s">
         <v>1261</v>
       </c>
-      <c r="K297" s="7" t="s">
+      <c r="L297" s="8" t="s">
         <v>1262</v>
-      </c>
-      <c r="L297" s="8" t="s">
-        <v>1263</v>
       </c>
       <c r="R297" s="7" t="s">
         <v>31</v>
@@ -18844,15 +18844,15 @@
         <v>2</v>
       </c>
       <c r="X297" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="298" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B298" t="s">
         <v>1243</v>
-      </c>
-      <c r="B298" t="s">
-        <v>1244</v>
       </c>
       <c r="D298" t="s">
         <v>33</v>
@@ -18864,13 +18864,13 @@
         <v>35</v>
       </c>
       <c r="J298" t="s">
+        <v>1263</v>
+      </c>
+      <c r="K298" t="s">
         <v>1264</v>
       </c>
-      <c r="K298" t="s">
+      <c r="L298" s="1" t="s">
         <v>1265</v>
-      </c>
-      <c r="L298" s="1" t="s">
-        <v>1266</v>
       </c>
       <c r="R298" t="s">
         <v>31</v>
@@ -18888,7 +18888,7 @@
         <v>2</v>
       </c>
       <c r="X298" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="299" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19825,13 +19825,13 @@
     </row>
     <row r="321" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B321" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D321" t="s">
         <v>1612</v>
-      </c>
-      <c r="D321" t="s">
-        <v>1613</v>
       </c>
       <c r="E321" t="s">
         <v>34</v>
@@ -19843,7 +19843,7 @@
         <v>67</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="R321" t="s">
         <v>31</v>
@@ -19861,18 +19861,18 @@
         <v>3</v>
       </c>
       <c r="X321" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="322" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B322" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="D322" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="E322" t="s">
         <v>59</v>
@@ -19881,10 +19881,10 @@
         <v>60</v>
       </c>
       <c r="J322" t="s">
+        <v>1615</v>
+      </c>
+      <c r="L322" s="1" t="s">
         <v>1616</v>
-      </c>
-      <c r="L322" s="1" t="s">
-        <v>1617</v>
       </c>
       <c r="R322" t="s">
         <v>408</v>
@@ -19902,15 +19902,15 @@
         <v>3</v>
       </c>
       <c r="X322" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="323" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B323" t="s">
         <v>1618</v>
-      </c>
-      <c r="B323" t="s">
-        <v>1619</v>
       </c>
       <c r="D323">
         <v>1480</v>
@@ -19922,13 +19922,13 @@
         <v>118</v>
       </c>
       <c r="J323" t="s">
+        <v>1619</v>
+      </c>
+      <c r="K323" t="s">
         <v>1620</v>
       </c>
-      <c r="K323" t="s">
+      <c r="L323" s="1" t="s">
         <v>1621</v>
-      </c>
-      <c r="L323" s="1" t="s">
-        <v>1622</v>
       </c>
       <c r="R323" t="s">
         <v>31</v>
@@ -19946,39 +19946,39 @@
         <v>3</v>
       </c>
       <c r="X323" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="324" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B324" t="s">
         <v>1618</v>
       </c>
-      <c r="B324" t="s">
-        <v>1619</v>
-      </c>
       <c r="D324" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="E324" t="s">
         <v>117</v>
       </c>
       <c r="F324" t="s">
+        <v>1623</v>
+      </c>
+      <c r="J324" t="s">
         <v>1624</v>
       </c>
-      <c r="J324" t="s">
+      <c r="K324" t="s">
         <v>1625</v>
       </c>
-      <c r="K324" t="s">
+      <c r="L324" s="1" t="s">
         <v>1626</v>
       </c>
-      <c r="L324" s="1" t="s">
+      <c r="R324" t="s">
+        <v>31</v>
+      </c>
+      <c r="S324" t="s">
         <v>1627</v>
-      </c>
-      <c r="R324" t="s">
-        <v>31</v>
-      </c>
-      <c r="S324" t="s">
-        <v>1628</v>
       </c>
       <c r="T324" s="2">
         <v>141</v>
@@ -19990,15 +19990,15 @@
         <v>3</v>
       </c>
       <c r="X324" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="325" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B325" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D325">
         <v>1444</v>
@@ -20007,7 +20007,7 @@
         <v>117</v>
       </c>
       <c r="F325" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="J325" t="s">
         <v>393</v>
@@ -20016,13 +20016,13 @@
         <v>394</v>
       </c>
       <c r="L325" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="R325" t="s">
+        <v>31</v>
+      </c>
+      <c r="S325" t="s">
         <v>1630</v>
-      </c>
-      <c r="R325" t="s">
-        <v>31</v>
-      </c>
-      <c r="S325" t="s">
-        <v>1631</v>
       </c>
       <c r="T325" s="2">
         <v>230</v>
@@ -20034,15 +20034,15 @@
         <v>3</v>
       </c>
       <c r="X325" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="326" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B326" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D326">
         <v>1446</v>
@@ -20054,19 +20054,19 @@
         <v>118</v>
       </c>
       <c r="J326" t="s">
+        <v>1631</v>
+      </c>
+      <c r="K326" t="s">
         <v>1632</v>
       </c>
-      <c r="K326" t="s">
+      <c r="L326" s="1" t="s">
         <v>1633</v>
-      </c>
-      <c r="L326" s="1" t="s">
-        <v>1634</v>
       </c>
       <c r="R326" t="s">
         <v>325</v>
       </c>
       <c r="S326" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="T326" s="2">
         <v>292</v>
@@ -20078,15 +20078,15 @@
         <v>3</v>
       </c>
       <c r="X326" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="327" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="B327" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D327">
         <v>1474</v>
@@ -20095,16 +20095,16 @@
         <v>117</v>
       </c>
       <c r="F327" t="s">
+        <v>1636</v>
+      </c>
+      <c r="J327" t="s">
         <v>1637</v>
       </c>
-      <c r="J327" t="s">
+      <c r="K327" t="s">
         <v>1638</v>
       </c>
-      <c r="K327" t="s">
+      <c r="L327" s="1" t="s">
         <v>1639</v>
-      </c>
-      <c r="L327" s="1" t="s">
-        <v>1640</v>
       </c>
       <c r="R327" t="s">
         <v>325</v>
@@ -20122,15 +20122,15 @@
         <v>3</v>
       </c>
       <c r="X327" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="328" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="B328" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D328">
         <v>1482</v>
@@ -20139,16 +20139,16 @@
         <v>117</v>
       </c>
       <c r="F328" t="s">
+        <v>1640</v>
+      </c>
+      <c r="J328" t="s">
         <v>1641</v>
       </c>
-      <c r="J328" t="s">
+      <c r="K328" t="s">
         <v>1642</v>
       </c>
-      <c r="K328" t="s">
+      <c r="L328" s="1" t="s">
         <v>1643</v>
-      </c>
-      <c r="L328" s="1" t="s">
-        <v>1644</v>
       </c>
       <c r="R328" t="s">
         <v>325</v>
@@ -20166,30 +20166,30 @@
         <v>3</v>
       </c>
       <c r="X328" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="329" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B329" t="s">
         <v>1645</v>
       </c>
-      <c r="B329" t="s">
+      <c r="D329" t="s">
         <v>1646</v>
       </c>
-      <c r="D329" t="s">
+      <c r="E329" t="s">
         <v>1647</v>
       </c>
-      <c r="E329" t="s">
+      <c r="F329" t="s">
         <v>1648</v>
       </c>
-      <c r="F329" t="s">
+      <c r="J329" t="s">
         <v>1649</v>
       </c>
-      <c r="J329" t="s">
+      <c r="L329" s="1" t="s">
         <v>1650</v>
-      </c>
-      <c r="L329" s="1" t="s">
-        <v>1651</v>
       </c>
       <c r="R329" t="s">
         <v>31</v>
@@ -20207,15 +20207,15 @@
         <v>3</v>
       </c>
       <c r="X329" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="330" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B330" t="s">
         <v>1645</v>
-      </c>
-      <c r="B330" t="s">
-        <v>1646</v>
       </c>
       <c r="D330" t="s">
         <v>557</v>
@@ -20227,10 +20227,10 @@
         <v>35</v>
       </c>
       <c r="J330" t="s">
+        <v>1651</v>
+      </c>
+      <c r="L330" s="1" t="s">
         <v>1652</v>
-      </c>
-      <c r="L330" s="1" t="s">
-        <v>1653</v>
       </c>
       <c r="R330" t="s">
         <v>31</v>
@@ -20248,7 +20248,7 @@
         <v>3</v>
       </c>
       <c r="X330" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -5162,7 +5162,7 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Petrus_Christus_-_The_Last_Judgement_(right_wing_of_the_altar),_1452_-Gem%C3%A4ldegalerie_Berlin.jpg#/media/File:Petrus_christus,_annunciazione,_nativit%C3%A0,_e_giudizio_universale,_1452,_01.JPG</t>
+          <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Petrus_Christus_-_The_Last_Judgement_(right_wing_of_the_altar),_1452_-Gem%C3%A4ldegalerie_Berlin.jpg</t>
         </is>
       </c>
       <c r="R68" s="5" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Petrus_Christus_-_The_Last_Judgement_(right_wing_of_the_altar),_1452_-Gem%C3%A4ldegalerie_Berlin.jpg#/media/File:Petrus_christus,_annunciazione,_nativit%C3%A0,_e_giudizio_universale,_1452,_01.JPG</t>
+          <t>https://commons.wikimedia.org/wiki/Special:Redirect/file/Petrus_Christus_-_The_Last_Judgement_(right_wing_of_the_altar),_1452_-Gem%C3%A4ldegalerie_Berlin.jpg</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr">
@@ -23585,14 +23585,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1a/Zuschreibung_unsicher%2C_Maelwael%2C_Johan_-_Madonna_with_Butterflies_-_87.1_-_Gem%C3%A4ldegalerie.jpg/960px-Zuschreibung_unsicher%2C_Maelwael%2C_Johan_-_Madonna_with_Butterflies_-_87.1_-_Gem%C3%A4ldegalerie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Accademia_-_Miracolo_della_reliquia_della_Croce_al_ponte_di_San_Lorenzo_-_Gentile_Bellini_-_cat.568.jpg/1280px-Accademia_-_Miracolo_della_reliquia_della_Croce_al_ponte_di_San_Lorenzo_-_Gentile_Bellini_-_cat.568.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
@@ -23600,8 +23600,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1f/Bartolom%C3%A9_bermejo%2C_san_michele_trionfa_sul_demonio%2C_1468%2C_01.jpg/500px-Bartolom%C3%A9_bermejo%2C_san_michele_trionfa_sul_demonio%2C_1468%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Bartolom%C3%A9_Bermejo_%281425_-_1500%29_-_The_Death_of_the_Virgin_-_552_-_Gem%C3%A4ldegalerie.jpg/960px-Bartolom%C3%A9_Bermejo_%281425_-_1500%29_-_The_Death_of_the_Virgin_-_552_-_Gem%C3%A4ldegalerie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
@@ -23618,22 +23618,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/23/Portrait_of_a_Man_with_a_Medal_of_Cosimo_the_Elder_-_Sandro_Botticelli.jpg/960px-Portrait_of_a_Man_with_a_Medal_of_Cosimo_the_Elder_-_Sandro_Botticelli.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bb/Dieric_Bouts_-_Passion_Altarpiece_%28central%29_-_WGA02989.jpg/1280px-Dieric_Bouts_-_Passion_Altarpiece_%28central%29_-_WGA02989.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Dierick_Bouts_%281410_-_6.5.1475%29_-_Christ_in_the_House_of_the_Pharisee_Simon_-_533A_-_Gem%C3%A4ldegalerie.jpg/1280px-Dierick_Bouts_%281410_-_6.5.1475%29_-_Christ_in_the_House_of_the_Pharisee_Simon_-_533A_-_Gem%C3%A4ldegalerie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ef/Robert_Campin_-_Triptych_with_the_Annunciation%2C_known_as_the_%22Merode_Altarpiece%22_-_Google_Art_Project.jpg/1280px-Robert_Campin_-_Triptych_with_the_Annunciation%2C_known_as_the_%22Merode_Altarpiece%22_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Master_of_Fl%C3%A9malle_%28Workshop_of_Robert_Campin%29_-_The_Fl%C3%A9malle_Panels_-_Google_Art_Project_%28cwF5YRuJkBMAXQ%29.jpg/500px-Master_of_Fl%C3%A9malle_%28Workshop_of_Robert_Campin%29_-_The_Fl%C3%A9malle_Panels_-_Google_Art_Project_%28cwF5YRuJkBMAXQ%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Robert_Campin_-_The_Virgin_and_Child_before_a_Firescreen_%28National_Gallery_London%29.jpg/960px-Robert_Campin_-_The_Virgin_and_Child_before_a_Firescreen_%28National_Gallery_London%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId58"/>
@@ -23646,9 +23646,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" location="/media/File:Petrus_christus,_annunciazione,_nativit%C3%A0,_e_giudizio_universale,_1452,_01.JPG" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" location="/media/File:Petrus_christus,_annunciazione,_nativit%C3%A0,_e_giudizio_universale,_1452,_01.JPG" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId73"/>
@@ -23659,7 +23659,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Carlo_Crivelli_-_The_Crucifixion_-_1929.862_-_Art_Institute_of_Chicago.jpg/960px-Carlo_Crivelli_-_The_Crucifixion_-_1929.862_-_Art_Institute_of_Chicago.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId84"/>
@@ -23671,17 +23671,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Antonello_da_Messina_-_St_Jerome_in_his_study_-_National_Gallery_London.jpg/960px-Antonello_da_Messina_-_St_Jerome_in_his_study_-_National_Gallery_London.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Calvarieberg%2C_Antonello_da_Messina%2C_1475%2C_Koninlijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_4.jpg/960px-Calvarieberg%2C_Antonello_da_Messina%2C_1475%2C_Koninlijk_Museum_voor_Schone_Kunsten_Antwerpen%2C_4.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/Antonello_da_Messina_-_St._Sebastian_-_Google_Art_Project.jpg/960px-Antonello_da_Messina_-_St._Sebastian_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2e/Gerard_David_-_Adoration_of_the_Shepherds_%28c._1485%29_Google_Art_Project.jpg/960px-Gerard_David_-_Adoration_of_the_Shepherds_%28c._1485%29_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/Mus%C3%A9e_Unterlinden_-_Martin_Schongauer_-_retable_des_Dominicains_%28~1480%29.jpg/1280px-Mus%C3%A9e_Unterlinden_-_Martin_Schongauer_-_retable_des_Dominicains_%28~1480%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N101" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId106"/>
@@ -23695,22 +23695,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/Mus%C3%A9e_Unterlinden_-_Martin_Schongauer_-_retable_des_Dominicains_%28~1480%29.jpg/1280px-Mus%C3%A9e_Unterlinden_-_Martin_Schongauer_-_retable_des_Dominicains_%28~1480%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N114" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/Mus%C3%A9e_Unterlinden_-_Martin_Schongauer_-_retable_des_Dominicains_%28~1480%29.jpg/1280px-Mus%C3%A9e_Unterlinden_-_Martin_Schongauer_-_retable_des_Dominicains_%28~1480%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Andrea_del_castagno%2C_scudo_di_david_con_la_testa_di_golia%2C_1450-55_circa%2C_02.JPG/960px-Andrea_del_castagno%2C_scudo_di_david_con_la_testa_di_golia%2C_1450-55_circa%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Francesco_del_Cossa%2C_santa_lucia%2C_dal_polittico_griffoni%2C_1472-73.JPG/960px-Francesco_del_Cossa%2C_santa_lucia%2C_dal_polittico_griffoni%2C_1472-73.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" display="https://upload.wikimedia.org/wikipedia/commons/2/24/Pala_dei_Mercanti._Madonna_col_Bambino_in_trono_fra_i_Santi_Petronio_e_Giovanni_Evangelista_adorata_dal_committente_Alberto_Cattani._Pinacoteca%2C_Bologna.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b6/Andrea_del_verrocchio_e_lorenzo_di_credi%2C_madonna_di_piazza%2C_1475-86_ca._%28pistoia%2C_duomo%29_02.jpg/1280px-Andrea_del_verrocchio_e_lorenzo_di_credi%2C_madonna_di_piazza%2C_1475-86_ca._%28pistoia%2C_duomo%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Andrea_del_Verrocchio_%281435_-_1488%29_-_Maria_mit_dem_Kind_-_104A_-_Gem%C3%A4ldegalerie.jpg/960px-Andrea_del_Verrocchio_%281435_-_1488%29_-_Maria_mit_dem_Kind_-_104A_-_Gem%C3%A4ldegalerie.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e4/The_Virgin_and_Child_with_Two_Angels%2C_Andrea_del_Verrocchio.jpg/960px-The_Virgin_and_Child_with_Two_Angels%2C_Andrea_del_Verrocchio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/11/Workshop_of_Andrea_del_Verrocchio%2C_1470s_Metropolitan_Museum_N-Y.jpg/960px-Workshop_of_Andrea_del_Verrocchio%2C_1470s_Metropolitan_Museum_N-Y.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId135"/>
@@ -23728,11 +23728,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Pinturicchio%2C_madonna_della_pace%2C_1490_circa._143x70_cm%2C_sanseverino_marche%2C_pinacoteca_civica%2C_dettaglio.jpg/960px-Pinturicchio%2C_madonna_della_pace%2C_1490_circa._143x70_cm%2C_sanseverino_marche%2C_pinacoteca_civica%2C_dettaglio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b4/Piero_di_Cosimo_-_Liberazione_di_Andromeda_-_Google_Art_Project.jpg/1280px-Piero_di_Cosimo_-_Liberazione_di_Andromeda_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N150" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId157"/>
@@ -23740,13 +23740,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N154" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Masaccio%2C_polittico_di_pisa%2C_madonna_col_bambino%2C_berlino_135%2C50x73_cm.jpg/500px-Masaccio%2C_polittico_di_pisa%2C_madonna_col_bambino%2C_berlino_135%2C50x73_cm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N155" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8b/Masaccio_-_Crocifissione_%28Cuspide_di_Polittico_di_Pisa%29.jpg/960px-Masaccio_-_Crocifissione_%28Cuspide_di_Polittico_di_Pisa%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N156" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N157" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Expulsion_from_the_Garden_of_Eden_Masaccio_Cappella_Brancacci.jpg/960px-Expulsion_from_the_Garden_of_Eden_Masaccio_Cappella_Brancacci.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N158" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P158" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId171"/>
@@ -23768,15 +23768,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fd/Ritratto_d%27uomo_detto_%22Principe_moscovita%22_PR_57_Musei_di_Strada_Nuova.jpg/960px-Ritratto_d%27uomo_detto_%22Principe_moscovita%22_PR_57_Musei_di_Strada_Nuova.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N178" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Saint_George_and_the_princess_by_Pisanello_-_Pellegrini_Chapel_-_Sant%27Anastasia_-_Verona_2016_%282%29.jpg/1280px-Saint_George_and_the_princess_by_Pisanello_-_Pellegrini_Chapel_-_Sant%27Anastasia_-_Verona_2016_%282%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N178" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9c/Pisanello%2C_ritratto_di_leonello_d%27este%2C_1441%2C_01.jpg/960px-Pisanello%2C_ritratto_di_leonello_d%27este%2C_1441%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c4/Portrait_d%27une_princesse_de_la_Maison_d%27Este_-_Pisanello_-_Mus%C3%A9e_du_Louvre_Peintures_RF_766.jpg/960px-Portrait_d%27une_princesse_de_la_Maison_d%27Este_-_Pisanello_-_Mus%C3%A9e_du_Louvre_Peintures_RF_766.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cc/Portrait_de_l%27artiste_tenant_un_chardon_-_Albrecht_D%C3%BCrer_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2382.jpg/960px-Portrait_de_l%27artiste_tenant_un_chardon_-_Albrecht_D%C3%BCrer_-_Mus%C3%A9e_du_Louvre_Peintures_RF_2382.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/11/Selbstportr%C3%A4t%2C_by_Albrecht_D%C3%BCrer%2C_from_Prado_in_Google_Earth.jpg/960px-Selbstportr%C3%A4t%2C_by_Albrecht_D%C3%BCrer%2C_from_Prado_in_Google_Earth.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId201"/>
@@ -23795,7 +23795,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId215"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/75/Domenico_ghirlandaio%2C_san_girolamo_nello_studio%2C_1480_ca._01.jpg/1920px-Domenico_ghirlandaio%2C_san_girolamo_nello_studio%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId219"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId220"/>
@@ -23806,13 +23806,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N211" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cc/Montefalco_-_Chiesa_di_San_Francesco%2C_Vita_di_San_Francesco_01.jpg/960px-Montefalco_-_Chiesa_di_San_Francesco%2C_Vita_di_San_Francesco_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N211" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0b/Benozzo_Gozzoli%2C_Partenza_di_sant%E2%80%99Agostino_per_Roma%2C_1465%2C_San_Gimignano%2C_Chiesa_di_Sant%E2%80%99Agostino.jpg/1280px-Benozzo_Gozzoli%2C_Partenza_di_sant%E2%80%99Agostino_per_Roma%2C_1465%2C_San_Gimignano%2C_Chiesa_di_Sant%E2%80%99Agostino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Benozzo_gozzoli%2C_pala_della_sapienza_nuova%2C_1456%2C_dal_collegio_della_sapienza_nuova_a_pg%2C_02.jpg/1280px-Benozzo_gozzoli%2C_pala_della_sapienza_nuova%2C_1456%2C_dal_collegio_della_sapienza_nuova_a_pg%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId231"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/37/Workshop_of_Benozzo_Gozzoli_-_The_Mystic_Marriage_of_St_Catherine_-_Google_Art_Project.jpg/960px-Workshop_of_Benozzo_Gozzoli_-_The_Mystic_Marriage_of_St_Catherine_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" display="https://upload.wikimedia.org/wikipedia/commons/6/6f/Benozzo_Gozzoli_%2C_St_Sebastian_%28on_the_pillar%29%2C_1464-65%2C_fresco%2C_Apsidal_chapel%2C_Sant%27Agostino%2C_San_Gimignano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId235"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId237"/>
@@ -23820,139 +23820,154 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId239"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/98/La_Vierge_et_l%27Enfant_entour%C3%A9s_d%27anges%2C_de_saint_Frediano_et_de_saint_Augustin_-_Fra_Filippo_Lippi_-_Mus%C3%A9e_du_Louvre_Peintures_INV_339_%3B_MR_327.jpg/1280px-La_Vierge_et_l%27Enfant_entour%C3%A9s_d%27anges%2C_de_saint_Frediano_et_de_saint_Augustin_-_Fra_Filippo_Lippi_-_Mus%C3%A9e_du_Louvre_Peintures_INV_339_%3B_MR_327.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="rId243"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N225" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="rId245"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N227" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/Adoration_of_the_Christ_child_with_the_young_St._John_the_baptist%2CSt._Romuald%2Cangels%2Cthe_hands_of_God_the_Father_and_the_Holy_Ghost_as_a_dove_-_Filippo_Lippi.jpg/1920px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId249"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N235" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L243" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L244" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L245" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Andrea_Mantegna%2C_Kunsthistorisches_Museum_Wien%2C_Gem%C3%A4ldegalerie_-_Hl._Sebastian_-_GG_301_-_Kunsthistorisches_Museum.jpg/500px-Andrea_Mantegna%2C_Kunsthistorisches_Museum_Wien%2C_Gem%C3%A4ldegalerie_-_Hl._Sebastian_-_GG_301_-_Kunsthistorisches_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L246" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L247" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7c/Minerve_chassant_les_Vices_du_jardin_des_Vertus%2C_Mantegna_%28Louvre_INV_371%29_02.jpg/1280px-Minerve_chassant_les_Vices_du_jardin_des_Vertus%2C_Mantegna_%28Louvre_INV_371%29_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L248" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L249" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L253" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L254" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L255" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L256" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L257" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L258" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L261" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N261" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L262" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N262" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L263" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N263" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L264" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N264" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N265" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N266" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L267" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N267" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L268" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N268" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L271" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L272" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L273" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L274" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d8/Perugino%2C_Fortitude_and_Temperance_with_Six_Antique_Heroes_00.jpg/1280px-Perugino%2C_Fortitude_and_Temperance_with_Six_Antique_Heroes_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N274" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L275" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Perugino_-_The_Crucifixion_with_the_Virgin%2C_Saints_John%2C_Jerome%2C_and_Mary_Magdalene_-_Galitzin-Triptych.jpg/1280px-Perugino_-_The_Crucifixion_with_the_Virgin%2C_Saints_John%2C_Jerome%2C_and_Mary_Magdalene_-_Galitzin-Triptych.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L276" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L277" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L278" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" display="https://upload.wikimedia.org/wikipedia/commons/thumb/d/dd/Enguerrand_QUARTON_-_Le_couronnement_de_la_Vierge_-_1454_-_Mus%C3%A9e_Pierre-de-Luxembourg_%28Villeneuve-l%C3%A8s-Avignon%29.jpg/1280px-Enguerrand_QUARTON_-_Le_couronnement_de_la_Vierge_-_1454_-_Mu" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/fb/Enguerrand_Quarton%2C_La_Piet%C3%A0_de_Villeneuve-l%C3%A8s-Avignon_%28c._1455%29.jpg/1280px-Enguerrand_Quarton%2C_La_Piet%C3%A0_de_Villeneuve-l%C3%A8s-Avignon_%28c._1455%29.jpg?utm_source=commons.w" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L287" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Colmar_%28Haut-Rhin%29_-_Eglise_des_Dominicains_-_Retable_%22La_Vierge_au_buisson_de_roses%22_%28Martin_Schongauer%2C_1473%29_%2850988295766%29.jpg/1280px-Colmar_%28Haut-Rhin%29_-_Eglise_des_Dominicains_-_Retable_%22La_Vierge_au_buisson_de_roses%22_%28Martin_Schongauer%2C_1473%29_%2850988295766%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L288" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L289" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d9/Colmar_-_Unterlinden_Museum_-_Altarpiece_of_the_Dominicans%2C_Childhood_and_Passion_of_Christ_-_Martin_Schongauer_%28ca_1445-1491%29_%26_Atelier_-_Adoration_of_the_magi.jpg/1280px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L290" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Colmar_-_Unterlinden_Museum_-_Altarpiece_of_the_Dominicans%2C_Childhood_and_Passion_of_Christ_-_Martin_Schongauer_%28ca_1445-1491%29_%26_Atelier%2C_ca_1480_-_Oil_on_wood_panel_-_The_Descent_from_the_Cross_or_Deposition_of_Christ.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L291" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L292" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L293" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L294" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L295" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L296" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L297" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L298" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L299" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L300" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L301" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L302" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L303" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L304" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L305" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L306" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L307" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L308" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L309" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L310" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L311" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L312" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L313" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L314" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f0/Circle_of_Hugo_van_der_Goes_-_Virgin_and_Child_%28c._1485%29.jpg/1280px-Circle_of_Hugo_van_der_Goes_-_Virgin_and_Child_%28c._1485%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L315" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L316" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L317" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L318" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L319" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L320" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L321" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L322" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L323" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L324" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L325" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L326" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L327" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L328" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L329" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L330" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L331" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L332" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L333" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L334" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L335" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L336" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L337" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L338" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L339" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L340" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L344" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L345" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L346" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L347" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L351" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L352" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L353" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Frari_%28Venice%29_-_Cappella_Bernardo_-_Polyptych_by_Bartolomeo_Vivarini.jpg/960px-Frari_%28Venice%29_-_Cappella_Bernardo_-_Polyptych_by_Bartolomeo_Vivarini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L354" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N235" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L243" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L244" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L245" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L246" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L247" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L248" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L249" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L251" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L253" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L254" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L255" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L256" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L257" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L258" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L261" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N261" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L262" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N262" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L263" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N263" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L264" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N264" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N265" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N266" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L267" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N267" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L268" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N268" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L271" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L272" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L273" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L274" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N274" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L275" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L276" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L277" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L278" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L283" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M283" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L284" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M284" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L285" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L286" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L287" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L288" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N288" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L289" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N289" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L290" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N290" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L291" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L292" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L293" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L294" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L295" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L296" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L297" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L298" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L299" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L300" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L301" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L302" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L303" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L304" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L305" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L306" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L307" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L308" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L309" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L310" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L311" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L312" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L313" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L314" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L315" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L316" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L317" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L318" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L319" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L320" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L321" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L322" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L323" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L324" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L325" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L326" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L327" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L328" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L329" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L330" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L331" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L332" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L333" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L334" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L335" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L336" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L337" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L338" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L339" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L340" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L341" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L342" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L343" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L344" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L345" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L346" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L347" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L348" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L349" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L350" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L351" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L352" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L353" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L354" r:id="rId389"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5795CC4-A6D2-4B58-A509-96DCC4EFAB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAD1040-7DCA-4356-A5FA-63C77EEF0EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="15480" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="1140" windowWidth="15480" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3600" uniqueCount="1635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="1637">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -4928,6 +4928,12 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Hieronymus_Bosch_-_Triptych_of_the_Adoration_of_the_Magi_-_WGA2606.jpg/1280px-Hieronymus_Bosch_-_Triptych_of_the_Adoration_of_the_Magi_-_WGA2606.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Le Calvaire</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Luca_signorelli%2C_crocifissione%2C_urbino%2C_gnm.jpg/960px-Luca_signorelli%2C_crocifissione%2C_urbino%2C_gnm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -5789,7 +5795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X352"/>
+  <dimension ref="A1:X353"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="25" customWidth="1"/>
@@ -18123,47 +18129,44 @@
       </c>
     </row>
     <row r="291" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A291" s="25" t="s">
-        <v>1385</v>
-      </c>
-      <c r="B291" s="25" t="s">
-        <v>1386</v>
-      </c>
-      <c r="D291" s="5">
-        <v>1469</v>
+      <c r="A291" s="5" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D291" s="6">
+        <v>1494</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>589</v>
+        <v>657</v>
       </c>
       <c r="F291" s="5" t="s">
-        <v>1387</v>
+        <v>658</v>
       </c>
       <c r="J291" s="5" t="s">
-        <v>1388</v>
+        <v>1635</v>
       </c>
       <c r="K291" s="5" t="s">
-        <v>1389</v>
-      </c>
-      <c r="L291" s="7" t="s">
-        <v>1390</v>
-      </c>
-      <c r="M291" s="5" t="s">
-        <v>1391</v>
+        <v>420</v>
+      </c>
+      <c r="L291" s="47" t="s">
+        <v>1636</v>
       </c>
       <c r="R291" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S291" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="T291" s="6">
+        <v>156</v>
+      </c>
+      <c r="U291" s="6">
         <v>104</v>
       </c>
-      <c r="T291" s="6">
-        <v>349</v>
-      </c>
-      <c r="U291" s="6">
-        <v>305</v>
-      </c>
       <c r="W291" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18173,38 +18176,38 @@
       <c r="B292" s="25" t="s">
         <v>1386</v>
       </c>
-      <c r="D292" s="5" t="s">
-        <v>1392</v>
+      <c r="D292" s="5">
+        <v>1469</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>86</v>
+        <v>589</v>
       </c>
       <c r="F292" s="5" t="s">
-        <v>87</v>
+        <v>1387</v>
       </c>
       <c r="J292" s="5" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="K292" s="5" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="L292" s="7" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="M292" s="5" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="R292" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S292" s="5" t="s">
-        <v>1397</v>
+        <v>104</v>
       </c>
       <c r="T292" s="6">
-        <v>239</v>
+        <v>349</v>
       </c>
       <c r="U292" s="6">
-        <v>102</v>
+        <v>305</v>
       </c>
       <c r="W292" s="6">
         <v>3</v>
@@ -18217,8 +18220,8 @@
       <c r="B293" s="25" t="s">
         <v>1386</v>
       </c>
-      <c r="D293" s="5">
-        <v>1460</v>
+      <c r="D293" s="5" t="s">
+        <v>1392</v>
       </c>
       <c r="E293" s="5" t="s">
         <v>86</v>
@@ -18227,22 +18230,28 @@
         <v>87</v>
       </c>
       <c r="J293" s="5" t="s">
-        <v>1398</v>
+        <v>1393</v>
+      </c>
+      <c r="K293" s="5" t="s">
+        <v>1394</v>
       </c>
       <c r="L293" s="7" t="s">
-        <v>1399</v>
+        <v>1395</v>
+      </c>
+      <c r="M293" s="5" t="s">
+        <v>1396</v>
       </c>
       <c r="R293" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S293" s="5" t="s">
-        <v>248</v>
+        <v>1397</v>
       </c>
       <c r="T293" s="6">
-        <v>116</v>
+        <v>239</v>
       </c>
       <c r="U293" s="6">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="W293" s="6">
         <v>3</v>
@@ -18256,32 +18265,31 @@
         <v>1386</v>
       </c>
       <c r="D294" s="5">
-        <v>1470</v>
+        <v>1460</v>
       </c>
       <c r="E294" s="5" t="s">
-        <v>280</v>
+        <v>86</v>
       </c>
       <c r="F294" s="5" t="s">
-        <v>281</v>
+        <v>87</v>
       </c>
       <c r="J294" s="5" t="s">
-        <v>1400</v>
-      </c>
-      <c r="K294" s="7"/>
+        <v>1398</v>
+      </c>
       <c r="L294" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="R294" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S294" s="5" t="s">
-        <v>45</v>
+        <v>248</v>
       </c>
       <c r="T294" s="6">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="U294" s="6">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="W294" s="6">
         <v>3</v>
@@ -18289,43 +18297,41 @@
     </row>
     <row r="295" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="25" t="s">
-        <v>1402</v>
+        <v>1385</v>
       </c>
       <c r="B295" s="25" t="s">
-        <v>1403</v>
+        <v>1386</v>
       </c>
       <c r="D295" s="5">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>25</v>
+        <v>280</v>
       </c>
       <c r="F295" s="5" t="s">
-        <v>571</v>
+        <v>281</v>
       </c>
       <c r="J295" s="5" t="s">
-        <v>1405</v>
-      </c>
-      <c r="K295" s="5" t="s">
-        <v>1406</v>
-      </c>
+        <v>1400</v>
+      </c>
+      <c r="K295" s="7"/>
       <c r="L295" s="7" t="s">
-        <v>1407</v>
+        <v>1401</v>
       </c>
       <c r="R295" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S295" s="5" t="s">
-        <v>1408</v>
+        <v>45</v>
       </c>
       <c r="T295" s="6">
-        <v>820</v>
+        <v>28</v>
       </c>
       <c r="U295" s="6">
-        <v>515</v>
+        <v>20</v>
       </c>
       <c r="W295" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18335,35 +18341,35 @@
       <c r="B296" s="25" t="s">
         <v>1403</v>
       </c>
-      <c r="D296" s="5" t="s">
-        <v>1409</v>
+      <c r="D296" s="5">
+        <v>1443</v>
       </c>
       <c r="E296" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F296" s="5" t="s">
-        <v>40</v>
+        <v>571</v>
       </c>
       <c r="J296" s="5" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="K296" s="5" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="L296" s="7" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="R296" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S296" s="5" t="s">
-        <v>924</v>
+        <v>1408</v>
       </c>
       <c r="T296" s="6">
-        <v>188</v>
+        <v>820</v>
       </c>
       <c r="U296" s="6">
-        <v>327</v>
+        <v>515</v>
       </c>
       <c r="W296" s="6">
         <v>2</v>
@@ -18377,31 +18383,34 @@
         <v>1403</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="E297" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F297" s="5" t="s">
-        <v>571</v>
+        <v>40</v>
       </c>
       <c r="J297" s="5" t="s">
-        <v>1414</v>
+        <v>1410</v>
+      </c>
+      <c r="K297" s="5" t="s">
+        <v>1411</v>
       </c>
       <c r="L297" s="7" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="R297" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S297" s="5" t="s">
-        <v>29</v>
+        <v>924</v>
       </c>
       <c r="T297" s="6">
-        <v>470</v>
+        <v>188</v>
       </c>
       <c r="U297" s="6">
-        <v>470</v>
+        <v>327</v>
       </c>
       <c r="W297" s="6">
         <v>2</v>
@@ -18415,34 +18424,31 @@
         <v>1403</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>826</v>
+        <v>1413</v>
       </c>
       <c r="E298" s="5" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="F298" s="5" t="s">
-        <v>87</v>
+        <v>571</v>
       </c>
       <c r="J298" s="5" t="s">
-        <v>1416</v>
-      </c>
-      <c r="K298" s="5" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="L298" s="7" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="R298" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S298" s="5" t="s">
-        <v>1419</v>
+        <v>29</v>
       </c>
       <c r="T298" s="6">
-        <v>182</v>
+        <v>470</v>
       </c>
       <c r="U298" s="6">
-        <v>320</v>
+        <v>470</v>
       </c>
       <c r="W298" s="6">
         <v>2</v>
@@ -18456,34 +18462,34 @@
         <v>1403</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>1420</v>
+        <v>826</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="F299" s="5" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="J299" s="5" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="K299" s="5" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="L299" s="7" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="R299" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S299" s="5" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="T299" s="6">
         <v>182</v>
       </c>
       <c r="U299" s="6">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="W299" s="6">
         <v>2</v>
@@ -18496,32 +18502,35 @@
       <c r="B300" s="25" t="s">
         <v>1403</v>
       </c>
-      <c r="D300" s="5">
-        <v>1447</v>
+      <c r="D300" s="5" t="s">
+        <v>1420</v>
       </c>
       <c r="E300" s="5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F300" s="5" t="s">
-        <v>751</v>
+        <v>33</v>
       </c>
       <c r="J300" s="5" t="s">
-        <v>1425</v>
+        <v>1421</v>
+      </c>
+      <c r="K300" s="5" t="s">
+        <v>1422</v>
       </c>
       <c r="L300" s="7" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="R300" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="S300" s="5" t="s">
-        <v>29</v>
+        <v>1424</v>
       </c>
       <c r="T300" s="6">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="U300" s="6">
-        <v>510</v>
+        <v>317</v>
       </c>
       <c r="W300" s="6">
         <v>2</v>
@@ -18534,32 +18543,32 @@
       <c r="B301" s="25" t="s">
         <v>1403</v>
       </c>
-      <c r="D301" s="5" t="s">
-        <v>116</v>
+      <c r="D301" s="5">
+        <v>1447</v>
       </c>
       <c r="E301" s="5" t="s">
-        <v>1427</v>
+        <v>25</v>
       </c>
       <c r="F301" s="5" t="s">
-        <v>1428</v>
+        <v>751</v>
       </c>
       <c r="J301" s="5" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="L301" s="7" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="R301" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S301" s="5" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="T301" s="6">
-        <v>73</v>
+        <v>215</v>
       </c>
       <c r="U301" s="6">
-        <v>177</v>
+        <v>510</v>
       </c>
       <c r="W301" s="6">
         <v>2</v>
@@ -18573,34 +18582,31 @@
         <v>1403</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>674</v>
+        <v>116</v>
       </c>
       <c r="E302" s="5" t="s">
-        <v>86</v>
+        <v>1427</v>
       </c>
       <c r="F302" s="5" t="s">
-        <v>87</v>
+        <v>1428</v>
       </c>
       <c r="J302" s="5" t="s">
-        <v>1388</v>
-      </c>
-      <c r="K302" s="5" t="s">
-        <v>1389</v>
+        <v>1429</v>
       </c>
       <c r="L302" s="7" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="R302" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S302" s="5" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="T302" s="6">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="U302" s="6">
-        <v>73</v>
+        <v>177</v>
       </c>
       <c r="W302" s="6">
         <v>2</v>
@@ -18608,43 +18614,40 @@
     </row>
     <row r="303" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="25" t="s">
-        <v>1432</v>
+        <v>1402</v>
       </c>
       <c r="B303" s="25" t="s">
-        <v>1433</v>
+        <v>1403</v>
       </c>
       <c r="D303" s="5" t="s">
         <v>674</v>
       </c>
       <c r="E303" s="5" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="F303" s="5" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="J303" s="5" t="s">
-        <v>1434</v>
+        <v>1388</v>
       </c>
       <c r="K303" s="5" t="s">
-        <v>1435</v>
+        <v>1389</v>
       </c>
       <c r="L303" s="7" t="s">
-        <v>1436</v>
-      </c>
-      <c r="M303" s="5" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="R303" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S303" s="5" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="T303" s="6">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="U303" s="6">
-        <v>242</v>
+        <v>73</v>
       </c>
       <c r="W303" s="6">
         <v>2</v>
@@ -18661,28 +18664,34 @@
         <v>674</v>
       </c>
       <c r="E304" s="5" t="s">
-        <v>854</v>
+        <v>67</v>
       </c>
       <c r="F304" s="5" t="s">
-        <v>855</v>
+        <v>68</v>
       </c>
       <c r="J304" s="5" t="s">
-        <v>1622</v>
-      </c>
-      <c r="L304" s="3" t="s">
-        <v>1621</v>
+        <v>1434</v>
+      </c>
+      <c r="K304" s="5" t="s">
+        <v>1435</v>
+      </c>
+      <c r="L304" s="7" t="s">
+        <v>1436</v>
+      </c>
+      <c r="M304" s="5" t="s">
+        <v>1437</v>
       </c>
       <c r="R304" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S304" s="5" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="T304" s="6">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="U304" s="6">
-        <v>61</v>
+        <v>242</v>
       </c>
       <c r="W304" s="6">
         <v>2</v>
@@ -18695,35 +18704,32 @@
       <c r="B305" s="25" t="s">
         <v>1433</v>
       </c>
-      <c r="D305" s="5">
-        <v>1475</v>
+      <c r="D305" s="5" t="s">
+        <v>674</v>
       </c>
       <c r="E305" s="5" t="s">
-        <v>25</v>
+        <v>854</v>
       </c>
       <c r="F305" s="5" t="s">
-        <v>40</v>
+        <v>855</v>
       </c>
       <c r="J305" s="5" t="s">
-        <v>1438</v>
-      </c>
-      <c r="K305" s="5" t="s">
-        <v>1439</v>
-      </c>
-      <c r="L305" s="7" t="s">
-        <v>1440</v>
+        <v>1622</v>
+      </c>
+      <c r="L305" s="3" t="s">
+        <v>1621</v>
       </c>
       <c r="R305" s="5" t="s">
-        <v>247</v>
+        <v>37</v>
       </c>
       <c r="S305" s="5" t="s">
         <v>100</v>
       </c>
       <c r="T305" s="6">
-        <v>253</v>
+        <v>41</v>
       </c>
       <c r="U305" s="6">
-        <v>586</v>
+        <v>61</v>
       </c>
       <c r="W305" s="6">
         <v>2</v>
@@ -18737,193 +18743,183 @@
         <v>1433</v>
       </c>
       <c r="D306" s="5">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="E306" s="5" t="s">
-        <v>1441</v>
+        <v>25</v>
       </c>
       <c r="F306" s="5" t="s">
-        <v>1442</v>
+        <v>40</v>
       </c>
       <c r="J306" s="5" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="K306" s="5" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="L306" s="7" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="R306" s="5" t="s">
-        <v>37</v>
+        <v>247</v>
       </c>
       <c r="S306" s="5" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="T306" s="6">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="U306" s="6">
-        <v>100</v>
+        <v>586</v>
       </c>
       <c r="W306" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="307" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="26" t="s">
+      <c r="A307" s="25" t="s">
         <v>1432</v>
       </c>
-      <c r="B307" s="26" t="s">
+      <c r="B307" s="25" t="s">
         <v>1433</v>
       </c>
-      <c r="C307" s="10"/>
-      <c r="D307" s="10">
+      <c r="D307" s="5">
+        <v>1478</v>
+      </c>
+      <c r="E307" s="5" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F307" s="5" t="s">
+        <v>1442</v>
+      </c>
+      <c r="J307" s="5" t="s">
+        <v>1443</v>
+      </c>
+      <c r="K307" s="5" t="s">
+        <v>1444</v>
+      </c>
+      <c r="L307" s="7" t="s">
+        <v>1445</v>
+      </c>
+      <c r="R307" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S307" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="T307" s="6">
+        <v>202</v>
+      </c>
+      <c r="U307" s="6">
+        <v>100</v>
+      </c>
+      <c r="W307" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A308" s="26" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B308" s="26" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C308" s="10"/>
+      <c r="D308" s="10">
         <v>1475</v>
       </c>
-      <c r="E307" s="10" t="s">
+      <c r="E308" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="F307" s="10" t="s">
+      <c r="F308" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="G307" s="10"/>
-      <c r="H307" s="10"/>
-      <c r="I307" s="10"/>
-      <c r="J307" s="10" t="s">
+      <c r="G308" s="10"/>
+      <c r="H308" s="10"/>
+      <c r="I308" s="10"/>
+      <c r="J308" s="10" t="s">
         <v>1446</v>
       </c>
-      <c r="K307" s="10" t="s">
+      <c r="K308" s="10" t="s">
         <v>1447</v>
       </c>
-      <c r="L307" s="11" t="s">
+      <c r="L308" s="11" t="s">
         <v>1448</v>
       </c>
-      <c r="M307" s="10"/>
-      <c r="N307" s="10"/>
-      <c r="O307" s="10"/>
-      <c r="P307" s="10"/>
-      <c r="Q307" s="10"/>
-      <c r="R307" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="S307" s="10" t="s">
+      <c r="M308" s="10"/>
+      <c r="N308" s="10"/>
+      <c r="O308" s="10"/>
+      <c r="P308" s="10"/>
+      <c r="Q308" s="10"/>
+      <c r="R308" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="S308" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="T307" s="12">
+      <c r="T308" s="12">
         <v>148</v>
       </c>
-      <c r="U307" s="12">
+      <c r="U308" s="12">
         <v>122</v>
       </c>
-      <c r="V307" s="12"/>
-      <c r="W307" s="12">
+      <c r="V308" s="12"/>
+      <c r="W308" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A308" s="28" t="s">
+    <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="28" t="s">
         <v>1432</v>
       </c>
-      <c r="B308" s="28" t="s">
+      <c r="B309" s="28" t="s">
         <v>1433</v>
       </c>
-      <c r="C308" s="16"/>
-      <c r="D308" s="16" t="s">
+      <c r="C309" s="16"/>
+      <c r="D309" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="E308" s="16" t="s">
+      <c r="E309" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F308" s="16" t="s">
+      <c r="F309" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G308" s="16"/>
-      <c r="H308" s="16"/>
-      <c r="I308" s="16"/>
-      <c r="J308" s="16" t="s">
+      <c r="G309" s="16"/>
+      <c r="H309" s="16"/>
+      <c r="I309" s="16"/>
+      <c r="J309" s="16" t="s">
         <v>1449</v>
       </c>
-      <c r="K308" s="16" t="s">
+      <c r="K309" s="16" t="s">
         <v>1450</v>
       </c>
-      <c r="L308" s="17" t="s">
+      <c r="L309" s="17" t="s">
         <v>1451</v>
       </c>
-      <c r="M308" s="16"/>
-      <c r="N308" s="16"/>
-      <c r="O308" s="16"/>
-      <c r="P308" s="16"/>
-      <c r="Q308" s="16"/>
-      <c r="R308" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="S308" s="16" t="s">
+      <c r="M309" s="16"/>
+      <c r="N309" s="16"/>
+      <c r="O309" s="16"/>
+      <c r="P309" s="16"/>
+      <c r="Q309" s="16"/>
+      <c r="R309" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="S309" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="T308" s="18">
+      <c r="T309" s="18">
         <v>97</v>
       </c>
-      <c r="U308" s="18">
+      <c r="U309" s="18">
         <v>245</v>
       </c>
-      <c r="V308" s="18"/>
-      <c r="W308" s="18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A309" s="30" t="s">
-        <v>1432</v>
-      </c>
-      <c r="B309" s="30" t="s">
-        <v>1433</v>
-      </c>
-      <c r="C309" s="23"/>
-      <c r="D309" s="23">
-        <v>1480</v>
-      </c>
-      <c r="E309" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F309" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="G309" s="24"/>
-      <c r="H309" s="24"/>
-      <c r="I309" s="24"/>
-      <c r="J309" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="K309" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="L309" s="7" t="s">
-        <v>1452</v>
-      </c>
-      <c r="M309" s="24"/>
-      <c r="N309" s="24"/>
-      <c r="O309" s="24"/>
-      <c r="P309" s="24"/>
-      <c r="Q309" s="24"/>
-      <c r="R309" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="S309" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="T309" s="23" t="s">
-        <v>1453</v>
-      </c>
-      <c r="U309" s="23">
-        <v>26</v>
-      </c>
-      <c r="V309" s="23"/>
+      <c r="V309" s="18"/>
       <c r="W309" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:23" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="30" t="s">
         <v>1432</v>
       </c>
@@ -18931,26 +18927,26 @@
         <v>1433</v>
       </c>
       <c r="C310" s="23"/>
-      <c r="D310" s="23" t="s">
-        <v>213</v>
+      <c r="D310" s="23">
+        <v>1480</v>
       </c>
       <c r="E310" s="23" t="s">
-        <v>86</v>
+        <v>280</v>
       </c>
       <c r="F310" s="24" t="s">
-        <v>87</v>
+        <v>281</v>
       </c>
       <c r="G310" s="24"/>
       <c r="H310" s="24"/>
       <c r="I310" s="24"/>
       <c r="J310" s="24" t="s">
-        <v>1454</v>
+        <v>294</v>
       </c>
       <c r="K310" s="24" t="s">
-        <v>1455</v>
+        <v>295</v>
       </c>
       <c r="L310" s="7" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="M310" s="24"/>
       <c r="N310" s="24"/>
@@ -18963,105 +18959,118 @@
       <c r="S310" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="T310" s="23">
+      <c r="T310" s="23" t="s">
+        <v>1453</v>
+      </c>
+      <c r="U310" s="23">
+        <v>26</v>
+      </c>
+      <c r="V310" s="23"/>
+      <c r="W310" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:23" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A311" s="30" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B311" s="30" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C311" s="23"/>
+      <c r="D311" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E311" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F311" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="G311" s="24"/>
+      <c r="H311" s="24"/>
+      <c r="I311" s="24"/>
+      <c r="J311" s="24" t="s">
+        <v>1454</v>
+      </c>
+      <c r="K311" s="24" t="s">
+        <v>1455</v>
+      </c>
+      <c r="L311" s="7" t="s">
+        <v>1456</v>
+      </c>
+      <c r="M311" s="24"/>
+      <c r="N311" s="24"/>
+      <c r="O311" s="24"/>
+      <c r="P311" s="24"/>
+      <c r="Q311" s="24"/>
+      <c r="R311" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="S311" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="T311" s="23">
         <v>32</v>
       </c>
-      <c r="U310" s="23">
+      <c r="U311" s="23">
         <v>21</v>
       </c>
-      <c r="V310" s="23"/>
-      <c r="W310" s="6">
+      <c r="V311" s="23"/>
+      <c r="W311" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="29" t="s">
+    <row r="312" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A312" s="29" t="s">
         <v>1457</v>
       </c>
-      <c r="B311" s="29" t="s">
+      <c r="B312" s="29" t="s">
         <v>1458</v>
       </c>
-      <c r="C311" s="19"/>
-      <c r="D311" s="19">
+      <c r="C312" s="19"/>
+      <c r="D312" s="19">
         <v>1440</v>
       </c>
-      <c r="E311" s="19" t="s">
+      <c r="E312" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="F311" s="19" t="s">
+      <c r="F312" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="G311" s="19"/>
-      <c r="H311" s="19"/>
-      <c r="I311" s="19"/>
-      <c r="J311" s="19" t="s">
+      <c r="G312" s="19"/>
+      <c r="H312" s="19"/>
+      <c r="I312" s="19"/>
+      <c r="J312" s="19" t="s">
         <v>819</v>
       </c>
-      <c r="K311" s="19"/>
-      <c r="L311" s="20" t="s">
+      <c r="K312" s="19"/>
+      <c r="L312" s="20" t="s">
         <v>1459</v>
       </c>
-      <c r="M311" s="19"/>
-      <c r="N311" s="19"/>
-      <c r="O311" s="19"/>
-      <c r="P311" s="19"/>
-      <c r="Q311" s="19"/>
-      <c r="R311" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="S311" s="19" t="s">
+      <c r="M312" s="19"/>
+      <c r="N312" s="19"/>
+      <c r="O312" s="19"/>
+      <c r="P312" s="19"/>
+      <c r="Q312" s="19"/>
+      <c r="R312" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="S312" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="T311" s="21">
+      <c r="T312" s="21">
         <v>220</v>
       </c>
-      <c r="U311" s="21">
+      <c r="U312" s="21">
         <v>262</v>
       </c>
-      <c r="V311" s="21"/>
-      <c r="W311" s="21">
+      <c r="V312" s="21"/>
+      <c r="W312" s="21">
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:23" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A312" s="25" t="s">
-        <v>1457</v>
-      </c>
-      <c r="B312" s="25" t="s">
-        <v>1458</v>
-      </c>
-      <c r="D312" s="5" t="s">
-        <v>1460</v>
-      </c>
-      <c r="E312" s="5" t="s">
-        <v>1461</v>
-      </c>
-      <c r="F312" s="5" t="s">
-        <v>1462</v>
-      </c>
-      <c r="J312" s="5" t="s">
-        <v>1463</v>
-      </c>
-      <c r="L312" s="7" t="s">
-        <v>1464</v>
-      </c>
-      <c r="R312" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S312" s="5" t="s">
-        <v>1290</v>
-      </c>
-      <c r="T312" s="6">
-        <v>138</v>
-      </c>
-      <c r="U312" s="6">
-        <v>111</v>
-      </c>
-      <c r="W312" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:23" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="25" t="s">
         <v>1457</v>
       </c>
@@ -19069,69 +19078,69 @@
         <v>1458</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>370</v>
+        <v>1461</v>
       </c>
       <c r="F313" s="5" t="s">
-        <v>371</v>
+        <v>1462</v>
       </c>
       <c r="J313" s="5" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="L313" s="7" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="R313" s="5" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="S313" s="5" t="s">
-        <v>100</v>
+        <v>1290</v>
       </c>
       <c r="T313" s="6">
-        <v>200</v>
+        <v>138</v>
       </c>
       <c r="U313" s="6">
-        <v>223</v>
+        <v>111</v>
       </c>
       <c r="W313" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="25" t="s">
         <v>1457</v>
       </c>
       <c r="B314" s="25" t="s">
         <v>1458</v>
       </c>
-      <c r="D314" s="5">
-        <v>1441</v>
+      <c r="D314" s="5" t="s">
+        <v>1465</v>
       </c>
       <c r="E314" s="5" t="s">
-        <v>237</v>
+        <v>370</v>
       </c>
       <c r="F314" s="5" t="s">
-        <v>1468</v>
+        <v>371</v>
       </c>
       <c r="J314" s="5" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="L314" s="7" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="R314" s="5" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="S314" s="5" t="s">
         <v>100</v>
       </c>
       <c r="T314" s="6">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="U314" s="6">
-        <v>47</v>
+        <v>223</v>
       </c>
       <c r="W314" s="6">
         <v>1</v>
@@ -19145,31 +19154,31 @@
         <v>1458</v>
       </c>
       <c r="D315" s="5">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="E315" s="5" t="s">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="F315" s="5" t="s">
-        <v>68</v>
+        <v>1468</v>
       </c>
       <c r="J315" s="5" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="L315" s="7" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="R315" s="5" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="S315" s="5" t="s">
         <v>100</v>
       </c>
       <c r="T315" s="6">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="U315" s="6">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="W315" s="6">
         <v>1</v>
@@ -19186,31 +19195,28 @@
         <v>1443</v>
       </c>
       <c r="E316" s="5" t="s">
-        <v>1473</v>
+        <v>67</v>
       </c>
       <c r="F316" s="5" t="s">
-        <v>1474</v>
+        <v>68</v>
       </c>
       <c r="J316" s="5" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="L316" s="7" t="s">
-        <v>1476</v>
-      </c>
-      <c r="M316" s="5" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="R316" s="5" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="S316" s="5" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="T316" s="6">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="U316" s="6">
-        <v>546</v>
+        <v>43</v>
       </c>
       <c r="W316" s="6">
         <v>1</v>
@@ -19223,32 +19229,35 @@
       <c r="B317" s="25" t="s">
         <v>1458</v>
       </c>
-      <c r="D317" s="5" t="s">
-        <v>1340</v>
+      <c r="D317" s="5">
+        <v>1443</v>
       </c>
       <c r="E317" s="5" t="s">
-        <v>67</v>
+        <v>1473</v>
       </c>
       <c r="F317" s="5" t="s">
-        <v>68</v>
+        <v>1474</v>
       </c>
       <c r="J317" s="5" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="L317" s="7" t="s">
-        <v>1479</v>
+        <v>1476</v>
+      </c>
+      <c r="M317" s="5" t="s">
+        <v>1477</v>
       </c>
       <c r="R317" s="5" t="s">
-        <v>247</v>
+        <v>37</v>
       </c>
       <c r="S317" s="5" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="T317" s="6">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="U317" s="6">
-        <v>89</v>
+        <v>546</v>
       </c>
       <c r="W317" s="6">
         <v>1</v>
@@ -19262,19 +19271,19 @@
         <v>1458</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>1480</v>
+        <v>1340</v>
       </c>
       <c r="E318" s="5" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="F318" s="5" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="J318" s="5" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="L318" s="7" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="R318" s="5" t="s">
         <v>247</v>
@@ -19283,10 +19292,10 @@
         <v>100</v>
       </c>
       <c r="T318" s="6">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="U318" s="6">
-        <v>137</v>
+        <v>89</v>
       </c>
       <c r="W318" s="6">
         <v>1</v>
@@ -19300,31 +19309,31 @@
         <v>1458</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>261</v>
+        <v>1480</v>
       </c>
       <c r="E319" s="5" t="s">
-        <v>889</v>
+        <v>32</v>
       </c>
       <c r="F319" s="5" t="s">
-        <v>890</v>
+        <v>33</v>
       </c>
       <c r="J319" s="5" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="L319" s="7" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="R319" s="5" t="s">
-        <v>59</v>
+        <v>247</v>
       </c>
       <c r="S319" s="5" t="s">
         <v>100</v>
       </c>
       <c r="T319" s="6">
-        <v>140</v>
+        <v>41</v>
       </c>
       <c r="U319" s="6">
-        <v>293</v>
+        <v>137</v>
       </c>
       <c r="W319" s="6">
         <v>1</v>
@@ -19338,31 +19347,31 @@
         <v>1458</v>
       </c>
       <c r="D320" s="5" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E320" s="5" t="s">
-        <v>375</v>
+        <v>889</v>
       </c>
       <c r="F320" s="5" t="s">
-        <v>376</v>
+        <v>890</v>
       </c>
       <c r="J320" s="5" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="L320" s="7" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="R320" s="5" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="S320" s="5" t="s">
         <v>100</v>
       </c>
       <c r="T320" s="6">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="U320" s="6">
-        <v>25</v>
+        <v>293</v>
       </c>
       <c r="W320" s="6">
         <v>1</v>
@@ -19376,19 +19385,19 @@
         <v>1458</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>1487</v>
+        <v>267</v>
       </c>
       <c r="E321" s="5" t="s">
-        <v>25</v>
+        <v>375</v>
       </c>
       <c r="F321" s="5" t="s">
-        <v>40</v>
+        <v>376</v>
       </c>
       <c r="J321" s="5" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="L321" s="7" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="R321" s="5" t="s">
         <v>37</v>
@@ -19397,101 +19406,98 @@
         <v>100</v>
       </c>
       <c r="T321" s="6">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="U321" s="6">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="W321" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A322" s="31" t="s">
+      <c r="A322" s="25" t="s">
         <v>1457</v>
       </c>
-      <c r="B322" s="31" t="s">
+      <c r="B322" s="25" t="s">
         <v>1458</v>
       </c>
-      <c r="C322" s="31"/>
-      <c r="D322" s="33">
-        <v>1450</v>
-      </c>
-      <c r="E322" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F322" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="G322" s="31"/>
-      <c r="H322" s="31"/>
-      <c r="I322" s="31"/>
-      <c r="J322" s="31" t="s">
-        <v>1490</v>
-      </c>
-      <c r="K322" s="31" t="s">
-        <v>1491</v>
-      </c>
-      <c r="L322" s="22" t="s">
-        <v>1492</v>
-      </c>
-      <c r="M322" s="31"/>
-      <c r="N322" s="31"/>
-      <c r="O322" s="31"/>
-      <c r="P322" s="31"/>
-      <c r="Q322" s="31"/>
-      <c r="R322" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="S322" s="31" t="s">
+      <c r="D322" s="5" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E322" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F322" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J322" s="5" t="s">
+        <v>1488</v>
+      </c>
+      <c r="L322" s="7" t="s">
+        <v>1489</v>
+      </c>
+      <c r="R322" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S322" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="T322" s="32">
-        <v>27</v>
-      </c>
-      <c r="U322" s="32">
-        <v>24</v>
+      <c r="T322" s="6">
+        <v>96</v>
+      </c>
+      <c r="U322" s="6">
+        <v>110</v>
       </c>
       <c r="W322" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="323" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A323" s="25" t="s">
-        <v>1493</v>
-      </c>
-      <c r="B323" s="25" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D323" s="5">
-        <v>1435</v>
-      </c>
-      <c r="E323" s="5" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F323" s="5" t="s">
-        <v>1496</v>
-      </c>
-      <c r="J323" s="5" t="s">
-        <v>1497</v>
-      </c>
-      <c r="K323" s="5" t="s">
-        <v>1498</v>
-      </c>
-      <c r="L323" s="7" t="s">
-        <v>1499</v>
-      </c>
-      <c r="R323" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S323" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="T323" s="6">
-        <v>19</v>
-      </c>
-      <c r="U323" s="6">
-        <v>13</v>
+      <c r="A323" s="31" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B323" s="31" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C323" s="31"/>
+      <c r="D323" s="33">
+        <v>1450</v>
+      </c>
+      <c r="E323" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F323" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G323" s="31"/>
+      <c r="H323" s="31"/>
+      <c r="I323" s="31"/>
+      <c r="J323" s="31" t="s">
+        <v>1490</v>
+      </c>
+      <c r="K323" s="31" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L323" s="22" t="s">
+        <v>1492</v>
+      </c>
+      <c r="M323" s="31"/>
+      <c r="N323" s="31"/>
+      <c r="O323" s="31"/>
+      <c r="P323" s="31"/>
+      <c r="Q323" s="31"/>
+      <c r="R323" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="S323" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="T323" s="32">
+        <v>27</v>
+      </c>
+      <c r="U323" s="32">
+        <v>24</v>
       </c>
       <c r="W323" s="6">
         <v>1</v>
@@ -19504,23 +19510,23 @@
       <c r="B324" s="25" t="s">
         <v>1494</v>
       </c>
-      <c r="D324" s="5" t="s">
-        <v>1500</v>
+      <c r="D324" s="5">
+        <v>1435</v>
       </c>
       <c r="E324" s="5" t="s">
-        <v>86</v>
+        <v>1495</v>
       </c>
       <c r="F324" s="5" t="s">
-        <v>87</v>
+        <v>1496</v>
       </c>
       <c r="J324" s="5" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="K324" s="5" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="L324" s="7" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="R324" s="5" t="s">
         <v>37</v>
@@ -19529,16 +19535,16 @@
         <v>60</v>
       </c>
       <c r="T324" s="6">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="U324" s="6">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="W324" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="25" t="s">
         <v>1493</v>
       </c>
@@ -19546,7 +19552,7 @@
         <v>1494</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>807</v>
+        <v>1500</v>
       </c>
       <c r="E325" s="5" t="s">
         <v>86</v>
@@ -19555,13 +19561,13 @@
         <v>87</v>
       </c>
       <c r="J325" s="5" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="K325" s="5" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="L325" s="7" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="R325" s="5" t="s">
         <v>37</v>
@@ -19570,7 +19576,7 @@
         <v>60</v>
       </c>
       <c r="T325" s="6">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="U325" s="6">
         <v>19</v>
@@ -19579,7 +19585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A326" s="25" t="s">
         <v>1493</v>
       </c>
@@ -19587,7 +19593,7 @@
         <v>1494</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>1507</v>
+        <v>807</v>
       </c>
       <c r="E326" s="5" t="s">
         <v>86</v>
@@ -19596,22 +19602,25 @@
         <v>87</v>
       </c>
       <c r="J326" s="5" t="s">
-        <v>1508</v>
+        <v>1504</v>
+      </c>
+      <c r="K326" s="5" t="s">
+        <v>1505</v>
       </c>
       <c r="L326" s="7" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="R326" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S326" s="5" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="T326" s="6">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="U326" s="6">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="W326" s="6">
         <v>1</v>
@@ -19625,34 +19634,31 @@
         <v>1494</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>301</v>
+        <v>1507</v>
       </c>
       <c r="E327" s="5" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="F327" s="5" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>1510</v>
-      </c>
-      <c r="K327" s="5" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="L327" s="7" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="R327" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S327" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="T327" s="6">
+        <v>82</v>
+      </c>
+      <c r="U327" s="6">
         <v>60</v>
-      </c>
-      <c r="T327" s="6">
-        <v>66</v>
-      </c>
-      <c r="U327" s="6">
-        <v>62</v>
       </c>
       <c r="W327" s="6">
         <v>1</v>
@@ -19666,34 +19672,34 @@
         <v>1494</v>
       </c>
       <c r="D328" s="5" t="s">
-        <v>1076</v>
+        <v>301</v>
       </c>
       <c r="E328" s="5" t="s">
-        <v>594</v>
+        <v>32</v>
       </c>
       <c r="F328" s="5" t="s">
-        <v>595</v>
+        <v>33</v>
       </c>
       <c r="J328" s="5" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="K328" s="5" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="L328" s="7" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="R328" s="5" t="s">
-        <v>247</v>
+        <v>37</v>
       </c>
       <c r="S328" s="5" t="s">
         <v>60</v>
       </c>
       <c r="T328" s="6">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="U328" s="6">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="W328" s="6">
         <v>1</v>
@@ -19707,34 +19713,34 @@
         <v>1494</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>1516</v>
+        <v>1076</v>
       </c>
       <c r="E329" s="5" t="s">
-        <v>505</v>
+        <v>594</v>
       </c>
       <c r="F329" s="5" t="s">
-        <v>506</v>
+        <v>595</v>
       </c>
       <c r="J329" s="5" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="K329" s="5" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="L329" s="7" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="R329" s="5" t="s">
-        <v>37</v>
+        <v>247</v>
       </c>
       <c r="S329" s="5" t="s">
         <v>60</v>
       </c>
       <c r="T329" s="6">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="U329" s="6">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="W329" s="6">
         <v>1</v>
@@ -19747,35 +19753,35 @@
       <c r="B330" s="25" t="s">
         <v>1494</v>
       </c>
-      <c r="D330" s="5">
-        <v>1432</v>
+      <c r="D330" s="5" t="s">
+        <v>1516</v>
       </c>
       <c r="E330" s="5" t="s">
-        <v>1520</v>
+        <v>505</v>
       </c>
       <c r="F330" s="5" t="s">
-        <v>1521</v>
+        <v>506</v>
       </c>
       <c r="J330" s="5" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="K330" s="5" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="L330" s="7" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="R330" s="5" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="S330" s="5" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="T330" s="6">
-        <v>340</v>
+        <v>33</v>
       </c>
       <c r="U330" s="6">
-        <v>520</v>
+        <v>26</v>
       </c>
       <c r="W330" s="6">
         <v>1</v>
@@ -19788,35 +19794,35 @@
       <c r="B331" s="25" t="s">
         <v>1494</v>
       </c>
-      <c r="D331" s="5" t="s">
-        <v>1525</v>
+      <c r="D331" s="5">
+        <v>1432</v>
       </c>
       <c r="E331" s="5" t="s">
-        <v>375</v>
+        <v>1520</v>
       </c>
       <c r="F331" s="5" t="s">
-        <v>376</v>
+        <v>1521</v>
       </c>
       <c r="J331" s="5" t="s">
-        <v>531</v>
+        <v>1522</v>
       </c>
       <c r="K331" s="5" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="L331" s="7" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="R331" s="5" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="S331" s="5" t="s">
-        <v>542</v>
+        <v>100</v>
       </c>
       <c r="T331" s="6">
-        <v>90</v>
+        <v>340</v>
       </c>
       <c r="U331" s="6">
-        <v>34</v>
+        <v>520</v>
       </c>
       <c r="W331" s="6">
         <v>1</v>
@@ -19833,31 +19839,31 @@
         <v>1525</v>
       </c>
       <c r="E332" s="5" t="s">
-        <v>505</v>
+        <v>375</v>
       </c>
       <c r="F332" s="5" t="s">
-        <v>506</v>
+        <v>376</v>
       </c>
       <c r="J332" s="5" t="s">
-        <v>1528</v>
+        <v>531</v>
       </c>
       <c r="K332" s="5" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
       <c r="L332" s="7" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="R332" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S332" s="5" t="s">
-        <v>60</v>
+        <v>542</v>
       </c>
       <c r="T332" s="6">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="U332" s="6">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="W332" s="6">
         <v>1</v>
@@ -19871,115 +19877,118 @@
         <v>1494</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="E333" s="5" t="s">
-        <v>280</v>
+        <v>505</v>
       </c>
       <c r="F333" s="5" t="s">
-        <v>281</v>
+        <v>506</v>
       </c>
       <c r="J333" s="5" t="s">
-        <v>1532</v>
+        <v>1528</v>
+      </c>
+      <c r="K333" s="5" t="s">
+        <v>1529</v>
       </c>
       <c r="L333" s="7" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="R333" s="5" t="s">
-        <v>672</v>
+        <v>37</v>
       </c>
       <c r="S333" s="5" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="T333" s="6">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="U333" s="6">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="W333" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
+      <c r="A334" s="25" t="s">
         <v>1493</v>
       </c>
-      <c r="B334" t="s">
+      <c r="B334" s="25" t="s">
         <v>1494</v>
       </c>
-      <c r="D334" t="s">
-        <v>1404</v>
-      </c>
-      <c r="E334" t="s">
-        <v>854</v>
-      </c>
-      <c r="F334" t="s">
-        <v>855</v>
-      </c>
-      <c r="J334" t="s">
-        <v>1534</v>
-      </c>
-      <c r="K334" t="s">
-        <v>1535</v>
-      </c>
-      <c r="L334" s="1" t="s">
-        <v>1536</v>
-      </c>
-      <c r="R334" t="s">
-        <v>37</v>
-      </c>
-      <c r="S334" t="s">
-        <v>60</v>
-      </c>
-      <c r="T334" s="2">
-        <v>24</v>
-      </c>
-      <c r="U334" s="2" t="s">
-        <v>1537</v>
+      <c r="D334" s="5" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E334" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F334" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J334" s="5" t="s">
+        <v>1532</v>
+      </c>
+      <c r="L334" s="7" t="s">
+        <v>1533</v>
+      </c>
+      <c r="R334" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="S334" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="T334" s="6">
+        <v>57</v>
+      </c>
+      <c r="U334" s="6">
+        <v>40</v>
       </c>
       <c r="W334" s="6">
         <v>1</v>
       </c>
-      <c r="X334" s="6"/>
     </row>
     <row r="335" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A335" s="25" t="s">
-        <v>944</v>
-      </c>
-      <c r="B335" s="25" t="s">
-        <v>1538</v>
-      </c>
-      <c r="D335" s="5" t="s">
-        <v>1539</v>
-      </c>
-      <c r="E335" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F335" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="J335" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="L335" s="7" t="s">
-        <v>1540</v>
-      </c>
-      <c r="R335" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S335" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T335" s="6">
-        <v>84</v>
-      </c>
-      <c r="U335" s="6">
-        <v>84</v>
+      <c r="A335" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B335" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D335" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E335" t="s">
+        <v>854</v>
+      </c>
+      <c r="F335" t="s">
+        <v>855</v>
+      </c>
+      <c r="J335" t="s">
+        <v>1534</v>
+      </c>
+      <c r="K335" t="s">
+        <v>1535</v>
+      </c>
+      <c r="L335" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="R335" t="s">
+        <v>37</v>
+      </c>
+      <c r="S335" t="s">
+        <v>60</v>
+      </c>
+      <c r="T335" s="2">
+        <v>24</v>
+      </c>
+      <c r="U335" s="2" t="s">
+        <v>1537</v>
       </c>
       <c r="W335" s="6">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X335" s="6"/>
     </row>
     <row r="336" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="25" t="s">
@@ -19989,31 +19998,31 @@
         <v>1538</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="E336" s="5" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="F336" s="5" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="J336" s="5" t="s">
-        <v>1542</v>
+        <v>186</v>
       </c>
       <c r="L336" s="7" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
       <c r="R336" s="5" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="S336" s="5" t="s">
         <v>45</v>
       </c>
       <c r="T336" s="6">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="U336" s="6">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="W336" s="6">
         <v>3</v>
@@ -20026,35 +20035,32 @@
       <c r="B337" s="25" t="s">
         <v>1538</v>
       </c>
-      <c r="D337" s="5">
-        <v>1432</v>
+      <c r="D337" s="5" t="s">
+        <v>1541</v>
       </c>
       <c r="E337" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F337" s="5" t="s">
-        <v>1544</v>
+        <v>40</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="K337" s="5" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="L337" s="7" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="R337" s="5" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="S337" s="5" t="s">
         <v>45</v>
       </c>
       <c r="T337" s="6">
-        <v>86</v>
+        <v>209</v>
       </c>
       <c r="U337" s="6">
-        <v>61</v>
+        <v>216</v>
       </c>
       <c r="W337" s="6">
         <v>3</v>
@@ -20068,209 +20074,208 @@
         <v>1538</v>
       </c>
       <c r="D338" s="5">
-        <v>14456</v>
+        <v>1432</v>
       </c>
       <c r="E338" s="5" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="F338" s="5" t="s">
-        <v>68</v>
+        <v>1544</v>
       </c>
       <c r="J338" s="5" t="s">
-        <v>1547</v>
+        <v>443</v>
       </c>
       <c r="K338" s="5" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="L338" s="7" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="R338" s="5" t="s">
-        <v>1550</v>
+        <v>37</v>
       </c>
       <c r="S338" s="5" t="s">
         <v>45</v>
       </c>
       <c r="T338" s="6">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="U338" s="6">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="W338" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="25" t="s">
-        <v>1551</v>
+        <v>944</v>
       </c>
       <c r="B339" s="25" t="s">
-        <v>1552</v>
+        <v>1538</v>
       </c>
       <c r="D339" s="5">
-        <v>1480</v>
+        <v>14456</v>
       </c>
       <c r="E339" s="5" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F339" s="5" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="J339" s="5" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="K339" s="5" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="L339" s="7" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="R339" s="5" t="s">
-        <v>37</v>
+        <v>1550</v>
       </c>
       <c r="S339" s="5" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="T339" s="6">
-        <v>175</v>
+        <v>26</v>
       </c>
       <c r="U339" s="6">
-        <v>196</v>
+        <v>29</v>
       </c>
       <c r="W339" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="340" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A340" s="28" t="s">
+      <c r="A340" s="25" t="s">
         <v>1551</v>
       </c>
-      <c r="B340" s="28" t="s">
+      <c r="B340" s="25" t="s">
         <v>1552</v>
       </c>
-      <c r="C340" s="16"/>
-      <c r="D340" s="16" t="s">
+      <c r="D340" s="5">
+        <v>1480</v>
+      </c>
+      <c r="E340" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F340" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J340" s="5" t="s">
+        <v>1553</v>
+      </c>
+      <c r="K340" s="5" t="s">
+        <v>1554</v>
+      </c>
+      <c r="L340" s="7" t="s">
+        <v>1555</v>
+      </c>
+      <c r="R340" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S340" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="T340" s="6">
+        <v>175</v>
+      </c>
+      <c r="U340" s="6">
+        <v>196</v>
+      </c>
+      <c r="W340" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="341" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="28" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B341" s="28" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C341" s="16"/>
+      <c r="D341" s="16" t="s">
         <v>1556</v>
       </c>
-      <c r="E340" s="16" t="s">
+      <c r="E341" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F340" s="16" t="s">
+      <c r="F341" s="16" t="s">
         <v>1557</v>
       </c>
-      <c r="G340" s="16"/>
-      <c r="H340" s="16"/>
-      <c r="I340" s="16"/>
-      <c r="J340" s="16" t="s">
+      <c r="G341" s="16"/>
+      <c r="H341" s="16"/>
+      <c r="I341" s="16"/>
+      <c r="J341" s="16" t="s">
         <v>1558</v>
       </c>
-      <c r="K340" s="16" t="s">
+      <c r="K341" s="16" t="s">
         <v>1559</v>
       </c>
-      <c r="L340" s="17" t="s">
+      <c r="L341" s="17" t="s">
         <v>1560</v>
       </c>
-      <c r="M340" s="16"/>
-      <c r="N340" s="16"/>
-      <c r="O340" s="16"/>
-      <c r="P340" s="16"/>
-      <c r="Q340" s="16"/>
-      <c r="R340" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="S340" s="16" t="s">
+      <c r="M341" s="16"/>
+      <c r="N341" s="16"/>
+      <c r="O341" s="16"/>
+      <c r="P341" s="16"/>
+      <c r="Q341" s="16"/>
+      <c r="R341" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="S341" s="16" t="s">
         <v>1561</v>
       </c>
-      <c r="T340" s="18">
+      <c r="T341" s="18">
         <v>141</v>
       </c>
-      <c r="U340" s="18">
+      <c r="U341" s="18">
         <v>100</v>
       </c>
-      <c r="V340" s="18"/>
-      <c r="W340" s="18">
+      <c r="V341" s="18"/>
+      <c r="W341" s="18">
         <v>3</v>
       </c>
     </row>
-    <row r="341" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A341" s="5" t="s">
-        <v>1551</v>
-      </c>
-      <c r="B341" s="5" t="s">
-        <v>1552</v>
-      </c>
-      <c r="D341" s="5">
-        <v>1475</v>
-      </c>
-      <c r="E341" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="F341" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="J341" s="5" t="s">
-        <v>1562</v>
-      </c>
-      <c r="K341" s="5" t="s">
-        <v>1563</v>
-      </c>
-      <c r="L341" s="7" t="s">
-        <v>1564</v>
-      </c>
-      <c r="R341" s="5" t="s">
-        <v>689</v>
-      </c>
-      <c r="S341" s="5" t="s">
-        <v>1565</v>
-      </c>
-      <c r="T341" s="6">
-        <v>120</v>
-      </c>
-      <c r="U341" s="6">
-        <v>170</v>
-      </c>
-      <c r="V341" s="5"/>
-      <c r="W341" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="342" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="s">
         <v>1551</v>
       </c>
       <c r="B342" s="5" t="s">
         <v>1552</v>
       </c>
-      <c r="D342" s="5" t="s">
-        <v>1151</v>
+      <c r="D342" s="5">
+        <v>1475</v>
       </c>
       <c r="E342" s="5" t="s">
-        <v>86</v>
+        <v>657</v>
       </c>
       <c r="F342" s="5" t="s">
-        <v>87</v>
+        <v>658</v>
       </c>
       <c r="J342" s="5" t="s">
-        <v>499</v>
+        <v>1562</v>
       </c>
       <c r="K342" s="5" t="s">
-        <v>863</v>
+        <v>1563</v>
       </c>
       <c r="L342" s="7" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="R342" s="5" t="s">
-        <v>37</v>
+        <v>689</v>
       </c>
       <c r="S342" s="5" t="s">
-        <v>248</v>
+        <v>1565</v>
       </c>
       <c r="T342" s="6">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="U342" s="6">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="V342" s="5"/>
       <c r="W342" s="35">
@@ -20278,94 +20283,95 @@
       </c>
     </row>
     <row r="343" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A343" s="29" t="s">
+      <c r="A343" s="5" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D343" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E343" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F343" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J343" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="K343" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="L343" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="R343" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S343" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="T343" s="6">
+        <v>63</v>
+      </c>
+      <c r="U343" s="6">
+        <v>47</v>
+      </c>
+      <c r="V343" s="5"/>
+      <c r="W343" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="344" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A344" s="29" t="s">
         <v>842</v>
       </c>
-      <c r="B343" s="29" t="s">
+      <c r="B344" s="29" t="s">
         <v>1552</v>
       </c>
-      <c r="C343" s="19"/>
-      <c r="D343" s="19">
+      <c r="C344" s="19"/>
+      <c r="D344" s="19">
         <v>1444</v>
       </c>
-      <c r="E343" s="19" t="s">
+      <c r="E344" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="F343" s="19" t="s">
+      <c r="F344" s="19" t="s">
         <v>1567</v>
       </c>
-      <c r="G343" s="19"/>
-      <c r="H343" s="19"/>
-      <c r="I343" s="19"/>
-      <c r="J343" s="19" t="s">
+      <c r="G344" s="19"/>
+      <c r="H344" s="19"/>
+      <c r="I344" s="19"/>
+      <c r="J344" s="19" t="s">
         <v>816</v>
       </c>
-      <c r="K343" s="19" t="s">
+      <c r="K344" s="19" t="s">
         <v>817</v>
       </c>
-      <c r="L343" s="20" t="s">
+      <c r="L344" s="20" t="s">
         <v>1568</v>
       </c>
-      <c r="M343" s="19"/>
-      <c r="N343" s="19"/>
-      <c r="O343" s="19"/>
-      <c r="P343" s="19"/>
-      <c r="Q343" s="19"/>
-      <c r="R343" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="S343" s="19" t="s">
+      <c r="M344" s="19"/>
+      <c r="N344" s="19"/>
+      <c r="O344" s="19"/>
+      <c r="P344" s="19"/>
+      <c r="Q344" s="19"/>
+      <c r="R344" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="S344" s="19" t="s">
         <v>1569</v>
       </c>
-      <c r="T343" s="21">
+      <c r="T344" s="21">
         <v>230</v>
       </c>
-      <c r="U343" s="21">
+      <c r="U344" s="21">
         <v>180</v>
       </c>
-      <c r="V343" s="21"/>
-      <c r="W343" s="21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="344" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A344" s="25" t="s">
-        <v>842</v>
-      </c>
-      <c r="B344" s="25" t="s">
-        <v>1552</v>
-      </c>
-      <c r="D344" s="5">
-        <v>1446</v>
-      </c>
-      <c r="E344" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F344" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="J344" s="5" t="s">
-        <v>1570</v>
-      </c>
-      <c r="K344" s="5" t="s">
-        <v>1571</v>
-      </c>
-      <c r="L344" s="7" t="s">
-        <v>1572</v>
-      </c>
-      <c r="R344" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="S344" s="5" t="s">
-        <v>1573</v>
-      </c>
-      <c r="T344" s="6">
-        <v>339</v>
-      </c>
-      <c r="U344" s="6">
-        <v>476</v>
-      </c>
-      <c r="W344" s="6">
+      <c r="V344" s="21"/>
+      <c r="W344" s="21">
         <v>3</v>
       </c>
     </row>
@@ -20376,41 +20382,41 @@
       <c r="B345" s="25" t="s">
         <v>1552</v>
       </c>
-      <c r="D345" s="5" t="s">
-        <v>1574</v>
+      <c r="D345" s="5">
+        <v>1446</v>
       </c>
       <c r="E345" s="5" t="s">
-        <v>598</v>
+        <v>80</v>
       </c>
       <c r="F345" s="5" t="s">
-        <v>605</v>
+        <v>81</v>
       </c>
       <c r="J345" s="5" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="K345" s="5" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="L345" s="7" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="R345" s="5" t="s">
-        <v>689</v>
+        <v>247</v>
       </c>
       <c r="S345" s="5" t="s">
-        <v>122</v>
+        <v>1573</v>
       </c>
       <c r="T345" s="6">
-        <v>393</v>
+        <v>339</v>
       </c>
       <c r="U345" s="6">
-        <v>263</v>
+        <v>476</v>
       </c>
       <c r="W345" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A346" s="25" t="s">
         <v>842</v>
       </c>
@@ -20418,22 +20424,22 @@
         <v>1552</v>
       </c>
       <c r="D346" s="5" t="s">
-        <v>1578</v>
+        <v>1574</v>
       </c>
       <c r="E346" s="5" t="s">
-        <v>466</v>
+        <v>598</v>
       </c>
       <c r="F346" s="5" t="s">
-        <v>201</v>
+        <v>605</v>
       </c>
       <c r="J346" s="5" t="s">
-        <v>1579</v>
+        <v>1575</v>
       </c>
       <c r="K346" s="5" t="s">
-        <v>1580</v>
+        <v>1576</v>
       </c>
       <c r="L346" s="7" t="s">
-        <v>1581</v>
+        <v>1577</v>
       </c>
       <c r="R346" s="5" t="s">
         <v>689</v>
@@ -20442,10 +20448,10 @@
         <v>122</v>
       </c>
       <c r="T346" s="6">
-        <v>280</v>
+        <v>393</v>
       </c>
       <c r="U346" s="6">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="W346" s="6">
         <v>3</v>
@@ -20453,40 +20459,40 @@
     </row>
     <row r="347" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="25" t="s">
-        <v>1582</v>
+        <v>842</v>
       </c>
       <c r="B347" s="25" t="s">
         <v>1552</v>
       </c>
-      <c r="D347" s="5">
-        <v>1474</v>
+      <c r="D347" s="5" t="s">
+        <v>1578</v>
       </c>
       <c r="E347" s="5" t="s">
-        <v>80</v>
+        <v>466</v>
       </c>
       <c r="F347" s="5" t="s">
-        <v>1583</v>
+        <v>201</v>
       </c>
       <c r="J347" s="5" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="K347" s="5" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="L347" s="7" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="R347" s="5" t="s">
-        <v>247</v>
+        <v>689</v>
       </c>
       <c r="S347" s="5" t="s">
         <v>122</v>
       </c>
       <c r="T347" s="6">
-        <v>165</v>
+        <v>280</v>
       </c>
       <c r="U347" s="6">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="W347" s="6">
         <v>3</v>
@@ -20500,22 +20506,22 @@
         <v>1552</v>
       </c>
       <c r="D348" s="5">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="E348" s="5" t="s">
         <v>80</v>
       </c>
       <c r="F348" s="5" t="s">
-        <v>1587</v>
+        <v>1583</v>
       </c>
       <c r="J348" s="5" t="s">
-        <v>1588</v>
+        <v>1584</v>
       </c>
       <c r="K348" s="5" t="s">
-        <v>1589</v>
+        <v>1585</v>
       </c>
       <c r="L348" s="7" t="s">
-        <v>1590</v>
+        <v>1586</v>
       </c>
       <c r="R348" s="5" t="s">
         <v>247</v>
@@ -20524,109 +20530,150 @@
         <v>122</v>
       </c>
       <c r="T348" s="6">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="U348" s="6">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="W348" s="6">
         <v>3</v>
       </c>
-      <c r="X348" s="6"/>
     </row>
     <row r="349" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A349" s="30" t="s">
+      <c r="A349" s="25" t="s">
         <v>1582</v>
       </c>
-      <c r="B349" s="30" t="s">
+      <c r="B349" s="25" t="s">
         <v>1552</v>
       </c>
       <c r="D349" s="5">
         <v>1482</v>
       </c>
-      <c r="E349" s="30" t="s">
+      <c r="E349" s="5" t="s">
         <v>80</v>
       </c>
       <c r="F349" s="5" t="s">
-        <v>1591</v>
+        <v>1587</v>
       </c>
       <c r="J349" s="5" t="s">
-        <v>1592</v>
+        <v>1588</v>
+      </c>
+      <c r="K349" s="5" t="s">
+        <v>1589</v>
       </c>
       <c r="L349" s="7" t="s">
-        <v>1593</v>
-      </c>
-      <c r="R349" s="30" t="s">
-        <v>689</v>
-      </c>
-      <c r="S349" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="T349" s="23">
-        <v>310</v>
-      </c>
-      <c r="U349" s="23">
-        <v>230</v>
-      </c>
-      <c r="V349" s="12"/>
+        <v>1590</v>
+      </c>
+      <c r="R349" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="S349" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="T349" s="6">
+        <v>143</v>
+      </c>
+      <c r="U349" s="6">
+        <v>180</v>
+      </c>
       <c r="W349" s="6">
         <v>3</v>
       </c>
       <c r="X349" s="6"/>
     </row>
     <row r="350" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A350" s="34" t="s">
+      <c r="A350" s="30" t="s">
         <v>1582</v>
       </c>
-      <c r="B350" s="34" t="s">
+      <c r="B350" s="30" t="s">
         <v>1552</v>
       </c>
-      <c r="C350" s="34"/>
-      <c r="D350" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="E350" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="F350" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="G350" s="34"/>
-      <c r="H350" s="34"/>
-      <c r="I350" s="34"/>
-      <c r="J350" s="34" t="s">
-        <v>680</v>
-      </c>
-      <c r="K350" s="34" t="s">
-        <v>1594</v>
-      </c>
-      <c r="L350" s="37" t="s">
-        <v>1595</v>
-      </c>
-      <c r="M350" s="34"/>
-      <c r="N350" s="34"/>
-      <c r="O350" s="34"/>
-      <c r="P350" s="34"/>
-      <c r="Q350" s="34"/>
-      <c r="R350" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="S350" s="34" t="s">
+      <c r="D350" s="5">
+        <v>1482</v>
+      </c>
+      <c r="E350" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="F350" s="5" t="s">
+        <v>1591</v>
+      </c>
+      <c r="J350" s="5" t="s">
+        <v>1592</v>
+      </c>
+      <c r="L350" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="R350" s="30" t="s">
+        <v>689</v>
+      </c>
+      <c r="S350" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="T350" s="36">
-        <v>118</v>
-      </c>
-      <c r="U350" s="36">
-        <v>118</v>
-      </c>
+      <c r="T350" s="23">
+        <v>310</v>
+      </c>
+      <c r="U350" s="23">
+        <v>230</v>
+      </c>
+      <c r="V350" s="12"/>
       <c r="W350" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="352" spans="1:24" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="X350" s="6"/>
+    </row>
+    <row r="351" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A351" s="34" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B351" s="34" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C351" s="34"/>
+      <c r="D351" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E351" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="F351" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G351" s="34"/>
+      <c r="H351" s="34"/>
+      <c r="I351" s="34"/>
+      <c r="J351" s="34" t="s">
+        <v>680</v>
+      </c>
+      <c r="K351" s="34" t="s">
+        <v>1594</v>
+      </c>
+      <c r="L351" s="37" t="s">
+        <v>1595</v>
+      </c>
+      <c r="M351" s="34"/>
+      <c r="N351" s="34"/>
+      <c r="O351" s="34"/>
+      <c r="P351" s="34"/>
+      <c r="Q351" s="34"/>
+      <c r="R351" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="S351" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="T351" s="36">
+        <v>118</v>
+      </c>
+      <c r="U351" s="36">
+        <v>118</v>
+      </c>
+      <c r="W351" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="353" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="X121:X140 X146 X150:X171 X174:X176 X179 X188:X193 X196:X203 X208:X215 X220:X227 X236:X247 X252:X259 X262:X263 X268:X275 X290:X293 X298:X309 X314:X322 X326:X334">
+  <conditionalFormatting sqref="X121:X140 X146 X150:X171 X174:X176 X179 X188:X193 X196:X203 X208:X215 X220:X227 X236:X247 X252:X259 X262:X263 X268:X275 X299:X310 X315:X323 X327:X335 X292:X294">
     <cfRule type="expression" dxfId="35" priority="10">
       <formula>IFERROR(--$W123,0)=1</formula>
     </cfRule>
@@ -20637,7 +20684,7 @@
       <formula>IFERROR(--$W123,0)=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X141:X142 X147:X149 X172:X173 X194:X195 X260 X264 X266 X280 X350">
+  <conditionalFormatting sqref="X141:X142 X147:X149 X172:X173 X194:X195 X260 X264 X266 X280 X351">
     <cfRule type="expression" dxfId="32" priority="37">
       <formula>IFERROR(--#REF!,0)=1</formula>
     </cfRule>
@@ -20648,7 +20695,7 @@
       <formula>IFERROR(--#REF!,0)=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X143:X144 X180 X186 X204:X205 X216:X218 X232:X234 X248:X250 X276:X277 X294:X296 X310:X311 X338:X339 X342:X343 X346:X348">
+  <conditionalFormatting sqref="X143:X144 X180 X186 X204:X205 X216:X218 X232:X234 X248:X250 X276:X277 X295:X297 X311:X312 X339:X340 X343:X344 X347:X349">
     <cfRule type="expression" dxfId="29" priority="49">
       <formula>IFERROR(--$W147,0)=1</formula>
     </cfRule>
@@ -20659,7 +20706,7 @@
       <formula>IFERROR(--$W147,0)=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X145 X187 X219 X235 X251 X297 X323:X325 X335:X336 X349">
+  <conditionalFormatting sqref="X145 X187 X219 X235 X251 X298 X324:X326 X336:X337 X350 X290">
     <cfRule type="expression" dxfId="26" priority="46">
       <formula>IFERROR(--$W148,0)=1</formula>
     </cfRule>
@@ -20681,7 +20728,7 @@
       <formula>IFERROR(--$W179,0)=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X181:X182">
+  <conditionalFormatting sqref="X181:X182 X286:X289">
     <cfRule type="expression" dxfId="17" priority="82">
       <formula>IFERROR(--$W188,0)=1</formula>
     </cfRule>
@@ -20692,7 +20739,7 @@
       <formula>IFERROR(--$W188,0)=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X183 X286:X289 X340 X344">
+  <conditionalFormatting sqref="X183 X341 X345">
     <cfRule type="expression" dxfId="14" priority="25">
       <formula>IFERROR(--$W189,0)=1</formula>
     </cfRule>
@@ -20703,7 +20750,7 @@
       <formula>IFERROR(--$W189,0)=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X184:X185 X341 X345">
+  <conditionalFormatting sqref="X184:X185 X342 X346">
     <cfRule type="expression" dxfId="11" priority="52">
       <formula>IFERROR(--$W189,0)=1</formula>
     </cfRule>
@@ -21063,73 +21110,74 @@
     <hyperlink ref="L288" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
     <hyperlink ref="L289" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
     <hyperlink ref="L290" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="L291" r:id="rId316" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="L292" r:id="rId317" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="L293" r:id="rId318" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="L294" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="L295" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="L296" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="L297" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="L298" r:id="rId323" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="L299" r:id="rId324" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="L300" r:id="rId325" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="L301" r:id="rId326" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="L302" r:id="rId327" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="L303" r:id="rId328" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="L305" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="L306" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="L307" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="L308" r:id="rId332" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="L309" r:id="rId333" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="L310" r:id="rId334" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="L311" r:id="rId335" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="L312" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="L313" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="L314" r:id="rId338" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="L315" r:id="rId339" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="L316" r:id="rId340" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="L317" r:id="rId341" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="L318" r:id="rId342" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="L319" r:id="rId343" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="L320" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="L321" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="L322" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="L323" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="L324" r:id="rId348" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="L325" r:id="rId349" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="L326" r:id="rId350" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="L327" r:id="rId351" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="L328" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="L329" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="L330" r:id="rId354" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="L331" r:id="rId355" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="L332" r:id="rId356" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="L333" r:id="rId357" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="L334" r:id="rId358" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="L335" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="L336" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="L337" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="L338" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="L339" r:id="rId363" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="L340" r:id="rId364" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="L341" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="L342" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="L343" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="L344" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="L345" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="L346" r:id="rId370" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="L347" r:id="rId371" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="L348" r:id="rId372" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="L349" r:id="rId373" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="L350" r:id="rId374" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="L292" r:id="rId316" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="L293" r:id="rId317" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="L294" r:id="rId318" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="L295" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="L296" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="L297" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="L298" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="L299" r:id="rId323" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="L300" r:id="rId324" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="L301" r:id="rId325" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="L302" r:id="rId326" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="L303" r:id="rId327" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="L304" r:id="rId328" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="L306" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="L307" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="L308" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="L309" r:id="rId332" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="L310" r:id="rId333" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="L311" r:id="rId334" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="L312" r:id="rId335" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="L313" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="L314" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="L315" r:id="rId338" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="L316" r:id="rId339" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="L317" r:id="rId340" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="L318" r:id="rId341" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="L319" r:id="rId342" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="L320" r:id="rId343" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="L321" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="L322" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="L323" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="L324" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="L325" r:id="rId348" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="L326" r:id="rId349" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="L327" r:id="rId350" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="L328" r:id="rId351" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="L329" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="L330" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="L331" r:id="rId354" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="L332" r:id="rId355" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="L333" r:id="rId356" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="L334" r:id="rId357" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="L335" r:id="rId358" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="L336" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="L337" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="L338" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="L339" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="L340" r:id="rId363" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="L341" r:id="rId364" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="L342" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="L343" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="L344" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="L345" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="L346" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="L347" r:id="rId370" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="L348" r:id="rId371" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="L349" r:id="rId372" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="L350" r:id="rId373" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="L351" r:id="rId374" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
     <hyperlink ref="L36" r:id="rId375" xr:uid="{53549D48-936B-4EB4-B241-2F8F9312D948}"/>
     <hyperlink ref="L158" r:id="rId376" xr:uid="{C8E8DE21-E096-442E-8906-042AB707EAD0}"/>
     <hyperlink ref="L182" r:id="rId377" xr:uid="{09BB8218-4537-4E85-8496-1D2BF3F79BA9}"/>
-    <hyperlink ref="L304" r:id="rId378" xr:uid="{EA177C80-6E63-4368-9802-12F80918229A}"/>
+    <hyperlink ref="L305" r:id="rId378" xr:uid="{EA177C80-6E63-4368-9802-12F80918229A}"/>
     <hyperlink ref="L27" r:id="rId379" xr:uid="{54E1358F-D0C6-4E27-99A2-8BEAA780B02D}"/>
     <hyperlink ref="L28" r:id="rId380" xr:uid="{35E7AD8E-F497-4D49-898C-9479F369C0C1}"/>
     <hyperlink ref="L29" r:id="rId381" xr:uid="{BA3F783F-C8BA-4E83-8F00-AA0EFCC62F00}"/>
     <hyperlink ref="L30" r:id="rId382" xr:uid="{0E291094-F7F9-44D8-BE97-ACE0D1BC461C}"/>
+    <hyperlink ref="L291" r:id="rId383" xr:uid="{C71CE794-173C-4267-BE3E-ED8936667C7A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAD1040-7DCA-4356-A5FA-63C77EEF0EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D61B095-37EE-43CA-8CC9-FC9ADE955FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1140" windowWidth="15480" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -3730,9 +3730,6 @@
     <t>Johannesaltaarstuk</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a6/Sint-Janshospitaal-Memling-Saint_John_triptych_DSC0018.jpg/1280px-Sint-Janshospitaal-Memling-Saint_John_triptych_DSC0018.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Birmingham</t>
   </si>
   <si>
@@ -4054,9 +4051,6 @@
     <t>Musée du Petit Palais</t>
   </si>
   <si>
-    <t>Le Retable Requin (Saint Siffrein entre saint Michel et sainte Catherine)</t>
-  </si>
-  <si>
     <t>Le Retable Requin</t>
   </si>
   <si>
@@ -4934,6 +4928,12 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/51/Luca_signorelli%2C_crocifissione%2C_urbino%2C_gnm.jpg/960px-Luca_signorelli%2C_crocifissione%2C_urbino%2C_gnm.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/e8/Memling%2C_polittico_di_san_giovanni_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Retable Requin </t>
   </si>
 </sst>
 </file>
@@ -5266,6 +5266,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC6E0B4"/>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF4B183"/>
           <bgColor rgb="FFF4B183"/>
         </patternFill>
@@ -5276,14 +5284,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC000"/>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FFC6E0B4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5362,14 +5362,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF4B183"/>
-          <bgColor rgb="FFF4B183"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFFC000"/>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
@@ -5380,6 +5372,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC6E0B4"/>
           <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4B183"/>
+          <bgColor rgb="FFF4B183"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6011,7 +6011,7 @@
         <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>25</v>
@@ -6920,19 +6920,19 @@
       </c>
       <c r="H27" s="13"/>
       <c r="J27" s="5" t="s">
+        <v>1621</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>1622</v>
+      </c>
+      <c r="L27" s="47" t="s">
         <v>1623</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="R27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S27" s="5" t="s">
         <v>1624</v>
-      </c>
-      <c r="L27" s="47" t="s">
-        <v>1625</v>
-      </c>
-      <c r="R27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S27" s="5" t="s">
-        <v>1626</v>
       </c>
       <c r="T27" s="6">
         <v>205</v>
@@ -6962,13 +6962,13 @@
       </c>
       <c r="H28" s="13"/>
       <c r="J28" s="5" t="s">
+        <v>1625</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>1626</v>
+      </c>
+      <c r="L28" s="47" t="s">
         <v>1627</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>1628</v>
-      </c>
-      <c r="L28" s="47" t="s">
-        <v>1629</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>37</v>
@@ -6997,20 +6997,20 @@
         <v>736</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>56</v>
       </c>
       <c r="H29" s="13"/>
       <c r="J29" s="5" t="s">
+        <v>1628</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>1629</v>
+      </c>
+      <c r="L29" s="47" t="s">
         <v>1630</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>1631</v>
-      </c>
-      <c r="L29" s="47" t="s">
-        <v>1632</v>
       </c>
       <c r="R29" s="5" t="s">
         <v>37</v>
@@ -7049,10 +7049,10 @@
         <v>186</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="L30" s="47" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="R30" s="5" t="s">
         <v>37</v>
@@ -7304,7 +7304,7 @@
         <v>204</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M36" s="5" t="s">
         <v>205</v>
@@ -7966,7 +7966,7 @@
         <v>279</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>55</v>
@@ -8297,7 +8297,7 @@
         <v>318</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>80</v>
@@ -9053,7 +9053,7 @@
         <v>386</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>117</v>
@@ -9141,7 +9141,7 @@
         <v>67</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>412</v>
@@ -9381,7 +9381,7 @@
         <v>429</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>375</v>
@@ -9463,7 +9463,7 @@
         <v>446</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>453</v>
@@ -9803,7 +9803,7 @@
         <v>490</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>176</v>
@@ -10638,7 +10638,7 @@
         <v>566</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>25</v>
@@ -11982,7 +11982,7 @@
         <v>743</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>25</v>
@@ -12464,7 +12464,7 @@
         <v>743</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="E158" s="5" t="s">
         <v>25</v>
@@ -12473,13 +12473,13 @@
         <v>802</v>
       </c>
       <c r="J158" s="5" t="s">
+        <v>1605</v>
+      </c>
+      <c r="K158" s="5" t="s">
         <v>1607</v>
       </c>
-      <c r="K158" s="5" t="s">
-        <v>1609</v>
-      </c>
       <c r="L158" s="3" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="M158" s="5" t="s">
         <v>803</v>
@@ -12687,13 +12687,13 @@
         <v>806</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="E163" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="J163" s="5" t="s">
         <v>824</v>
@@ -13344,7 +13344,7 @@
         <v>844</v>
       </c>
       <c r="D178" s="42" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="E178" s="42" t="s">
         <v>32</v>
@@ -13373,7 +13373,7 @@
         <v>37</v>
       </c>
       <c r="S178" s="42" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="T178" s="44" t="s">
         <v>885</v>
@@ -13532,7 +13532,7 @@
         <v>420</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="R182" s="5" t="s">
         <v>37</v>
@@ -13678,7 +13678,7 @@
         <v>918</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="E186" s="5" t="s">
         <v>32</v>
@@ -13795,7 +13795,7 @@
         <v>918</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="E189" t="s">
         <v>728</v>
@@ -13912,7 +13912,7 @@
         <v>918</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="E192" t="s">
         <v>728</v>
@@ -14737,10 +14737,10 @@
         <v>1497</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="J211" s="5" t="s">
         <v>1043</v>
@@ -16006,7 +16006,7 @@
         <v>855</v>
       </c>
       <c r="J241" s="5" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="K241" s="5" t="s">
         <v>494</v>
@@ -16047,7 +16047,7 @@
         <v>1185</v>
       </c>
       <c r="J242" s="5" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="K242" s="5" t="s">
         <v>494</v>
@@ -16500,8 +16500,8 @@
       <c r="K253" s="5" t="s">
         <v>1234</v>
       </c>
-      <c r="L253" s="7" t="s">
-        <v>1235</v>
+      <c r="L253" s="3" t="s">
+        <v>1635</v>
       </c>
       <c r="R253" s="5" t="s">
         <v>59</v>
@@ -16513,7 +16513,7 @@
         <v>193</v>
       </c>
       <c r="U253" s="6">
-        <v>289</v>
+        <v>389</v>
       </c>
       <c r="W253" s="6">
         <v>2</v>
@@ -16530,16 +16530,16 @@
         <v>1485</v>
       </c>
       <c r="E254" s="5" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F254" s="5" t="s">
         <v>1236</v>
       </c>
-      <c r="F254" s="5" t="s">
+      <c r="J254" s="5" t="s">
         <v>1237</v>
       </c>
-      <c r="J254" s="5" t="s">
+      <c r="L254" s="7" t="s">
         <v>1238</v>
-      </c>
-      <c r="L254" s="7" t="s">
-        <v>1239</v>
       </c>
       <c r="R254" s="5" t="s">
         <v>37</v>
@@ -16565,7 +16565,7 @@
         <v>1213</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E255" s="5" t="s">
         <v>505</v>
@@ -16574,10 +16574,10 @@
         <v>506</v>
       </c>
       <c r="J255" s="5" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L255" s="7" t="s">
         <v>1241</v>
-      </c>
-      <c r="L255" s="7" t="s">
-        <v>1242</v>
       </c>
       <c r="R255" s="5" t="s">
         <v>247</v>
@@ -16606,16 +16606,16 @@
         <v>1467</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="J256" s="5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="L256" s="7" t="s">
         <v>1243</v>
-      </c>
-      <c r="L256" s="7" t="s">
-        <v>1244</v>
       </c>
       <c r="R256" s="5" t="s">
         <v>37</v>
@@ -16635,31 +16635,31 @@
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="25" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B257" s="25" t="s">
         <v>1245</v>
       </c>
-      <c r="B257" s="25" t="s">
+      <c r="D257" s="5" t="s">
         <v>1246</v>
-      </c>
-      <c r="D257" s="5" t="s">
-        <v>1247</v>
       </c>
       <c r="E257" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F257" s="5" t="s">
+        <v>1247</v>
+      </c>
+      <c r="J257" s="5" t="s">
         <v>1248</v>
       </c>
-      <c r="J257" s="5" t="s">
+      <c r="K257" s="5" t="s">
         <v>1249</v>
       </c>
-      <c r="K257" s="5" t="s">
+      <c r="L257" s="7" t="s">
         <v>1250</v>
       </c>
-      <c r="L257" s="7" t="s">
+      <c r="N257" s="7" t="s">
         <v>1251</v>
-      </c>
-      <c r="N257" s="7" t="s">
-        <v>1252</v>
       </c>
       <c r="R257" s="5" t="s">
         <v>689</v>
@@ -16679,13 +16679,13 @@
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="25" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B258" s="25" t="s">
         <v>1245</v>
       </c>
-      <c r="B258" s="25" t="s">
-        <v>1246</v>
-      </c>
       <c r="D258" s="5" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E258" s="5" t="s">
         <v>25</v>
@@ -16697,13 +16697,13 @@
         <v>1070</v>
       </c>
       <c r="K258" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="L258" s="7" t="s">
         <v>1254</v>
       </c>
-      <c r="L258" s="7" t="s">
-        <v>1255</v>
-      </c>
       <c r="N258" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="R258" s="5" t="s">
         <v>37</v>
@@ -16723,31 +16723,31 @@
     </row>
     <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="25" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B259" s="25" t="s">
         <v>1245</v>
       </c>
-      <c r="B259" s="25" t="s">
-        <v>1246</v>
-      </c>
       <c r="D259" s="5" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E259" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="J259" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="K259" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="L259" s="7" t="s">
         <v>1257</v>
       </c>
-      <c r="K259" s="5" t="s">
-        <v>1257</v>
-      </c>
-      <c r="L259" s="7" t="s">
-        <v>1258</v>
-      </c>
       <c r="N259" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="R259" s="5" t="s">
         <v>37</v>
@@ -16767,13 +16767,13 @@
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="25" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B260" s="25" t="s">
         <v>1245</v>
       </c>
-      <c r="B260" s="25" t="s">
-        <v>1246</v>
-      </c>
       <c r="D260" s="5" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E260" s="5" t="s">
         <v>86</v>
@@ -16782,19 +16782,19 @@
         <v>87</v>
       </c>
       <c r="J260" s="5" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="K260" s="5" t="s">
         <v>817</v>
       </c>
       <c r="L260" s="7" t="s">
+        <v>1260</v>
+      </c>
+      <c r="M260" s="5" t="s">
         <v>1261</v>
       </c>
-      <c r="M260" s="5" t="s">
+      <c r="N260" s="7" t="s">
         <v>1262</v>
-      </c>
-      <c r="N260" s="7" t="s">
-        <v>1263</v>
       </c>
       <c r="R260" s="5" t="s">
         <v>37</v>
@@ -16814,13 +16814,13 @@
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="25" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B261" s="25" t="s">
         <v>1245</v>
       </c>
-      <c r="B261" s="25" t="s">
-        <v>1246</v>
-      </c>
       <c r="D261" s="5" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E261" s="5" t="s">
         <v>86</v>
@@ -16829,19 +16829,19 @@
         <v>87</v>
       </c>
       <c r="J261" s="5" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="K261" s="5" t="s">
         <v>817</v>
       </c>
       <c r="L261" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="M261" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="N261" s="7" t="s">
         <v>1262</v>
-      </c>
-      <c r="N261" s="7" t="s">
-        <v>1263</v>
       </c>
       <c r="R261" s="5" t="s">
         <v>37</v>
@@ -16861,13 +16861,13 @@
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="25" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B262" s="25" t="s">
         <v>1245</v>
       </c>
-      <c r="B262" s="25" t="s">
-        <v>1246</v>
-      </c>
       <c r="D262" s="5" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E262" s="5" t="s">
         <v>86</v>
@@ -16876,19 +16876,19 @@
         <v>87</v>
       </c>
       <c r="J262" s="5" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="K262" s="5" t="s">
         <v>817</v>
       </c>
       <c r="L262" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="M262" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="N262" s="7" t="s">
         <v>1262</v>
-      </c>
-      <c r="N262" s="7" t="s">
-        <v>1263</v>
       </c>
       <c r="R262" s="5" t="s">
         <v>37</v>
@@ -16908,10 +16908,10 @@
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="25" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B263" s="25" t="s">
         <v>1245</v>
-      </c>
-      <c r="B263" s="25" t="s">
-        <v>1246</v>
       </c>
       <c r="D263" s="5">
         <v>1420</v>
@@ -16923,16 +16923,16 @@
         <v>40</v>
       </c>
       <c r="J263" s="5" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="K263" s="5" t="s">
         <v>187</v>
       </c>
       <c r="L263" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="N263" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="R263" s="5" t="s">
         <v>37</v>
@@ -16952,13 +16952,13 @@
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="25" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B264" s="25" t="s">
         <v>1245</v>
       </c>
-      <c r="B264" s="25" t="s">
-        <v>1246</v>
-      </c>
       <c r="D264" s="5" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E264" s="5" t="s">
         <v>25</v>
@@ -16967,16 +16967,16 @@
         <v>961</v>
       </c>
       <c r="J264" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="K264" s="5" t="s">
         <v>1271</v>
       </c>
-      <c r="K264" s="5" t="s">
+      <c r="L264" s="7" t="s">
         <v>1272</v>
       </c>
-      <c r="L264" s="7" t="s">
-        <v>1273</v>
-      </c>
       <c r="N264" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="R264" s="5" t="s">
         <v>37</v>
@@ -16996,13 +16996,13 @@
     </row>
     <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="25" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B265" s="25" t="s">
         <v>1274</v>
       </c>
-      <c r="B265" s="25" t="s">
+      <c r="D265" s="5" t="s">
         <v>1275</v>
-      </c>
-      <c r="D265" s="5" t="s">
-        <v>1276</v>
       </c>
       <c r="E265" s="5" t="s">
         <v>889</v>
@@ -17011,10 +17011,10 @@
         <v>890</v>
       </c>
       <c r="J265" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="L265" s="7" t="s">
         <v>1277</v>
-      </c>
-      <c r="L265" s="7" t="s">
-        <v>1278</v>
       </c>
       <c r="R265" s="5" t="s">
         <v>59</v>
@@ -17034,31 +17034,31 @@
     </row>
     <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="25" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B266" s="25" t="s">
         <v>1274</v>
       </c>
-      <c r="B266" s="25" t="s">
-        <v>1275</v>
-      </c>
       <c r="D266" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E266" s="5" t="s">
         <v>1279</v>
       </c>
-      <c r="E266" s="5" t="s">
+      <c r="F266" s="5" t="s">
         <v>1280</v>
       </c>
-      <c r="F266" s="5" t="s">
+      <c r="J266" s="5" t="s">
         <v>1281</v>
       </c>
-      <c r="J266" s="5" t="s">
+      <c r="L266" s="7" t="s">
         <v>1282</v>
-      </c>
-      <c r="L266" s="7" t="s">
-        <v>1283</v>
       </c>
       <c r="R266" s="5" t="s">
         <v>59</v>
       </c>
       <c r="S266" s="5" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="T266" s="6">
         <v>1088</v>
@@ -17072,10 +17072,10 @@
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="25" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B267" s="25" t="s">
         <v>1274</v>
-      </c>
-      <c r="B267" s="25" t="s">
-        <v>1275</v>
       </c>
       <c r="D267" s="5">
         <v>1480</v>
@@ -17084,22 +17084,22 @@
         <v>854</v>
       </c>
       <c r="F267" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J267" s="5" t="s">
         <v>1285</v>
       </c>
-      <c r="J267" s="5" t="s">
+      <c r="K267" s="5" t="s">
         <v>1286</v>
       </c>
-      <c r="K267" s="5" t="s">
+      <c r="L267" s="7" t="s">
         <v>1287</v>
       </c>
-      <c r="L267" s="7" t="s">
+      <c r="R267" s="5" t="s">
         <v>1288</v>
       </c>
-      <c r="R267" s="5" t="s">
+      <c r="S267" s="5" t="s">
         <v>1289</v>
-      </c>
-      <c r="S267" s="5" t="s">
-        <v>1290</v>
       </c>
       <c r="T267" s="6">
         <v>103</v>
@@ -17113,10 +17113,10 @@
     </row>
     <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="25" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B268" s="25" t="s">
         <v>1274</v>
-      </c>
-      <c r="B268" s="25" t="s">
-        <v>1275</v>
       </c>
       <c r="D268" s="5">
         <v>1470</v>
@@ -17131,16 +17131,16 @@
         <v>162</v>
       </c>
       <c r="K268" s="5" t="s">
+        <v>1290</v>
+      </c>
+      <c r="L268" s="7" t="s">
         <v>1291</v>
       </c>
-      <c r="L268" s="7" t="s">
-        <v>1292</v>
-      </c>
       <c r="R268" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S268" s="5" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="T268" s="6">
         <v>102</v>
@@ -17154,13 +17154,13 @@
     </row>
     <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="25" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B269" s="25" t="s">
         <v>1293</v>
       </c>
-      <c r="B269" s="25" t="s">
+      <c r="C269" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="C269" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="D269" s="5">
         <v>1495</v>
@@ -17175,10 +17175,10 @@
         <v>1174</v>
       </c>
       <c r="K269" s="5" t="s">
+        <v>1295</v>
+      </c>
+      <c r="L269" s="7" t="s">
         <v>1296</v>
-      </c>
-      <c r="L269" s="7" t="s">
-        <v>1297</v>
       </c>
       <c r="R269" s="5" t="s">
         <v>37</v>
@@ -17198,13 +17198,13 @@
     </row>
     <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="25" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B270" s="25" t="s">
         <v>1293</v>
       </c>
-      <c r="B270" s="25" t="s">
+      <c r="C270" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="C270" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="D270" s="5">
         <v>1497</v>
@@ -17213,22 +17213,22 @@
         <v>438</v>
       </c>
       <c r="F270" s="5" t="s">
+        <v>1297</v>
+      </c>
+      <c r="J270" s="5" t="s">
         <v>1298</v>
       </c>
-      <c r="J270" s="5" t="s">
+      <c r="K270" s="5" t="s">
+        <v>1298</v>
+      </c>
+      <c r="L270" s="7" t="s">
         <v>1299</v>
       </c>
-      <c r="K270" s="5" t="s">
-        <v>1299</v>
-      </c>
-      <c r="L270" s="7" t="s">
+      <c r="M270" s="5" t="s">
         <v>1300</v>
       </c>
-      <c r="M270" s="5" t="s">
+      <c r="N270" s="7" t="s">
         <v>1301</v>
-      </c>
-      <c r="N270" s="7" t="s">
-        <v>1302</v>
       </c>
       <c r="R270" s="5" t="s">
         <v>29</v>
@@ -17248,13 +17248,13 @@
     </row>
     <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="25" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B271" s="25" t="s">
         <v>1293</v>
       </c>
-      <c r="B271" s="25" t="s">
+      <c r="C271" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="D271" s="5">
         <v>1481</v>
@@ -17266,13 +17266,13 @@
         <v>376</v>
       </c>
       <c r="J271" s="5" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="K271" s="5" t="s">
         <v>420</v>
       </c>
       <c r="L271" s="7" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="R271" s="5" t="s">
         <v>37</v>
@@ -17292,13 +17292,13 @@
     </row>
     <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="25" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B272" s="25" t="s">
         <v>1293</v>
       </c>
-      <c r="B272" s="25" t="s">
+      <c r="C272" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="C272" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="D272" s="5">
         <v>1495</v>
@@ -17310,13 +17310,13 @@
         <v>33</v>
       </c>
       <c r="J272" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="K272" s="5" t="s">
         <v>1305</v>
       </c>
-      <c r="K272" s="5" t="s">
+      <c r="L272" s="7" t="s">
         <v>1306</v>
-      </c>
-      <c r="L272" s="7" t="s">
-        <v>1307</v>
       </c>
       <c r="R272" s="5" t="s">
         <v>37</v>
@@ -17336,13 +17336,13 @@
     </row>
     <row r="273" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="25" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B273" s="25" t="s">
         <v>1293</v>
       </c>
-      <c r="B273" s="25" t="s">
+      <c r="C273" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="C273" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="D273" s="5">
         <v>1493</v>
@@ -17360,7 +17360,7 @@
         <v>494</v>
       </c>
       <c r="L273" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="R273" s="5" t="s">
         <v>37</v>
@@ -17380,13 +17380,13 @@
     </row>
     <row r="274" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="25" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B274" s="25" t="s">
         <v>1293</v>
       </c>
-      <c r="B274" s="25" t="s">
+      <c r="C274" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="C274" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="D274" s="5" t="s">
         <v>733</v>
@@ -17395,19 +17395,19 @@
         <v>25</v>
       </c>
       <c r="F274" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="H274" s="5" t="s">
         <v>1309</v>
       </c>
-      <c r="H274" s="5" t="s">
+      <c r="J274" s="5" t="s">
         <v>1310</v>
       </c>
-      <c r="J274" s="5" t="s">
+      <c r="K274" s="5" t="s">
         <v>1311</v>
       </c>
-      <c r="K274" s="5" t="s">
+      <c r="L274" s="7" t="s">
         <v>1312</v>
-      </c>
-      <c r="L274" s="7" t="s">
-        <v>1313</v>
       </c>
       <c r="R274" s="5" t="s">
         <v>29</v>
@@ -17427,31 +17427,31 @@
     </row>
     <row r="275" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B275" s="5" t="s">
         <v>1293</v>
       </c>
-      <c r="B275" s="5" t="s">
+      <c r="C275" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="D275" s="5">
         <v>1496</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="F275" s="5" t="s">
         <v>56</v>
       </c>
       <c r="J275" s="5" t="s">
+        <v>1314</v>
+      </c>
+      <c r="K275" s="5" t="s">
         <v>1315</v>
       </c>
-      <c r="K275" s="5" t="s">
+      <c r="L275" s="7" t="s">
         <v>1316</v>
-      </c>
-      <c r="L275" s="7" t="s">
-        <v>1317</v>
       </c>
       <c r="R275" s="5" t="s">
         <v>59</v>
@@ -17472,34 +17472,34 @@
     </row>
     <row r="276" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B276" s="5" t="s">
         <v>1293</v>
       </c>
-      <c r="B276" s="5" t="s">
+      <c r="C276" s="5" t="s">
         <v>1294</v>
-      </c>
-      <c r="C276" s="5" t="s">
-        <v>1295</v>
       </c>
       <c r="D276" s="5">
         <v>1497</v>
       </c>
       <c r="E276" s="5" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F276" s="5" t="s">
         <v>1318</v>
       </c>
-      <c r="F276" s="5" t="s">
+      <c r="H276" s="5" t="s">
         <v>1319</v>
       </c>
-      <c r="H276" s="5" t="s">
+      <c r="J276" s="5" t="s">
         <v>1320</v>
       </c>
-      <c r="J276" s="5" t="s">
+      <c r="K276" s="5" t="s">
         <v>1321</v>
       </c>
-      <c r="K276" s="5" t="s">
+      <c r="L276" s="7" t="s">
         <v>1322</v>
-      </c>
-      <c r="L276" s="7" t="s">
-        <v>1323</v>
       </c>
       <c r="R276" s="5" t="s">
         <v>37</v>
@@ -17523,7 +17523,7 @@
         <v>842</v>
       </c>
       <c r="B277" s="25" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="D277" s="5">
         <v>1475</v>
@@ -17541,7 +17541,7 @@
         <v>914</v>
       </c>
       <c r="L277" s="7" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="R277" s="5" t="s">
         <v>37</v>
@@ -17564,7 +17564,7 @@
         <v>842</v>
       </c>
       <c r="B278" s="25" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="D278" s="5">
         <v>1475</v>
@@ -17576,16 +17576,16 @@
         <v>40</v>
       </c>
       <c r="J278" s="5" t="s">
+        <v>1325</v>
+      </c>
+      <c r="K278" s="5" t="s">
         <v>1326</v>
       </c>
-      <c r="K278" s="5" t="s">
+      <c r="L278" s="7" t="s">
         <v>1327</v>
       </c>
-      <c r="L278" s="7" t="s">
+      <c r="M278" s="5" t="s">
         <v>1328</v>
-      </c>
-      <c r="M278" s="5" t="s">
-        <v>1329</v>
       </c>
       <c r="R278" s="5" t="s">
         <v>37</v>
@@ -17605,19 +17605,19 @@
     </row>
     <row r="279" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="25" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B279" s="25" t="s">
         <v>1330</v>
       </c>
-      <c r="B279" s="25" t="s">
+      <c r="D279" s="5" t="s">
         <v>1331</v>
       </c>
-      <c r="D279" s="5" t="s">
+      <c r="E279" s="5" t="s">
         <v>1332</v>
       </c>
-      <c r="E279" s="5" t="s">
+      <c r="F279" s="5" t="s">
         <v>1333</v>
-      </c>
-      <c r="F279" s="5" t="s">
-        <v>1334</v>
       </c>
       <c r="J279" s="5" t="s">
         <v>1070</v>
@@ -17626,10 +17626,10 @@
         <v>1070</v>
       </c>
       <c r="L279" s="5" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="M279" s="7" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="R279" s="5" t="s">
         <v>37</v>
@@ -17650,10 +17650,10 @@
     </row>
     <row r="280" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="25" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B280" s="25" t="s">
         <v>1330</v>
-      </c>
-      <c r="B280" s="25" t="s">
-        <v>1331</v>
       </c>
       <c r="D280" s="5" t="s">
         <v>261</v>
@@ -17665,16 +17665,16 @@
         <v>33</v>
       </c>
       <c r="J280" s="5" t="s">
+        <v>1335</v>
+      </c>
+      <c r="K280" s="5" t="s">
+        <v>1335</v>
+      </c>
+      <c r="L280" s="5" t="s">
         <v>1336</v>
       </c>
-      <c r="K280" s="5" t="s">
+      <c r="M280" s="7" t="s">
         <v>1336</v>
-      </c>
-      <c r="L280" s="5" t="s">
-        <v>1337</v>
-      </c>
-      <c r="M280" s="7" t="s">
-        <v>1337</v>
       </c>
       <c r="R280" s="5" t="s">
         <v>37</v>
@@ -17695,10 +17695,10 @@
     </row>
     <row r="281" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="25" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B281" s="25" t="s">
         <v>1330</v>
-      </c>
-      <c r="B281" s="25" t="s">
-        <v>1331</v>
       </c>
       <c r="D281" s="5" t="s">
         <v>361</v>
@@ -17710,13 +17710,13 @@
         <v>729</v>
       </c>
       <c r="J281" s="5" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K281" s="5" t="s">
+        <v>1337</v>
+      </c>
+      <c r="L281" s="5" t="s">
         <v>1338</v>
-      </c>
-      <c r="K281" s="5" t="s">
-        <v>1338</v>
-      </c>
-      <c r="L281" s="5" t="s">
-        <v>1339</v>
       </c>
       <c r="M281" s="7"/>
       <c r="R281" s="5" t="s">
@@ -17738,32 +17738,32 @@
     </row>
     <row r="282" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="25" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B282" s="25" t="s">
         <v>1330</v>
       </c>
-      <c r="B282" s="25" t="s">
-        <v>1331</v>
-      </c>
       <c r="D282" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E282" s="5" t="s">
         <v>1340</v>
       </c>
-      <c r="E282" s="5" t="s">
+      <c r="F282" s="5" t="s">
         <v>1341</v>
       </c>
-      <c r="F282" s="5" t="s">
+      <c r="J282" s="5" t="s">
+        <v>1636</v>
+      </c>
+      <c r="K282" s="5" t="s">
         <v>1342</v>
       </c>
-      <c r="J282" s="5" t="s">
+      <c r="L282" s="5" t="s">
         <v>1343</v>
-      </c>
-      <c r="K282" s="5" t="s">
-        <v>1344</v>
-      </c>
-      <c r="L282" s="5" t="s">
-        <v>1345</v>
       </c>
       <c r="M282" s="7"/>
       <c r="R282" s="5" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="S282" s="5" t="s">
         <v>122</v>
@@ -17781,34 +17781,34 @@
     </row>
     <row r="283" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="25" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B283" s="25" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D283" s="5" t="s">
         <v>1347</v>
       </c>
-      <c r="B283" s="25" t="s">
+      <c r="E283" s="5" t="s">
         <v>1348</v>
-      </c>
-      <c r="D283" s="5" t="s">
-        <v>1349</v>
-      </c>
-      <c r="E283" s="5" t="s">
-        <v>1350</v>
       </c>
       <c r="F283" s="5" t="s">
         <v>940</v>
       </c>
       <c r="J283" s="5" t="s">
+        <v>1349</v>
+      </c>
+      <c r="K283" s="5" t="s">
+        <v>1350</v>
+      </c>
+      <c r="L283" s="7" t="s">
         <v>1351</v>
-      </c>
-      <c r="K283" s="5" t="s">
-        <v>1352</v>
-      </c>
-      <c r="L283" s="7" t="s">
-        <v>1353</v>
       </c>
       <c r="R283" s="5" t="s">
         <v>59</v>
       </c>
       <c r="S283" s="5" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="T283" s="6" t="s">
         <v>668</v>
@@ -17822,40 +17822,40 @@
     </row>
     <row r="284" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="25" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B284" s="25" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E284" s="5" t="s">
         <v>1348</v>
       </c>
-      <c r="D284" s="5" t="s">
-        <v>1355</v>
-      </c>
-      <c r="E284" s="5" t="s">
-        <v>1350</v>
-      </c>
       <c r="F284" s="5" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="J284" s="5" t="s">
         <v>287</v>
       </c>
       <c r="K284" s="5" t="s">
+        <v>1355</v>
+      </c>
+      <c r="L284" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="M284" s="5" t="s">
         <v>1357</v>
-      </c>
-      <c r="L284" s="7" t="s">
-        <v>1358</v>
-      </c>
-      <c r="M284" s="5" t="s">
-        <v>1359</v>
       </c>
       <c r="N284" s="7" t="s">
         <v>520</v>
       </c>
       <c r="R284" s="5" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="S284" s="5" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="T284" s="6" t="s">
         <v>277</v>
@@ -17869,40 +17869,40 @@
     </row>
     <row r="285" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="25" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B285" s="25" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E285" s="5" t="s">
         <v>1348</v>
       </c>
-      <c r="D285" s="5" t="s">
-        <v>1355</v>
-      </c>
-      <c r="E285" s="5" t="s">
-        <v>1350</v>
-      </c>
       <c r="F285" s="5" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="J285" s="5" t="s">
+        <v>1359</v>
+      </c>
+      <c r="K285" s="5" t="s">
+        <v>1360</v>
+      </c>
+      <c r="L285" s="7" t="s">
         <v>1361</v>
       </c>
-      <c r="K285" s="5" t="s">
-        <v>1362</v>
-      </c>
-      <c r="L285" s="7" t="s">
-        <v>1363</v>
-      </c>
       <c r="M285" s="5" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="N285" s="7" t="s">
         <v>520</v>
       </c>
       <c r="R285" s="5" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="S285" s="5" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="T285" s="6" t="s">
         <v>277</v>
@@ -17916,40 +17916,40 @@
     </row>
     <row r="286" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="25" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B286" s="25" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E286" s="5" t="s">
         <v>1348</v>
       </c>
-      <c r="D286" s="5" t="s">
-        <v>1355</v>
-      </c>
-      <c r="E286" s="5" t="s">
-        <v>1350</v>
-      </c>
       <c r="F286" s="5" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="J286" s="5" t="s">
         <v>1210</v>
       </c>
       <c r="K286" s="5" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="L286" s="7" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="M286" s="5" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="N286" s="7" t="s">
         <v>520</v>
       </c>
       <c r="R286" s="5" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="S286" s="5" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="T286" s="6" t="s">
         <v>277</v>
@@ -17963,13 +17963,13 @@
     </row>
     <row r="287" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="25" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B287" s="25" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D287" s="5" t="s">
         <v>1366</v>
-      </c>
-      <c r="B287" s="25" t="s">
-        <v>1367</v>
-      </c>
-      <c r="D287" s="5" t="s">
-        <v>1368</v>
       </c>
       <c r="E287" s="5" t="s">
         <v>117</v>
@@ -17978,13 +17978,13 @@
         <v>118</v>
       </c>
       <c r="J287" s="5" t="s">
+        <v>1367</v>
+      </c>
+      <c r="K287" s="5" t="s">
+        <v>1368</v>
+      </c>
+      <c r="L287" s="7" t="s">
         <v>1369</v>
-      </c>
-      <c r="K287" s="5" t="s">
-        <v>1370</v>
-      </c>
-      <c r="L287" s="7" t="s">
-        <v>1371</v>
       </c>
       <c r="R287" s="5" t="s">
         <v>37</v>
@@ -18004,31 +18004,31 @@
     </row>
     <row r="288" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="25" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B288" s="25" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="E288" s="5" t="s">
         <v>438</v>
       </c>
       <c r="F288" s="5" t="s">
+        <v>1371</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J288" s="5" t="s">
         <v>1373</v>
       </c>
-      <c r="H288" s="5" t="s">
+      <c r="K288" s="5" t="s">
         <v>1374</v>
       </c>
-      <c r="J288" s="5" t="s">
+      <c r="L288" s="7" t="s">
         <v>1375</v>
-      </c>
-      <c r="K288" s="5" t="s">
-        <v>1376</v>
-      </c>
-      <c r="L288" s="7" t="s">
-        <v>1377</v>
       </c>
       <c r="R288" s="5" t="s">
         <v>37</v>
@@ -18048,28 +18048,28 @@
     </row>
     <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="25" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B289" s="25" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="D289" s="5" t="s">
         <v>323</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="J289" s="5" t="s">
         <v>42</v>
       </c>
       <c r="K289" s="5" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="L289" s="7" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="R289" s="5" t="s">
         <v>37</v>
@@ -18089,10 +18089,10 @@
     </row>
     <row r="290" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="25" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B290" s="25" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="D290" s="5">
         <v>1490</v>
@@ -18104,13 +18104,13 @@
         <v>40</v>
       </c>
       <c r="J290" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="K290" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="L290" s="7" t="s">
         <v>1382</v>
-      </c>
-      <c r="K290" s="5" t="s">
-        <v>1383</v>
-      </c>
-      <c r="L290" s="7" t="s">
-        <v>1384</v>
       </c>
       <c r="R290" s="5" t="s">
         <v>37</v>
@@ -18130,10 +18130,10 @@
     </row>
     <row r="291" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="D291" s="6">
         <v>1494</v>
@@ -18145,13 +18145,13 @@
         <v>658</v>
       </c>
       <c r="J291" s="5" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="K291" s="5" t="s">
         <v>420</v>
       </c>
       <c r="L291" s="47" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="R291" s="5" t="s">
         <v>37</v>
@@ -18171,10 +18171,10 @@
     </row>
     <row r="292" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="25" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B292" s="25" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D292" s="5">
         <v>1469</v>
@@ -18183,19 +18183,19 @@
         <v>589</v>
       </c>
       <c r="F292" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="J292" s="5" t="s">
+        <v>1386</v>
+      </c>
+      <c r="K292" s="5" t="s">
         <v>1387</v>
       </c>
-      <c r="J292" s="5" t="s">
+      <c r="L292" s="7" t="s">
         <v>1388</v>
       </c>
-      <c r="K292" s="5" t="s">
+      <c r="M292" s="5" t="s">
         <v>1389</v>
-      </c>
-      <c r="L292" s="7" t="s">
-        <v>1390</v>
-      </c>
-      <c r="M292" s="5" t="s">
-        <v>1391</v>
       </c>
       <c r="R292" s="5" t="s">
         <v>37</v>
@@ -18215,13 +18215,13 @@
     </row>
     <row r="293" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="25" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B293" s="25" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E293" s="5" t="s">
         <v>86</v>
@@ -18230,22 +18230,22 @@
         <v>87</v>
       </c>
       <c r="J293" s="5" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K293" s="5" t="s">
+        <v>1392</v>
+      </c>
+      <c r="L293" s="7" t="s">
         <v>1393</v>
       </c>
-      <c r="K293" s="5" t="s">
+      <c r="M293" s="5" t="s">
         <v>1394</v>
       </c>
-      <c r="L293" s="7" t="s">
+      <c r="R293" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S293" s="5" t="s">
         <v>1395</v>
-      </c>
-      <c r="M293" s="5" t="s">
-        <v>1396</v>
-      </c>
-      <c r="R293" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S293" s="5" t="s">
-        <v>1397</v>
       </c>
       <c r="T293" s="6">
         <v>239</v>
@@ -18259,10 +18259,10 @@
     </row>
     <row r="294" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="25" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B294" s="25" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D294" s="5">
         <v>1460</v>
@@ -18274,10 +18274,10 @@
         <v>87</v>
       </c>
       <c r="J294" s="5" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="L294" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="R294" s="5" t="s">
         <v>37</v>
@@ -18297,10 +18297,10 @@
     </row>
     <row r="295" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="25" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B295" s="25" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D295" s="5">
         <v>1470</v>
@@ -18312,11 +18312,11 @@
         <v>281</v>
       </c>
       <c r="J295" s="5" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="R295" s="5" t="s">
         <v>37</v>
@@ -18336,10 +18336,10 @@
     </row>
     <row r="296" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="25" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B296" s="25" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D296" s="5">
         <v>1443</v>
@@ -18351,19 +18351,19 @@
         <v>571</v>
       </c>
       <c r="J296" s="5" t="s">
+        <v>1403</v>
+      </c>
+      <c r="K296" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="L296" s="7" t="s">
         <v>1405</v>
-      </c>
-      <c r="K296" s="5" t="s">
-        <v>1406</v>
-      </c>
-      <c r="L296" s="7" t="s">
-        <v>1407</v>
       </c>
       <c r="R296" s="5" t="s">
         <v>29</v>
       </c>
       <c r="S296" s="5" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="T296" s="6">
         <v>820</v>
@@ -18377,13 +18377,13 @@
     </row>
     <row r="297" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="25" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B297" s="25" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="E297" s="5" t="s">
         <v>25</v>
@@ -18392,13 +18392,13 @@
         <v>40</v>
       </c>
       <c r="J297" s="5" t="s">
+        <v>1408</v>
+      </c>
+      <c r="K297" s="5" t="s">
+        <v>1409</v>
+      </c>
+      <c r="L297" s="7" t="s">
         <v>1410</v>
-      </c>
-      <c r="K297" s="5" t="s">
-        <v>1411</v>
-      </c>
-      <c r="L297" s="7" t="s">
-        <v>1412</v>
       </c>
       <c r="R297" s="5" t="s">
         <v>37</v>
@@ -18418,13 +18418,13 @@
     </row>
     <row r="298" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="25" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B298" s="25" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E298" s="5" t="s">
         <v>25</v>
@@ -18433,10 +18433,10 @@
         <v>571</v>
       </c>
       <c r="J298" s="5" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="L298" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="R298" s="5" t="s">
         <v>29</v>
@@ -18456,10 +18456,10 @@
     </row>
     <row r="299" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="25" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B299" s="25" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D299" s="5" t="s">
         <v>826</v>
@@ -18471,19 +18471,19 @@
         <v>87</v>
       </c>
       <c r="J299" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="K299" s="5" t="s">
+        <v>1415</v>
+      </c>
+      <c r="L299" s="7" t="s">
         <v>1416</v>
       </c>
-      <c r="K299" s="5" t="s">
+      <c r="R299" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S299" s="5" t="s">
         <v>1417</v>
-      </c>
-      <c r="L299" s="7" t="s">
-        <v>1418</v>
-      </c>
-      <c r="R299" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S299" s="5" t="s">
-        <v>1419</v>
       </c>
       <c r="T299" s="6">
         <v>182</v>
@@ -18497,13 +18497,13 @@
     </row>
     <row r="300" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="25" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B300" s="25" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="E300" s="5" t="s">
         <v>32</v>
@@ -18512,19 +18512,19 @@
         <v>33</v>
       </c>
       <c r="J300" s="5" t="s">
+        <v>1419</v>
+      </c>
+      <c r="K300" s="5" t="s">
+        <v>1420</v>
+      </c>
+      <c r="L300" s="7" t="s">
         <v>1421</v>
       </c>
-      <c r="K300" s="5" t="s">
+      <c r="R300" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S300" s="5" t="s">
         <v>1422</v>
-      </c>
-      <c r="L300" s="7" t="s">
-        <v>1423</v>
-      </c>
-      <c r="R300" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S300" s="5" t="s">
-        <v>1424</v>
       </c>
       <c r="T300" s="6">
         <v>182</v>
@@ -18538,10 +18538,10 @@
     </row>
     <row r="301" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="25" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B301" s="25" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D301" s="5">
         <v>1447</v>
@@ -18553,10 +18553,10 @@
         <v>751</v>
       </c>
       <c r="J301" s="5" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="L301" s="7" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="R301" s="5" t="s">
         <v>29</v>
@@ -18576,25 +18576,25 @@
     </row>
     <row r="302" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="25" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B302" s="25" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D302" s="5" t="s">
         <v>116</v>
       </c>
       <c r="E302" s="5" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F302" s="5" t="s">
+        <v>1426</v>
+      </c>
+      <c r="J302" s="5" t="s">
         <v>1427</v>
       </c>
-      <c r="F302" s="5" t="s">
+      <c r="L302" s="7" t="s">
         <v>1428</v>
-      </c>
-      <c r="J302" s="5" t="s">
-        <v>1429</v>
-      </c>
-      <c r="L302" s="7" t="s">
-        <v>1430</v>
       </c>
       <c r="R302" s="5" t="s">
         <v>37</v>
@@ -18614,10 +18614,10 @@
     </row>
     <row r="303" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="25" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B303" s="25" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="D303" s="5" t="s">
         <v>674</v>
@@ -18629,13 +18629,13 @@
         <v>87</v>
       </c>
       <c r="J303" s="5" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="K303" s="5" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="L303" s="7" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="R303" s="5" t="s">
         <v>37</v>
@@ -18655,10 +18655,10 @@
     </row>
     <row r="304" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="25" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B304" s="25" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="D304" s="5" t="s">
         <v>674</v>
@@ -18670,16 +18670,16 @@
         <v>68</v>
       </c>
       <c r="J304" s="5" t="s">
+        <v>1432</v>
+      </c>
+      <c r="K304" s="5" t="s">
+        <v>1433</v>
+      </c>
+      <c r="L304" s="7" t="s">
         <v>1434</v>
       </c>
-      <c r="K304" s="5" t="s">
+      <c r="M304" s="5" t="s">
         <v>1435</v>
-      </c>
-      <c r="L304" s="7" t="s">
-        <v>1436</v>
-      </c>
-      <c r="M304" s="5" t="s">
-        <v>1437</v>
       </c>
       <c r="R304" s="5" t="s">
         <v>37</v>
@@ -18699,10 +18699,10 @@
     </row>
     <row r="305" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="25" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B305" s="25" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="D305" s="5" t="s">
         <v>674</v>
@@ -18714,10 +18714,10 @@
         <v>855</v>
       </c>
       <c r="J305" s="5" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="L305" s="3" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="R305" s="5" t="s">
         <v>37</v>
@@ -18737,10 +18737,10 @@
     </row>
     <row r="306" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="25" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B306" s="25" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="D306" s="5">
         <v>1475</v>
@@ -18752,13 +18752,13 @@
         <v>40</v>
       </c>
       <c r="J306" s="5" t="s">
+        <v>1436</v>
+      </c>
+      <c r="K306" s="5" t="s">
+        <v>1437</v>
+      </c>
+      <c r="L306" s="7" t="s">
         <v>1438</v>
-      </c>
-      <c r="K306" s="5" t="s">
-        <v>1439</v>
-      </c>
-      <c r="L306" s="7" t="s">
-        <v>1440</v>
       </c>
       <c r="R306" s="5" t="s">
         <v>247</v>
@@ -18778,28 +18778,28 @@
     </row>
     <row r="307" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="25" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B307" s="25" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="D307" s="5">
         <v>1478</v>
       </c>
       <c r="E307" s="5" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F307" s="5" t="s">
+        <v>1440</v>
+      </c>
+      <c r="J307" s="5" t="s">
         <v>1441</v>
       </c>
-      <c r="F307" s="5" t="s">
+      <c r="K307" s="5" t="s">
         <v>1442</v>
       </c>
-      <c r="J307" s="5" t="s">
+      <c r="L307" s="7" t="s">
         <v>1443</v>
-      </c>
-      <c r="K307" s="5" t="s">
-        <v>1444</v>
-      </c>
-      <c r="L307" s="7" t="s">
-        <v>1445</v>
       </c>
       <c r="R307" s="5" t="s">
         <v>37</v>
@@ -18819,10 +18819,10 @@
     </row>
     <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="26" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B308" s="26" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C308" s="10"/>
       <c r="D308" s="10">
@@ -18838,13 +18838,13 @@
       <c r="H308" s="10"/>
       <c r="I308" s="10"/>
       <c r="J308" s="10" t="s">
+        <v>1444</v>
+      </c>
+      <c r="K308" s="10" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L308" s="11" t="s">
         <v>1446</v>
-      </c>
-      <c r="K308" s="10" t="s">
-        <v>1447</v>
-      </c>
-      <c r="L308" s="11" t="s">
-        <v>1448</v>
       </c>
       <c r="M308" s="10"/>
       <c r="N308" s="10"/>
@@ -18870,10 +18870,10 @@
     </row>
     <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="28" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B309" s="28" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C309" s="16"/>
       <c r="D309" s="16" t="s">
@@ -18889,13 +18889,13 @@
       <c r="H309" s="16"/>
       <c r="I309" s="16"/>
       <c r="J309" s="16" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K309" s="16" t="s">
+        <v>1448</v>
+      </c>
+      <c r="L309" s="17" t="s">
         <v>1449</v>
-      </c>
-      <c r="K309" s="16" t="s">
-        <v>1450</v>
-      </c>
-      <c r="L309" s="17" t="s">
-        <v>1451</v>
       </c>
       <c r="M309" s="16"/>
       <c r="N309" s="16"/>
@@ -18921,10 +18921,10 @@
     </row>
     <row r="310" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="30" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B310" s="30" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C310" s="23"/>
       <c r="D310" s="23">
@@ -18946,7 +18946,7 @@
         <v>295</v>
       </c>
       <c r="L310" s="7" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="M310" s="24"/>
       <c r="N310" s="24"/>
@@ -18960,7 +18960,7 @@
         <v>100</v>
       </c>
       <c r="T310" s="23" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="U310" s="23">
         <v>26</v>
@@ -18972,10 +18972,10 @@
     </row>
     <row r="311" spans="1:23" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="30" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B311" s="30" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C311" s="23"/>
       <c r="D311" s="23" t="s">
@@ -18991,13 +18991,13 @@
       <c r="H311" s="24"/>
       <c r="I311" s="24"/>
       <c r="J311" s="24" t="s">
+        <v>1452</v>
+      </c>
+      <c r="K311" s="24" t="s">
+        <v>1453</v>
+      </c>
+      <c r="L311" s="7" t="s">
         <v>1454</v>
-      </c>
-      <c r="K311" s="24" t="s">
-        <v>1455</v>
-      </c>
-      <c r="L311" s="7" t="s">
-        <v>1456</v>
       </c>
       <c r="M311" s="24"/>
       <c r="N311" s="24"/>
@@ -19023,10 +19023,10 @@
     </row>
     <row r="312" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="29" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B312" s="29" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="C312" s="19"/>
       <c r="D312" s="19">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K312" s="19"/>
       <c r="L312" s="20" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="M312" s="19"/>
       <c r="N312" s="19"/>
@@ -19072,31 +19072,31 @@
     </row>
     <row r="313" spans="1:23" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B313" s="25" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D313" s="5" t="s">
         <v>1458</v>
       </c>
-      <c r="D313" s="5" t="s">
+      <c r="E313" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F313" s="5" t="s">
         <v>1460</v>
       </c>
-      <c r="E313" s="5" t="s">
+      <c r="J313" s="5" t="s">
         <v>1461</v>
       </c>
-      <c r="F313" s="5" t="s">
+      <c r="L313" s="7" t="s">
         <v>1462</v>
       </c>
-      <c r="J313" s="5" t="s">
-        <v>1463</v>
-      </c>
-      <c r="L313" s="7" t="s">
-        <v>1464</v>
-      </c>
       <c r="R313" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S313" s="5" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="T313" s="6">
         <v>138</v>
@@ -19110,13 +19110,13 @@
     </row>
     <row r="314" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B314" s="25" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="E314" s="5" t="s">
         <v>370</v>
@@ -19125,10 +19125,10 @@
         <v>371</v>
       </c>
       <c r="J314" s="5" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="L314" s="7" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="R314" s="5" t="s">
         <v>59</v>
@@ -19148,10 +19148,10 @@
     </row>
     <row r="315" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B315" s="25" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D315" s="5">
         <v>1441</v>
@@ -19160,13 +19160,13 @@
         <v>237</v>
       </c>
       <c r="F315" s="5" t="s">
+        <v>1466</v>
+      </c>
+      <c r="J315" s="5" t="s">
+        <v>1467</v>
+      </c>
+      <c r="L315" s="7" t="s">
         <v>1468</v>
-      </c>
-      <c r="J315" s="5" t="s">
-        <v>1469</v>
-      </c>
-      <c r="L315" s="7" t="s">
-        <v>1470</v>
       </c>
       <c r="R315" s="5" t="s">
         <v>37</v>
@@ -19186,10 +19186,10 @@
     </row>
     <row r="316" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B316" s="25" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D316" s="5">
         <v>1443</v>
@@ -19201,10 +19201,10 @@
         <v>68</v>
       </c>
       <c r="J316" s="5" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="L316" s="7" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="R316" s="5" t="s">
         <v>59</v>
@@ -19224,28 +19224,28 @@
     </row>
     <row r="317" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B317" s="25" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D317" s="5">
         <v>1443</v>
       </c>
       <c r="E317" s="5" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F317" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="J317" s="5" t="s">
         <v>1473</v>
       </c>
-      <c r="F317" s="5" t="s">
+      <c r="L317" s="7" t="s">
         <v>1474</v>
       </c>
-      <c r="J317" s="5" t="s">
+      <c r="M317" s="5" t="s">
         <v>1475</v>
-      </c>
-      <c r="L317" s="7" t="s">
-        <v>1476</v>
-      </c>
-      <c r="M317" s="5" t="s">
-        <v>1477</v>
       </c>
       <c r="R317" s="5" t="s">
         <v>37</v>
@@ -19265,13 +19265,13 @@
     </row>
     <row r="318" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B318" s="25" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="E318" s="5" t="s">
         <v>67</v>
@@ -19280,10 +19280,10 @@
         <v>68</v>
       </c>
       <c r="J318" s="5" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="L318" s="7" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="R318" s="5" t="s">
         <v>247</v>
@@ -19303,13 +19303,13 @@
     </row>
     <row r="319" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B319" s="25" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="E319" s="5" t="s">
         <v>32</v>
@@ -19318,10 +19318,10 @@
         <v>33</v>
       </c>
       <c r="J319" s="5" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="L319" s="7" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="R319" s="5" t="s">
         <v>247</v>
@@ -19341,10 +19341,10 @@
     </row>
     <row r="320" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B320" s="25" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D320" s="5" t="s">
         <v>261</v>
@@ -19356,10 +19356,10 @@
         <v>890</v>
       </c>
       <c r="J320" s="5" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="L320" s="7" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="R320" s="5" t="s">
         <v>59</v>
@@ -19379,10 +19379,10 @@
     </row>
     <row r="321" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B321" s="25" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D321" s="5" t="s">
         <v>267</v>
@@ -19394,10 +19394,10 @@
         <v>376</v>
       </c>
       <c r="J321" s="5" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="L321" s="7" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="R321" s="5" t="s">
         <v>37</v>
@@ -19417,13 +19417,13 @@
     </row>
     <row r="322" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B322" s="25" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="E322" s="5" t="s">
         <v>25</v>
@@ -19432,10 +19432,10 @@
         <v>40</v>
       </c>
       <c r="J322" s="5" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="L322" s="7" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="R322" s="5" t="s">
         <v>37</v>
@@ -19455,10 +19455,10 @@
     </row>
     <row r="323" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="31" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B323" s="31" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="C323" s="31"/>
       <c r="D323" s="33">
@@ -19474,13 +19474,13 @@
       <c r="H323" s="31"/>
       <c r="I323" s="31"/>
       <c r="J323" s="31" t="s">
+        <v>1488</v>
+      </c>
+      <c r="K323" s="31" t="s">
+        <v>1489</v>
+      </c>
+      <c r="L323" s="22" t="s">
         <v>1490</v>
-      </c>
-      <c r="K323" s="31" t="s">
-        <v>1491</v>
-      </c>
-      <c r="L323" s="22" t="s">
-        <v>1492</v>
       </c>
       <c r="M323" s="31"/>
       <c r="N323" s="31"/>
@@ -19505,28 +19505,28 @@
     </row>
     <row r="324" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B324" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D324" s="5">
         <v>1435</v>
       </c>
       <c r="E324" s="5" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F324" s="5" t="s">
+        <v>1494</v>
+      </c>
+      <c r="J324" s="5" t="s">
         <v>1495</v>
       </c>
-      <c r="F324" s="5" t="s">
+      <c r="K324" s="5" t="s">
         <v>1496</v>
       </c>
-      <c r="J324" s="5" t="s">
+      <c r="L324" s="7" t="s">
         <v>1497</v>
-      </c>
-      <c r="K324" s="5" t="s">
-        <v>1498</v>
-      </c>
-      <c r="L324" s="7" t="s">
-        <v>1499</v>
       </c>
       <c r="R324" s="5" t="s">
         <v>37</v>
@@ -19546,13 +19546,13 @@
     </row>
     <row r="325" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B325" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="E325" s="5" t="s">
         <v>86</v>
@@ -19561,13 +19561,13 @@
         <v>87</v>
       </c>
       <c r="J325" s="5" t="s">
+        <v>1499</v>
+      </c>
+      <c r="K325" s="5" t="s">
+        <v>1500</v>
+      </c>
+      <c r="L325" s="7" t="s">
         <v>1501</v>
-      </c>
-      <c r="K325" s="5" t="s">
-        <v>1502</v>
-      </c>
-      <c r="L325" s="7" t="s">
-        <v>1503</v>
       </c>
       <c r="R325" s="5" t="s">
         <v>37</v>
@@ -19587,10 +19587,10 @@
     </row>
     <row r="326" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A326" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B326" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D326" s="5" t="s">
         <v>807</v>
@@ -19602,13 +19602,13 @@
         <v>87</v>
       </c>
       <c r="J326" s="5" t="s">
+        <v>1502</v>
+      </c>
+      <c r="K326" s="5" t="s">
+        <v>1503</v>
+      </c>
+      <c r="L326" s="7" t="s">
         <v>1504</v>
-      </c>
-      <c r="K326" s="5" t="s">
-        <v>1505</v>
-      </c>
-      <c r="L326" s="7" t="s">
-        <v>1506</v>
       </c>
       <c r="R326" s="5" t="s">
         <v>37</v>
@@ -19628,13 +19628,13 @@
     </row>
     <row r="327" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B327" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="E327" s="5" t="s">
         <v>86</v>
@@ -19643,10 +19643,10 @@
         <v>87</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="L327" s="7" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="R327" s="5" t="s">
         <v>37</v>
@@ -19666,10 +19666,10 @@
     </row>
     <row r="328" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B328" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D328" s="5" t="s">
         <v>301</v>
@@ -19681,13 +19681,13 @@
         <v>33</v>
       </c>
       <c r="J328" s="5" t="s">
+        <v>1508</v>
+      </c>
+      <c r="K328" s="5" t="s">
+        <v>1509</v>
+      </c>
+      <c r="L328" s="7" t="s">
         <v>1510</v>
-      </c>
-      <c r="K328" s="5" t="s">
-        <v>1511</v>
-      </c>
-      <c r="L328" s="7" t="s">
-        <v>1512</v>
       </c>
       <c r="R328" s="5" t="s">
         <v>37</v>
@@ -19707,10 +19707,10 @@
     </row>
     <row r="329" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B329" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D329" s="5" t="s">
         <v>1076</v>
@@ -19722,13 +19722,13 @@
         <v>595</v>
       </c>
       <c r="J329" s="5" t="s">
+        <v>1511</v>
+      </c>
+      <c r="K329" s="5" t="s">
+        <v>1512</v>
+      </c>
+      <c r="L329" s="7" t="s">
         <v>1513</v>
-      </c>
-      <c r="K329" s="5" t="s">
-        <v>1514</v>
-      </c>
-      <c r="L329" s="7" t="s">
-        <v>1515</v>
       </c>
       <c r="R329" s="5" t="s">
         <v>247</v>
@@ -19748,13 +19748,13 @@
     </row>
     <row r="330" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B330" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="E330" s="5" t="s">
         <v>505</v>
@@ -19763,13 +19763,13 @@
         <v>506</v>
       </c>
       <c r="J330" s="5" t="s">
+        <v>1515</v>
+      </c>
+      <c r="K330" s="5" t="s">
+        <v>1516</v>
+      </c>
+      <c r="L330" s="7" t="s">
         <v>1517</v>
-      </c>
-      <c r="K330" s="5" t="s">
-        <v>1518</v>
-      </c>
-      <c r="L330" s="7" t="s">
-        <v>1519</v>
       </c>
       <c r="R330" s="5" t="s">
         <v>37</v>
@@ -19789,28 +19789,28 @@
     </row>
     <row r="331" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B331" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D331" s="5">
         <v>1432</v>
       </c>
       <c r="E331" s="5" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F331" s="5" t="s">
+        <v>1519</v>
+      </c>
+      <c r="J331" s="5" t="s">
         <v>1520</v>
       </c>
-      <c r="F331" s="5" t="s">
+      <c r="K331" s="5" t="s">
         <v>1521</v>
       </c>
-      <c r="J331" s="5" t="s">
+      <c r="L331" s="7" t="s">
         <v>1522</v>
-      </c>
-      <c r="K331" s="5" t="s">
-        <v>1523</v>
-      </c>
-      <c r="L331" s="7" t="s">
-        <v>1524</v>
       </c>
       <c r="R331" s="5" t="s">
         <v>59</v>
@@ -19830,13 +19830,13 @@
     </row>
     <row r="332" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B332" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="E332" s="5" t="s">
         <v>375</v>
@@ -19848,10 +19848,10 @@
         <v>531</v>
       </c>
       <c r="K332" s="5" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="L332" s="7" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="R332" s="5" t="s">
         <v>37</v>
@@ -19871,13 +19871,13 @@
     </row>
     <row r="333" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B333" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="E333" s="5" t="s">
         <v>505</v>
@@ -19886,13 +19886,13 @@
         <v>506</v>
       </c>
       <c r="J333" s="5" t="s">
+        <v>1526</v>
+      </c>
+      <c r="K333" s="5" t="s">
+        <v>1527</v>
+      </c>
+      <c r="L333" s="7" t="s">
         <v>1528</v>
-      </c>
-      <c r="K333" s="5" t="s">
-        <v>1529</v>
-      </c>
-      <c r="L333" s="7" t="s">
-        <v>1530</v>
       </c>
       <c r="R333" s="5" t="s">
         <v>37</v>
@@ -19912,13 +19912,13 @@
     </row>
     <row r="334" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B334" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="E334" s="5" t="s">
         <v>280</v>
@@ -19927,10 +19927,10 @@
         <v>281</v>
       </c>
       <c r="J334" s="5" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="L334" s="7" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="R334" s="5" t="s">
         <v>672</v>
@@ -19950,13 +19950,13 @@
     </row>
     <row r="335" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B335" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D335" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="E335" t="s">
         <v>854</v>
@@ -19965,13 +19965,13 @@
         <v>855</v>
       </c>
       <c r="J335" t="s">
+        <v>1532</v>
+      </c>
+      <c r="K335" t="s">
+        <v>1533</v>
+      </c>
+      <c r="L335" s="1" t="s">
         <v>1534</v>
-      </c>
-      <c r="K335" t="s">
-        <v>1535</v>
-      </c>
-      <c r="L335" s="1" t="s">
-        <v>1536</v>
       </c>
       <c r="R335" t="s">
         <v>37</v>
@@ -19983,7 +19983,7 @@
         <v>24</v>
       </c>
       <c r="U335" s="2" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="W335" s="6">
         <v>1</v>
@@ -19995,10 +19995,10 @@
         <v>944</v>
       </c>
       <c r="B336" s="25" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="E336" s="5" t="s">
         <v>67</v>
@@ -20010,7 +20010,7 @@
         <v>186</v>
       </c>
       <c r="L336" s="7" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="R336" s="5" t="s">
         <v>37</v>
@@ -20033,10 +20033,10 @@
         <v>944</v>
       </c>
       <c r="B337" s="25" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="E337" s="5" t="s">
         <v>25</v>
@@ -20045,10 +20045,10 @@
         <v>40</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="L337" s="7" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="R337" s="5" t="s">
         <v>59</v>
@@ -20071,7 +20071,7 @@
         <v>944</v>
       </c>
       <c r="B338" s="25" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="D338" s="5">
         <v>1432</v>
@@ -20080,16 +20080,16 @@
         <v>25</v>
       </c>
       <c r="F338" s="5" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="J338" s="5" t="s">
         <v>443</v>
       </c>
       <c r="K338" s="5" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="L338" s="7" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="R338" s="5" t="s">
         <v>37</v>
@@ -20112,7 +20112,7 @@
         <v>944</v>
       </c>
       <c r="B339" s="25" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="D339" s="5">
         <v>14456</v>
@@ -20124,16 +20124,16 @@
         <v>68</v>
       </c>
       <c r="J339" s="5" t="s">
+        <v>1545</v>
+      </c>
+      <c r="K339" s="5" t="s">
+        <v>1546</v>
+      </c>
+      <c r="L339" s="7" t="s">
         <v>1547</v>
       </c>
-      <c r="K339" s="5" t="s">
+      <c r="R339" s="5" t="s">
         <v>1548</v>
-      </c>
-      <c r="L339" s="7" t="s">
-        <v>1549</v>
-      </c>
-      <c r="R339" s="5" t="s">
-        <v>1550</v>
       </c>
       <c r="S339" s="5" t="s">
         <v>45</v>
@@ -20150,10 +20150,10 @@
     </row>
     <row r="340" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="25" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B340" s="25" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D340" s="5">
         <v>1480</v>
@@ -20165,13 +20165,13 @@
         <v>81</v>
       </c>
       <c r="J340" s="5" t="s">
+        <v>1551</v>
+      </c>
+      <c r="K340" s="5" t="s">
+        <v>1552</v>
+      </c>
+      <c r="L340" s="7" t="s">
         <v>1553</v>
-      </c>
-      <c r="K340" s="5" t="s">
-        <v>1554</v>
-      </c>
-      <c r="L340" s="7" t="s">
-        <v>1555</v>
       </c>
       <c r="R340" s="5" t="s">
         <v>37</v>
@@ -20191,32 +20191,32 @@
     </row>
     <row r="341" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="28" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B341" s="28" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="C341" s="16"/>
       <c r="D341" s="16" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="E341" s="16" t="s">
         <v>80</v>
       </c>
       <c r="F341" s="16" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="G341" s="16"/>
       <c r="H341" s="16"/>
       <c r="I341" s="16"/>
       <c r="J341" s="16" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K341" s="16" t="s">
+        <v>1557</v>
+      </c>
+      <c r="L341" s="17" t="s">
         <v>1558</v>
-      </c>
-      <c r="K341" s="16" t="s">
-        <v>1559</v>
-      </c>
-      <c r="L341" s="17" t="s">
-        <v>1560</v>
       </c>
       <c r="M341" s="16"/>
       <c r="N341" s="16"/>
@@ -20227,7 +20227,7 @@
         <v>37</v>
       </c>
       <c r="S341" s="16" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="T341" s="18">
         <v>141</v>
@@ -20242,10 +20242,10 @@
     </row>
     <row r="342" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D342" s="5">
         <v>1475</v>
@@ -20257,19 +20257,19 @@
         <v>658</v>
       </c>
       <c r="J342" s="5" t="s">
+        <v>1560</v>
+      </c>
+      <c r="K342" s="5" t="s">
+        <v>1561</v>
+      </c>
+      <c r="L342" s="7" t="s">
         <v>1562</v>
-      </c>
-      <c r="K342" s="5" t="s">
-        <v>1563</v>
-      </c>
-      <c r="L342" s="7" t="s">
-        <v>1564</v>
       </c>
       <c r="R342" s="5" t="s">
         <v>689</v>
       </c>
       <c r="S342" s="5" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="T342" s="6">
         <v>120</v>
@@ -20284,10 +20284,10 @@
     </row>
     <row r="343" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D343" s="5" t="s">
         <v>1151</v>
@@ -20305,7 +20305,7 @@
         <v>863</v>
       </c>
       <c r="L343" s="7" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="R343" s="5" t="s">
         <v>37</v>
@@ -20329,7 +20329,7 @@
         <v>842</v>
       </c>
       <c r="B344" s="29" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="C344" s="19"/>
       <c r="D344" s="19">
@@ -20339,7 +20339,7 @@
         <v>80</v>
       </c>
       <c r="F344" s="19" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G344" s="19"/>
       <c r="H344" s="19"/>
@@ -20351,7 +20351,7 @@
         <v>817</v>
       </c>
       <c r="L344" s="20" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="M344" s="19"/>
       <c r="N344" s="19"/>
@@ -20362,7 +20362,7 @@
         <v>37</v>
       </c>
       <c r="S344" s="19" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="T344" s="21">
         <v>230</v>
@@ -20380,7 +20380,7 @@
         <v>842</v>
       </c>
       <c r="B345" s="25" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D345" s="5">
         <v>1446</v>
@@ -20392,19 +20392,19 @@
         <v>81</v>
       </c>
       <c r="J345" s="5" t="s">
+        <v>1568</v>
+      </c>
+      <c r="K345" s="5" t="s">
+        <v>1569</v>
+      </c>
+      <c r="L345" s="7" t="s">
         <v>1570</v>
-      </c>
-      <c r="K345" s="5" t="s">
-        <v>1571</v>
-      </c>
-      <c r="L345" s="7" t="s">
-        <v>1572</v>
       </c>
       <c r="R345" s="5" t="s">
         <v>247</v>
       </c>
       <c r="S345" s="5" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="T345" s="6">
         <v>339</v>
@@ -20421,10 +20421,10 @@
         <v>842</v>
       </c>
       <c r="B346" s="25" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D346" s="5" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="E346" s="5" t="s">
         <v>598</v>
@@ -20433,13 +20433,13 @@
         <v>605</v>
       </c>
       <c r="J346" s="5" t="s">
+        <v>1573</v>
+      </c>
+      <c r="K346" s="5" t="s">
+        <v>1574</v>
+      </c>
+      <c r="L346" s="7" t="s">
         <v>1575</v>
-      </c>
-      <c r="K346" s="5" t="s">
-        <v>1576</v>
-      </c>
-      <c r="L346" s="7" t="s">
-        <v>1577</v>
       </c>
       <c r="R346" s="5" t="s">
         <v>689</v>
@@ -20462,10 +20462,10 @@
         <v>842</v>
       </c>
       <c r="B347" s="25" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D347" s="5" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="E347" s="5" t="s">
         <v>466</v>
@@ -20474,13 +20474,13 @@
         <v>201</v>
       </c>
       <c r="J347" s="5" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K347" s="5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="L347" s="7" t="s">
         <v>1579</v>
-      </c>
-      <c r="K347" s="5" t="s">
-        <v>1580</v>
-      </c>
-      <c r="L347" s="7" t="s">
-        <v>1581</v>
       </c>
       <c r="R347" s="5" t="s">
         <v>689</v>
@@ -20500,10 +20500,10 @@
     </row>
     <row r="348" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="25" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B348" s="25" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D348" s="5">
         <v>1474</v>
@@ -20512,16 +20512,16 @@
         <v>80</v>
       </c>
       <c r="F348" s="5" t="s">
+        <v>1581</v>
+      </c>
+      <c r="J348" s="5" t="s">
+        <v>1582</v>
+      </c>
+      <c r="K348" s="5" t="s">
         <v>1583</v>
       </c>
-      <c r="J348" s="5" t="s">
+      <c r="L348" s="7" t="s">
         <v>1584</v>
-      </c>
-      <c r="K348" s="5" t="s">
-        <v>1585</v>
-      </c>
-      <c r="L348" s="7" t="s">
-        <v>1586</v>
       </c>
       <c r="R348" s="5" t="s">
         <v>247</v>
@@ -20541,10 +20541,10 @@
     </row>
     <row r="349" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="25" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B349" s="25" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D349" s="5">
         <v>1482</v>
@@ -20553,16 +20553,16 @@
         <v>80</v>
       </c>
       <c r="F349" s="5" t="s">
+        <v>1585</v>
+      </c>
+      <c r="J349" s="5" t="s">
+        <v>1586</v>
+      </c>
+      <c r="K349" s="5" t="s">
         <v>1587</v>
       </c>
-      <c r="J349" s="5" t="s">
+      <c r="L349" s="7" t="s">
         <v>1588</v>
-      </c>
-      <c r="K349" s="5" t="s">
-        <v>1589</v>
-      </c>
-      <c r="L349" s="7" t="s">
-        <v>1590</v>
       </c>
       <c r="R349" s="5" t="s">
         <v>247</v>
@@ -20583,10 +20583,10 @@
     </row>
     <row r="350" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="30" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B350" s="30" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D350" s="5">
         <v>1482</v>
@@ -20595,13 +20595,13 @@
         <v>80</v>
       </c>
       <c r="F350" s="5" t="s">
+        <v>1589</v>
+      </c>
+      <c r="J350" s="5" t="s">
+        <v>1590</v>
+      </c>
+      <c r="L350" s="7" t="s">
         <v>1591</v>
-      </c>
-      <c r="J350" s="5" t="s">
-        <v>1592</v>
-      </c>
-      <c r="L350" s="7" t="s">
-        <v>1593</v>
       </c>
       <c r="R350" s="30" t="s">
         <v>689</v>
@@ -20623,10 +20623,10 @@
     </row>
     <row r="351" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="34" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B351" s="34" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="C351" s="34"/>
       <c r="D351" s="36" t="s">
@@ -20645,10 +20645,10 @@
         <v>680</v>
       </c>
       <c r="K351" s="34" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="L351" s="37" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="M351" s="34"/>
       <c r="N351" s="34"/>
@@ -20673,7 +20673,7 @@
     </row>
     <row r="353" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="X121:X140 X146 X150:X171 X174:X176 X179 X188:X193 X196:X203 X208:X215 X220:X227 X236:X247 X252:X259 X262:X263 X268:X275 X299:X310 X315:X323 X327:X335 X292:X294">
+  <conditionalFormatting sqref="X121:X140 X146 X150:X171 X174:X176 X179 X188:X193 X196:X203 X208:X215 X220:X227 X236:X247 X252:X259 X262:X263 X268:X275 X292:X294 X299:X310 X315:X323 X327:X335">
     <cfRule type="expression" dxfId="35" priority="10">
       <formula>IFERROR(--$W123,0)=1</formula>
     </cfRule>
@@ -20706,7 +20706,7 @@
       <formula>IFERROR(--$W147,0)=3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X145 X187 X219 X235 X251 X298 X324:X326 X336:X337 X350 X290">
+  <conditionalFormatting sqref="X145 X187 X219 X235 X251 X290 X298 X324:X326 X336:X337 X350">
     <cfRule type="expression" dxfId="26" priority="46">
       <formula>IFERROR(--$W148,0)=1</formula>
     </cfRule>
@@ -20751,14 +20751,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X184:X185 X342 X346">
-    <cfRule type="expression" dxfId="11" priority="52">
-      <formula>IFERROR(--$W189,0)=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="53">
+    <cfRule type="expression" dxfId="11" priority="53">
       <formula>IFERROR(--$W189,0)=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="54">
+    <cfRule type="expression" dxfId="10" priority="54">
       <formula>IFERROR(--$W189,0)=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="52">
+      <formula>IFERROR(--$W189,0)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X228:X229">
@@ -21060,130 +21060,141 @@
     <hyperlink ref="L250" r:id="rId263" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
     <hyperlink ref="L251" r:id="rId264" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
     <hyperlink ref="L252" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="L253" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="L254" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="L255" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="L256" r:id="rId269" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="L257" r:id="rId270" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="N257" r:id="rId271" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="L258" r:id="rId272" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="N258" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="L259" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="N259" r:id="rId275" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="L260" r:id="rId276" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="N260" r:id="rId277" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="L261" r:id="rId278" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="N261" r:id="rId279" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="L262" r:id="rId280" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="N262" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="L263" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="N263" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="L264" r:id="rId284" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="N264" r:id="rId285" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="L265" r:id="rId286" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="L266" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="L267" r:id="rId288" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="L268" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="L269" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="L270" r:id="rId291" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="N270" r:id="rId292" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="L271" r:id="rId293" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="L272" r:id="rId294" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="L273" r:id="rId295" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="L274" r:id="rId296" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="L275" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="L276" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="L277" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="L278" r:id="rId300" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="L279" r:id="rId301" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="L280" r:id="rId302" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="L281" r:id="rId303" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="L282" r:id="rId304" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="L283" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="L284" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="N284" r:id="rId307" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="L285" r:id="rId308" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="N285" r:id="rId309" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="L286" r:id="rId310" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="N286" r:id="rId311" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="L287" r:id="rId312" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="L288" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="L289" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="L290" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="L292" r:id="rId316" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="L293" r:id="rId317" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="L294" r:id="rId318" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="L295" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="L296" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="L297" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="L298" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="L299" r:id="rId323" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="L300" r:id="rId324" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="L301" r:id="rId325" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="L302" r:id="rId326" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="L303" r:id="rId327" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="L304" r:id="rId328" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="L306" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="L307" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="L308" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="L309" r:id="rId332" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="L310" r:id="rId333" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="L311" r:id="rId334" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="L312" r:id="rId335" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="L313" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="L314" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="L315" r:id="rId338" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="L316" r:id="rId339" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="L317" r:id="rId340" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="L318" r:id="rId341" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="L319" r:id="rId342" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="L320" r:id="rId343" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="L321" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="L322" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="L323" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="L324" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="L325" r:id="rId348" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="L326" r:id="rId349" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="L327" r:id="rId350" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="L328" r:id="rId351" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="L329" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="L330" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="L331" r:id="rId354" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="L332" r:id="rId355" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="L333" r:id="rId356" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="L334" r:id="rId357" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="L335" r:id="rId358" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="L336" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="L337" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="L338" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="L339" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="L340" r:id="rId363" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="L341" r:id="rId364" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="L342" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="L343" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="L344" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="L345" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="L346" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="L347" r:id="rId370" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="L348" r:id="rId371" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="L349" r:id="rId372" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="L350" r:id="rId373" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="L351" r:id="rId374" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="L36" r:id="rId375" xr:uid="{53549D48-936B-4EB4-B241-2F8F9312D948}"/>
-    <hyperlink ref="L158" r:id="rId376" xr:uid="{C8E8DE21-E096-442E-8906-042AB707EAD0}"/>
-    <hyperlink ref="L182" r:id="rId377" xr:uid="{09BB8218-4537-4E85-8496-1D2BF3F79BA9}"/>
-    <hyperlink ref="L305" r:id="rId378" xr:uid="{EA177C80-6E63-4368-9802-12F80918229A}"/>
-    <hyperlink ref="L27" r:id="rId379" xr:uid="{54E1358F-D0C6-4E27-99A2-8BEAA780B02D}"/>
-    <hyperlink ref="L28" r:id="rId380" xr:uid="{35E7AD8E-F497-4D49-898C-9479F369C0C1}"/>
-    <hyperlink ref="L29" r:id="rId381" xr:uid="{BA3F783F-C8BA-4E83-8F00-AA0EFCC62F00}"/>
-    <hyperlink ref="L30" r:id="rId382" xr:uid="{0E291094-F7F9-44D8-BE97-ACE0D1BC461C}"/>
-    <hyperlink ref="L291" r:id="rId383" xr:uid="{C71CE794-173C-4267-BE3E-ED8936667C7A}"/>
+    <hyperlink ref="L254" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="L255" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="L256" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="L257" r:id="rId269" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="N257" r:id="rId270" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="L258" r:id="rId271" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="N258" r:id="rId272" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="L259" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="N259" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="L260" r:id="rId275" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="N260" r:id="rId276" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="L261" r:id="rId277" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="N261" r:id="rId278" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="L262" r:id="rId279" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="N262" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="L263" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="N263" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="L264" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="N264" r:id="rId284" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="L265" r:id="rId285" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="L266" r:id="rId286" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="L267" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="L268" r:id="rId288" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="L269" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="L270" r:id="rId290" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="N270" r:id="rId291" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="L271" r:id="rId292" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="L272" r:id="rId293" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="L273" r:id="rId294" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="L274" r:id="rId295" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="L275" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="L276" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="L277" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="L278" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="L279" r:id="rId300" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="L280" r:id="rId301" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="L281" r:id="rId302" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="L282" r:id="rId303" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="L283" r:id="rId304" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="L284" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="N284" r:id="rId306" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="L285" r:id="rId307" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="N285" r:id="rId308" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="L286" r:id="rId309" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="N286" r:id="rId310" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="L287" r:id="rId311" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="L288" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="L289" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="L290" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="L292" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="L293" r:id="rId316" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="L294" r:id="rId317" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="L295" r:id="rId318" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="L296" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="L297" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="L298" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="L299" r:id="rId322" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="L300" r:id="rId323" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="L301" r:id="rId324" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="L302" r:id="rId325" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="L303" r:id="rId326" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="L304" r:id="rId327" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="L306" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="L307" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="L308" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="L309" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="L310" r:id="rId332" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="L311" r:id="rId333" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="L312" r:id="rId334" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="L313" r:id="rId335" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="L314" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="L315" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="L316" r:id="rId338" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="L317" r:id="rId339" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="L318" r:id="rId340" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="L319" r:id="rId341" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="L320" r:id="rId342" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="L321" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="L322" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="L323" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="L324" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="L325" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="L326" r:id="rId348" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="L327" r:id="rId349" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="L328" r:id="rId350" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="L329" r:id="rId351" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="L330" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="L331" r:id="rId353" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="L332" r:id="rId354" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="L333" r:id="rId355" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="L334" r:id="rId356" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="L335" r:id="rId357" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="L336" r:id="rId358" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="L337" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="L338" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="L339" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="L340" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="L341" r:id="rId363" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="L342" r:id="rId364" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="L343" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="L344" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="L345" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="L346" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="L347" r:id="rId369" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="L348" r:id="rId370" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="L349" r:id="rId371" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="L350" r:id="rId372" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="L351" r:id="rId373" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="L36" r:id="rId374" xr:uid="{53549D48-936B-4EB4-B241-2F8F9312D948}"/>
+    <hyperlink ref="L158" r:id="rId375" xr:uid="{C8E8DE21-E096-442E-8906-042AB707EAD0}"/>
+    <hyperlink ref="L182" r:id="rId376" xr:uid="{09BB8218-4537-4E85-8496-1D2BF3F79BA9}"/>
+    <hyperlink ref="L305" r:id="rId377" xr:uid="{EA177C80-6E63-4368-9802-12F80918229A}"/>
+    <hyperlink ref="L27" r:id="rId378" xr:uid="{54E1358F-D0C6-4E27-99A2-8BEAA780B02D}"/>
+    <hyperlink ref="L28" r:id="rId379" xr:uid="{35E7AD8E-F497-4D49-898C-9479F369C0C1}"/>
+    <hyperlink ref="L29" r:id="rId380" xr:uid="{BA3F783F-C8BA-4E83-8F00-AA0EFCC62F00}"/>
+    <hyperlink ref="L30" r:id="rId381" xr:uid="{0E291094-F7F9-44D8-BE97-ACE0D1BC461C}"/>
+    <hyperlink ref="L291" r:id="rId382" xr:uid="{C71CE794-173C-4267-BE3E-ED8936667C7A}"/>
+    <hyperlink ref="L253" r:id="rId383" xr:uid="{9ADD3719-B05F-47CC-B31A-ACA3F5E88B43}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="93" id="{00000000-000E-0000-0000-00000C000000}">
+            <xm:f>IFERROR(--'[peinture-16e.xlsx]Feuil1'!#REF!,0)=3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFF4B183"/>
+                  <bgColor rgb="FFF4B183"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
           <x14:cfRule type="expression" priority="91" id="{00000000-000E-0000-0000-00000A000000}">
             <xm:f>IFERROR(--'[peinture-16e.xlsx]Feuil1'!#REF!,0)=1</xm:f>
             <x14:dxf>
@@ -21206,17 +21217,6 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="93" id="{00000000-000E-0000-0000-00000C000000}">
-            <xm:f>IFERROR(--'[peinture-16e.xlsx]Feuil1'!#REF!,0)=3</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFF4B183"/>
-                  <bgColor rgb="FFF4B183"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
           <xm:sqref>X177</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D61B095-37EE-43CA-8CC9-FC9ADE955FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B27169E-87CB-4E85-9C43-37C3AEC165B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16463,16 +16463,16 @@
         <v>1231</v>
       </c>
       <c r="R252" s="5" t="s">
-        <v>37</v>
+        <v>247</v>
       </c>
       <c r="S252" s="5" t="s">
         <v>132</v>
       </c>
       <c r="T252" s="6">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="U252" s="6">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="W252" s="6">
         <v>2</v>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B27169E-87CB-4E85-9C43-37C3AEC165B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16D97C3-C5D8-4C1A-830A-3073F965B879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1597,7 +1597,7 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/c/cb/Pala_d_santa_maria_in_porto%2C_ercole_de%27_roberti.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>vers 1480</t>
+    <t>1480 environ</t>
   </si>
   <si>
     <t>Portrait de Giovanni II Bentivoglio</t>
@@ -4084,7 +4084,7 @@
     <t>Huile sur bois de sapin</t>
   </si>
   <si>
-    <t>vers 1475-1480</t>
+    <t>1475-1480 environ</t>
   </si>
   <si>
     <t>Musée Unterlinden</t>
@@ -20115,7 +20115,7 @@
         <v>1536</v>
       </c>
       <c r="D339" s="5">
-        <v>14456</v>
+        <v>1445</v>
       </c>
       <c r="E339" s="5" t="s">
         <v>67</v>

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -5806,7 +5806,7 @@
     <col min="11" max="11" width="37.85546875" style="5" customWidth="1"/>
     <col min="12" max="19" width="9.140625" style="5" customWidth="1"/>
     <col min="20" max="23" width="9.140625" style="6" customWidth="1"/>
-    <col min="24" max="24" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5878,6 +5878,11 @@
       </c>
       <c r="W1" s="6" t="s">
         <v>22</v>
+      </c>
+      <c r="X1" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artiste associé</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/quizzes/peinture-15e.xlsx
+++ b/quizzes/peinture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16D97C3-C5D8-4C1A-830A-3073F965B879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1918B2D-B273-4277-847A-84732E3C5ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3610" uniqueCount="1638">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -2302,9 +2302,6 @@
     <t>Trittico di San Giovenale</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/30/Masaccio%2C_trittico_ di_san_giovenale%2C_1422%2C_01.jpg/1280px-Masaccio%2C_trittico_di_san_giovenale%2C_1422%2C_01.jpg</t>
-  </si>
-  <si>
     <t>108</t>
   </si>
   <si>
@@ -2320,9 +2317,6 @@
     <t>Sant'Anna Metterza</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Masaccio_and_Masolino_-_Madonna_and_Child_with_St_Anne_-_WGA14197.jpg/800px-Masaccio_and_Masolino_-_Madonna_and_Child_with_St_Anne_-_WGA14197.jpg</t>
-  </si>
-  <si>
     <t>177</t>
   </si>
   <si>
@@ -4934,6 +4928,15 @@
   </si>
   <si>
     <t xml:space="preserve">Le Retable Requin </t>
+  </si>
+  <si>
+    <t>Artiste associé</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Masaccio%2C_trittico_di_san_giovenale%2C_1422%2C_01.JPG/1280px-Masaccio%2C_trittico_di_san_giovenale%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Masaccio._The_Madonna_and_Child_with_st._Anna._ca._1424._Uffizi%2C_Florence.jpg/960px-Masaccio._The_Madonna_and_Child_with_st._Anna._ca._1424._Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -5809,7 +5812,7 @@
     <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -5879,13 +5882,11 @@
       <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artiste associé</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X1" s="6" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>23</v>
       </c>
@@ -5923,7 +5924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>23</v>
       </c>
@@ -5964,7 +5965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>23</v>
       </c>
@@ -6008,7 +6009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>23</v>
       </c>
@@ -6016,7 +6017,7 @@
         <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>25</v>
@@ -6052,7 +6053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>53</v>
       </c>
@@ -6090,7 +6091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>53</v>
       </c>
@@ -6128,7 +6129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>53</v>
       </c>
@@ -6166,7 +6167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>53</v>
       </c>
@@ -6205,7 +6206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>77</v>
       </c>
@@ -6243,7 +6244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>77</v>
       </c>
@@ -6281,7 +6282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>77</v>
       </c>
@@ -6319,7 +6320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
         <v>77</v>
       </c>
@@ -6357,7 +6358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>77</v>
       </c>
@@ -6406,7 +6407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>77</v>
       </c>
@@ -6448,7 +6449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>110</v>
       </c>
@@ -6925,19 +6926,19 @@
       </c>
       <c r="H27" s="13"/>
       <c r="J27" s="5" t="s">
+        <v>1619</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>1620</v>
+      </c>
+      <c r="L27" s="47" t="s">
         <v>1621</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="R27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S27" s="5" t="s">
         <v>1622</v>
-      </c>
-      <c r="L27" s="47" t="s">
-        <v>1623</v>
-      </c>
-      <c r="R27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S27" s="5" t="s">
-        <v>1624</v>
       </c>
       <c r="T27" s="6">
         <v>205</v>
@@ -6967,13 +6968,13 @@
       </c>
       <c r="H28" s="13"/>
       <c r="J28" s="5" t="s">
+        <v>1623</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>1624</v>
+      </c>
+      <c r="L28" s="47" t="s">
         <v>1625</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>1626</v>
-      </c>
-      <c r="L28" s="47" t="s">
-        <v>1627</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>37</v>
@@ -7002,20 +7003,20 @@
         <v>736</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>56</v>
       </c>
       <c r="H29" s="13"/>
       <c r="J29" s="5" t="s">
+        <v>1626</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>1627</v>
+      </c>
+      <c r="L29" s="47" t="s">
         <v>1628</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L29" s="47" t="s">
-        <v>1630</v>
       </c>
       <c r="R29" s="5" t="s">
         <v>37</v>
@@ -7054,10 +7055,10 @@
         <v>186</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="L30" s="47" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="R30" s="5" t="s">
         <v>37</v>
@@ -7309,7 +7310,7 @@
         <v>204</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="M36" s="5" t="s">
         <v>205</v>
@@ -7971,7 +7972,7 @@
         <v>279</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>55</v>
@@ -8302,7 +8303,7 @@
         <v>318</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>80</v>
@@ -9058,7 +9059,7 @@
         <v>386</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>117</v>
@@ -9146,7 +9147,7 @@
         <v>67</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>412</v>
@@ -9386,7 +9387,7 @@
         <v>429</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>375</v>
@@ -9468,7 +9469,7 @@
         <v>446</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>453</v>
@@ -9808,7 +9809,7 @@
         <v>490</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>176</v>
@@ -10643,7 +10644,7 @@
         <v>566</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>25</v>
@@ -11987,7 +11988,7 @@
         <v>743</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>25</v>
@@ -12042,8 +12043,8 @@
       <c r="K149" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="L149" s="7" t="s">
-        <v>759</v>
+      <c r="L149" s="3" t="s">
+        <v>1636</v>
       </c>
       <c r="R149" s="5" t="s">
         <v>247</v>
@@ -12052,10 +12053,10 @@
         <v>396</v>
       </c>
       <c r="T149" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="U149" s="6" t="s">
         <v>760</v>
-      </c>
-      <c r="U149" s="6" t="s">
-        <v>761</v>
       </c>
       <c r="W149" s="6">
         <v>1</v>
@@ -12072,7 +12073,7 @@
         <v>743</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E150" s="5" t="s">
         <v>25</v>
@@ -12081,13 +12082,13 @@
         <v>40</v>
       </c>
       <c r="J150" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="K150" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="K150" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="L150" s="7" t="s">
-        <v>765</v>
+      <c r="L150" s="3" t="s">
+        <v>1637</v>
       </c>
       <c r="R150" s="5" t="s">
         <v>37</v>
@@ -12096,10 +12097,10 @@
         <v>122</v>
       </c>
       <c r="T150" s="6" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="U150" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="W150" s="6">
         <v>1</v>
@@ -12116,28 +12117,28 @@
         <v>743</v>
       </c>
       <c r="D151" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="F151" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="E151" s="5" t="s">
+      <c r="J151" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="F151" s="5" t="s">
+      <c r="K151" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="J151" s="5" t="s">
+      <c r="L151" s="7" t="s">
         <v>771</v>
       </c>
-      <c r="K151" s="5" t="s">
+      <c r="M151" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="L151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>773</v>
-      </c>
-      <c r="M151" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>775</v>
       </c>
       <c r="R151" s="5" t="s">
         <v>689</v>
@@ -12146,7 +12147,7 @@
         <v>122</v>
       </c>
       <c r="T151" s="6" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="U151" s="6" t="s">
         <v>316</v>
@@ -12166,7 +12167,7 @@
         <v>743</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E152" s="5" t="s">
         <v>86</v>
@@ -12175,19 +12176,19 @@
         <v>87</v>
       </c>
       <c r="J152" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="K152" s="5" t="s">
         <v>35</v>
       </c>
       <c r="L152" s="7" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="M152" s="5" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="N152" s="7" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="R152" s="5" t="s">
         <v>689</v>
@@ -12196,10 +12197,10 @@
         <v>122</v>
       </c>
       <c r="T152" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="U152" s="6" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="W152" s="6">
         <v>1</v>
@@ -12216,7 +12217,7 @@
         <v>743</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E153" s="5" t="s">
         <v>123</v>
@@ -12225,19 +12226,19 @@
         <v>124</v>
       </c>
       <c r="J153" s="5" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="K153" s="5" t="s">
         <v>420</v>
       </c>
       <c r="L153" s="7" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="M153" s="5" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="N153" s="7" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="R153" s="5" t="s">
         <v>689</v>
@@ -12266,7 +12267,7 @@
         <v>743</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E154" s="5" t="s">
         <v>67</v>
@@ -12275,19 +12276,19 @@
         <v>68</v>
       </c>
       <c r="J154" s="5" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="K154" s="5" t="s">
         <v>187</v>
       </c>
       <c r="L154" s="7" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="M154" s="5" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="N154" s="7" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="R154" s="5" t="s">
         <v>689</v>
@@ -12296,7 +12297,7 @@
         <v>122</v>
       </c>
       <c r="T154" s="6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="U154" s="6" t="s">
         <v>271</v>
@@ -12328,22 +12329,22 @@
         <v>745</v>
       </c>
       <c r="J155" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="K155" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="L155" s="7" t="s">
         <v>787</v>
       </c>
-      <c r="K155" s="5" t="s">
+      <c r="M155" s="5" t="s">
         <v>788</v>
-      </c>
-      <c r="L155" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="M155" s="5" t="s">
-        <v>790</v>
       </c>
       <c r="N155" s="7" t="s">
         <v>748</v>
       </c>
       <c r="P155" s="7" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="R155" s="5" t="s">
         <v>29</v>
@@ -12352,10 +12353,10 @@
         <v>29</v>
       </c>
       <c r="T155" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="U155" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="W155" s="6">
         <v>1</v>
@@ -12372,7 +12373,7 @@
         <v>743</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E156" s="5" t="s">
         <v>25</v>
@@ -12384,16 +12385,16 @@
         <v>745</v>
       </c>
       <c r="J156" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="K156" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="L156" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="K156" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="L156" s="8" t="s">
-        <v>796</v>
-      </c>
       <c r="M156" s="5" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="N156" s="7" t="s">
         <v>748</v>
@@ -12434,13 +12435,13 @@
         <v>68</v>
       </c>
       <c r="J157" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="K157" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="L157" s="7" t="s">
         <v>798</v>
-      </c>
-      <c r="K157" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="L157" s="7" t="s">
-        <v>800</v>
       </c>
       <c r="R157" s="5" t="s">
         <v>37</v>
@@ -12469,25 +12470,25 @@
         <v>743</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="E158" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="J158" s="5" t="s">
+        <v>1603</v>
+      </c>
+      <c r="K158" s="5" t="s">
         <v>1605</v>
       </c>
-      <c r="K158" s="5" t="s">
-        <v>1607</v>
-      </c>
       <c r="L158" s="3" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="M158" s="5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="R158" s="5" t="s">
         <v>37</v>
@@ -12507,13 +12508,13 @@
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B159" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C159" s="5" t="s">
         <v>804</v>
-      </c>
-      <c r="B159" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>806</v>
       </c>
       <c r="D159" s="5">
         <v>1432</v>
@@ -12522,13 +12523,13 @@
         <v>25</v>
       </c>
       <c r="F159" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="J159" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="L159" s="7" t="s">
         <v>808</v>
-      </c>
-      <c r="J159" s="5" t="s">
-        <v>809</v>
-      </c>
-      <c r="L159" s="7" t="s">
-        <v>810</v>
       </c>
       <c r="R159" s="5" t="s">
         <v>37</v>
@@ -12548,16 +12549,16 @@
     </row>
     <row r="160" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B160" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C160" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B160" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>806</v>
-      </c>
       <c r="D160" s="5" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E160" s="5" t="s">
         <v>147</v>
@@ -12569,16 +12570,16 @@
         <v>531</v>
       </c>
       <c r="K160" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="L160" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="R160" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S160" s="5" t="s">
         <v>812</v>
-      </c>
-      <c r="L160" s="7" t="s">
-        <v>813</v>
-      </c>
-      <c r="R160" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S160" s="5" t="s">
-        <v>814</v>
       </c>
       <c r="T160" s="6">
         <v>162</v>
@@ -12592,16 +12593,16 @@
     </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B161" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C161" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B161" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>806</v>
-      </c>
       <c r="D161" s="5" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E161" s="5" t="s">
         <v>32</v>
@@ -12610,19 +12611,19 @@
         <v>33</v>
       </c>
       <c r="J161" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="K161" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="L161" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="K161" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="L161" s="7" t="s">
-        <v>818</v>
-      </c>
       <c r="R161" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S161" s="5" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="T161" s="6">
         <v>213</v>
@@ -12636,13 +12637,13 @@
     </row>
     <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B162" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C162" s="5" t="s">
         <v>804</v>
-      </c>
-      <c r="B162" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>806</v>
       </c>
       <c r="D162" s="5">
         <v>1432</v>
@@ -12651,19 +12652,19 @@
         <v>25</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="J162" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="K162" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="L162" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="K162" s="5" t="s">
+      <c r="M162" s="5" t="s">
         <v>820</v>
-      </c>
-      <c r="L162" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="M162" s="5" t="s">
-        <v>822</v>
       </c>
       <c r="R162" s="5" t="s">
         <v>37</v>
@@ -12683,28 +12684,28 @@
     </row>
     <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B163" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C163" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B163" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>806</v>
-      </c>
       <c r="D163" s="5" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="E163" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="J163" s="5" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="L163" s="7" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="R163" s="5" t="s">
         <v>37</v>
@@ -12724,28 +12725,28 @@
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B164" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C164" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B164" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>806</v>
-      </c>
       <c r="D164" s="5" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E164" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="J164" s="5" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="L164" s="7" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="R164" s="5" t="s">
         <v>59</v>
@@ -12765,13 +12766,13 @@
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B165" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C165" s="5" t="s">
         <v>804</v>
-      </c>
-      <c r="B165" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>806</v>
       </c>
       <c r="D165" s="5">
         <v>1438</v>
@@ -12780,13 +12781,13 @@
         <v>25</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="J165" s="5" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="R165" s="5" t="s">
         <v>29</v>
@@ -12806,28 +12807,28 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B166" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C166" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B166" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>806</v>
-      </c>
       <c r="D166" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="J166" s="5" t="s">
         <v>531</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="R166" s="5" t="s">
         <v>29</v>
@@ -12847,28 +12848,28 @@
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B167" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C167" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B167" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>806</v>
-      </c>
       <c r="D167" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E167" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="J167" s="5" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="R167" s="5" t="s">
         <v>29</v>
@@ -12888,22 +12889,22 @@
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="26" t="s">
+        <v>802</v>
+      </c>
+      <c r="B168" s="26" t="s">
+        <v>803</v>
+      </c>
+      <c r="C168" s="10" t="s">
         <v>804</v>
       </c>
-      <c r="B168" s="26" t="s">
-        <v>805</v>
-      </c>
-      <c r="C168" s="10" t="s">
-        <v>806</v>
-      </c>
       <c r="D168" s="10" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E168" s="10" t="s">
         <v>25</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G168" s="10"/>
       <c r="H168" s="10"/>
@@ -12912,10 +12913,10 @@
         <v>531</v>
       </c>
       <c r="K168" s="10" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="L168" s="11" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="M168" s="10"/>
       <c r="N168" s="10"/>
@@ -12941,13 +12942,13 @@
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B169" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C169" s="5" t="s">
         <v>804</v>
-      </c>
-      <c r="B169" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>806</v>
       </c>
       <c r="D169" s="5">
         <v>1441</v>
@@ -12956,13 +12957,13 @@
         <v>25</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="J169" s="5" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="R169" s="5" t="s">
         <v>29</v>
@@ -12982,13 +12983,13 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="25" t="s">
+        <v>802</v>
+      </c>
+      <c r="B170" s="25" t="s">
+        <v>803</v>
+      </c>
+      <c r="C170" s="5" t="s">
         <v>804</v>
-      </c>
-      <c r="B170" s="25" t="s">
-        <v>805</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>806</v>
       </c>
       <c r="D170" s="5">
         <v>1447</v>
@@ -13000,10 +13001,10 @@
         <v>201</v>
       </c>
       <c r="J170" s="5" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="R170" s="5" t="s">
         <v>29</v>
@@ -13023,31 +13024,31 @@
     </row>
     <row r="171" spans="1:23" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="B171" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="C171" s="5" t="s">
         <v>842</v>
-      </c>
-      <c r="B171" s="25" t="s">
-        <v>843</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>844</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>442</v>
       </c>
       <c r="E171" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="J171" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="F171" s="5" t="s">
+      <c r="K171" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="J171" s="5" t="s">
+      <c r="L171" s="7" t="s">
         <v>847</v>
-      </c>
-      <c r="K171" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="L171" s="7" t="s">
-        <v>849</v>
       </c>
       <c r="R171" s="5" t="s">
         <v>37</v>
@@ -13067,34 +13068,34 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="B172" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="C172" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="B172" s="25" t="s">
+      <c r="D172" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="E172" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="C172" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="E172" s="5" t="s">
-        <v>845</v>
-      </c>
       <c r="F172" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="J172" s="5" t="s">
         <v>850</v>
-      </c>
-      <c r="H172" s="5" t="s">
-        <v>851</v>
-      </c>
-      <c r="J172" s="5" t="s">
-        <v>852</v>
       </c>
       <c r="K172" s="5" t="s">
         <v>43</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="R172" s="5" t="s">
         <v>29</v>
@@ -13114,43 +13115,43 @@
     </row>
     <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="B173" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="C173" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="B173" s="25" t="s">
-        <v>843</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>844</v>
-      </c>
       <c r="D173" s="5" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E173" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="J173" s="5" t="s">
         <v>854</v>
       </c>
-      <c r="F173" s="5" t="s">
+      <c r="K173" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="J173" s="5" t="s">
+      <c r="L173" s="7" t="s">
         <v>856</v>
       </c>
-      <c r="K173" s="5" t="s">
+      <c r="R173" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S173" s="5" t="s">
         <v>857</v>
-      </c>
-      <c r="L173" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="R173" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S173" s="5" t="s">
-        <v>859</v>
       </c>
       <c r="T173" s="6">
         <v>58</v>
       </c>
       <c r="U173" s="6" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="W173" s="6">
         <v>2</v>
@@ -13158,31 +13159,31 @@
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="B174" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="C174" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="B174" s="25" t="s">
-        <v>843</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>844</v>
-      </c>
       <c r="D174" s="5" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J174" s="5" t="s">
         <v>294</v>
       </c>
       <c r="K174" s="5" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="R174" s="5" t="s">
         <v>37</v>
@@ -13202,37 +13203,37 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="B175" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="C175" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="B175" s="25" t="s">
+      <c r="D175" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="C175" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="D175" s="5" t="s">
+      <c r="F175" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="H175" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="E175" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="F175" s="5" t="s">
+      <c r="J175" s="5" t="s">
         <v>866</v>
       </c>
-      <c r="H175" s="5" t="s">
+      <c r="K175" s="5" t="s">
         <v>867</v>
       </c>
-      <c r="J175" s="5" t="s">
+      <c r="L175" s="7" t="s">
         <v>868</v>
       </c>
-      <c r="K175" s="5" t="s">
+      <c r="N175" s="7" t="s">
         <v>869</v>
-      </c>
-      <c r="L175" s="7" t="s">
-        <v>870</v>
-      </c>
-      <c r="N175" s="7" t="s">
-        <v>871</v>
       </c>
       <c r="R175" s="5" t="s">
         <v>29</v>
@@ -13252,16 +13253,16 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="B176" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="C176" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="B176" s="25" t="s">
-        <v>843</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>844</v>
-      </c>
       <c r="D176" s="5" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="E176" s="5" t="s">
         <v>86</v>
@@ -13270,13 +13271,13 @@
         <v>87</v>
       </c>
       <c r="J176" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="K176" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="L176" s="7" t="s">
         <v>873</v>
-      </c>
-      <c r="K176" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="L176" s="7" t="s">
-        <v>875</v>
       </c>
       <c r="R176" s="5" t="s">
         <v>37</v>
@@ -13296,31 +13297,31 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="25" t="s">
+        <v>840</v>
+      </c>
+      <c r="B177" s="25" t="s">
+        <v>841</v>
+      </c>
+      <c r="C177" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="B177" s="25" t="s">
-        <v>843</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>844</v>
-      </c>
       <c r="D177" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="F177" s="5" t="s">
         <v>876</v>
       </c>
-      <c r="E177" s="5" t="s">
+      <c r="J177" s="5" t="s">
         <v>877</v>
       </c>
-      <c r="F177" s="5" t="s">
+      <c r="K177" s="5" t="s">
         <v>878</v>
       </c>
-      <c r="J177" s="5" t="s">
+      <c r="L177" s="7" t="s">
         <v>879</v>
-      </c>
-      <c r="K177" s="5" t="s">
-        <v>880</v>
-      </c>
-      <c r="L177" s="7" t="s">
-        <v>881</v>
       </c>
       <c r="R177" s="5" t="s">
         <v>37</v>
@@ -13340,16 +13341,16 @@
     </row>
     <row r="178" spans="1:23" s="45" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="41" t="s">
+        <v>840</v>
+      </c>
+      <c r="B178" s="41" t="s">
+        <v>841</v>
+      </c>
+      <c r="C178" s="42" t="s">
         <v>842</v>
       </c>
-      <c r="B178" s="41" t="s">
-        <v>843</v>
-      </c>
-      <c r="C178" s="42" t="s">
-        <v>844</v>
-      </c>
       <c r="D178" s="42" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="E178" s="42" t="s">
         <v>32</v>
@@ -13361,13 +13362,13 @@
       <c r="H178" s="42"/>
       <c r="I178" s="42"/>
       <c r="J178" s="42" t="s">
+        <v>880</v>
+      </c>
+      <c r="K178" s="42" t="s">
+        <v>881</v>
+      </c>
+      <c r="L178" s="43" t="s">
         <v>882</v>
-      </c>
-      <c r="K178" s="42" t="s">
-        <v>883</v>
-      </c>
-      <c r="L178" s="43" t="s">
-        <v>884</v>
       </c>
       <c r="M178" s="42"/>
       <c r="N178" s="42"/>
@@ -13378,13 +13379,13 @@
         <v>37</v>
       </c>
       <c r="S178" s="42" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="T178" s="44" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="U178" s="44" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="V178" s="44"/>
       <c r="W178" s="44">
@@ -13393,10 +13394,10 @@
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="25" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B179" s="25" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>330</v>
@@ -13408,25 +13409,25 @@
         <v>33</v>
       </c>
       <c r="J179" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="K179" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="L179" s="7" t="s">
         <v>891</v>
       </c>
-      <c r="K179" s="5" t="s">
+      <c r="R179" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S179" s="5" t="s">
         <v>892</v>
-      </c>
-      <c r="L179" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="R179" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S179" s="5" t="s">
-        <v>894</v>
       </c>
       <c r="T179" s="6" t="s">
         <v>604</v>
       </c>
       <c r="U179" s="6" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="W179" s="6">
         <v>1</v>
@@ -13434,13 +13435,13 @@
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="25" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B180" s="25" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E180" s="5" t="s">
         <v>147</v>
@@ -13449,13 +13450,13 @@
         <v>148</v>
       </c>
       <c r="J180" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="K180" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="L180" s="7" t="s">
         <v>897</v>
-      </c>
-      <c r="K180" s="5" t="s">
-        <v>898</v>
-      </c>
-      <c r="L180" s="7" t="s">
-        <v>899</v>
       </c>
       <c r="R180" s="5" t="s">
         <v>37</v>
@@ -13464,10 +13465,10 @@
         <v>100</v>
       </c>
       <c r="T180" s="6" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="U180" s="6" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="W180" s="6">
         <v>1</v>
@@ -13475,10 +13476,10 @@
     </row>
     <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="25" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B181" s="25" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>154</v>
@@ -13487,16 +13488,16 @@
         <v>117</v>
       </c>
       <c r="F181" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="J181" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="K181" s="5" t="s">
         <v>904</v>
       </c>
-      <c r="J181" s="5" t="s">
+      <c r="L181" s="7" t="s">
         <v>905</v>
-      </c>
-      <c r="K181" s="5" t="s">
-        <v>906</v>
-      </c>
-      <c r="L181" s="7" t="s">
-        <v>907</v>
       </c>
       <c r="R181" s="5" t="s">
         <v>29</v>
@@ -13516,19 +13517,19 @@
     </row>
     <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="25" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B182" s="25" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D182" s="5">
         <v>1456</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="J182" s="5" t="s">
         <v>488</v>
@@ -13537,7 +13538,7 @@
         <v>420</v>
       </c>
       <c r="L182" s="3" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="R182" s="5" t="s">
         <v>37</v>
@@ -13557,28 +13558,28 @@
     </row>
     <row r="183" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="25" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B183" s="25" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="E183" s="5" t="s">
         <v>117</v>
       </c>
       <c r="F183" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="J183" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="K183" s="5" t="s">
         <v>909</v>
       </c>
-      <c r="J183" s="5" t="s">
+      <c r="L183" s="7" t="s">
         <v>910</v>
-      </c>
-      <c r="K183" s="5" t="s">
-        <v>911</v>
-      </c>
-      <c r="L183" s="7" t="s">
-        <v>912</v>
       </c>
       <c r="R183" s="5" t="s">
         <v>37</v>
@@ -13598,10 +13599,10 @@
     </row>
     <row r="184" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="25" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B184" s="25" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D184" s="5">
         <v>1489</v>
@@ -13613,13 +13614,13 @@
         <v>118</v>
       </c>
       <c r="J184" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="K184" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="L184" s="7" t="s">
         <v>913</v>
-      </c>
-      <c r="K184" s="5" t="s">
-        <v>914</v>
-      </c>
-      <c r="L184" s="7" t="s">
-        <v>915</v>
       </c>
       <c r="R184" s="5" t="s">
         <v>37</v>
@@ -13628,7 +13629,7 @@
         <v>452</v>
       </c>
       <c r="T184" s="6" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="U184" s="6" t="s">
         <v>684</v>
@@ -13639,10 +13640,10 @@
     </row>
     <row r="185" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="25" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B185" s="25" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D185" s="5" t="s">
         <v>254</v>
@@ -13657,13 +13658,13 @@
         <v>93</v>
       </c>
       <c r="L185" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="R185" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="S185" s="5" t="s">
         <v>919</v>
-      </c>
-      <c r="R185" s="9" t="s">
-        <v>920</v>
-      </c>
-      <c r="S185" s="5" t="s">
-        <v>921</v>
       </c>
       <c r="T185" s="6">
         <v>7</v>
@@ -13677,13 +13678,13 @@
     </row>
     <row r="186" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="25" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B186" s="25" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="E186" s="5" t="s">
         <v>32</v>
@@ -13692,16 +13693,16 @@
         <v>33</v>
       </c>
       <c r="J186" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="L186" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="R186" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S186" s="5" t="s">
         <v>922</v>
-      </c>
-      <c r="L186" s="7" t="s">
-        <v>923</v>
-      </c>
-      <c r="R186" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S186" s="5" t="s">
-        <v>924</v>
       </c>
       <c r="T186" s="6">
         <v>86</v>
@@ -13715,13 +13716,13 @@
     </row>
     <row r="187" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="25" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B187" s="25" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="E187" s="5" t="s">
         <v>370</v>
@@ -13730,10 +13731,10 @@
         <v>371</v>
       </c>
       <c r="J187" s="5" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="L187" s="7" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="R187" s="5" t="s">
         <v>37</v>
@@ -13753,13 +13754,13 @@
     </row>
     <row r="188" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="25" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B188" s="25" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="E188" s="5" t="s">
         <v>67</v>
@@ -13768,13 +13769,13 @@
         <v>68</v>
       </c>
       <c r="J188" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="L188" s="7" t="s">
+        <v>928</v>
+      </c>
+      <c r="M188" s="5" t="s">
         <v>929</v>
-      </c>
-      <c r="L188" s="7" t="s">
-        <v>930</v>
-      </c>
-      <c r="M188" s="5" t="s">
-        <v>931</v>
       </c>
       <c r="R188" s="5" t="s">
         <v>37</v>
@@ -13794,13 +13795,13 @@
     </row>
     <row r="189" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="25" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B189" s="25" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="E189" t="s">
         <v>728</v>
@@ -13812,16 +13813,16 @@
         <v>186</v>
       </c>
       <c r="L189" s="7" t="s">
+        <v>930</v>
+      </c>
+      <c r="M189" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="R189" s="9" t="s">
         <v>932</v>
       </c>
-      <c r="M189" s="5" t="s">
+      <c r="S189" s="5" t="s">
         <v>933</v>
-      </c>
-      <c r="R189" s="9" t="s">
-        <v>934</v>
-      </c>
-      <c r="S189" s="5" t="s">
-        <v>935</v>
       </c>
       <c r="T189" s="6">
         <v>21</v>
@@ -13835,13 +13836,13 @@
     </row>
     <row r="190" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="25" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B190" s="25" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E190" s="5" t="s">
         <v>32</v>
@@ -13850,10 +13851,10 @@
         <v>33</v>
       </c>
       <c r="J190" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="L190" s="7" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="R190" s="5" t="s">
         <v>37</v>
@@ -13873,25 +13874,25 @@
     </row>
     <row r="191" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="25" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B191" s="25" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E191" s="5" t="s">
+        <v>937</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>938</v>
+      </c>
+      <c r="J191" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="F191" s="5" t="s">
+      <c r="L191" s="7" t="s">
         <v>940</v>
-      </c>
-      <c r="J191" s="5" t="s">
-        <v>941</v>
-      </c>
-      <c r="L191" s="7" t="s">
-        <v>942</v>
       </c>
       <c r="R191" s="5" t="s">
         <v>37</v>
@@ -13911,13 +13912,13 @@
     </row>
     <row r="192" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="25" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="E192" t="s">
         <v>728</v>
@@ -13926,19 +13927,19 @@
         <v>729</v>
       </c>
       <c r="J192" s="5" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="L192" s="7" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="M192" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="R192" s="9" t="s">
+        <v>932</v>
+      </c>
+      <c r="S192" s="5" t="s">
         <v>933</v>
-      </c>
-      <c r="R192" s="9" t="s">
-        <v>934</v>
-      </c>
-      <c r="S192" s="5" t="s">
-        <v>935</v>
       </c>
       <c r="T192" s="6">
         <v>17</v>
@@ -13952,10 +13953,10 @@
     </row>
     <row r="193" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B193" s="25" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>139</v>
@@ -13967,13 +13968,13 @@
         <v>33</v>
       </c>
       <c r="J193" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="K193" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="L193" s="7" t="s">
         <v>946</v>
-      </c>
-      <c r="K193" s="5" t="s">
-        <v>947</v>
-      </c>
-      <c r="L193" s="7" t="s">
-        <v>948</v>
       </c>
       <c r="R193" s="5" t="s">
         <v>37</v>
@@ -13985,7 +13986,7 @@
         <v>63</v>
       </c>
       <c r="U193" s="6" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="W193" s="6">
         <v>2</v>
@@ -13993,10 +13994,10 @@
     </row>
     <row r="194" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B194" s="25" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D194" s="5">
         <v>1485</v>
@@ -14008,19 +14009,19 @@
         <v>751</v>
       </c>
       <c r="H194" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="J194" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="K194" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="J194" s="5" t="s">
+      <c r="L194" s="7" t="s">
         <v>951</v>
       </c>
-      <c r="K194" s="5" t="s">
+      <c r="M194" s="5" t="s">
         <v>952</v>
-      </c>
-      <c r="L194" s="7" t="s">
-        <v>953</v>
-      </c>
-      <c r="M194" s="5" t="s">
-        <v>954</v>
       </c>
       <c r="R194" s="5" t="s">
         <v>29</v>
@@ -14029,10 +14030,10 @@
         <v>29</v>
       </c>
       <c r="T194" s="6" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="U194" s="6" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="W194" s="6">
         <v>2</v>
@@ -14040,10 +14041,10 @@
     </row>
     <row r="195" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B195" s="25" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D195" s="5">
         <v>1485</v>
@@ -14052,16 +14053,16 @@
         <v>25</v>
       </c>
       <c r="F195" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="J195" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="K195" s="5" t="s">
         <v>956</v>
       </c>
-      <c r="J195" s="5" t="s">
+      <c r="L195" s="7" t="s">
         <v>957</v>
-      </c>
-      <c r="K195" s="5" t="s">
-        <v>958</v>
-      </c>
-      <c r="L195" s="7" t="s">
-        <v>959</v>
       </c>
       <c r="R195" s="5" t="s">
         <v>37</v>
@@ -14070,7 +14071,7 @@
         <v>122</v>
       </c>
       <c r="T195" s="6" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="U195" s="6">
         <v>240</v>
@@ -14081,10 +14082,10 @@
     </row>
     <row r="196" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B196" s="25" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D196" s="5">
         <v>1485</v>
@@ -14093,19 +14094,19 @@
         <v>25</v>
       </c>
       <c r="F196" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="H196" s="5" t="s">
+        <v>960</v>
+      </c>
+      <c r="J196" s="5" t="s">
         <v>961</v>
       </c>
-      <c r="H196" s="5" t="s">
+      <c r="K196" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="J196" s="5" t="s">
+      <c r="L196" s="7" t="s">
         <v>963</v>
-      </c>
-      <c r="K196" s="5" t="s">
-        <v>964</v>
-      </c>
-      <c r="L196" s="7" t="s">
-        <v>965</v>
       </c>
       <c r="R196" s="5" t="s">
         <v>37</v>
@@ -14125,10 +14126,10 @@
     </row>
     <row r="197" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B197" s="25" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>504</v>
@@ -14137,16 +14138,16 @@
         <v>147</v>
       </c>
       <c r="F197" s="5" t="s">
+        <v>964</v>
+      </c>
+      <c r="J197" s="5" t="s">
+        <v>965</v>
+      </c>
+      <c r="K197" s="5" t="s">
         <v>966</v>
       </c>
-      <c r="J197" s="5" t="s">
+      <c r="L197" s="7" t="s">
         <v>967</v>
-      </c>
-      <c r="K197" s="5" t="s">
-        <v>968</v>
-      </c>
-      <c r="L197" s="7" t="s">
-        <v>969</v>
       </c>
       <c r="R197" s="5" t="s">
         <v>37</v>
@@ -14166,10 +14167,10 @@
     </row>
     <row r="198" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B198" s="25" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D198" s="5">
         <v>1481</v>
@@ -14184,13 +14185,13 @@
         <v>202</v>
       </c>
       <c r="J198" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="K198" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="L198" s="7" t="s">
         <v>970</v>
-      </c>
-      <c r="K198" s="5" t="s">
-        <v>971</v>
-      </c>
-      <c r="L198" s="7" t="s">
-        <v>972</v>
       </c>
       <c r="R198" s="5" t="s">
         <v>29</v>
@@ -14199,10 +14200,10 @@
         <v>29</v>
       </c>
       <c r="T198" s="6" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="U198" s="6" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="W198" s="6">
         <v>2</v>
@@ -14210,10 +14211,10 @@
     </row>
     <row r="199" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B199" s="25" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D199" s="5" t="s">
         <v>85</v>
@@ -14222,7 +14223,7 @@
         <v>25</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="J199" s="5" t="s">
         <v>481</v>
@@ -14231,7 +14232,7 @@
         <v>482</v>
       </c>
       <c r="L199" s="7" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="R199" s="5" t="s">
         <v>29</v>
@@ -14243,7 +14244,7 @@
         <v>740</v>
       </c>
       <c r="U199" s="6" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="W199" s="6">
         <v>2</v>
@@ -14251,10 +14252,10 @@
     </row>
     <row r="200" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B200" s="25" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D200" s="5" t="s">
         <v>85</v>
@@ -14263,19 +14264,19 @@
         <v>25</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="H200" s="5" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="J200" s="5" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="K200" s="5" t="s">
         <v>569</v>
       </c>
       <c r="L200" s="7" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="R200" s="5" t="s">
         <v>29</v>
@@ -14284,7 +14285,7 @@
         <v>29</v>
       </c>
       <c r="T200" s="6" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="U200" s="6">
         <v>880</v>
@@ -14295,31 +14296,31 @@
     </row>
     <row r="201" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="25" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B201" s="25" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D201" s="5">
         <v>1450</v>
       </c>
       <c r="E201" s="5" t="s">
+        <v>982</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="J201" s="5" t="s">
         <v>984</v>
       </c>
-      <c r="F201" s="5" t="s">
+      <c r="L201" s="7" t="s">
         <v>985</v>
       </c>
-      <c r="J201" s="5" t="s">
+      <c r="R201" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S201" s="5" t="s">
         <v>986</v>
-      </c>
-      <c r="L201" s="7" t="s">
-        <v>987</v>
-      </c>
-      <c r="R201" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S201" s="5" t="s">
-        <v>988</v>
       </c>
       <c r="T201" s="6">
         <v>207</v>
@@ -14333,34 +14334,34 @@
     </row>
     <row r="202" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="25" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B202" s="25" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>674</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="J202" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="K202" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="L202" s="7" t="s">
         <v>989</v>
       </c>
-      <c r="K202" s="5" t="s">
+      <c r="R202" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S202" s="5" t="s">
         <v>990</v>
-      </c>
-      <c r="L202" s="7" t="s">
-        <v>991</v>
-      </c>
-      <c r="R202" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S202" s="5" t="s">
-        <v>992</v>
       </c>
       <c r="T202" s="6">
         <v>211</v>
@@ -14374,31 +14375,31 @@
     </row>
     <row r="203" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="25" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B203" s="25" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D203" s="5">
         <v>1470</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="J203" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="L203" s="7" t="s">
+        <v>992</v>
+      </c>
+      <c r="R203" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S203" s="5" t="s">
         <v>993</v>
-      </c>
-      <c r="L203" s="7" t="s">
-        <v>994</v>
-      </c>
-      <c r="R203" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S203" s="5" t="s">
-        <v>995</v>
       </c>
       <c r="T203" s="6">
         <v>135</v>
@@ -14414,31 +14415,31 @@
     </row>
     <row r="204" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="25" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B204" s="25" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="D204" s="5">
         <v>1460</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="J204" s="5" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="L204" s="7" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="R204" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S204" s="5" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="T204" s="6">
         <v>118</v>
@@ -14454,10 +14455,10 @@
     </row>
     <row r="205" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B205" s="25" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D205" s="5">
         <v>1450</v>
@@ -14466,22 +14467,22 @@
         <v>25</v>
       </c>
       <c r="F205" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="H205" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="J205" s="5" t="s">
         <v>1000</v>
       </c>
-      <c r="H205" s="5" t="s">
+      <c r="K205" s="5" t="s">
         <v>1001</v>
       </c>
-      <c r="J205" s="5" t="s">
+      <c r="L205" s="7" t="s">
         <v>1002</v>
       </c>
-      <c r="K205" s="5" t="s">
+      <c r="M205" s="5" t="s">
         <v>1003</v>
-      </c>
-      <c r="L205" s="7" t="s">
-        <v>1004</v>
-      </c>
-      <c r="M205" s="5" t="s">
-        <v>1005</v>
       </c>
       <c r="R205" s="5" t="s">
         <v>29</v>
@@ -14490,10 +14491,10 @@
         <v>29</v>
       </c>
       <c r="T205" s="6" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="U205" s="6" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="W205" s="6">
         <v>2</v>
@@ -14501,10 +14502,10 @@
     </row>
     <row r="206" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B206" s="25" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D206" s="5">
         <v>1472</v>
@@ -14516,13 +14517,13 @@
         <v>33</v>
       </c>
       <c r="J206" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K206" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L206" s="7" t="s">
         <v>1008</v>
-      </c>
-      <c r="K206" s="5" t="s">
-        <v>1009</v>
-      </c>
-      <c r="L206" s="7" t="s">
-        <v>1010</v>
       </c>
       <c r="R206" s="5" t="s">
         <v>37</v>
@@ -14534,7 +14535,7 @@
         <v>697</v>
       </c>
       <c r="U206" s="6" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="W206" s="6">
         <v>2</v>
@@ -14542,43 +14543,43 @@
     </row>
     <row r="207" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B207" s="25" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>361</v>
       </c>
       <c r="E207" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G207" s="7" t="s">
         <v>1012</v>
       </c>
-      <c r="F207" s="5" t="s">
+      <c r="H207" s="5" t="s">
         <v>1013</v>
       </c>
-      <c r="G207" s="7" t="s">
+      <c r="I207" s="7" t="s">
         <v>1014</v>
       </c>
-      <c r="H207" s="5" t="s">
+      <c r="J207" s="5" t="s">
         <v>1015</v>
       </c>
-      <c r="I207" s="7" t="s">
+      <c r="K207" s="5" t="s">
         <v>1016</v>
       </c>
-      <c r="J207" s="5" t="s">
+      <c r="L207" s="7" t="s">
         <v>1017</v>
       </c>
-      <c r="K207" s="5" t="s">
+      <c r="M207" s="5" t="s">
         <v>1018</v>
       </c>
-      <c r="L207" s="7" t="s">
+      <c r="N207" s="7" t="s">
         <v>1019</v>
-      </c>
-      <c r="M207" s="5" t="s">
-        <v>1020</v>
-      </c>
-      <c r="N207" s="7" t="s">
-        <v>1021</v>
       </c>
       <c r="R207" s="5" t="s">
         <v>29</v>
@@ -14598,37 +14599,37 @@
     </row>
     <row r="208" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B208" s="25" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D208" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F208" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="E208" s="5" t="s">
+      <c r="H208" s="5" t="s">
         <v>1024</v>
       </c>
-      <c r="F208" s="5" t="s">
+      <c r="I208" s="7" t="s">
         <v>1025</v>
       </c>
-      <c r="H208" s="5" t="s">
+      <c r="J208" s="5" t="s">
         <v>1026</v>
       </c>
-      <c r="I208" s="7" t="s">
+      <c r="K208" s="5" t="s">
         <v>1027</v>
       </c>
-      <c r="J208" s="5" t="s">
+      <c r="L208" s="7" t="s">
         <v>1028</v>
       </c>
-      <c r="K208" s="5" t="s">
+      <c r="M208" s="5" t="s">
         <v>1029</v>
-      </c>
-      <c r="L208" s="7" t="s">
-        <v>1030</v>
-      </c>
-      <c r="M208" s="5" t="s">
-        <v>1031</v>
       </c>
       <c r="R208" s="5" t="s">
         <v>29</v>
@@ -14637,7 +14638,7 @@
         <v>29</v>
       </c>
       <c r="T208" s="6" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="U208" s="6" t="s">
         <v>697</v>
@@ -14648,13 +14649,13 @@
     </row>
     <row r="209" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B209" s="25" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="E209" s="5" t="s">
         <v>438</v>
@@ -14663,13 +14664,13 @@
         <v>439</v>
       </c>
       <c r="J209" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K209" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L209" s="7" t="s">
         <v>1033</v>
-      </c>
-      <c r="K209" s="5" t="s">
-        <v>1034</v>
-      </c>
-      <c r="L209" s="7" t="s">
-        <v>1035</v>
       </c>
       <c r="R209" s="5" t="s">
         <v>59</v>
@@ -14678,10 +14679,10 @@
         <v>122</v>
       </c>
       <c r="T209" s="6" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="U209" s="6" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="W209" s="6">
         <v>2</v>
@@ -14689,13 +14690,13 @@
     </row>
     <row r="210" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B210" s="25" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E210" s="5" t="s">
         <v>86</v>
@@ -14704,16 +14705,16 @@
         <v>87</v>
       </c>
       <c r="J210" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K210" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L210" s="7" t="s">
         <v>1039</v>
       </c>
-      <c r="K210" s="5" t="s">
+      <c r="M210" s="5" t="s">
         <v>1040</v>
-      </c>
-      <c r="L210" s="7" t="s">
-        <v>1041</v>
-      </c>
-      <c r="M210" s="5" t="s">
-        <v>1042</v>
       </c>
       <c r="R210" s="5" t="s">
         <v>37</v>
@@ -14733,28 +14734,28 @@
     </row>
     <row r="211" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B211" s="25" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D211" s="5">
         <v>1497</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="J211" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K211" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="L211" s="7" t="s">
         <v>1043</v>
-      </c>
-      <c r="K211" s="5" t="s">
-        <v>1044</v>
-      </c>
-      <c r="L211" s="7" t="s">
-        <v>1045</v>
       </c>
       <c r="R211" s="5" t="s">
         <v>37</v>
@@ -14774,28 +14775,28 @@
     </row>
     <row r="212" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="25" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B212" s="25" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="D212" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F212" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="E212" s="5" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F212" s="5" t="s">
-        <v>1025</v>
-      </c>
       <c r="J212" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K212" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L212" s="7" t="s">
         <v>1047</v>
-      </c>
-      <c r="K212" s="5" t="s">
-        <v>1048</v>
-      </c>
-      <c r="L212" s="7" t="s">
-        <v>1049</v>
       </c>
       <c r="R212" s="5" t="s">
         <v>29</v>
@@ -14815,10 +14816,10 @@
     </row>
     <row r="213" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="25" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B213" s="25" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D213" s="5">
         <v>1464</v>
@@ -14827,13 +14828,13 @@
         <v>140</v>
       </c>
       <c r="F213" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="J213" s="5" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L213" s="7" t="s">
         <v>1052</v>
-      </c>
-      <c r="J213" s="5" t="s">
-        <v>1053</v>
-      </c>
-      <c r="L213" s="7" t="s">
-        <v>1054</v>
       </c>
       <c r="R213" s="5" t="s">
         <v>59</v>
@@ -14853,10 +14854,10 @@
     </row>
     <row r="214" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="25" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B214" s="25" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D214" s="5" t="s">
         <v>387</v>
@@ -14865,13 +14866,13 @@
         <v>140</v>
       </c>
       <c r="F214" s="5" t="s">
+        <v>1053</v>
+      </c>
+      <c r="J214" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L214" s="7" t="s">
         <v>1055</v>
-      </c>
-      <c r="J214" s="5" t="s">
-        <v>1056</v>
-      </c>
-      <c r="L214" s="7" t="s">
-        <v>1057</v>
       </c>
       <c r="R214" s="5" t="s">
         <v>59</v>
@@ -14891,28 +14892,28 @@
     </row>
     <row r="215" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="25" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B215" s="25" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D215" s="5">
         <v>1458</v>
       </c>
       <c r="E215" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J215" s="5" t="s">
         <v>1058</v>
       </c>
-      <c r="F215" s="5" t="s">
+      <c r="K215" s="5" t="s">
         <v>1059</v>
       </c>
-      <c r="J215" s="5" t="s">
+      <c r="L215" s="7" t="s">
         <v>1060</v>
-      </c>
-      <c r="K215" s="5" t="s">
-        <v>1061</v>
-      </c>
-      <c r="L215" s="7" t="s">
-        <v>1062</v>
       </c>
       <c r="R215" s="5" t="s">
         <v>59</v>
@@ -14933,10 +14934,10 @@
     </row>
     <row r="216" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="25" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B216" s="25" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D216" s="5">
         <v>1450</v>
@@ -14945,16 +14946,16 @@
         <v>140</v>
       </c>
       <c r="F216" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J216" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="L216" s="7" t="s">
         <v>1063</v>
       </c>
-      <c r="J216" s="5" t="s">
+      <c r="R216" s="5" t="s">
         <v>1064</v>
-      </c>
-      <c r="L216" s="7" t="s">
-        <v>1065</v>
-      </c>
-      <c r="R216" s="5" t="s">
-        <v>1066</v>
       </c>
       <c r="S216" s="5" t="s">
         <v>396</v>
@@ -14972,13 +14973,13 @@
     </row>
     <row r="217" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="25" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B217" s="25" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D217" s="5" t="s">
         <v>1067</v>
-      </c>
-      <c r="B217" s="25" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>1069</v>
       </c>
       <c r="E217" s="5" t="s">
         <v>25</v>
@@ -14987,13 +14988,13 @@
         <v>40</v>
       </c>
       <c r="J217" s="5" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="K217" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="L217" s="7" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="R217" s="5" t="s">
         <v>37</v>
@@ -15013,13 +15014,13 @@
     </row>
     <row r="218" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="25" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B218" s="25" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="E218" s="5" t="s">
         <v>25</v>
@@ -15028,13 +15029,13 @@
         <v>40</v>
       </c>
       <c r="J218" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K218" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L218" s="7" t="s">
         <v>1073</v>
-      </c>
-      <c r="K218" s="5" t="s">
-        <v>1074</v>
-      </c>
-      <c r="L218" s="7" t="s">
-        <v>1075</v>
       </c>
       <c r="R218" s="5" t="s">
         <v>37</v>
@@ -15054,28 +15055,28 @@
     </row>
     <row r="219" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="25" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B219" s="25" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D219" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F219" s="5" t="s">
         <v>1076</v>
       </c>
-      <c r="E219" s="5" t="s">
+      <c r="J219" s="5" t="s">
         <v>1077</v>
       </c>
-      <c r="F219" s="5" t="s">
+      <c r="K219" s="5" t="s">
         <v>1078</v>
       </c>
-      <c r="J219" s="5" t="s">
+      <c r="L219" s="7" t="s">
         <v>1079</v>
-      </c>
-      <c r="K219" s="5" t="s">
-        <v>1080</v>
-      </c>
-      <c r="L219" s="7" t="s">
-        <v>1081</v>
       </c>
       <c r="R219" s="5" t="s">
         <v>37</v>
@@ -15095,10 +15096,10 @@
     </row>
     <row r="220" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="26" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B220" s="26" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C220" s="10"/>
       <c r="D220" s="10">
@@ -15114,13 +15115,13 @@
       <c r="H220" s="10"/>
       <c r="I220" s="10"/>
       <c r="J220" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K220" s="10" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L220" s="11" t="s">
         <v>1082</v>
-      </c>
-      <c r="K220" s="10" t="s">
-        <v>1083</v>
-      </c>
-      <c r="L220" s="11" t="s">
-        <v>1084</v>
       </c>
       <c r="M220" s="10"/>
       <c r="N220" s="10"/>
@@ -15146,10 +15147,10 @@
     </row>
     <row r="221" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="25" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B221" s="25" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D221" s="5">
         <v>1445</v>
@@ -15158,25 +15159,25 @@
         <v>25</v>
       </c>
       <c r="F221" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H221" s="5" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J221" s="5" t="s">
         <v>1085</v>
       </c>
-      <c r="H221" s="5" t="s">
+      <c r="K221" s="5" t="s">
         <v>1086</v>
       </c>
-      <c r="J221" s="5" t="s">
+      <c r="L221" s="7" t="s">
         <v>1087</v>
       </c>
-      <c r="K221" s="5" t="s">
+      <c r="M221" s="5" t="s">
         <v>1088</v>
       </c>
-      <c r="L221" s="7" t="s">
+      <c r="N221" s="7" t="s">
         <v>1089</v>
-      </c>
-      <c r="M221" s="5" t="s">
-        <v>1090</v>
-      </c>
-      <c r="N221" s="7" t="s">
-        <v>1091</v>
       </c>
       <c r="R221" s="5" t="s">
         <v>37</v>
@@ -15196,10 +15197,10 @@
     </row>
     <row r="222" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="25" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B222" s="25" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D222" s="5" t="s">
         <v>361</v>
@@ -15211,16 +15212,16 @@
         <v>637</v>
       </c>
       <c r="H222" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J222" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K222" s="5" t="s">
         <v>1092</v>
       </c>
-      <c r="J222" s="5" t="s">
+      <c r="L222" s="7" t="s">
         <v>1093</v>
-      </c>
-      <c r="K222" s="5" t="s">
-        <v>1094</v>
-      </c>
-      <c r="L222" s="7" t="s">
-        <v>1095</v>
       </c>
       <c r="R222" s="5" t="s">
         <v>37</v>
@@ -15240,37 +15241,37 @@
     </row>
     <row r="223" spans="1:23" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="25" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B223" s="25" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D223" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F223" s="5" t="s">
         <v>1096</v>
       </c>
-      <c r="E223" s="5" t="s">
+      <c r="H223" s="5" t="s">
         <v>1097</v>
       </c>
-      <c r="F223" s="5" t="s">
+      <c r="J223" s="5" t="s">
         <v>1098</v>
       </c>
-      <c r="H223" s="5" t="s">
+      <c r="K223" s="5" t="s">
         <v>1099</v>
       </c>
-      <c r="J223" s="5" t="s">
+      <c r="L223" s="7" t="s">
         <v>1100</v>
       </c>
-      <c r="K223" s="5" t="s">
+      <c r="M223" s="5" t="s">
         <v>1101</v>
       </c>
-      <c r="L223" s="7" t="s">
+      <c r="N223" s="7" t="s">
         <v>1102</v>
-      </c>
-      <c r="M223" s="5" t="s">
-        <v>1103</v>
-      </c>
-      <c r="N223" s="7" t="s">
-        <v>1104</v>
       </c>
       <c r="R223" s="5" t="s">
         <v>29</v>
@@ -15290,10 +15291,10 @@
     </row>
     <row r="224" spans="1:23" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="26" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B224" s="26" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C224" s="10"/>
       <c r="D224" s="10">
@@ -15309,13 +15310,13 @@
       <c r="H224" s="10"/>
       <c r="I224" s="10"/>
       <c r="J224" s="10" t="s">
+        <v>1104</v>
+      </c>
+      <c r="K224" s="10" t="s">
+        <v>1105</v>
+      </c>
+      <c r="L224" s="11" t="s">
         <v>1106</v>
-      </c>
-      <c r="K224" s="10" t="s">
-        <v>1107</v>
-      </c>
-      <c r="L224" s="11" t="s">
-        <v>1108</v>
       </c>
       <c r="M224" s="10"/>
       <c r="N224" s="10"/>
@@ -15341,10 +15342,10 @@
     </row>
     <row r="225" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="25" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B225" s="25" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D225" s="5" t="s">
         <v>91</v>
@@ -15359,13 +15360,13 @@
         <v>186</v>
       </c>
       <c r="L225" s="7" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="R225" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S225" s="5" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="T225" s="6">
         <v>258</v>
@@ -15379,10 +15380,10 @@
     </row>
     <row r="226" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="25" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B226" s="25" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D226" s="5">
         <v>1486</v>
@@ -15391,16 +15392,16 @@
         <v>25</v>
       </c>
       <c r="F226" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="J226" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="K226" s="5" t="s">
         <v>1112</v>
       </c>
-      <c r="J226" s="5" t="s">
+      <c r="L226" s="7" t="s">
         <v>1113</v>
-      </c>
-      <c r="K226" s="5" t="s">
-        <v>1114</v>
-      </c>
-      <c r="L226" s="7" t="s">
-        <v>1115</v>
       </c>
       <c r="R226" s="5" t="s">
         <v>37</v>
@@ -15420,10 +15421,10 @@
     </row>
     <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="25" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B227" s="25" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D227" s="5">
         <v>1481</v>
@@ -15438,13 +15439,13 @@
         <v>745</v>
       </c>
       <c r="J227" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="K227" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="L227" s="7" t="s">
         <v>1116</v>
-      </c>
-      <c r="K227" s="5" t="s">
-        <v>1117</v>
-      </c>
-      <c r="L227" s="7" t="s">
-        <v>1118</v>
       </c>
       <c r="R227" s="5" t="s">
         <v>29</v>
@@ -15464,10 +15465,10 @@
     </row>
     <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="25" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B228" s="25" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="D228" s="5">
         <v>1486</v>
@@ -15479,13 +15480,13 @@
         <v>40</v>
       </c>
       <c r="J228" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="K228" s="5" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L228" s="7" t="s">
         <v>1119</v>
-      </c>
-      <c r="K228" s="5" t="s">
-        <v>1120</v>
-      </c>
-      <c r="L228" s="7" t="s">
-        <v>1121</v>
       </c>
       <c r="R228" s="5" t="s">
         <v>37</v>
@@ -15505,25 +15506,25 @@
     </row>
     <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="25" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B229" s="25" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D229" s="5" t="s">
         <v>1122</v>
       </c>
-      <c r="B229" s="25" t="s">
+      <c r="E229" s="5" t="s">
         <v>1123</v>
       </c>
-      <c r="D229" s="5" t="s">
+      <c r="F229" s="5" t="s">
         <v>1124</v>
       </c>
-      <c r="E229" s="5" t="s">
+      <c r="J229" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="L229" s="7" t="s">
         <v>1125</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>1126</v>
-      </c>
-      <c r="J229" s="5" t="s">
-        <v>824</v>
-      </c>
-      <c r="L229" s="7" t="s">
-        <v>1127</v>
       </c>
       <c r="R229" s="5" t="s">
         <v>37</v>
@@ -15543,25 +15544,25 @@
     </row>
     <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="25" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B230" s="25" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E230" s="5" t="s">
         <v>1123</v>
       </c>
-      <c r="D230" s="5" t="s">
+      <c r="F230" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="J230" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="L230" s="7" t="s">
         <v>1128</v>
-      </c>
-      <c r="E230" s="5" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F230" s="5" t="s">
-        <v>1126</v>
-      </c>
-      <c r="J230" s="5" t="s">
-        <v>1129</v>
-      </c>
-      <c r="L230" s="7" t="s">
-        <v>1130</v>
       </c>
       <c r="R230" s="5" t="s">
         <v>37</v>
@@ -15581,31 +15582,31 @@
     </row>
     <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="25" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B231" s="25" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E231" s="5" t="s">
         <v>1123</v>
       </c>
-      <c r="D231" s="5" t="s">
+      <c r="F231" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J231" s="5" t="s">
         <v>1131</v>
       </c>
-      <c r="E231" s="5" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F231" s="5" t="s">
+      <c r="K231" s="5" t="s">
         <v>1132</v>
       </c>
-      <c r="J231" s="5" t="s">
+      <c r="L231" s="7" t="s">
         <v>1133</v>
       </c>
-      <c r="K231" s="5" t="s">
+      <c r="N231" s="7" t="s">
         <v>1134</v>
-      </c>
-      <c r="L231" s="7" t="s">
-        <v>1135</v>
-      </c>
-      <c r="N231" s="7" t="s">
-        <v>1136</v>
       </c>
       <c r="R231" s="5" t="s">
         <v>59</v>
@@ -15626,28 +15627,28 @@
     </row>
     <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="25" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B232" s="25" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="D232" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E232" s="5" t="s">
+        <v>982</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="J232" s="5" t="s">
         <v>1137</v>
       </c>
-      <c r="E232" s="5" t="s">
-        <v>984</v>
-      </c>
-      <c r="F232" s="5" t="s">
+      <c r="K232" s="5" t="s">
         <v>1138</v>
       </c>
-      <c r="J232" s="5" t="s">
+      <c r="L232" s="7" t="s">
         <v>1139</v>
-      </c>
-      <c r="K232" s="5" t="s">
-        <v>1140</v>
-      </c>
-      <c r="L232" s="7" t="s">
-        <v>1141</v>
       </c>
       <c r="R232" s="5" t="s">
         <v>37</v>
@@ -15656,10 +15657,10 @@
         <v>122</v>
       </c>
       <c r="T232" s="6" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="U232" s="6" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="V232" s="5"/>
       <c r="W232" s="35">
@@ -15671,7 +15672,7 @@
         <v>565</v>
       </c>
       <c r="B233" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>85</v>
@@ -15689,7 +15690,7 @@
         <v>494</v>
       </c>
       <c r="L233" s="7" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="R233" s="5" t="s">
         <v>37</v>
@@ -15701,7 +15702,7 @@
         <v>749</v>
       </c>
       <c r="U233" s="6" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="W233" s="6">
         <v>1</v>
@@ -15712,7 +15713,7 @@
         <v>565</v>
       </c>
       <c r="B234" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D234" s="5" t="s">
         <v>91</v>
@@ -15724,13 +15725,13 @@
         <v>33</v>
       </c>
       <c r="J234" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K234" s="5" t="s">
+        <v>1146</v>
+      </c>
+      <c r="L234" s="7" t="s">
         <v>1147</v>
-      </c>
-      <c r="K234" s="5" t="s">
-        <v>1148</v>
-      </c>
-      <c r="L234" s="7" t="s">
-        <v>1149</v>
       </c>
       <c r="R234" s="5" t="s">
         <v>37</v>
@@ -15742,7 +15743,7 @@
         <v>402</v>
       </c>
       <c r="U234" s="6" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="W234" s="6">
         <v>1</v>
@@ -15753,10 +15754,10 @@
         <v>565</v>
       </c>
       <c r="B235" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="E235" s="5" t="s">
         <v>32</v>
@@ -15765,16 +15766,16 @@
         <v>33</v>
       </c>
       <c r="J235" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K235" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L235" s="7" t="s">
         <v>1152</v>
       </c>
-      <c r="K235" s="5" t="s">
+      <c r="M235" s="5" t="s">
         <v>1153</v>
-      </c>
-      <c r="L235" s="7" t="s">
-        <v>1154</v>
-      </c>
-      <c r="M235" s="5" t="s">
-        <v>1155</v>
       </c>
       <c r="R235" s="5" t="s">
         <v>37</v>
@@ -15783,10 +15784,10 @@
         <v>391</v>
       </c>
       <c r="T235" s="6" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="U235" s="6" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="W235" s="6">
         <v>1</v>
@@ -15797,25 +15798,25 @@
         <v>565</v>
       </c>
       <c r="B236" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D236" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E236" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="J236" s="5" t="s">
         <v>1158</v>
       </c>
-      <c r="E236" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="F236" s="5" t="s">
+      <c r="K236" s="5" t="s">
         <v>1159</v>
       </c>
-      <c r="J236" s="5" t="s">
+      <c r="L236" s="7" t="s">
         <v>1160</v>
-      </c>
-      <c r="K236" s="5" t="s">
-        <v>1161</v>
-      </c>
-      <c r="L236" s="7" t="s">
-        <v>1162</v>
       </c>
       <c r="R236" s="5" t="s">
         <v>59</v>
@@ -15824,10 +15825,10 @@
         <v>122</v>
       </c>
       <c r="T236" s="6" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="U236" s="6" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="W236" s="6">
         <v>1</v>
@@ -15838,10 +15839,10 @@
         <v>565</v>
       </c>
       <c r="B237" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="E237" s="5" t="s">
         <v>86</v>
@@ -15850,13 +15851,13 @@
         <v>87</v>
       </c>
       <c r="J237" s="5" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="K237" s="5" t="s">
         <v>113</v>
       </c>
       <c r="L237" s="7" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="R237" s="5" t="s">
         <v>37</v>
@@ -15865,10 +15866,10 @@
         <v>122</v>
       </c>
       <c r="T237" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="U237" s="6" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="W237" s="6">
         <v>1</v>
@@ -15879,25 +15880,25 @@
         <v>565</v>
       </c>
       <c r="B238" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D238" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E238" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F238" s="5" t="s">
         <v>1167</v>
       </c>
-      <c r="E238" s="5" t="s">
+      <c r="J238" s="5" t="s">
         <v>1168</v>
       </c>
-      <c r="F238" s="5" t="s">
+      <c r="K238" s="5" t="s">
         <v>1169</v>
       </c>
-      <c r="J238" s="5" t="s">
+      <c r="L238" s="7" t="s">
         <v>1170</v>
-      </c>
-      <c r="K238" s="5" t="s">
-        <v>1171</v>
-      </c>
-      <c r="L238" s="7" t="s">
-        <v>1172</v>
       </c>
       <c r="R238" s="5" t="s">
         <v>29</v>
@@ -15906,10 +15907,10 @@
         <v>29</v>
       </c>
       <c r="T238" s="6" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="U238" s="6" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="W238" s="6">
         <v>1</v>
@@ -15920,7 +15921,7 @@
         <v>565</v>
       </c>
       <c r="B239" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D239" s="5">
         <v>1483</v>
@@ -15932,13 +15933,13 @@
         <v>118</v>
       </c>
       <c r="J239" s="5" t="s">
+        <v>1172</v>
+      </c>
+      <c r="K239" s="5" t="s">
+        <v>1173</v>
+      </c>
+      <c r="L239" s="7" t="s">
         <v>1174</v>
-      </c>
-      <c r="K239" s="5" t="s">
-        <v>1175</v>
-      </c>
-      <c r="L239" s="7" t="s">
-        <v>1176</v>
       </c>
       <c r="R239" s="5" t="s">
         <v>37</v>
@@ -15947,10 +15948,10 @@
         <v>104</v>
       </c>
       <c r="T239" s="6" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="U239" s="6" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="W239" s="6">
         <v>1</v>
@@ -15961,7 +15962,7 @@
         <v>565</v>
       </c>
       <c r="B240" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D240" s="5" t="s">
         <v>733</v>
@@ -15973,10 +15974,10 @@
         <v>376</v>
       </c>
       <c r="J240" s="5" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="L240" s="7" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="R240" s="5" t="s">
         <v>37</v>
@@ -15988,7 +15989,7 @@
         <v>316</v>
       </c>
       <c r="U240" s="6" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="W240" s="6">
         <v>1</v>
@@ -15999,25 +16000,25 @@
         <v>565</v>
       </c>
       <c r="B241" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="J241" s="5" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="K241" s="5" t="s">
         <v>494</v>
       </c>
       <c r="L241" s="7" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="R241" s="5" t="s">
         <v>37</v>
@@ -16026,7 +16027,7 @@
         <v>122</v>
       </c>
       <c r="T241" s="6" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="U241" s="6" t="s">
         <v>316</v>
@@ -16040,25 +16041,25 @@
         <v>565</v>
       </c>
       <c r="B242" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="E242" s="5" t="s">
         <v>80</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="J242" s="5" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="K242" s="5" t="s">
         <v>494</v>
       </c>
       <c r="L242" s="7" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="R242" s="5" t="s">
         <v>37</v>
@@ -16081,10 +16082,10 @@
         <v>565</v>
       </c>
       <c r="B243" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="E243" s="5" t="s">
         <v>32</v>
@@ -16093,16 +16094,16 @@
         <v>33</v>
       </c>
       <c r="J243" s="5" t="s">
+        <v>1186</v>
+      </c>
+      <c r="K243" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="L243" s="7" t="s">
         <v>1188</v>
       </c>
-      <c r="K243" s="5" t="s">
-        <v>1189</v>
-      </c>
-      <c r="L243" s="7" t="s">
-        <v>1190</v>
-      </c>
       <c r="M243" s="5" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="R243" s="5" t="s">
         <v>37</v>
@@ -16111,10 +16112,10 @@
         <v>104</v>
       </c>
       <c r="T243" s="6" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="U243" s="6" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="W243" s="6">
         <v>1</v>
@@ -16125,25 +16126,25 @@
         <v>565</v>
       </c>
       <c r="B244" s="25" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="D244" s="5">
         <v>1488</v>
       </c>
       <c r="E244" s="5" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="J244" s="5" t="s">
         <v>1191</v>
       </c>
-      <c r="F244" s="5" t="s">
+      <c r="K244" s="5" t="s">
         <v>1192</v>
       </c>
-      <c r="J244" s="5" t="s">
+      <c r="L244" s="7" t="s">
         <v>1193</v>
-      </c>
-      <c r="K244" s="5" t="s">
-        <v>1194</v>
-      </c>
-      <c r="L244" s="7" t="s">
-        <v>1195</v>
       </c>
       <c r="R244" s="5" t="s">
         <v>37</v>
@@ -16163,10 +16164,10 @@
     </row>
     <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="25" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B245" s="25" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D245" s="5">
         <v>1459</v>
@@ -16178,13 +16179,13 @@
         <v>68</v>
       </c>
       <c r="J245" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="K245" s="5" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L245" s="7" t="s">
         <v>1198</v>
-      </c>
-      <c r="K245" s="5" t="s">
-        <v>1199</v>
-      </c>
-      <c r="L245" s="7" t="s">
-        <v>1200</v>
       </c>
       <c r="R245" s="5" t="s">
         <v>59</v>
@@ -16204,28 +16205,28 @@
     </row>
     <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="25" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B246" s="25" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D246" s="5" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E246" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F246" s="5" t="s">
         <v>1201</v>
       </c>
-      <c r="E246" s="5" t="s">
+      <c r="J246" s="5" t="s">
         <v>1202</v>
       </c>
-      <c r="F246" s="5" t="s">
+      <c r="K246" s="5" t="s">
         <v>1203</v>
       </c>
-      <c r="J246" s="5" t="s">
+      <c r="L246" s="7" t="s">
         <v>1204</v>
-      </c>
-      <c r="K246" s="5" t="s">
-        <v>1205</v>
-      </c>
-      <c r="L246" s="7" t="s">
-        <v>1206</v>
       </c>
       <c r="R246" s="5" t="s">
         <v>37</v>
@@ -16245,25 +16246,25 @@
     </row>
     <row r="247" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="25" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B247" s="25" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D247" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>56</v>
       </c>
       <c r="J247" s="5" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="L247" s="7" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="R247" s="5" t="s">
         <v>672</v>
@@ -16283,10 +16284,10 @@
     </row>
     <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="25" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B248" s="25" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D248" s="5">
         <v>1473</v>
@@ -16298,10 +16299,10 @@
         <v>281</v>
       </c>
       <c r="J248" s="5" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="L248" s="3" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="R248" s="5" t="s">
         <v>37</v>
@@ -16321,28 +16322,28 @@
     </row>
     <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="25" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B249" s="25" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D249" s="5" t="s">
         <v>85</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="J249" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K249" s="5" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L249" s="7" t="s">
         <v>1214</v>
-      </c>
-      <c r="K249" s="5" t="s">
-        <v>1215</v>
-      </c>
-      <c r="L249" s="7" t="s">
-        <v>1216</v>
       </c>
       <c r="R249" s="5" t="s">
         <v>37</v>
@@ -16362,28 +16363,28 @@
     </row>
     <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="25" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B250" s="25" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="E250" s="5" t="s">
         <v>505</v>
       </c>
       <c r="F250" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J250" s="5" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K250" s="5" t="s">
         <v>1218</v>
       </c>
-      <c r="J250" s="5" t="s">
+      <c r="L250" s="7" t="s">
         <v>1219</v>
-      </c>
-      <c r="K250" s="5" t="s">
-        <v>1220</v>
-      </c>
-      <c r="L250" s="7" t="s">
-        <v>1221</v>
       </c>
       <c r="R250" s="5" t="s">
         <v>672</v>
@@ -16403,34 +16404,34 @@
     </row>
     <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="25" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B251" s="25" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="E251" s="5" t="s">
         <v>505</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="J251" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="K251" s="5" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L251" s="7" t="s">
         <v>1223</v>
       </c>
-      <c r="K251" s="5" t="s">
+      <c r="R251" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S251" s="5" t="s">
         <v>1224</v>
-      </c>
-      <c r="L251" s="7" t="s">
-        <v>1225</v>
-      </c>
-      <c r="R251" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S251" s="5" t="s">
-        <v>1226</v>
       </c>
       <c r="T251" s="6">
         <v>87</v>
@@ -16444,28 +16445,28 @@
     </row>
     <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="25" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B252" s="25" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D252" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E252" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F252" s="5" t="s">
         <v>1227</v>
       </c>
-      <c r="E252" s="5" t="s">
+      <c r="J252" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="K252" s="5" t="s">
         <v>1228</v>
       </c>
-      <c r="F252" s="5" t="s">
+      <c r="L252" s="7" t="s">
         <v>1229</v>
-      </c>
-      <c r="J252" s="5" t="s">
-        <v>824</v>
-      </c>
-      <c r="K252" s="5" t="s">
-        <v>1230</v>
-      </c>
-      <c r="L252" s="7" t="s">
-        <v>1231</v>
       </c>
       <c r="R252" s="5" t="s">
         <v>247</v>
@@ -16485,28 +16486,28 @@
     </row>
     <row r="253" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="25" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B253" s="25" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="E253" s="5" t="s">
         <v>505</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="J253" s="5" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="K253" s="5" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="L253" s="3" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="R253" s="5" t="s">
         <v>59</v>
@@ -16526,25 +16527,25 @@
     </row>
     <row r="254" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="25" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B254" s="25" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D254" s="5">
         <v>1485</v>
       </c>
       <c r="E254" s="5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J254" s="5" t="s">
         <v>1235</v>
       </c>
-      <c r="F254" s="5" t="s">
+      <c r="L254" s="7" t="s">
         <v>1236</v>
-      </c>
-      <c r="J254" s="5" t="s">
-        <v>1237</v>
-      </c>
-      <c r="L254" s="7" t="s">
-        <v>1238</v>
       </c>
       <c r="R254" s="5" t="s">
         <v>37</v>
@@ -16564,13 +16565,13 @@
     </row>
     <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="25" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B255" s="25" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="E255" s="5" t="s">
         <v>505</v>
@@ -16579,10 +16580,10 @@
         <v>506</v>
       </c>
       <c r="J255" s="5" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="L255" s="7" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="R255" s="5" t="s">
         <v>247</v>
@@ -16602,25 +16603,25 @@
     </row>
     <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="25" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B256" s="25" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D256" s="5">
         <v>1467</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="J256" s="5" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="L256" s="7" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="R256" s="5" t="s">
         <v>37</v>
@@ -16640,31 +16641,31 @@
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="25" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B257" s="25" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D257" s="5" t="s">
         <v>1244</v>
-      </c>
-      <c r="B257" s="25" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D257" s="5" t="s">
-        <v>1246</v>
       </c>
       <c r="E257" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F257" s="5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="J257" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K257" s="5" t="s">
         <v>1247</v>
       </c>
-      <c r="J257" s="5" t="s">
+      <c r="L257" s="7" t="s">
         <v>1248</v>
       </c>
-      <c r="K257" s="5" t="s">
+      <c r="N257" s="7" t="s">
         <v>1249</v>
-      </c>
-      <c r="L257" s="7" t="s">
-        <v>1250</v>
-      </c>
-      <c r="N257" s="7" t="s">
-        <v>1251</v>
       </c>
       <c r="R257" s="5" t="s">
         <v>689</v>
@@ -16684,13 +16685,13 @@
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="25" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B258" s="25" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="E258" s="5" t="s">
         <v>25</v>
@@ -16699,16 +16700,16 @@
         <v>40</v>
       </c>
       <c r="J258" s="5" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="K258" s="5" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="L258" s="7" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="N258" s="7" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="R258" s="5" t="s">
         <v>37</v>
@@ -16728,31 +16729,31 @@
     </row>
     <row r="259" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="25" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B259" s="25" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E259" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="J259" s="5" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="K259" s="5" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="L259" s="7" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="N259" s="7" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="R259" s="5" t="s">
         <v>37</v>
@@ -16772,13 +16773,13 @@
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="25" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B260" s="25" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="E260" s="5" t="s">
         <v>86</v>
@@ -16787,19 +16788,19 @@
         <v>87</v>
       </c>
       <c r="J260" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="K260" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="L260" s="7" t="s">
+        <v>1258</v>
+      </c>
+      <c r="M260" s="5" t="s">
         <v>1259</v>
       </c>
-      <c r="K260" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="L260" s="7" t="s">
+      <c r="N260" s="7" t="s">
         <v>1260</v>
-      </c>
-      <c r="M260" s="5" t="s">
-        <v>1261</v>
-      </c>
-      <c r="N260" s="7" t="s">
-        <v>1262</v>
       </c>
       <c r="R260" s="5" t="s">
         <v>37</v>
@@ -16819,13 +16820,13 @@
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="25" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B261" s="25" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="E261" s="5" t="s">
         <v>86</v>
@@ -16834,19 +16835,19 @@
         <v>87</v>
       </c>
       <c r="J261" s="5" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="K261" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="L261" s="7" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="M261" s="5" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="N261" s="7" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="R261" s="5" t="s">
         <v>37</v>
@@ -16866,13 +16867,13 @@
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="25" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B262" s="25" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="E262" s="5" t="s">
         <v>86</v>
@@ -16881,19 +16882,19 @@
         <v>87</v>
       </c>
       <c r="J262" s="5" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="K262" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="L262" s="7" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="M262" s="5" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="N262" s="7" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="R262" s="5" t="s">
         <v>37</v>
@@ -16913,10 +16914,10 @@
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="25" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B263" s="25" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D263" s="5">
         <v>1420</v>
@@ -16928,16 +16929,16 @@
         <v>40</v>
       </c>
       <c r="J263" s="5" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="K263" s="5" t="s">
         <v>187</v>
       </c>
       <c r="L263" s="7" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="N263" s="7" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="R263" s="5" t="s">
         <v>37</v>
@@ -16957,31 +16958,31 @@
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="25" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B264" s="25" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="E264" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="J264" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="K264" s="5" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L264" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="K264" s="5" t="s">
-        <v>1271</v>
-      </c>
-      <c r="L264" s="7" t="s">
-        <v>1272</v>
-      </c>
       <c r="N264" s="7" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="R264" s="5" t="s">
         <v>37</v>
@@ -17001,25 +17002,25 @@
     </row>
     <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="25" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B265" s="25" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D265" s="5" t="s">
         <v>1273</v>
       </c>
-      <c r="B265" s="25" t="s">
+      <c r="E265" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="J265" s="5" t="s">
         <v>1274</v>
       </c>
-      <c r="D265" s="5" t="s">
+      <c r="L265" s="7" t="s">
         <v>1275</v>
-      </c>
-      <c r="E265" s="5" t="s">
-        <v>889</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>890</v>
-      </c>
-      <c r="J265" s="5" t="s">
-        <v>1276</v>
-      </c>
-      <c r="L265" s="7" t="s">
-        <v>1277</v>
       </c>
       <c r="R265" s="5" t="s">
         <v>59</v>
@@ -17039,31 +17040,31 @@
     </row>
     <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="25" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B266" s="25" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D266" s="5" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E266" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F266" s="5" t="s">
         <v>1278</v>
       </c>
-      <c r="E266" s="5" t="s">
+      <c r="J266" s="5" t="s">
         <v>1279</v>
       </c>
-      <c r="F266" s="5" t="s">
+      <c r="L266" s="7" t="s">
         <v>1280</v>
-      </c>
-      <c r="J266" s="5" t="s">
-        <v>1281</v>
-      </c>
-      <c r="L266" s="7" t="s">
-        <v>1282</v>
       </c>
       <c r="R266" s="5" t="s">
         <v>59</v>
       </c>
       <c r="S266" s="5" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="T266" s="6">
         <v>1088</v>
@@ -17077,34 +17078,34 @@
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="25" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B267" s="25" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D267" s="5">
         <v>1480</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F267" s="5" t="s">
+        <v>1282</v>
+      </c>
+      <c r="J267" s="5" t="s">
+        <v>1283</v>
+      </c>
+      <c r="K267" s="5" t="s">
         <v>1284</v>
       </c>
-      <c r="J267" s="5" t="s">
+      <c r="L267" s="7" t="s">
         <v>1285</v>
       </c>
-      <c r="K267" s="5" t="s">
+      <c r="R267" s="5" t="s">
         <v>1286</v>
       </c>
-      <c r="L267" s="7" t="s">
+      <c r="S267" s="5" t="s">
         <v>1287</v>
-      </c>
-      <c r="R267" s="5" t="s">
-        <v>1288</v>
-      </c>
-      <c r="S267" s="5" t="s">
-        <v>1289</v>
       </c>
       <c r="T267" s="6">
         <v>103</v>
@@ -17118,34 +17119,34 @@
     </row>
     <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="25" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B268" s="25" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D268" s="5">
         <v>1470</v>
       </c>
       <c r="E268" s="5" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="J268" s="5" t="s">
         <v>162</v>
       </c>
       <c r="K268" s="5" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="L268" s="7" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="R268" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S268" s="5" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="T268" s="6">
         <v>102</v>
@@ -17159,13 +17160,13 @@
     </row>
     <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="25" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B269" s="25" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C269" s="5" t="s">
         <v>1292</v>
-      </c>
-      <c r="B269" s="25" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C269" s="5" t="s">
-        <v>1294</v>
       </c>
       <c r="D269" s="5">
         <v>1495</v>
@@ -17177,13 +17178,13 @@
         <v>637</v>
       </c>
       <c r="J269" s="5" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="K269" s="5" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="L269" s="7" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="R269" s="5" t="s">
         <v>37</v>
@@ -17203,13 +17204,13 @@
     </row>
     <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="25" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B270" s="25" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C270" s="5" t="s">
         <v>1292</v>
-      </c>
-      <c r="B270" s="25" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C270" s="5" t="s">
-        <v>1294</v>
       </c>
       <c r="D270" s="5">
         <v>1497</v>
@@ -17218,22 +17219,22 @@
         <v>438</v>
       </c>
       <c r="F270" s="5" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J270" s="5" t="s">
+        <v>1296</v>
+      </c>
+      <c r="K270" s="5" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L270" s="7" t="s">
         <v>1297</v>
       </c>
-      <c r="J270" s="5" t="s">
+      <c r="M270" s="5" t="s">
         <v>1298</v>
       </c>
-      <c r="K270" s="5" t="s">
-        <v>1298</v>
-      </c>
-      <c r="L270" s="7" t="s">
+      <c r="N270" s="7" t="s">
         <v>1299</v>
-      </c>
-      <c r="M270" s="5" t="s">
-        <v>1300</v>
-      </c>
-      <c r="N270" s="7" t="s">
-        <v>1301</v>
       </c>
       <c r="R270" s="5" t="s">
         <v>29</v>
@@ -17253,13 +17254,13 @@
     </row>
     <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="25" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B271" s="25" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C271" s="5" t="s">
         <v>1292</v>
-      </c>
-      <c r="B271" s="25" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>1294</v>
       </c>
       <c r="D271" s="5">
         <v>1481</v>
@@ -17271,13 +17272,13 @@
         <v>376</v>
       </c>
       <c r="J271" s="5" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="K271" s="5" t="s">
         <v>420</v>
       </c>
       <c r="L271" s="7" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="R271" s="5" t="s">
         <v>37</v>
@@ -17297,13 +17298,13 @@
     </row>
     <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="25" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B272" s="25" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C272" s="5" t="s">
         <v>1292</v>
-      </c>
-      <c r="B272" s="25" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C272" s="5" t="s">
-        <v>1294</v>
       </c>
       <c r="D272" s="5">
         <v>1495</v>
@@ -17315,13 +17316,13 @@
         <v>33</v>
       </c>
       <c r="J272" s="5" t="s">
+        <v>1302</v>
+      </c>
+      <c r="K272" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="L272" s="7" t="s">
         <v>1304</v>
-      </c>
-      <c r="K272" s="5" t="s">
-        <v>1305</v>
-      </c>
-      <c r="L272" s="7" t="s">
-        <v>1306</v>
       </c>
       <c r="R272" s="5" t="s">
         <v>37</v>
@@ -17341,13 +17342,13 @@
     </row>
     <row r="273" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="25" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B273" s="25" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C273" s="5" t="s">
         <v>1292</v>
-      </c>
-      <c r="B273" s="25" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C273" s="5" t="s">
-        <v>1294</v>
       </c>
       <c r="D273" s="5">
         <v>1493</v>
@@ -17365,7 +17366,7 @@
         <v>494</v>
       </c>
       <c r="L273" s="7" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="R273" s="5" t="s">
         <v>37</v>
@@ -17385,13 +17386,13 @@
     </row>
     <row r="274" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="25" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B274" s="25" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C274" s="5" t="s">
         <v>1292</v>
-      </c>
-      <c r="B274" s="25" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C274" s="5" t="s">
-        <v>1294</v>
       </c>
       <c r="D274" s="5" t="s">
         <v>733</v>
@@ -17400,19 +17401,19 @@
         <v>25</v>
       </c>
       <c r="F274" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H274" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="J274" s="5" t="s">
         <v>1308</v>
       </c>
-      <c r="H274" s="5" t="s">
+      <c r="K274" s="5" t="s">
         <v>1309</v>
       </c>
-      <c r="J274" s="5" t="s">
+      <c r="L274" s="7" t="s">
         <v>1310</v>
-      </c>
-      <c r="K274" s="5" t="s">
-        <v>1311</v>
-      </c>
-      <c r="L274" s="7" t="s">
-        <v>1312</v>
       </c>
       <c r="R274" s="5" t="s">
         <v>29</v>
@@ -17432,31 +17433,31 @@
     </row>
     <row r="275" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C275" s="5" t="s">
         <v>1292</v>
-      </c>
-      <c r="B275" s="5" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>1294</v>
       </c>
       <c r="D275" s="5">
         <v>1496</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="F275" s="5" t="s">
         <v>56</v>
       </c>
       <c r="J275" s="5" t="s">
+        <v>1312</v>
+      </c>
+      <c r="K275" s="5" t="s">
+        <v>1313</v>
+      </c>
+      <c r="L275" s="7" t="s">
         <v>1314</v>
-      </c>
-      <c r="K275" s="5" t="s">
-        <v>1315</v>
-      </c>
-      <c r="L275" s="7" t="s">
-        <v>1316</v>
       </c>
       <c r="R275" s="5" t="s">
         <v>59</v>
@@ -17477,34 +17478,34 @@
     </row>
     <row r="276" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C276" s="5" t="s">
         <v>1292</v>
-      </c>
-      <c r="B276" s="5" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C276" s="5" t="s">
-        <v>1294</v>
       </c>
       <c r="D276" s="5">
         <v>1497</v>
       </c>
       <c r="E276" s="5" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H276" s="5" t="s">
         <v>1317</v>
       </c>
-      <c r="F276" s="5" t="s">
+      <c r="J276" s="5" t="s">
         <v>1318</v>
       </c>
-      <c r="H276" s="5" t="s">
+      <c r="K276" s="5" t="s">
         <v>1319</v>
       </c>
-      <c r="J276" s="5" t="s">
+      <c r="L276" s="7" t="s">
         <v>1320</v>
-      </c>
-      <c r="K276" s="5" t="s">
-        <v>1321</v>
-      </c>
-      <c r="L276" s="7" t="s">
-        <v>1322</v>
       </c>
       <c r="R276" s="5" t="s">
         <v>37</v>
@@ -17525,10 +17526,10 @@
     </row>
     <row r="277" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="25" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B277" s="25" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="D277" s="5">
         <v>1475</v>
@@ -17540,13 +17541,13 @@
         <v>87</v>
       </c>
       <c r="J277" s="5" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="K277" s="5" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="L277" s="7" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="R277" s="5" t="s">
         <v>37</v>
@@ -17566,10 +17567,10 @@
     </row>
     <row r="278" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="25" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B278" s="25" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="D278" s="5">
         <v>1475</v>
@@ -17581,16 +17582,16 @@
         <v>40</v>
       </c>
       <c r="J278" s="5" t="s">
+        <v>1323</v>
+      </c>
+      <c r="K278" s="5" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L278" s="7" t="s">
         <v>1325</v>
       </c>
-      <c r="K278" s="5" t="s">
+      <c r="M278" s="5" t="s">
         <v>1326</v>
-      </c>
-      <c r="L278" s="7" t="s">
-        <v>1327</v>
-      </c>
-      <c r="M278" s="5" t="s">
-        <v>1328</v>
       </c>
       <c r="R278" s="5" t="s">
         <v>37</v>
@@ -17610,31 +17611,31 @@
     </row>
     <row r="279" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="25" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B279" s="25" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D279" s="5" t="s">
         <v>1329</v>
       </c>
-      <c r="B279" s="25" t="s">
+      <c r="E279" s="5" t="s">
         <v>1330</v>
       </c>
-      <c r="D279" s="5" t="s">
+      <c r="F279" s="5" t="s">
         <v>1331</v>
       </c>
-      <c r="E279" s="5" t="s">
+      <c r="J279" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="K279" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="L279" s="5" t="s">
         <v>1332</v>
       </c>
-      <c r="F279" s="5" t="s">
-        <v>1333</v>
-      </c>
-      <c r="J279" s="5" t="s">
-        <v>1070</v>
-      </c>
-      <c r="K279" s="5" t="s">
-        <v>1070</v>
-      </c>
-      <c r="L279" s="5" t="s">
-        <v>1334</v>
-      </c>
       <c r="M279" s="7" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="R279" s="5" t="s">
         <v>37</v>
@@ -17655,10 +17656,10 @@
     </row>
     <row r="280" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="25" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B280" s="25" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="D280" s="5" t="s">
         <v>261</v>
@@ -17670,16 +17671,16 @@
         <v>33</v>
       </c>
       <c r="J280" s="5" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="K280" s="5" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="L280" s="5" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="M280" s="7" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="R280" s="5" t="s">
         <v>37</v>
@@ -17700,10 +17701,10 @@
     </row>
     <row r="281" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="25" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B281" s="25" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="D281" s="5" t="s">
         <v>361</v>
@@ -17715,13 +17716,13 @@
         <v>729</v>
       </c>
       <c r="J281" s="5" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="K281" s="5" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="L281" s="5" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="M281" s="7"/>
       <c r="R281" s="5" t="s">
@@ -17743,32 +17744,32 @@
     </row>
     <row r="282" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="25" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B282" s="25" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="D282" s="5" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E282" s="5" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F282" s="5" t="s">
         <v>1339</v>
       </c>
-      <c r="E282" s="5" t="s">
+      <c r="J282" s="5" t="s">
+        <v>1634</v>
+      </c>
+      <c r="K282" s="5" t="s">
         <v>1340</v>
       </c>
-      <c r="F282" s="5" t="s">
+      <c r="L282" s="5" t="s">
         <v>1341</v>
-      </c>
-      <c r="J282" s="5" t="s">
-        <v>1636</v>
-      </c>
-      <c r="K282" s="5" t="s">
-        <v>1342</v>
-      </c>
-      <c r="L282" s="5" t="s">
-        <v>1343</v>
       </c>
       <c r="M282" s="7"/>
       <c r="R282" s="5" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="S282" s="5" t="s">
         <v>122</v>
@@ -17786,34 +17787,34 @@
     </row>
     <row r="283" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="25" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B283" s="25" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D283" s="5" t="s">
         <v>1345</v>
       </c>
-      <c r="B283" s="25" t="s">
+      <c r="E283" s="5" t="s">
         <v>1346</v>
       </c>
-      <c r="D283" s="5" t="s">
+      <c r="F283" s="5" t="s">
+        <v>938</v>
+      </c>
+      <c r="J283" s="5" t="s">
         <v>1347</v>
       </c>
-      <c r="E283" s="5" t="s">
+      <c r="K283" s="5" t="s">
         <v>1348</v>
       </c>
-      <c r="F283" s="5" t="s">
-        <v>940</v>
-      </c>
-      <c r="J283" s="5" t="s">
+      <c r="L283" s="7" t="s">
         <v>1349</v>
-      </c>
-      <c r="K283" s="5" t="s">
-        <v>1350</v>
-      </c>
-      <c r="L283" s="7" t="s">
-        <v>1351</v>
       </c>
       <c r="R283" s="5" t="s">
         <v>59</v>
       </c>
       <c r="S283" s="5" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="T283" s="6" t="s">
         <v>668</v>
@@ -17827,46 +17828,46 @@
     </row>
     <row r="284" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="25" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B284" s="25" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E284" s="5" t="s">
         <v>1346</v>
       </c>
-      <c r="D284" s="5" t="s">
-        <v>1353</v>
-      </c>
-      <c r="E284" s="5" t="s">
-        <v>1348</v>
-      </c>
       <c r="F284" s="5" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="J284" s="5" t="s">
         <v>287</v>
       </c>
       <c r="K284" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="L284" s="7" t="s">
+        <v>1354</v>
+      </c>
+      <c r="M284" s="5" t="s">
         <v>1355</v>
-      </c>
-      <c r="L284" s="7" t="s">
-        <v>1356</v>
-      </c>
-      <c r="M284" s="5" t="s">
-        <v>1357</v>
       </c>
       <c r="N284" s="7" t="s">
         <v>520</v>
       </c>
       <c r="R284" s="5" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="S284" s="5" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="T284" s="6" t="s">
         <v>277</v>
       </c>
       <c r="U284" s="6" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="W284" s="6">
         <v>3</v>
@@ -17874,46 +17875,46 @@
     </row>
     <row r="285" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="25" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B285" s="25" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E285" s="5" t="s">
         <v>1346</v>
       </c>
-      <c r="D285" s="5" t="s">
-        <v>1353</v>
-      </c>
-      <c r="E285" s="5" t="s">
-        <v>1348</v>
-      </c>
       <c r="F285" s="5" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="J285" s="5" t="s">
+        <v>1357</v>
+      </c>
+      <c r="K285" s="5" t="s">
+        <v>1358</v>
+      </c>
+      <c r="L285" s="7" t="s">
         <v>1359</v>
       </c>
-      <c r="K285" s="5" t="s">
-        <v>1360</v>
-      </c>
-      <c r="L285" s="7" t="s">
-        <v>1361</v>
-      </c>
       <c r="M285" s="5" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="N285" s="7" t="s">
         <v>520</v>
       </c>
       <c r="R285" s="5" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="S285" s="5" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="T285" s="6" t="s">
         <v>277</v>
       </c>
       <c r="U285" s="6" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="W285" s="6">
         <v>3</v>
@@ -17921,46 +17922,46 @@
     </row>
     <row r="286" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="25" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="B286" s="25" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E286" s="5" t="s">
         <v>1346</v>
       </c>
-      <c r="D286" s="5" t="s">
-        <v>1353</v>
-      </c>
-      <c r="E286" s="5" t="s">
-        <v>1348</v>
-      </c>
       <c r="F286" s="5" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="J286" s="5" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="K286" s="5" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="L286" s="7" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="M286" s="5" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="N286" s="7" t="s">
         <v>520</v>
       </c>
       <c r="R286" s="5" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="S286" s="5" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="T286" s="6" t="s">
         <v>277</v>
       </c>
       <c r="U286" s="6" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="W286" s="6">
         <v>3</v>
@@ -17968,13 +17969,13 @@
     </row>
     <row r="287" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="25" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B287" s="25" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D287" s="5" t="s">
         <v>1364</v>
-      </c>
-      <c r="B287" s="25" t="s">
-        <v>1365</v>
-      </c>
-      <c r="D287" s="5" t="s">
-        <v>1366</v>
       </c>
       <c r="E287" s="5" t="s">
         <v>117</v>
@@ -17983,13 +17984,13 @@
         <v>118</v>
       </c>
       <c r="J287" s="5" t="s">
+        <v>1365</v>
+      </c>
+      <c r="K287" s="5" t="s">
+        <v>1366</v>
+      </c>
+      <c r="L287" s="7" t="s">
         <v>1367</v>
-      </c>
-      <c r="K287" s="5" t="s">
-        <v>1368</v>
-      </c>
-      <c r="L287" s="7" t="s">
-        <v>1369</v>
       </c>
       <c r="R287" s="5" t="s">
         <v>37</v>
@@ -18009,31 +18010,31 @@
     </row>
     <row r="288" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="25" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B288" s="25" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E288" s="5" t="s">
         <v>438</v>
       </c>
       <c r="F288" s="5" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="J288" s="5" t="s">
         <v>1371</v>
       </c>
-      <c r="H288" s="5" t="s">
+      <c r="K288" s="5" t="s">
         <v>1372</v>
       </c>
-      <c r="J288" s="5" t="s">
+      <c r="L288" s="7" t="s">
         <v>1373</v>
-      </c>
-      <c r="K288" s="5" t="s">
-        <v>1374</v>
-      </c>
-      <c r="L288" s="7" t="s">
-        <v>1375</v>
       </c>
       <c r="R288" s="5" t="s">
         <v>37</v>
@@ -18053,28 +18054,28 @@
     </row>
     <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="25" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B289" s="25" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D289" s="5" t="s">
         <v>323</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="J289" s="5" t="s">
         <v>42</v>
       </c>
       <c r="K289" s="5" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="L289" s="7" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="R289" s="5" t="s">
         <v>37</v>
@@ -18094,10 +18095,10 @@
     </row>
     <row r="290" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="25" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B290" s="25" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D290" s="5">
         <v>1490</v>
@@ -18109,13 +18110,13 @@
         <v>40</v>
       </c>
       <c r="J290" s="5" t="s">
+        <v>1378</v>
+      </c>
+      <c r="K290" s="5" t="s">
+        <v>1379</v>
+      </c>
+      <c r="L290" s="7" t="s">
         <v>1380</v>
-      </c>
-      <c r="K290" s="5" t="s">
-        <v>1381</v>
-      </c>
-      <c r="L290" s="7" t="s">
-        <v>1382</v>
       </c>
       <c r="R290" s="5" t="s">
         <v>37</v>
@@ -18135,10 +18136,10 @@
     </row>
     <row r="291" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D291" s="6">
         <v>1494</v>
@@ -18150,13 +18151,13 @@
         <v>658</v>
       </c>
       <c r="J291" s="5" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="K291" s="5" t="s">
         <v>420</v>
       </c>
       <c r="L291" s="47" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="R291" s="5" t="s">
         <v>37</v>
@@ -18176,10 +18177,10 @@
     </row>
     <row r="292" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="25" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B292" s="25" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D292" s="5">
         <v>1469</v>
@@ -18188,19 +18189,19 @@
         <v>589</v>
       </c>
       <c r="F292" s="5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J292" s="5" t="s">
+        <v>1384</v>
+      </c>
+      <c r="K292" s="5" t="s">
         <v>1385</v>
       </c>
-      <c r="J292" s="5" t="s">
+      <c r="L292" s="7" t="s">
         <v>1386</v>
       </c>
-      <c r="K292" s="5" t="s">
+      <c r="M292" s="5" t="s">
         <v>1387</v>
-      </c>
-      <c r="L292" s="7" t="s">
-        <v>1388</v>
-      </c>
-      <c r="M292" s="5" t="s">
-        <v>1389</v>
       </c>
       <c r="R292" s="5" t="s">
         <v>37</v>
@@ -18220,13 +18221,13 @@
     </row>
     <row r="293" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="25" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B293" s="25" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E293" s="5" t="s">
         <v>86</v>
@@ -18235,22 +18236,22 @@
         <v>87</v>
       </c>
       <c r="J293" s="5" t="s">
+        <v>1389</v>
+      </c>
+      <c r="K293" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="L293" s="7" t="s">
         <v>1391</v>
       </c>
-      <c r="K293" s="5" t="s">
+      <c r="M293" s="5" t="s">
         <v>1392</v>
       </c>
-      <c r="L293" s="7" t="s">
+      <c r="R293" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S293" s="5" t="s">
         <v>1393</v>
-      </c>
-      <c r="M293" s="5" t="s">
-        <v>1394</v>
-      </c>
-      <c r="R293" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S293" s="5" t="s">
-        <v>1395</v>
       </c>
       <c r="T293" s="6">
         <v>239</v>
@@ -18264,10 +18265,10 @@
     </row>
     <row r="294" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="25" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B294" s="25" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D294" s="5">
         <v>1460</v>
@@ -18279,10 +18280,10 @@
         <v>87</v>
       </c>
       <c r="J294" s="5" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="L294" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="R294" s="5" t="s">
         <v>37</v>
@@ -18302,10 +18303,10 @@
     </row>
     <row r="295" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="25" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B295" s="25" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D295" s="5">
         <v>1470</v>
@@ -18317,11 +18318,11 @@
         <v>281</v>
       </c>
       <c r="J295" s="5" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="R295" s="5" t="s">
         <v>37</v>
@@ -18341,10 +18342,10 @@
     </row>
     <row r="296" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="25" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B296" s="25" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D296" s="5">
         <v>1443</v>
@@ -18356,19 +18357,19 @@
         <v>571</v>
       </c>
       <c r="J296" s="5" t="s">
+        <v>1401</v>
+      </c>
+      <c r="K296" s="5" t="s">
+        <v>1402</v>
+      </c>
+      <c r="L296" s="7" t="s">
         <v>1403</v>
-      </c>
-      <c r="K296" s="5" t="s">
-        <v>1404</v>
-      </c>
-      <c r="L296" s="7" t="s">
-        <v>1405</v>
       </c>
       <c r="R296" s="5" t="s">
         <v>29</v>
       </c>
       <c r="S296" s="5" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="T296" s="6">
         <v>820</v>
@@ -18382,13 +18383,13 @@
     </row>
     <row r="297" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="25" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B297" s="25" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="E297" s="5" t="s">
         <v>25</v>
@@ -18397,19 +18398,19 @@
         <v>40</v>
       </c>
       <c r="J297" s="5" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K297" s="5" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L297" s="7" t="s">
         <v>1408</v>
       </c>
-      <c r="K297" s="5" t="s">
-        <v>1409</v>
-      </c>
-      <c r="L297" s="7" t="s">
-        <v>1410</v>
-      </c>
       <c r="R297" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S297" s="5" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="T297" s="6">
         <v>188</v>
@@ -18423,13 +18424,13 @@
     </row>
     <row r="298" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="25" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B298" s="25" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="E298" s="5" t="s">
         <v>25</v>
@@ -18438,10 +18439,10 @@
         <v>571</v>
       </c>
       <c r="J298" s="5" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="L298" s="7" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="R298" s="5" t="s">
         <v>29</v>
@@ -18461,13 +18462,13 @@
     </row>
     <row r="299" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="25" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B299" s="25" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E299" s="5" t="s">
         <v>86</v>
@@ -18476,19 +18477,19 @@
         <v>87</v>
       </c>
       <c r="J299" s="5" t="s">
+        <v>1412</v>
+      </c>
+      <c r="K299" s="5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="L299" s="7" t="s">
         <v>1414</v>
       </c>
-      <c r="K299" s="5" t="s">
+      <c r="R299" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S299" s="5" t="s">
         <v>1415</v>
-      </c>
-      <c r="L299" s="7" t="s">
-        <v>1416</v>
-      </c>
-      <c r="R299" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S299" s="5" t="s">
-        <v>1417</v>
       </c>
       <c r="T299" s="6">
         <v>182</v>
@@ -18502,13 +18503,13 @@
     </row>
     <row r="300" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="25" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B300" s="25" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="E300" s="5" t="s">
         <v>32</v>
@@ -18517,19 +18518,19 @@
         <v>33</v>
       </c>
       <c r="J300" s="5" t="s">
+        <v>1417</v>
+      </c>
+      <c r="K300" s="5" t="s">
+        <v>1418</v>
+      </c>
+      <c r="L300" s="7" t="s">
         <v>1419</v>
       </c>
-      <c r="K300" s="5" t="s">
+      <c r="R300" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S300" s="5" t="s">
         <v>1420</v>
-      </c>
-      <c r="L300" s="7" t="s">
-        <v>1421</v>
-      </c>
-      <c r="R300" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="S300" s="5" t="s">
-        <v>1422</v>
       </c>
       <c r="T300" s="6">
         <v>182</v>
@@ -18543,10 +18544,10 @@
     </row>
     <row r="301" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="25" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B301" s="25" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D301" s="5">
         <v>1447</v>
@@ -18558,10 +18559,10 @@
         <v>751</v>
       </c>
       <c r="J301" s="5" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="L301" s="7" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="R301" s="5" t="s">
         <v>29</v>
@@ -18581,25 +18582,25 @@
     </row>
     <row r="302" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="25" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B302" s="25" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D302" s="5" t="s">
         <v>116</v>
       </c>
       <c r="E302" s="5" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F302" s="5" t="s">
+        <v>1424</v>
+      </c>
+      <c r="J302" s="5" t="s">
         <v>1425</v>
       </c>
-      <c r="F302" s="5" t="s">
+      <c r="L302" s="7" t="s">
         <v>1426</v>
-      </c>
-      <c r="J302" s="5" t="s">
-        <v>1427</v>
-      </c>
-      <c r="L302" s="7" t="s">
-        <v>1428</v>
       </c>
       <c r="R302" s="5" t="s">
         <v>37</v>
@@ -18619,10 +18620,10 @@
     </row>
     <row r="303" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="25" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B303" s="25" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D303" s="5" t="s">
         <v>674</v>
@@ -18634,13 +18635,13 @@
         <v>87</v>
       </c>
       <c r="J303" s="5" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="K303" s="5" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="L303" s="7" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="R303" s="5" t="s">
         <v>37</v>
@@ -18660,10 +18661,10 @@
     </row>
     <row r="304" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="25" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B304" s="25" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D304" s="5" t="s">
         <v>674</v>
@@ -18675,16 +18676,16 @@
         <v>68</v>
       </c>
       <c r="J304" s="5" t="s">
+        <v>1430</v>
+      </c>
+      <c r="K304" s="5" t="s">
+        <v>1431</v>
+      </c>
+      <c r="L304" s="7" t="s">
         <v>1432</v>
       </c>
-      <c r="K304" s="5" t="s">
+      <c r="M304" s="5" t="s">
         <v>1433</v>
-      </c>
-      <c r="L304" s="7" t="s">
-        <v>1434</v>
-      </c>
-      <c r="M304" s="5" t="s">
-        <v>1435</v>
       </c>
       <c r="R304" s="5" t="s">
         <v>37</v>
@@ -18704,25 +18705,25 @@
     </row>
     <row r="305" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="25" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B305" s="25" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D305" s="5" t="s">
         <v>674</v>
       </c>
       <c r="E305" s="5" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F305" s="5" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="J305" s="5" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="L305" s="3" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="R305" s="5" t="s">
         <v>37</v>
@@ -18742,10 +18743,10 @@
     </row>
     <row r="306" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="25" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B306" s="25" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D306" s="5">
         <v>1475</v>
@@ -18757,13 +18758,13 @@
         <v>40</v>
       </c>
       <c r="J306" s="5" t="s">
+        <v>1434</v>
+      </c>
+      <c r="K306" s="5" t="s">
+        <v>1435</v>
+      </c>
+      <c r="L306" s="7" t="s">
         <v>1436</v>
-      </c>
-      <c r="K306" s="5" t="s">
-        <v>1437</v>
-      </c>
-      <c r="L306" s="7" t="s">
-        <v>1438</v>
       </c>
       <c r="R306" s="5" t="s">
         <v>247</v>
@@ -18783,28 +18784,28 @@
     </row>
     <row r="307" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="25" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B307" s="25" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D307" s="5">
         <v>1478</v>
       </c>
       <c r="E307" s="5" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F307" s="5" t="s">
+        <v>1438</v>
+      </c>
+      <c r="J307" s="5" t="s">
         <v>1439</v>
       </c>
-      <c r="F307" s="5" t="s">
+      <c r="K307" s="5" t="s">
         <v>1440</v>
       </c>
-      <c r="J307" s="5" t="s">
+      <c r="L307" s="7" t="s">
         <v>1441</v>
-      </c>
-      <c r="K307" s="5" t="s">
-        <v>1442</v>
-      </c>
-      <c r="L307" s="7" t="s">
-        <v>1443</v>
       </c>
       <c r="R307" s="5" t="s">
         <v>37</v>
@@ -18824,10 +18825,10 @@
     </row>
     <row r="308" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="26" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B308" s="26" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C308" s="10"/>
       <c r="D308" s="10">
@@ -18843,13 +18844,13 @@
       <c r="H308" s="10"/>
       <c r="I308" s="10"/>
       <c r="J308" s="10" t="s">
+        <v>1442</v>
+      </c>
+      <c r="K308" s="10" t="s">
+        <v>1443</v>
+      </c>
+      <c r="L308" s="11" t="s">
         <v>1444</v>
-      </c>
-      <c r="K308" s="10" t="s">
-        <v>1445</v>
-      </c>
-      <c r="L308" s="11" t="s">
-        <v>1446</v>
       </c>
       <c r="M308" s="10"/>
       <c r="N308" s="10"/>
@@ -18875,10 +18876,10 @@
     </row>
     <row r="309" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="28" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B309" s="28" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C309" s="16"/>
       <c r="D309" s="16" t="s">
@@ -18894,13 +18895,13 @@
       <c r="H309" s="16"/>
       <c r="I309" s="16"/>
       <c r="J309" s="16" t="s">
+        <v>1445</v>
+      </c>
+      <c r="K309" s="16" t="s">
+        <v>1446</v>
+      </c>
+      <c r="L309" s="17" t="s">
         <v>1447</v>
-      </c>
-      <c r="K309" s="16" t="s">
-        <v>1448</v>
-      </c>
-      <c r="L309" s="17" t="s">
-        <v>1449</v>
       </c>
       <c r="M309" s="16"/>
       <c r="N309" s="16"/>
@@ -18926,10 +18927,10 @@
     </row>
     <row r="310" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="30" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B310" s="30" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C310" s="23"/>
       <c r="D310" s="23">
@@ -18951,7 +18952,7 @@
         <v>295</v>
       </c>
       <c r="L310" s="7" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="M310" s="24"/>
       <c r="N310" s="24"/>
@@ -18965,7 +18966,7 @@
         <v>100</v>
       </c>
       <c r="T310" s="23" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="U310" s="23">
         <v>26</v>
@@ -18977,10 +18978,10 @@
     </row>
     <row r="311" spans="1:23" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="30" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B311" s="30" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C311" s="23"/>
       <c r="D311" s="23" t="s">
@@ -18996,13 +18997,13 @@
       <c r="H311" s="24"/>
       <c r="I311" s="24"/>
       <c r="J311" s="24" t="s">
+        <v>1450</v>
+      </c>
+      <c r="K311" s="24" t="s">
+        <v>1451</v>
+      </c>
+      <c r="L311" s="7" t="s">
         <v>1452</v>
-      </c>
-      <c r="K311" s="24" t="s">
-        <v>1453</v>
-      </c>
-      <c r="L311" s="7" t="s">
-        <v>1454</v>
       </c>
       <c r="M311" s="24"/>
       <c r="N311" s="24"/>
@@ -19028,10 +19029,10 @@
     </row>
     <row r="312" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="29" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B312" s="29" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="C312" s="19"/>
       <c r="D312" s="19">
@@ -19047,11 +19048,11 @@
       <c r="H312" s="19"/>
       <c r="I312" s="19"/>
       <c r="J312" s="19" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="K312" s="19"/>
       <c r="L312" s="20" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="M312" s="19"/>
       <c r="N312" s="19"/>
@@ -19077,31 +19078,31 @@
     </row>
     <row r="313" spans="1:23" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B313" s="25" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D313" s="5" t="s">
         <v>1456</v>
       </c>
-      <c r="D313" s="5" t="s">
+      <c r="E313" s="5" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F313" s="5" t="s">
         <v>1458</v>
       </c>
-      <c r="E313" s="5" t="s">
+      <c r="J313" s="5" t="s">
         <v>1459</v>
       </c>
-      <c r="F313" s="5" t="s">
+      <c r="L313" s="7" t="s">
         <v>1460</v>
       </c>
-      <c r="J313" s="5" t="s">
-        <v>1461</v>
-      </c>
-      <c r="L313" s="7" t="s">
-        <v>1462</v>
-      </c>
       <c r="R313" s="5" t="s">
         <v>37</v>
       </c>
       <c r="S313" s="5" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="T313" s="6">
         <v>138</v>
@@ -19115,13 +19116,13 @@
     </row>
     <row r="314" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B314" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="E314" s="5" t="s">
         <v>370</v>
@@ -19130,10 +19131,10 @@
         <v>371</v>
       </c>
       <c r="J314" s="5" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="L314" s="7" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="R314" s="5" t="s">
         <v>59</v>
@@ -19153,10 +19154,10 @@
     </row>
     <row r="315" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B315" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D315" s="5">
         <v>1441</v>
@@ -19165,13 +19166,13 @@
         <v>237</v>
       </c>
       <c r="F315" s="5" t="s">
+        <v>1464</v>
+      </c>
+      <c r="J315" s="5" t="s">
+        <v>1465</v>
+      </c>
+      <c r="L315" s="7" t="s">
         <v>1466</v>
-      </c>
-      <c r="J315" s="5" t="s">
-        <v>1467</v>
-      </c>
-      <c r="L315" s="7" t="s">
-        <v>1468</v>
       </c>
       <c r="R315" s="5" t="s">
         <v>37</v>
@@ -19191,10 +19192,10 @@
     </row>
     <row r="316" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B316" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D316" s="5">
         <v>1443</v>
@@ -19206,10 +19207,10 @@
         <v>68</v>
       </c>
       <c r="J316" s="5" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="L316" s="7" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="R316" s="5" t="s">
         <v>59</v>
@@ -19229,28 +19230,28 @@
     </row>
     <row r="317" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B317" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D317" s="5">
         <v>1443</v>
       </c>
       <c r="E317" s="5" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F317" s="5" t="s">
+        <v>1470</v>
+      </c>
+      <c r="J317" s="5" t="s">
         <v>1471</v>
       </c>
-      <c r="F317" s="5" t="s">
+      <c r="L317" s="7" t="s">
         <v>1472</v>
       </c>
-      <c r="J317" s="5" t="s">
+      <c r="M317" s="5" t="s">
         <v>1473</v>
-      </c>
-      <c r="L317" s="7" t="s">
-        <v>1474</v>
-      </c>
-      <c r="M317" s="5" t="s">
-        <v>1475</v>
       </c>
       <c r="R317" s="5" t="s">
         <v>37</v>
@@ -19270,13 +19271,13 @@
     </row>
     <row r="318" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B318" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="E318" s="5" t="s">
         <v>67</v>
@@ -19285,10 +19286,10 @@
         <v>68</v>
       </c>
       <c r="J318" s="5" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="L318" s="7" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="R318" s="5" t="s">
         <v>247</v>
@@ -19308,13 +19309,13 @@
     </row>
     <row r="319" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B319" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="E319" s="5" t="s">
         <v>32</v>
@@ -19323,10 +19324,10 @@
         <v>33</v>
       </c>
       <c r="J319" s="5" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="L319" s="7" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="R319" s="5" t="s">
         <v>247</v>
@@ -19346,25 +19347,25 @@
     </row>
     <row r="320" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B320" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D320" s="5" t="s">
         <v>261</v>
       </c>
       <c r="E320" s="5" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="F320" s="5" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="J320" s="5" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="L320" s="7" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="R320" s="5" t="s">
         <v>59</v>
@@ -19384,10 +19385,10 @@
     </row>
     <row r="321" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B321" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D321" s="5" t="s">
         <v>267</v>
@@ -19399,10 +19400,10 @@
         <v>376</v>
       </c>
       <c r="J321" s="5" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="L321" s="7" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="R321" s="5" t="s">
         <v>37</v>
@@ -19422,13 +19423,13 @@
     </row>
     <row r="322" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B322" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="E322" s="5" t="s">
         <v>25</v>
@@ -19437,10 +19438,10 @@
         <v>40</v>
       </c>
       <c r="J322" s="5" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="L322" s="7" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="R322" s="5" t="s">
         <v>37</v>
@@ -19460,10 +19461,10 @@
     </row>
     <row r="323" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="31" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B323" s="31" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="C323" s="31"/>
       <c r="D323" s="33">
@@ -19479,13 +19480,13 @@
       <c r="H323" s="31"/>
       <c r="I323" s="31"/>
       <c r="J323" s="31" t="s">
+        <v>1486</v>
+      </c>
+      <c r="K323" s="31" t="s">
+        <v>1487</v>
+      </c>
+      <c r="L323" s="22" t="s">
         <v>1488</v>
-      </c>
-      <c r="K323" s="31" t="s">
-        <v>1489</v>
-      </c>
-      <c r="L323" s="22" t="s">
-        <v>1490</v>
       </c>
       <c r="M323" s="31"/>
       <c r="N323" s="31"/>
@@ -19510,28 +19511,28 @@
     </row>
     <row r="324" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B324" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D324" s="5">
         <v>1435</v>
       </c>
       <c r="E324" s="5" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F324" s="5" t="s">
+        <v>1492</v>
+      </c>
+      <c r="J324" s="5" t="s">
         <v>1493</v>
       </c>
-      <c r="F324" s="5" t="s">
+      <c r="K324" s="5" t="s">
         <v>1494</v>
       </c>
-      <c r="J324" s="5" t="s">
+      <c r="L324" s="7" t="s">
         <v>1495</v>
-      </c>
-      <c r="K324" s="5" t="s">
-        <v>1496</v>
-      </c>
-      <c r="L324" s="7" t="s">
-        <v>1497</v>
       </c>
       <c r="R324" s="5" t="s">
         <v>37</v>
@@ -19551,13 +19552,13 @@
     </row>
     <row r="325" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B325" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="E325" s="5" t="s">
         <v>86</v>
@@ -19566,13 +19567,13 @@
         <v>87</v>
       </c>
       <c r="J325" s="5" t="s">
+        <v>1497</v>
+      </c>
+      <c r="K325" s="5" t="s">
+        <v>1498</v>
+      </c>
+      <c r="L325" s="7" t="s">
         <v>1499</v>
-      </c>
-      <c r="K325" s="5" t="s">
-        <v>1500</v>
-      </c>
-      <c r="L325" s="7" t="s">
-        <v>1501</v>
       </c>
       <c r="R325" s="5" t="s">
         <v>37</v>
@@ -19592,13 +19593,13 @@
     </row>
     <row r="326" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A326" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B326" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="E326" s="5" t="s">
         <v>86</v>
@@ -19607,13 +19608,13 @@
         <v>87</v>
       </c>
       <c r="J326" s="5" t="s">
+        <v>1500</v>
+      </c>
+      <c r="K326" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="L326" s="7" t="s">
         <v>1502</v>
-      </c>
-      <c r="K326" s="5" t="s">
-        <v>1503</v>
-      </c>
-      <c r="L326" s="7" t="s">
-        <v>1504</v>
       </c>
       <c r="R326" s="5" t="s">
         <v>37</v>
@@ -19633,13 +19634,13 @@
     </row>
     <row r="327" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B327" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="E327" s="5" t="s">
         <v>86</v>
@@ -19648,10 +19649,10 @@
         <v>87</v>
       </c>
       <c r="J327" s="5" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="L327" s="7" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="R327" s="5" t="s">
         <v>37</v>
@@ -19671,10 +19672,10 @@
     </row>
     <row r="328" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B328" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D328" s="5" t="s">
         <v>301</v>
@@ -19686,13 +19687,13 @@
         <v>33</v>
       </c>
       <c r="J328" s="5" t="s">
+        <v>1506</v>
+      </c>
+      <c r="K328" s="5" t="s">
+        <v>1507</v>
+      </c>
+      <c r="L328" s="7" t="s">
         <v>1508</v>
-      </c>
-      <c r="K328" s="5" t="s">
-        <v>1509</v>
-      </c>
-      <c r="L328" s="7" t="s">
-        <v>1510</v>
       </c>
       <c r="R328" s="5" t="s">
         <v>37</v>
@@ -19712,13 +19713,13 @@
     </row>
     <row r="329" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B329" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="E329" s="5" t="s">
         <v>594</v>
@@ -19727,13 +19728,13 @@
         <v>595</v>
       </c>
       <c r="J329" s="5" t="s">
+        <v>1509</v>
+      </c>
+      <c r="K329" s="5" t="s">
+        <v>1510</v>
+      </c>
+      <c r="L329" s="7" t="s">
         <v>1511</v>
-      </c>
-      <c r="K329" s="5" t="s">
-        <v>1512</v>
-      </c>
-      <c r="L329" s="7" t="s">
-        <v>1513</v>
       </c>
       <c r="R329" s="5" t="s">
         <v>247</v>
@@ -19753,13 +19754,13 @@
     </row>
     <row r="330" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B330" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="E330" s="5" t="s">
         <v>505</v>
@@ -19768,13 +19769,13 @@
         <v>506</v>
       </c>
       <c r="J330" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="K330" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="L330" s="7" t="s">
         <v>1515</v>
-      </c>
-      <c r="K330" s="5" t="s">
-        <v>1516</v>
-      </c>
-      <c r="L330" s="7" t="s">
-        <v>1517</v>
       </c>
       <c r="R330" s="5" t="s">
         <v>37</v>
@@ -19794,28 +19795,28 @@
     </row>
     <row r="331" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B331" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D331" s="5">
         <v>1432</v>
       </c>
       <c r="E331" s="5" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F331" s="5" t="s">
+        <v>1517</v>
+      </c>
+      <c r="J331" s="5" t="s">
         <v>1518</v>
       </c>
-      <c r="F331" s="5" t="s">
+      <c r="K331" s="5" t="s">
         <v>1519</v>
       </c>
-      <c r="J331" s="5" t="s">
+      <c r="L331" s="7" t="s">
         <v>1520</v>
-      </c>
-      <c r="K331" s="5" t="s">
-        <v>1521</v>
-      </c>
-      <c r="L331" s="7" t="s">
-        <v>1522</v>
       </c>
       <c r="R331" s="5" t="s">
         <v>59</v>
@@ -19835,13 +19836,13 @@
     </row>
     <row r="332" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B332" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="E332" s="5" t="s">
         <v>375</v>
@@ -19853,10 +19854,10 @@
         <v>531</v>
       </c>
       <c r="K332" s="5" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="L332" s="7" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="R332" s="5" t="s">
         <v>37</v>
@@ -19876,13 +19877,13 @@
     </row>
     <row r="333" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B333" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="E333" s="5" t="s">
         <v>505</v>
@@ -19891,13 +19892,13 @@
         <v>506</v>
       </c>
       <c r="J333" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K333" s="5" t="s">
+        <v>1525</v>
+      </c>
+      <c r="L333" s="7" t="s">
         <v>1526</v>
-      </c>
-      <c r="K333" s="5" t="s">
-        <v>1527</v>
-      </c>
-      <c r="L333" s="7" t="s">
-        <v>1528</v>
       </c>
       <c r="R333" s="5" t="s">
         <v>37</v>
@@ -19917,13 +19918,13 @@
     </row>
     <row r="334" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B334" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="E334" s="5" t="s">
         <v>280</v>
@@ -19932,10 +19933,10 @@
         <v>281</v>
       </c>
       <c r="J334" s="5" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="L334" s="7" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="R334" s="5" t="s">
         <v>672</v>
@@ -19955,28 +19956,28 @@
     </row>
     <row r="335" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B335" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D335" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E335" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F335" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="J335" t="s">
+        <v>1530</v>
+      </c>
+      <c r="K335" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L335" s="1" t="s">
         <v>1532</v>
-      </c>
-      <c r="K335" t="s">
-        <v>1533</v>
-      </c>
-      <c r="L335" s="1" t="s">
-        <v>1534</v>
       </c>
       <c r="R335" t="s">
         <v>37</v>
@@ -19988,7 +19989,7 @@
         <v>24</v>
       </c>
       <c r="U335" s="2" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="W335" s="6">
         <v>1</v>
@@ -19997,13 +19998,13 @@
     </row>
     <row r="336" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B336" s="25" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="E336" s="5" t="s">
         <v>67</v>
@@ -20015,7 +20016,7 @@
         <v>186</v>
       </c>
       <c r="L336" s="7" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="R336" s="5" t="s">
         <v>37</v>
@@ -20035,13 +20036,13 @@
     </row>
     <row r="337" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B337" s="25" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="E337" s="5" t="s">
         <v>25</v>
@@ -20050,10 +20051,10 @@
         <v>40</v>
       </c>
       <c r="J337" s="5" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="L337" s="7" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="R337" s="5" t="s">
         <v>59</v>
@@ -20073,10 +20074,10 @@
     </row>
     <row r="338" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B338" s="25" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="D338" s="5">
         <v>1432</v>
@@ -20085,16 +20086,16 @@
         <v>25</v>
       </c>
       <c r="F338" s="5" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="J338" s="5" t="s">
         <v>443</v>
       </c>
       <c r="K338" s="5" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="L338" s="7" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="R338" s="5" t="s">
         <v>37</v>
@@ -20114,10 +20115,10 @@
     </row>
     <row r="339" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="25" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B339" s="25" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="D339" s="5">
         <v>1445</v>
@@ -20129,16 +20130,16 @@
         <v>68</v>
       </c>
       <c r="J339" s="5" t="s">
+        <v>1543</v>
+      </c>
+      <c r="K339" s="5" t="s">
+        <v>1544</v>
+      </c>
+      <c r="L339" s="7" t="s">
         <v>1545</v>
       </c>
-      <c r="K339" s="5" t="s">
+      <c r="R339" s="5" t="s">
         <v>1546</v>
-      </c>
-      <c r="L339" s="7" t="s">
-        <v>1547</v>
-      </c>
-      <c r="R339" s="5" t="s">
-        <v>1548</v>
       </c>
       <c r="S339" s="5" t="s">
         <v>45</v>
@@ -20155,10 +20156,10 @@
     </row>
     <row r="340" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="25" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="B340" s="25" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D340" s="5">
         <v>1480</v>
@@ -20170,13 +20171,13 @@
         <v>81</v>
       </c>
       <c r="J340" s="5" t="s">
+        <v>1549</v>
+      </c>
+      <c r="K340" s="5" t="s">
+        <v>1550</v>
+      </c>
+      <c r="L340" s="7" t="s">
         <v>1551</v>
-      </c>
-      <c r="K340" s="5" t="s">
-        <v>1552</v>
-      </c>
-      <c r="L340" s="7" t="s">
-        <v>1553</v>
       </c>
       <c r="R340" s="5" t="s">
         <v>37</v>
@@ -20196,32 +20197,32 @@
     </row>
     <row r="341" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="28" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="B341" s="28" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C341" s="16"/>
       <c r="D341" s="16" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="E341" s="16" t="s">
         <v>80</v>
       </c>
       <c r="F341" s="16" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="G341" s="16"/>
       <c r="H341" s="16"/>
       <c r="I341" s="16"/>
       <c r="J341" s="16" t="s">
+        <v>1554</v>
+      </c>
+      <c r="K341" s="16" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L341" s="17" t="s">
         <v>1556</v>
-      </c>
-      <c r="K341" s="16" t="s">
-        <v>1557</v>
-      </c>
-      <c r="L341" s="17" t="s">
-        <v>1558</v>
       </c>
       <c r="M341" s="16"/>
       <c r="N341" s="16"/>
@@ -20232,7 +20233,7 @@
         <v>37</v>
       </c>
       <c r="S341" s="16" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="T341" s="18">
         <v>141</v>
@@ -20247,10 +20248,10 @@
     </row>
     <row r="342" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D342" s="5">
         <v>1475</v>
@@ -20262,19 +20263,19 @@
         <v>658</v>
       </c>
       <c r="J342" s="5" t="s">
+        <v>1558</v>
+      </c>
+      <c r="K342" s="5" t="s">
+        <v>1559</v>
+      </c>
+      <c r="L342" s="7" t="s">
         <v>1560</v>
-      </c>
-      <c r="K342" s="5" t="s">
-        <v>1561</v>
-      </c>
-      <c r="L342" s="7" t="s">
-        <v>1562</v>
       </c>
       <c r="R342" s="5" t="s">
         <v>689</v>
       </c>
       <c r="S342" s="5" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="T342" s="6">
         <v>120</v>
@@ -20289,13 +20290,13 @@
     </row>
     <row r="343" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D343" s="5" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="E343" s="5" t="s">
         <v>86</v>
@@ -20307,10 +20308,10 @@
         <v>499</v>
       </c>
       <c r="K343" s="5" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="L343" s="7" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="R343" s="5" t="s">
         <v>37</v>
@@ -20331,10 +20332,10 @@
     </row>
     <row r="344" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="29" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B344" s="29" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C344" s="19"/>
       <c r="D344" s="19">
@@ -20344,19 +20345,19 @@
         <v>80</v>
       </c>
       <c r="F344" s="19" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="G344" s="19"/>
       <c r="H344" s="19"/>
       <c r="I344" s="19"/>
       <c r="J344" s="19" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="K344" s="19" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="L344" s="20" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="M344" s="19"/>
       <c r="N344" s="19"/>
@@ -20367,7 +20368,7 @@
         <v>37</v>
       </c>
       <c r="S344" s="19" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="T344" s="21">
         <v>230</v>
@@ -20382,10 +20383,10 @@
     </row>
     <row r="345" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A345" s="25" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B345" s="25" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D345" s="5">
         <v>1446</v>
@@ -20397,19 +20398,19 @@
         <v>81</v>
       </c>
       <c r="J345" s="5" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K345" s="5" t="s">
+        <v>1567</v>
+      </c>
+      <c r="L345" s="7" t="s">
         <v>1568</v>
-      </c>
-      <c r="K345" s="5" t="s">
-        <v>1569</v>
-      </c>
-      <c r="L345" s="7" t="s">
-        <v>1570</v>
       </c>
       <c r="R345" s="5" t="s">
         <v>247</v>
       </c>
       <c r="S345" s="5" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="T345" s="6">
         <v>339</v>
@@ -20423,13 +20424,13 @@
     </row>
     <row r="346" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A346" s="25" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B346" s="25" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D346" s="5" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="E346" s="5" t="s">
         <v>598</v>
@@ -20438,13 +20439,13 @@
         <v>605</v>
       </c>
       <c r="J346" s="5" t="s">
+        <v>1571</v>
+      </c>
+      <c r="K346" s="5" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L346" s="7" t="s">
         <v>1573</v>
-      </c>
-      <c r="K346" s="5" t="s">
-        <v>1574</v>
-      </c>
-      <c r="L346" s="7" t="s">
-        <v>1575</v>
       </c>
       <c r="R346" s="5" t="s">
         <v>689</v>
@@ -20464,13 +20465,13 @@
     </row>
     <row r="347" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="25" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B347" s="25" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D347" s="5" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="E347" s="5" t="s">
         <v>466</v>
@@ -20479,13 +20480,13 @@
         <v>201</v>
       </c>
       <c r="J347" s="5" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K347" s="5" t="s">
+        <v>1576</v>
+      </c>
+      <c r="L347" s="7" t="s">
         <v>1577</v>
-      </c>
-      <c r="K347" s="5" t="s">
-        <v>1578</v>
-      </c>
-      <c r="L347" s="7" t="s">
-        <v>1579</v>
       </c>
       <c r="R347" s="5" t="s">
         <v>689</v>
@@ -20505,10 +20506,10 @@
     </row>
     <row r="348" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="25" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="B348" s="25" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D348" s="5">
         <v>1474</v>
@@ -20517,16 +20518,16 @@
         <v>80</v>
       </c>
       <c r="F348" s="5" t="s">
+        <v>1579</v>
+      </c>
+      <c r="J348" s="5" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K348" s="5" t="s">
         <v>1581</v>
       </c>
-      <c r="J348" s="5" t="s">
+      <c r="L348" s="7" t="s">
         <v>1582</v>
-      </c>
-      <c r="K348" s="5" t="s">
-        <v>1583</v>
-      </c>
-      <c r="L348" s="7" t="s">
-        <v>1584</v>
       </c>
       <c r="R348" s="5" t="s">
         <v>247</v>
@@ -20546,10 +20547,10 @@
     </row>
     <row r="349" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="25" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="B349" s="25" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D349" s="5">
         <v>1482</v>
@@ -20558,16 +20559,16 @@
         <v>80</v>
       </c>
       <c r="F349" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="J349" s="5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="K349" s="5" t="s">
         <v>1585</v>
       </c>
-      <c r="J349" s="5" t="s">
+      <c r="L349" s="7" t="s">
         <v>1586</v>
-      </c>
-      <c r="K349" s="5" t="s">
-        <v>1587</v>
-      </c>
-      <c r="L349" s="7" t="s">
-        <v>1588</v>
       </c>
       <c r="R349" s="5" t="s">
         <v>247</v>
@@ -20588,10 +20589,10 @@
     </row>
     <row r="350" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="30" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="B350" s="30" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D350" s="5">
         <v>1482</v>
@@ -20600,13 +20601,13 @@
         <v>80</v>
       </c>
       <c r="F350" s="5" t="s">
+        <v>1587</v>
+      </c>
+      <c r="J350" s="5" t="s">
+        <v>1588</v>
+      </c>
+      <c r="L350" s="7" t="s">
         <v>1589</v>
-      </c>
-      <c r="J350" s="5" t="s">
-        <v>1590</v>
-      </c>
-      <c r="L350" s="7" t="s">
-        <v>1591</v>
       </c>
       <c r="R350" s="30" t="s">
         <v>689</v>
@@ -20628,10 +20629,10 @@
     </row>
     <row r="351" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="34" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="B351" s="34" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C351" s="34"/>
       <c r="D351" s="36" t="s">
@@ -20650,10 +20651,10 @@
         <v>680</v>
       </c>
       <c r="K351" s="34" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="L351" s="37" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="M351" s="34"/>
       <c r="N351" s="34"/>
@@ -20948,241 +20949,241 @@
     <hyperlink ref="L147" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
     <hyperlink ref="N147" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
     <hyperlink ref="L148" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="L149" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="L150" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="L151" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="N151" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="L152" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="N152" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="L153" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="N153" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="L154" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="N154" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="L155" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="N155" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="P155" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="L156" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="N156" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="L157" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="L159" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="L160" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="L161" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="L162" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="L163" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="L164" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="L165" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="L166" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="L167" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="L168" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="L169" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="L170" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="L171" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="L172" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="L173" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="L174" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="L175" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="N175" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="L176" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="L177" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="L178" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="L179" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="L180" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="L181" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="L183" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="L184" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="L185" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="L186" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="L187" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="L188" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="L189" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="L190" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="L191" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="L192" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="L193" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="L194" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="L195" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="L196" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="L197" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="L198" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="L199" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="L200" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="L201" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="L202" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="L203" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="L204" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="L205" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="L206" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="G207" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="I207" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="L207" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="N207" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="I208" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="L208" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="L209" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="L210" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="L211" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="L212" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="L213" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="L214" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="L215" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="L216" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="L217" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="L218" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="L219" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="L220" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="L221" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="N221" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="L222" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="L223" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="N223" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="L224" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="L225" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="L226" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="L227" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="L228" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="L229" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="L230" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="L231" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="N231" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="L232" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="L233" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="L234" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="L235" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="L236" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="L237" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="L238" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="L239" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="L240" r:id="rId253" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="L241" r:id="rId254" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="L242" r:id="rId255" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="L243" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="L244" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="L245" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="L246" r:id="rId259" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="L247" r:id="rId260" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="L248" r:id="rId261" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="L249" r:id="rId262" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="L250" r:id="rId263" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="L251" r:id="rId264" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="L252" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="L254" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="L255" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="L256" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="L257" r:id="rId269" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="N257" r:id="rId270" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="L258" r:id="rId271" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="N258" r:id="rId272" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="L259" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="N259" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="L260" r:id="rId275" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="N260" r:id="rId276" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="L261" r:id="rId277" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="N261" r:id="rId278" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="L262" r:id="rId279" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="N262" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="L263" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="N263" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="L264" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="N264" r:id="rId284" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="L265" r:id="rId285" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="L266" r:id="rId286" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="L267" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="L268" r:id="rId288" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="L269" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="L270" r:id="rId290" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="N270" r:id="rId291" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="L271" r:id="rId292" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="L272" r:id="rId293" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="L273" r:id="rId294" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="L274" r:id="rId295" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="L275" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="L276" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="L277" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="L278" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="L279" r:id="rId300" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="L280" r:id="rId301" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="L281" r:id="rId302" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="L282" r:id="rId303" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="L283" r:id="rId304" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="L284" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="N284" r:id="rId306" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="L285" r:id="rId307" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="N285" r:id="rId308" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="L286" r:id="rId309" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="N286" r:id="rId310" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="L287" r:id="rId311" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="L288" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="L289" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="L290" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="L292" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="L293" r:id="rId316" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="L294" r:id="rId317" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="L295" r:id="rId318" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="L296" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="L297" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="L298" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="L299" r:id="rId322" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="L300" r:id="rId323" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="L301" r:id="rId324" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="L302" r:id="rId325" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="L303" r:id="rId326" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="L304" r:id="rId327" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="L306" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="L307" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="L308" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="L309" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="L310" r:id="rId332" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="L311" r:id="rId333" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="L312" r:id="rId334" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="L313" r:id="rId335" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="L314" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="L315" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="L316" r:id="rId338" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="L317" r:id="rId339" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="L318" r:id="rId340" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="L319" r:id="rId341" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="L320" r:id="rId342" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="L321" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="L322" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="L323" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="L324" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="L325" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="L326" r:id="rId348" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="L327" r:id="rId349" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="L328" r:id="rId350" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="L329" r:id="rId351" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="L330" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="L331" r:id="rId353" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="L332" r:id="rId354" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="L333" r:id="rId355" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="L334" r:id="rId356" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="L335" r:id="rId357" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="L336" r:id="rId358" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="L337" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="L338" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="L339" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="L340" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="L341" r:id="rId363" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="L342" r:id="rId364" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="L343" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="L344" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="L345" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="L346" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="L347" r:id="rId369" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="L348" r:id="rId370" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="L349" r:id="rId371" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="L350" r:id="rId372" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="L351" r:id="rId373" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="L36" r:id="rId374" xr:uid="{53549D48-936B-4EB4-B241-2F8F9312D948}"/>
-    <hyperlink ref="L158" r:id="rId375" xr:uid="{C8E8DE21-E096-442E-8906-042AB707EAD0}"/>
-    <hyperlink ref="L182" r:id="rId376" xr:uid="{09BB8218-4537-4E85-8496-1D2BF3F79BA9}"/>
-    <hyperlink ref="L305" r:id="rId377" xr:uid="{EA177C80-6E63-4368-9802-12F80918229A}"/>
-    <hyperlink ref="L27" r:id="rId378" xr:uid="{54E1358F-D0C6-4E27-99A2-8BEAA780B02D}"/>
-    <hyperlink ref="L28" r:id="rId379" xr:uid="{35E7AD8E-F497-4D49-898C-9479F369C0C1}"/>
-    <hyperlink ref="L29" r:id="rId380" xr:uid="{BA3F783F-C8BA-4E83-8F00-AA0EFCC62F00}"/>
-    <hyperlink ref="L30" r:id="rId381" xr:uid="{0E291094-F7F9-44D8-BE97-ACE0D1BC461C}"/>
-    <hyperlink ref="L291" r:id="rId382" xr:uid="{C71CE794-173C-4267-BE3E-ED8936667C7A}"/>
-    <hyperlink ref="L253" r:id="rId383" xr:uid="{9ADD3719-B05F-47CC-B31A-ACA3F5E88B43}"/>
+    <hyperlink ref="L151" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="N151" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="L152" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="N152" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="L153" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="N153" r:id="rId154" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="L154" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="N154" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="L155" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="N155" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="P155" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="L156" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="N156" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="L157" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="L159" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="L160" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="L161" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="L162" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="L163" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="L164" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="L165" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="L166" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="L167" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="L168" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="L169" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="L170" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="L171" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="L172" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="L173" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="L174" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="L175" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="N175" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="L176" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="L177" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="L178" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="L179" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="L180" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="L181" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="L183" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="L184" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="L185" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="L186" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="L187" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="L188" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="L189" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="L190" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="L191" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="L192" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="L193" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="L194" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="L195" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="L196" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="L197" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="L198" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="L199" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="L200" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="L201" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="L202" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="L203" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="L204" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="L205" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="L206" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="G207" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="I207" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="L207" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="N207" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="I208" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="L208" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="L209" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="L210" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="L211" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="L212" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="L213" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="L214" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="L215" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="L216" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="L217" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="L218" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="L219" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="L220" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="L221" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="N221" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="L222" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="L223" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="N223" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="L224" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="L225" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="L226" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="L227" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="L228" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="L229" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="L230" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="L231" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="N231" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="L232" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="L233" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="L234" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="L235" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="L236" r:id="rId247" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="L237" r:id="rId248" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="L238" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="L239" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="L240" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="L241" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="L242" r:id="rId253" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="L243" r:id="rId254" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="L244" r:id="rId255" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="L245" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="L246" r:id="rId257" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="L247" r:id="rId258" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="L248" r:id="rId259" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="L249" r:id="rId260" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="L250" r:id="rId261" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="L251" r:id="rId262" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="L252" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="L254" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="L255" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="L256" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="L257" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="N257" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="L258" r:id="rId269" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="N258" r:id="rId270" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="L259" r:id="rId271" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="N259" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="L260" r:id="rId273" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="N260" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="L261" r:id="rId275" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="N261" r:id="rId276" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="L262" r:id="rId277" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="N262" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="L263" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="N263" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="L264" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="N264" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="L265" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="L266" r:id="rId284" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="L267" r:id="rId285" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="L268" r:id="rId286" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="L269" r:id="rId287" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="L270" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="N270" r:id="rId289" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="L271" r:id="rId290" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="L272" r:id="rId291" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="L273" r:id="rId292" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="L274" r:id="rId293" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="L275" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="L276" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="L277" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="L278" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="L279" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="L280" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="L281" r:id="rId300" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="L282" r:id="rId301" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="L283" r:id="rId302" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="L284" r:id="rId303" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="N284" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="L285" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="N285" r:id="rId306" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="L286" r:id="rId307" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="N286" r:id="rId308" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="L287" r:id="rId309" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="L288" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="L289" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="L290" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="L292" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="L293" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="L294" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="L295" r:id="rId316" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="L296" r:id="rId317" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="L297" r:id="rId318" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="L298" r:id="rId319" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="L299" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="L300" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="L301" r:id="rId322" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="L302" r:id="rId323" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="L303" r:id="rId324" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="L304" r:id="rId325" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="L306" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="L307" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="L308" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="L309" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="L310" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="L311" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="L312" r:id="rId332" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="L313" r:id="rId333" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="L314" r:id="rId334" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="L315" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="L316" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="L317" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="L318" r:id="rId338" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="L319" r:id="rId339" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="L320" r:id="rId340" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="L321" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="L322" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="L323" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="L324" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="L325" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="L326" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="L327" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="L328" r:id="rId348" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="L329" r:id="rId349" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="L330" r:id="rId350" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="L331" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="L332" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="L333" r:id="rId353" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="L334" r:id="rId354" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="L335" r:id="rId355" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="L336" r:id="rId356" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="L337" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="L338" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="L339" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="L340" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="L341" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="L342" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="L343" r:id="rId363" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="L344" r:id="rId364" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="L345" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="L346" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="L347" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="L348" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="L349" r:id="rId369" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="L350" r:id="rId370" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="L351" r:id="rId371" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="L36" r:id="rId372" xr:uid="{53549D48-936B-4EB4-B241-2F8F9312D948}"/>
+    <hyperlink ref="L158" r:id="rId373" xr:uid="{C8E8DE21-E096-442E-8906-042AB707EAD0}"/>
+    <hyperlink ref="L182" r:id="rId374" xr:uid="{09BB8218-4537-4E85-8496-1D2BF3F79BA9}"/>
+    <hyperlink ref="L305" r:id="rId375" xr:uid="{EA177C80-6E63-4368-9802-12F80918229A}"/>
+    <hyperlink ref="L27" r:id="rId376" xr:uid="{54E1358F-D0C6-4E27-99A2-8BEAA780B02D}"/>
+    <hyperlink ref="L28" r:id="rId377" xr:uid="{35E7AD8E-F497-4D49-898C-9479F369C0C1}"/>
+    <hyperlink ref="L29" r:id="rId378" xr:uid="{BA3F783F-C8BA-4E83-8F00-AA0EFCC62F00}"/>
+    <hyperlink ref="L30" r:id="rId379" xr:uid="{0E291094-F7F9-44D8-BE97-ACE0D1BC461C}"/>
+    <hyperlink ref="L291" r:id="rId380" xr:uid="{C71CE794-173C-4267-BE3E-ED8936667C7A}"/>
+    <hyperlink ref="L253" r:id="rId381" xr:uid="{9ADD3719-B05F-47CC-B31A-ACA3F5E88B43}"/>
+    <hyperlink ref="L149" r:id="rId382" xr:uid="{376EDAFD-E5D8-487C-B90A-FDB657F30322}"/>
+    <hyperlink ref="L150" r:id="rId383" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Masaccio._The_Madonna_and_Child_with_st._Anna._ca._1424._Uffizi%2C_Florence.jpg/960px-Masaccio._The_Madonna_and_Child_with_st._Anna._ca._1424._Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{440644BC-28D0-481E-9968-DCD9DF613C28}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
